--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -11160,7 +11160,7 @@
         <v>141</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>334</v>
+        <v>142</v>
       </c>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
@@ -11187,7 +11187,7 @@
         <v>141</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>334</v>
+        <v>142</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -505,7 +505,7 @@
     <t>豆类蔬菜</t>
   </si>
   <si>
-    <t>块根和块茎蔬菜(例如:薯类、胡萝卜、萝卜、生姜等)</t>
+    <t>块根和块茎蔬菜（例如：薯类、胡萝卜、萝卜、生姜等）</t>
   </si>
   <si>
     <t>生姜</t>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -11964,7 +11964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -13520,11 +13520,7 @@
           <t>谷物</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>稻谷</t>
-        </is>
-      </c>
+      <c r="C35" s="4" t="n"/>
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -13569,11 +13565,7 @@
           <t>谷物</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>稻谷</t>
-        </is>
-      </c>
+      <c r="C36" s="4" t="n"/>
       <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
@@ -13791,12 +13783,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>谷物</t>
+          <t>谷物碾磨加工品</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>玉米</t>
+          <t>玉米粉、玉米糁(渣)</t>
         </is>
       </c>
       <c r="D41" s="4" t="n"/>
@@ -13836,15 +13828,14 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>谷物</t>
+          <t>谷物碾磨加工品</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>玉米</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="n"/>
+          <t>玉米粉、玉米糁(渣)</t>
+        </is>
+      </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
           <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
@@ -13866,7 +13857,6 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13886,7 +13876,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>玉米粉、玉米糁(渣)</t>
+          <t>小麦粉(包括食用麸皮)</t>
         </is>
       </c>
       <c r="D43" s="4" t="n"/>
@@ -13931,9 +13921,10 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>玉米粉、玉米糁(渣)</t>
-        </is>
-      </c>
+          <t>小麦粉(包括食用麸皮)</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="inlineStr">
         <is>
           <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
@@ -13955,6 +13946,7 @@
           <t>mg/kg</t>
         </is>
       </c>
+      <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13964,23 +13956,19 @@
     <row r="45" ht="28" customHeight="1" s="23">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>谷物</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>小麦</t>
-        </is>
-      </c>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>新鲜蔬菜</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -13990,7 +13978,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H45" s="4" t="n"/>
@@ -14009,23 +13997,19 @@
     <row r="46" ht="28" customHeight="1" s="23">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>谷物</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>小麦</t>
-        </is>
-      </c>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>新鲜蔬菜</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -14054,23 +14038,19 @@
     <row r="47" ht="28" customHeight="1" s="23">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>小麦粉(包括食用麸皮)</t>
-        </is>
-      </c>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="n"/>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -14080,7 +14060,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H47" s="4" t="n"/>
@@ -14099,28 +14079,24 @@
     <row r="48" ht="28" customHeight="1" s="23">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>小麦粉(包括食用麸皮)</t>
-        </is>
-      </c>
+          <t>食用菌制品</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>甲基汞 a</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -14144,29 +14120,29 @@
     <row r="49" ht="28" customHeight="1" s="23">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C49" s="4" t="n"/>
       <c r="D49" s="4" t="n"/>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜</t>
+          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞 a</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H49" s="4" t="n"/>
@@ -14175,7 +14151,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J49" s="4" t="n"/>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -14185,19 +14165,19 @@
     <row r="50" ht="28" customHeight="1" s="23">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+          <t>食用菌制品</t>
         </is>
       </c>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="4" t="n"/>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜</t>
+          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -14207,7 +14187,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H50" s="4" t="n"/>
@@ -14216,7 +14196,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J50" s="4" t="n"/>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -14234,11 +14218,15 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C51" s="4" t="n"/>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>木耳（毛木耳,黑木耳）</t>
+        </is>
+      </c>
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -14275,11 +14263,19 @@
           <t>食用菌制品</t>
         </is>
       </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>木耳制品、银耳制品</t>
+        </is>
+      </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -14316,11 +14312,15 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C53" s="4" t="n"/>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>木耳（毛木耳,黑木耳）</t>
+        </is>
+      </c>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -14333,7 +14333,11 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="H53" s="4" t="n"/>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>干重计</t>
+        </is>
+      </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -14361,11 +14365,19 @@
           <t>食用菌制品</t>
         </is>
       </c>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>木耳制品、银耳制品</t>
+        </is>
+      </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -14378,7 +14390,11 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="H54" s="4" t="n"/>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>干重计</t>
+        </is>
+      </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -14408,7 +14424,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>木耳（毛木耳,黑木耳）</t>
+          <t>银耳</t>
         </is>
       </c>
       <c r="D55" s="4" t="n"/>
@@ -14448,19 +14464,15 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>木耳制品、银耳制品</t>
-        </is>
-      </c>
+          <t>银耳</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="n"/>
       <c r="E56" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
@@ -14468,21 +14480,29 @@
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞 a</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="n"/>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>干重计</t>
+        </is>
+      </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J56" s="4" t="n"/>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -14492,50 +14512,38 @@
     <row r="57" ht="28" customHeight="1" s="23">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>木耳（毛木耳,黑木耳）</t>
-        </is>
-      </c>
+          <t>肉类(生鲜肉、冷却肉、冷冻肉等)</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n"/>
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>肉类</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>甲基汞 a</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>干重计</t>
-        </is>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="n"/>
       <c r="I57" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -14545,27 +14553,19 @@
     <row r="58" ht="28" customHeight="1" s="23">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>木耳制品、银耳制品</t>
-        </is>
-      </c>
+          <t>肉类(生鲜肉、冷却肉、冷冻肉等)</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>肉类</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -14575,24 +14575,16 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>干重计</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="n"/>
       <c r="I58" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -14602,23 +14594,19 @@
     <row r="59" ht="28" customHeight="1" s="23">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>银耳</t>
-        </is>
-      </c>
+          <t>生乳</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n"/>
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -14628,7 +14616,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H59" s="4" t="n"/>
@@ -14647,23 +14635,19 @@
     <row r="60" ht="28" customHeight="1" s="23">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>银耳</t>
-        </is>
-      </c>
+          <t>生乳</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n"/>
       <c r="D60" s="4" t="n"/>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
@@ -14673,24 +14657,16 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>干重计</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="n"/>
       <c r="I60" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -14700,19 +14676,19 @@
     <row r="61" ht="28" customHeight="1" s="23">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>肉类(生鲜肉、冷却肉、冷冻肉等)</t>
+          <t>巴氏杀菌乳</t>
         </is>
       </c>
       <c r="C61" s="4" t="n"/>
       <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>肉类</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -14722,7 +14698,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H61" s="4" t="n"/>
@@ -14741,19 +14717,19 @@
     <row r="62" ht="28" customHeight="1" s="23">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>肉类(生鲜肉、冷却肉、冷冻肉等)</t>
+          <t>巴氏杀菌乳</t>
         </is>
       </c>
       <c r="C62" s="4" t="n"/>
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>肉类</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
@@ -14787,7 +14763,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>生乳</t>
+          <t>灭菌乳</t>
         </is>
       </c>
       <c r="C63" s="4" t="n"/>
@@ -14828,7 +14804,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>生乳</t>
+          <t>灭菌乳</t>
         </is>
       </c>
       <c r="C64" s="4" t="n"/>
@@ -14869,7 +14845,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>巴氏杀菌乳</t>
+          <t>调制乳</t>
         </is>
       </c>
       <c r="C65" s="4" t="n"/>
@@ -14910,7 +14886,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>巴氏杀菌乳</t>
+          <t>调制乳</t>
         </is>
       </c>
       <c r="C66" s="4" t="n"/>
@@ -14951,7 +14927,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>灭菌乳</t>
+          <t>发酵乳</t>
         </is>
       </c>
       <c r="C67" s="4" t="n"/>
@@ -14992,7 +14968,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>灭菌乳</t>
+          <t>发酵乳</t>
         </is>
       </c>
       <c r="C68" s="4" t="n"/>
@@ -15028,19 +15004,19 @@
     <row r="69" ht="28" customHeight="1" s="23">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>乳及乳制品</t>
+          <t>蛋及蛋制品</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>调制乳</t>
+          <t>鲜蛋</t>
         </is>
       </c>
       <c r="C69" s="4" t="n"/>
       <c r="D69" s="4" t="n"/>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
+          <t>鲜蛋</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -15050,7 +15026,7 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H69" s="4" t="n"/>
@@ -15069,19 +15045,19 @@
     <row r="70" ht="28" customHeight="1" s="23">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>乳及乳制品</t>
+          <t>蛋及蛋制品</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>调制乳</t>
+          <t>鲜蛋</t>
         </is>
       </c>
       <c r="C70" s="4" t="n"/>
       <c r="D70" s="4" t="n"/>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
+          <t>鲜蛋</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -15110,19 +15086,19 @@
     <row r="71" ht="28" customHeight="1" s="23">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>乳及乳制品</t>
+          <t>调味品</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>发酵乳</t>
+          <t>食用盐</t>
         </is>
       </c>
       <c r="C71" s="4" t="n"/>
       <c r="D71" s="4" t="n"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
+          <t>食用盐</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -15132,7 +15108,7 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H71" s="4" t="n"/>
@@ -15151,19 +15127,19 @@
     <row r="72" ht="28" customHeight="1" s="23">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>乳及乳制品</t>
+          <t>调味品</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>发酵乳</t>
+          <t>食用盐</t>
         </is>
       </c>
       <c r="C72" s="4" t="n"/>
       <c r="D72" s="4" t="n"/>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
+          <t>食用盐</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -15192,19 +15168,23 @@
     <row r="73" ht="28" customHeight="1" s="23">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>蛋及蛋制品</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>鲜蛋</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="n"/>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>饮用天然矿泉水</t>
+        </is>
+      </c>
       <c r="D73" s="4" t="n"/>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>鲜蛋</t>
+          <t>饮用天然矿泉水</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -15214,38 +15194,42 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="H73" s="4" t="n"/>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>GB 5009.17</t>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
     <row r="74" ht="28" customHeight="1" s="23">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>蛋及蛋制品</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>鲜蛋</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="n"/>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>饮用天然矿泉水</t>
+        </is>
+      </c>
       <c r="D74" s="4" t="n"/>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>鲜蛋</t>
+          <t>饮用天然矿泉水</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
@@ -15261,32 +15245,36 @@
       <c r="H74" s="4" t="n"/>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>GB 5009.17</t>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
     <row r="75" ht="28" customHeight="1" s="23">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>调味品</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>食用盐</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="n"/>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>婴幼儿罐装辅助食品</t>
+        </is>
+      </c>
       <c r="D75" s="4" t="n"/>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>食用盐</t>
+          <t>婴幼儿罐装辅助食品</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -15296,7 +15284,7 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H75" s="4" t="n"/>
@@ -15315,19 +15303,23 @@
     <row r="76" ht="28" customHeight="1" s="23">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>调味品</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>食用盐</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="n"/>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>婴幼儿罐装辅助食品</t>
+        </is>
+      </c>
       <c r="D76" s="4" t="n"/>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>食用盐</t>
+          <t>婴幼儿罐装辅助食品</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
@@ -15353,186 +15345,10 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="28" customHeight="1" s="23">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>饮用天然矿泉水</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="n"/>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>饮用天然矿泉水</t>
-        </is>
-      </c>
-      <c r="F77" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="n"/>
-      <c r="I77" s="4" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="J77" s="4" t="n"/>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t>GB 8538</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="28" customHeight="1" s="23">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>饮用天然矿泉水</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="n"/>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>饮用天然矿泉水</t>
-        </is>
-      </c>
-      <c r="F78" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="n"/>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="J78" s="4" t="n"/>
-      <c r="K78" s="4" t="inlineStr">
-        <is>
-          <t>GB 8538</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="28" customHeight="1" s="23">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>特殊膳食用食品</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿罐装辅助食品</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿罐装辅助食品</t>
-        </is>
-      </c>
-      <c r="F79" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="n"/>
-      <c r="I79" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J79" s="4" t="n"/>
-      <c r="K79" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="28" customHeight="1" s="23">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>特殊膳食用食品</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿罐装辅助食品</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="n"/>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿罐装辅助食品</t>
-        </is>
-      </c>
-      <c r="F80" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="n"/>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J80" s="4" t="n"/>
-      <c r="K80" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
+    <row r="77" ht="28" customHeight="1" s="23"/>
+    <row r="78" ht="28" customHeight="1" s="23"/>
+    <row r="79" ht="28" customHeight="1" s="23"/>
+    <row r="80" ht="28" customHeight="1" s="23"/>
   </sheetData>
   <autoFilter ref="A4:K80"/>
   <mergeCells count="1">
@@ -18702,82 +18518,82 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="0" t="inlineStr">
         <is>
           <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="0" t="inlineStr">
         <is>
           <t>谷物</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
+      <c r="C75" s="0" t="inlineStr"/>
+      <c r="D75" s="0" t="inlineStr"/>
+      <c r="E75" s="0" t="inlineStr">
         <is>
           <t>谷物(稻谷除外)</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="0" t="inlineStr">
         <is>
           <t>无机砷 a</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
+      <c r="H75" s="0" t="inlineStr"/>
+      <c r="I75" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J75" s="0" t="inlineStr"/>
+      <c r="K75" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="0" t="inlineStr">
         <is>
           <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="0" t="inlineStr">
         <is>
           <t>谷物碾磨加工品</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
+      <c r="C76" s="0" t="inlineStr"/>
+      <c r="D76" s="0" t="inlineStr"/>
+      <c r="E76" s="0" t="inlineStr">
         <is>
           <t>谷物碾磨加工品[糙米、大米(粉)除外]</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" s="0" t="inlineStr">
         <is>
           <t>无机砷 a</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G76" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
+      <c r="H76" s="0" t="inlineStr"/>
+      <c r="I76" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J76" s="0" t="inlineStr"/>
+      <c r="K76" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -6905,15 +6905,19 @@
       </c>
       <c r="B89" s="19" t="inlineStr">
         <is>
-          <t>其他谷物制品</t>
+          <t>谷物制品</t>
         </is>
       </c>
       <c r="C89" s="19" t="inlineStr">
         <is>
+          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
+        </is>
+      </c>
+      <c r="D89" s="19" t="inlineStr">
+        <is>
           <t>粥类罐头</t>
         </is>
       </c>
-      <c r="D89" s="19" t="n"/>
       <c r="E89" s="19" t="inlineStr">
         <is>
           <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
@@ -8901,10 +8905,15 @@
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>其他谷物制品</t>
+          <t>谷物制品</t>
         </is>
       </c>
       <c r="C138" s="0" t="inlineStr">
+        <is>
+          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
         <is>
           <t>带馅料面米制品</t>
         </is>
@@ -13606,12 +13615,8 @@
           <t>谷物碾磨加工品</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>糙米(包括色稻米)</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="n"/>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
           <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
@@ -13633,7 +13638,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J37" s="4" t="n"/>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13651,12 +13660,8 @@
           <t>谷物碾磨加工品</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>糙米(包括色稻米)</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="n"/>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
           <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
@@ -13678,7 +13683,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J38" s="4" t="n"/>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13696,12 +13705,8 @@
           <t>谷物碾磨加工品</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>大米(粉)</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="n"/>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
       <c r="E39" s="4" t="inlineStr">
         <is>
           <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
@@ -13723,7 +13728,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J39" s="4" t="n"/>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13741,12 +13750,8 @@
           <t>谷物碾磨加工品</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>大米(粉)</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="n"/>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
           <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
@@ -13768,7 +13773,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J40" s="4" t="n"/>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13786,12 +13795,8 @@
           <t>谷物碾磨加工品</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>玉米粉、玉米糁(渣)</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="n"/>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
           <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
@@ -13813,7 +13818,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J41" s="4" t="n"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13831,11 +13840,8 @@
           <t>谷物碾磨加工品</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>玉米粉、玉米糁(渣)</t>
-        </is>
-      </c>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="0" t="inlineStr"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
           <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
@@ -13857,6 +13863,11 @@
           <t>mg/kg</t>
         </is>
       </c>
+      <c r="J42" s="0" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13874,12 +13885,8 @@
           <t>谷物碾磨加工品</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>小麦粉(包括食用麸皮)</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="n"/>
+      <c r="C43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
           <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
@@ -13901,7 +13908,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J43" s="4" t="n"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13919,12 +13930,8 @@
           <t>谷物碾磨加工品</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>小麦粉(包括食用麸皮)</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="n"/>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr"/>
       <c r="E44" s="4" t="inlineStr">
         <is>
           <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
@@ -13946,7 +13953,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J44" s="4" t="n"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -4058,11 +4058,7 @@
           <t>生干坚果及籽类</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>生咖啡豆</t>
-        </is>
-      </c>
+      <c r="C23" s="19" t="n"/>
       <c r="D23" s="19" t="n"/>
       <c r="E23" s="19" t="inlineStr">
         <is>
@@ -4103,11 +4099,7 @@
           <t>生干坚果及籽类</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>烘焙咖啡豆</t>
-        </is>
-      </c>
+      <c r="C24" s="19" t="n"/>
       <c r="D24" s="19" t="n"/>
       <c r="E24" s="19" t="inlineStr">
         <is>
@@ -8913,7 +8905,7 @@
           <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D138" s="0" t="inlineStr">
         <is>
           <t>带馅料面米制品</t>
         </is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -4055,10 +4055,14 @@
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>生干坚果及籽类</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="n"/>
+          <t>坚果及籽类制品</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>熟制坚果及籽类(带壳、脱壳、包衣)</t>
+        </is>
+      </c>
       <c r="D23" s="19" t="n"/>
       <c r="E23" s="19" t="inlineStr">
         <is>
@@ -4096,10 +4100,14 @@
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>生干坚果及籽类</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="n"/>
+          <t>坚果及籽类制品</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>熟制坚果及籽类(带壳、脱壳、包衣)</t>
+        </is>
+      </c>
       <c r="D24" s="19" t="n"/>
       <c r="E24" s="19" t="inlineStr">
         <is>
@@ -11021,10 +11029,14 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>生干坚果及籽类(不包括谷物种子和豆类,包括咖啡豆、可可豆)</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n"/>
+          <t>坚果及籽类制品</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>熟制坚果及籽类(带壳、脱壳、包衣)</t>
+        </is>
+      </c>
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="4" t="inlineStr">
         <is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -8960,7 +8960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -11072,12 +11072,20 @@
           <t>肉及肉制品</t>
         </is>
       </c>
-      <c r="B49" s="4" t="n"/>
-      <c r="C49" s="4" t="n"/>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>肉类(生鲜肉、冷却肉、冷冻肉等)</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>畜禽内脏</t>
+        </is>
+      </c>
       <c r="D49" s="4" t="n"/>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>肉及肉制品(畜禽内脏及其制品除外)</t>
+          <t>畜禽肝脏及其制品</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -11087,7 +11095,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H49" s="4" t="n"/>
@@ -11122,7 +11130,7 @@
       <c r="D50" s="4" t="n"/>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>畜禽肝脏及其制品</t>
+          <t>畜禽肾脏及其制品</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -11132,7 +11140,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H50" s="4" t="n"/>
@@ -11156,18 +11164,14 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>肉类(生鲜肉、冷却肉、冷冻肉等)</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>畜禽内脏</t>
-        </is>
-      </c>
+          <t>肉制品(包括内脏制品、血制品)</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n"/>
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>畜禽肾脏及其制品</t>
+          <t>畜禽肝脏及其制品</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -11177,7 +11181,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H51" s="4" t="n"/>
@@ -11208,7 +11212,7 @@
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>畜禽肝脏及其制品</t>
+          <t>畜禽肾脏及其制品</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -11218,7 +11222,7 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H52" s="4" t="n"/>
@@ -11237,19 +11241,23 @@
     <row r="53" ht="42" customHeight="1" s="23">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>肉制品(包括内脏制品、血制品)</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n"/>
+          <t>鲜、冻水产动物</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>鱼类</t>
+        </is>
+      </c>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>畜禽肾脏及其制品</t>
+          <t>鱼类</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -11259,7 +11267,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H53" s="4" t="n"/>
@@ -11288,13 +11296,13 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>鱼类</t>
+          <t>甲壳类</t>
         </is>
       </c>
       <c r="D54" s="4" t="n"/>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>鱼类</t>
+          <t>甲壳类(海蟹、虾蛄除外)</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -11304,7 +11312,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H54" s="4" t="n"/>
@@ -11339,7 +11347,7 @@
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>甲壳类(海蟹、虾蛄除外)</t>
+          <t>海蟹、虾蛄</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -11349,7 +11357,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H55" s="4" t="n"/>
@@ -11376,15 +11384,19 @@
           <t>鲜、冻水产动物</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>甲壳类</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="n"/>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>软体动物</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>双壳贝类</t>
+        </is>
+      </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>海蟹、虾蛄</t>
+          <t>双壳贝类、腹足类、头足类、棘皮类</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -11394,10 +11406,14 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="n"/>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>去除内脏</t>
+        </is>
+      </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -11428,7 +11444,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>双壳贝类</t>
+          <t>腹足类</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -11481,7 +11497,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>腹足类</t>
+          <t>头足类</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -11527,16 +11543,12 @@
           <t>鲜、冻水产动物</t>
         </is>
       </c>
-      <c r="C59" s="18" t="inlineStr">
-        <is>
-          <t>软体动物</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>头足类</t>
-        </is>
-      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>棘皮类</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
           <t>双壳贝类、腹足类、头足类、棘皮类</t>
@@ -11577,18 +11589,18 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
+          <t>水产制品</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>棘皮类</t>
+          <t>水产品罐头</t>
         </is>
       </c>
       <c r="D60" s="4" t="n"/>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>双壳贝类、腹足类、头足类、棘皮类</t>
+          <t>鱼类罐头</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
@@ -11598,14 +11610,10 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>去除内脏</t>
-        </is>
-      </c>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="n"/>
       <c r="I60" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -11631,13 +11639,13 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>水产品罐头</t>
+          <t>其他鱼类制品</t>
         </is>
       </c>
       <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>鱼类罐头</t>
+          <t>其他鱼类制品</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -11647,7 +11655,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H61" s="4" t="n"/>
@@ -11666,23 +11674,15 @@
     <row r="62" ht="42" customHeight="1" s="23">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>其他鱼类制品</t>
-        </is>
-      </c>
+          <t>蛋及蛋制品</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="n"/>
+      <c r="C62" s="4" t="n"/>
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>其他鱼类制品</t>
+          <t>蛋及蛋制品</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H62" s="4" t="n"/>
@@ -11711,15 +11711,19 @@
     <row r="63" ht="42" customHeight="1" s="23">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>蛋及蛋制品</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="n"/>
+          <t>调味品</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>食用盐</t>
+        </is>
+      </c>
       <c r="C63" s="4" t="n"/>
       <c r="D63" s="4" t="n"/>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>蛋及蛋制品</t>
+          <t>食用盐</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -11729,7 +11733,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H63" s="4" t="n"/>
@@ -11753,14 +11757,18 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>食用盐</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="n"/>
+          <t>水产调味品</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>鱼类调味品（例如：鱼露等）</t>
+        </is>
+      </c>
       <c r="D64" s="4" t="n"/>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>食用盐</t>
+          <t>鱼类调味品</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
@@ -11770,7 +11778,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H64" s="4" t="n"/>
@@ -11789,23 +11797,19 @@
     <row r="65" ht="42" customHeight="1" s="23">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>调味品</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>水产调味品</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>鱼类调味品（例如：鱼露等）</t>
-        </is>
-      </c>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="n"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>鱼类调味品</t>
+          <t>包装饮用水(饮用天然矿泉水除外)</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -11815,19 +11819,19 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="H65" s="4" t="n"/>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>GB 5009.15</t>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
@@ -11842,11 +11846,15 @@
           <t>包装饮用水</t>
         </is>
       </c>
-      <c r="C66" s="4" t="n"/>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>饮用天然矿泉水</t>
+        </is>
+      </c>
       <c r="D66" s="4" t="n"/>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>包装饮用水(饮用天然矿泉水除外)</t>
+          <t>饮用天然矿泉水</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
@@ -11856,7 +11864,7 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="H66" s="4" t="n"/>
@@ -11875,23 +11883,23 @@
     <row r="67" ht="56" customHeight="1" s="23">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>饮料类</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
+          <t>婴幼儿辅助食品</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>饮用天然矿泉水</t>
+          <t>婴幼儿谷类辅助食品</t>
         </is>
       </c>
       <c r="D67" s="4" t="n"/>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>饮用天然矿泉水</t>
+          <t>婴幼儿谷类辅助食品</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -11901,67 +11909,23 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="H67" s="4" t="n"/>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>mg/kg</t>
         </is>
       </c>
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>GB 8538</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="56" customHeight="1" s="23">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>特殊膳食用食品</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿谷类辅助食品</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿谷类辅助食品</t>
-        </is>
-      </c>
-      <c r="F68" s="12" t="inlineStr">
-        <is>
-          <t>镉</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="n"/>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J68" s="4" t="n"/>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
           <t>GB 5009.15</t>
         </is>
       </c>
     </row>
+    <row r="68" ht="56" customHeight="1" s="23"/>
   </sheetData>
   <autoFilter ref="A4:K68"/>
   <mergeCells count="1">
@@ -15380,7 +15344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -18609,6 +18573,78 @@
       </c>
       <c r="J76" s="0" t="inlineStr"/>
       <c r="K76" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>肉及肉制品</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>肉及肉制品</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>肉及肉制品</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>肉及肉制品</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -8960,7 +8960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -11925,7 +11925,84 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="56" customHeight="1" s="23"/>
+    <row r="68" ht="56" customHeight="1" s="23">
+      <c r="A68" s="0" t="inlineStr">
+        <is>
+          <t>肉及肉制品</t>
+        </is>
+      </c>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>肉类（生鲜肉、冷却肉、冷冻肉等）</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr"/>
+      <c r="D68" s="0" t="inlineStr"/>
+      <c r="E68" s="0" t="inlineStr">
+        <is>
+          <t>肉类(畜禽内脏除外)</t>
+        </is>
+      </c>
+      <c r="F68" s="0" t="inlineStr">
+        <is>
+          <t>镉</t>
+        </is>
+      </c>
+      <c r="G68" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H68" s="0" t="inlineStr"/>
+      <c r="I68" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J68" s="0" t="inlineStr"/>
+      <c r="K68" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="inlineStr">
+        <is>
+          <t>肉及肉制品</t>
+        </is>
+      </c>
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t>肉制品（包括内脏制品、血制品）</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr"/>
+      <c r="D69" s="0" t="inlineStr"/>
+      <c r="E69" s="0" t="inlineStr">
+        <is>
+          <t>肉制品(畜禽内脏制品除外)</t>
+        </is>
+      </c>
+      <c r="F69" s="0" t="inlineStr">
+        <is>
+          <t>镉</t>
+        </is>
+      </c>
+      <c r="G69" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H69" s="0" t="inlineStr"/>
+      <c r="I69" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J69" s="0" t="inlineStr"/>
+      <c r="K69" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:K68"/>
   <mergeCells count="1">
@@ -18579,72 +18656,72 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="0" t="inlineStr">
         <is>
           <t>肉及肉制品</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
+      <c r="B77" s="0" t="inlineStr"/>
+      <c r="C77" s="0" t="inlineStr"/>
+      <c r="D77" s="0" t="inlineStr"/>
+      <c r="E77" s="0" t="inlineStr">
         <is>
           <t>肉及肉制品</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" s="0" t="inlineStr">
         <is>
           <t>总砷</t>
         </is>
       </c>
-      <c r="G77" t="n">
+      <c r="G77" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
+      <c r="H77" s="0" t="inlineStr"/>
+      <c r="I77" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J77" s="0" t="inlineStr"/>
+      <c r="K77" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="0" t="inlineStr">
         <is>
           <t>肉及肉制品</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
+      <c r="B78" s="0" t="inlineStr"/>
+      <c r="C78" s="0" t="inlineStr"/>
+      <c r="D78" s="0" t="inlineStr"/>
+      <c r="E78" s="0" t="inlineStr">
         <is>
           <t>肉及肉制品</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F78" s="0" t="inlineStr">
         <is>
           <t>无机砷 a</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G78" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
+      <c r="H78" s="0" t="inlineStr"/>
+      <c r="I78" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J78" s="0" t="inlineStr"/>
+      <c r="K78" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -3320,7 +3320,7 @@
       <c r="D5" s="19" t="n"/>
       <c r="E5" s="19" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳除外</t>
+          <t>乳及乳制品(生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳除外)</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr">
@@ -6461,7 +6461,7 @@
       <c r="D78" s="19" t="n"/>
       <c r="E78" s="19" t="inlineStr">
         <is>
-          <t>香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外)</t>
+          <t>调味品(香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外))</t>
         </is>
       </c>
       <c r="F78" s="19" t="inlineStr">
@@ -6502,7 +6502,7 @@
       <c r="D79" s="19" t="n"/>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t>香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外)</t>
+          <t>调味品(香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外))</t>
         </is>
       </c>
       <c r="F79" s="19" t="inlineStr">
@@ -6543,7 +6543,7 @@
       <c r="D80" s="19" t="n"/>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外)</t>
+          <t>调味品(香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外))</t>
         </is>
       </c>
       <c r="F80" s="19" t="inlineStr">
@@ -6584,7 +6584,7 @@
       <c r="D81" s="19" t="n"/>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外)</t>
+          <t>调味品(香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外))</t>
         </is>
       </c>
       <c r="F81" s="19" t="inlineStr">
@@ -6625,7 +6625,7 @@
       <c r="D82" s="19" t="n"/>
       <c r="E82" s="19" t="inlineStr">
         <is>
-          <t>花椒、桂皮、肉桂、多种香辛料混合的香辛料</t>
+          <t>调味品(花椒、桂皮、肉桂、多种香辛料混合的香辛料)</t>
         </is>
       </c>
       <c r="F82" s="19" t="inlineStr">
@@ -6662,7 +6662,7 @@
       <c r="D83" s="19" t="n"/>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t>花椒、桂皮、肉桂、多种香辛料混合的香辛料</t>
+          <t>调味品(花椒、桂皮、肉桂、多种香辛料混合的香辛料)</t>
         </is>
       </c>
       <c r="F83" s="19" t="inlineStr">
@@ -6699,7 +6699,7 @@
       <c r="D84" s="19" t="n"/>
       <c r="E84" s="19" t="inlineStr">
         <is>
-          <t>花椒、桂皮、肉桂、多种香辛料混合的香辛料</t>
+          <t>调味品(花椒、桂皮、肉桂、多种香辛料混合的香辛料)</t>
         </is>
       </c>
       <c r="F84" s="19" t="inlineStr">
@@ -6736,7 +6736,7 @@
       <c r="D85" s="19" t="n"/>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>花椒、桂皮、肉桂、多种香辛料混合的香辛料</t>
+          <t>调味品(花椒、桂皮、肉桂、多种香辛料混合的香辛料)</t>
         </is>
       </c>
       <c r="F85" s="19" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="E129" s="0" t="inlineStr">
         <is>
-          <t>果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外)</t>
+          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
         </is>
       </c>
       <c r="F129" s="0" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="E130" s="0" t="inlineStr">
         <is>
-          <t>果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外)</t>
+          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
         </is>
       </c>
       <c r="F130" s="0" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="E131" s="0" t="inlineStr">
         <is>
-          <t>含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外)</t>
+          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
         </is>
       </c>
       <c r="F131" s="0" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="E132" s="0" t="inlineStr">
         <is>
-          <t>含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外)</t>
+          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
         </is>
       </c>
       <c r="F132" s="0" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="E133" s="0" t="inlineStr">
         <is>
-          <t>葡萄汁</t>
+          <t>饮料类(葡萄汁)</t>
         </is>
       </c>
       <c r="F133" s="0" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="E134" s="0" t="inlineStr">
         <is>
-          <t>固体饮料</t>
+          <t>饮料类(固体饮料)</t>
         </is>
       </c>
       <c r="F134" s="0" t="inlineStr">
@@ -21295,7 +21295,7 @@
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>包装饮用水(饮用天然矿泉水除外)</t>
+          <t>饮料类(包装饮用水(饮用天然矿泉水除外))</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -21336,7 +21336,7 @@
       <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>包装饮用水(饮用天然矿泉水除外)</t>
+          <t>饮料类(包装饮用水(饮用天然矿泉水除外))</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -15421,7 +15421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -18722,6 +18722,78 @@
       </c>
       <c r="J78" s="0" t="inlineStr"/>
       <c r="K78" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>油脂及其制品</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>油脂及其制品</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -3222,7 +3222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K138"/>
+  <dimension ref="A1:K136"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -4017,11 +4017,15 @@
           <t>生干坚果及籽类</t>
         </is>
       </c>
-      <c r="C22" s="19" t="n"/>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>生咖啡豆及烘焙咖啡豆</t>
+        </is>
+      </c>
       <c r="D22" s="19" t="n"/>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>坚果及籽类(生咖啡豆及烘焙咖啡豆除外)</t>
+          <t>生咖啡豆及烘焙咖啡豆</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
@@ -4031,7 +4035,7 @@
       </c>
       <c r="G22" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H22" s="19" t="n"/>
@@ -4040,7 +4044,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J22" s="19" t="n"/>
+      <c r="J22" s="19" t="inlineStr">
+        <is>
+          <t>d 仅限生咖啡豆及烘焙咖啡豆</t>
+        </is>
+      </c>
       <c r="K22" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -4048,25 +4056,21 @@
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" s="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>坚果及籽类</t>
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>坚果及籽类制品</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>熟制坚果及籽类(带壳、脱壳、包衣)</t>
-        </is>
-      </c>
+          <t>水产制品</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="n"/>
       <c r="D23" s="19" t="n"/>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>生咖啡豆及烘焙咖啡豆</t>
+          <t>水产制品(鱼类制品、海蜇制品除外)</t>
         </is>
       </c>
       <c r="F23" s="19" t="inlineStr">
@@ -4076,7 +4080,7 @@
       </c>
       <c r="G23" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H23" s="19" t="n"/>
@@ -4093,25 +4097,25 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>坚果及籽类</t>
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>坚果及籽类制品</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>熟制坚果及籽类(带壳、脱壳、包衣)</t>
+          <t>水产制品</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>鱼类制品</t>
         </is>
       </c>
       <c r="D24" s="19" t="n"/>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>生咖啡豆及烘焙咖啡豆</t>
+          <t>水产制品(鱼类制品、海蜇制品除外)</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
@@ -4121,7 +4125,7 @@
       </c>
       <c r="G24" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H24" s="19" t="n"/>
@@ -4148,7 +4152,11 @@
           <t>水产制品</t>
         </is>
       </c>
-      <c r="C25" s="19" t="n"/>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>海蜇制品</t>
+        </is>
+      </c>
       <c r="D25" s="19" t="n"/>
       <c r="E25" s="19" t="inlineStr">
         <is>
@@ -4189,15 +4197,15 @@
           <t>水产制品</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>海蜇制品</t>
         </is>
       </c>
       <c r="D26" s="19" t="n"/>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>水产制品(鱼类制品、海蜇制品除外)</t>
+          <t>海蜇制品</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
@@ -4205,9 +4213,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G26" s="19" t="inlineStr">
-        <is>
-          <t>1.0</t>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
       <c r="H26" s="19" t="n"/>
@@ -4236,13 +4244,13 @@
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>海蜇制品</t>
+          <t>鱼类制品</t>
         </is>
       </c>
       <c r="D27" s="19" t="n"/>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>水产制品(鱼类制品、海蜇制品除外)</t>
+          <t>鱼类制品</t>
         </is>
       </c>
       <c r="F27" s="19" t="inlineStr">
@@ -4252,7 +4260,7 @@
       </c>
       <c r="G27" s="19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H27" s="19" t="n"/>
@@ -4269,25 +4277,29 @@
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" s="23">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>水产制品</t>
+          <t>鲜、冻水产动物</t>
         </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>海蜇制品</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="n"/>
+          <t>软体动物</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>双壳贝类</t>
+        </is>
+      </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>海蜇制品</t>
+          <t>双壳贝类</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
@@ -4295,9 +4307,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
-        <is>
-          <t>2.0</t>
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H28" s="19" t="n"/>
@@ -4314,25 +4326,29 @@
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" s="23">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>水产制品</t>
+          <t>鲜、冻水产动物</t>
         </is>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="n"/>
+          <t>鱼类</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>非肉食性鱼类</t>
+        </is>
+      </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>鱼类制品</t>
+          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
@@ -4342,7 +4358,7 @@
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H29" s="19" t="n"/>
@@ -4371,17 +4387,17 @@
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>软体动物</t>
+          <t>鱼类</t>
         </is>
       </c>
       <c r="D30" s="19" t="inlineStr">
         <is>
-          <t>双壳贝类</t>
+          <t>非肉食性鱼类</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>双壳贝类</t>
+          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
@@ -4391,7 +4407,7 @@
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H30" s="19" t="n"/>
@@ -4528,7 +4544,7 @@
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
+          <t>鱼类、甲壳类</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
@@ -4538,7 +4554,7 @@
       </c>
       <c r="G33" s="19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H33" s="19" t="n"/>
@@ -4577,7 +4593,7 @@
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
+          <t>鱼类、甲壳类</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
@@ -4587,7 +4603,7 @@
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H34" s="19" t="n"/>
@@ -4655,27 +4671,19 @@
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>水果及其制品</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C36" s="19" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>非肉食性鱼类</t>
-        </is>
-      </c>
+          <t>新鲜水果（未经加工的、经表面处理的、去皮或预切的、冷冻的水果）</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="19" t="n"/>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>鱼类、甲壳类</t>
+          <t>新鲜水果(蔓越莓、醋栗除外)</t>
         </is>
       </c>
       <c r="F36" s="19" t="inlineStr">
@@ -4685,7 +4693,7 @@
       </c>
       <c r="G36" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H36" s="19" t="n"/>
@@ -4704,27 +4712,19 @@
     <row r="37" ht="42" customHeight="1" s="23">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>水果及其制品</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C37" s="19" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>非肉食性鱼类</t>
-        </is>
-      </c>
+          <t>水果制品</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="19" t="n"/>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>鱼类、甲壳类</t>
+          <t>水果制品(果酱(泥)、蜜饯、水果干类除外)</t>
         </is>
       </c>
       <c r="F37" s="19" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="G37" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H37" s="19" t="n"/>
@@ -4761,11 +4761,15 @@
           <t>新鲜水果（未经加工的、经表面处理的、去皮或预切的、冷冻的水果）</t>
         </is>
       </c>
-      <c r="C38" s="19" t="n"/>
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>浆果和其他小粒水果（例如：蔓越莓、醋栗等）</t>
+        </is>
+      </c>
       <c r="D38" s="19" t="n"/>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>新鲜水果(蔓越莓、醋栗除外)</t>
+          <t>蔓越莓、醋栗</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
@@ -4775,7 +4779,7 @@
       </c>
       <c r="G38" s="19" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H38" s="19" t="n"/>
@@ -4802,11 +4806,15 @@
           <t>水果制品</t>
         </is>
       </c>
-      <c r="C39" s="19" t="n"/>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>果酱（泥）</t>
+        </is>
+      </c>
       <c r="D39" s="19" t="n"/>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>水果制品(果酱(泥)、蜜饯、水果干类除外)</t>
+          <t>果酱(泥)</t>
         </is>
       </c>
       <c r="F39" s="19" t="inlineStr">
@@ -4816,7 +4824,7 @@
       </c>
       <c r="G39" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="H39" s="19" t="n"/>
@@ -4840,18 +4848,18 @@
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>新鲜水果（未经加工的、经表面处理的、去皮或预切的、冷冻的水果）</t>
+          <t>水果制品</t>
         </is>
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
-          <t>浆果和其他小粒水果（例如：蔓越莓、醋栗等）</t>
+          <t>水果干类</t>
         </is>
       </c>
       <c r="D40" s="19" t="n"/>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>蔓越莓、醋栗</t>
+          <t>水果干类</t>
         </is>
       </c>
       <c r="F40" s="19" t="inlineStr">
@@ -4861,7 +4869,7 @@
       </c>
       <c r="G40" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H40" s="19" t="n"/>
@@ -4890,13 +4898,13 @@
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
-          <t>果酱（泥）</t>
+          <t>蜜饯（包括果丹皮）</t>
         </is>
       </c>
       <c r="D41" s="19" t="n"/>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>果酱(泥)</t>
+          <t>蜜饯</t>
         </is>
       </c>
       <c r="F41" s="19" t="inlineStr">
@@ -4906,7 +4914,7 @@
       </c>
       <c r="G41" s="19" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="H41" s="19" t="n"/>
@@ -4925,23 +4933,15 @@
     <row r="42" ht="28" customHeight="1" s="23">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>水果及其制品</t>
-        </is>
-      </c>
-      <c r="B42" s="19" t="inlineStr">
-        <is>
-          <t>水果制品</t>
-        </is>
-      </c>
-      <c r="C42" s="19" t="inlineStr">
-        <is>
-          <t>水果干类</t>
-        </is>
-      </c>
+          <t>油脂及其制品</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="n"/>
+      <c r="C42" s="19" t="n"/>
       <c r="D42" s="19" t="n"/>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>水果干类</t>
+          <t>油脂及其制品</t>
         </is>
       </c>
       <c r="F42" s="19" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="G42" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="H42" s="19" t="n"/>
@@ -4970,23 +4970,19 @@
     <row r="43" ht="28" customHeight="1" s="23">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>水果及其制品</t>
+          <t>淀粉及淀粉制品（包括谷物、豆类和块根植物提取的淀粉）</t>
         </is>
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t>水果制品</t>
-        </is>
-      </c>
-      <c r="C43" s="19" t="inlineStr">
-        <is>
-          <t>蜜饯（包括果丹皮）</t>
-        </is>
-      </c>
+          <t>淀粉制品（包括虾味片）</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="n"/>
       <c r="D43" s="19" t="n"/>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>蜜饯</t>
+          <t>淀粉制品</t>
         </is>
       </c>
       <c r="F43" s="19" t="inlineStr">
@@ -4996,7 +4992,7 @@
       </c>
       <c r="G43" s="19" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H43" s="19" t="n"/>
@@ -5015,15 +5011,19 @@
     <row r="44" ht="28" customHeight="1" s="23">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
-        </is>
-      </c>
-      <c r="B44" s="19" t="n"/>
+          <t>淀粉及淀粉制品（包括谷物、豆类和块根植物提取的淀粉）</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>食用淀粉</t>
+        </is>
+      </c>
       <c r="C44" s="19" t="n"/>
       <c r="D44" s="19" t="n"/>
       <c r="E44" s="19" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
+          <t>食用淀粉</t>
         </is>
       </c>
       <c r="F44" s="19" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="G44" s="19" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H44" s="19" t="n"/>
@@ -5052,19 +5052,15 @@
     <row r="45" ht="42" customHeight="1" s="23">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>淀粉及淀粉制品（包括谷物、豆类和块根植物提取的淀粉）</t>
-        </is>
-      </c>
-      <c r="B45" s="19" t="inlineStr">
-        <is>
-          <t>淀粉制品（包括虾味片）</t>
-        </is>
-      </c>
+          <t>焙烤食品</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="n"/>
       <c r="C45" s="19" t="n"/>
       <c r="D45" s="19" t="n"/>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>淀粉制品</t>
+          <t>焙烤食品</t>
         </is>
       </c>
       <c r="F45" s="19" t="inlineStr">
@@ -5093,19 +5089,19 @@
     <row r="46" ht="42" customHeight="1" s="23">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>淀粉及淀粉制品（包括谷物、豆类和块根植物提取的淀粉）</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>食用淀粉</t>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
         </is>
       </c>
       <c r="C46" s="19" t="n"/>
       <c r="D46" s="19" t="n"/>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>食用淀粉</t>
+          <t>辅食营养补充品</t>
         </is>
       </c>
       <c r="F46" s="19" t="inlineStr">
@@ -5115,7 +5111,7 @@
       </c>
       <c r="G46" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H46" s="19" t="n"/>
@@ -5134,15 +5130,19 @@
     <row r="47" ht="42" customHeight="1" s="23">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>焙烤食品</t>
-        </is>
-      </c>
-      <c r="B47" s="19" t="n"/>
+          <t>特殊膳食用食品</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+        </is>
+      </c>
       <c r="C47" s="19" t="n"/>
       <c r="D47" s="19" t="n"/>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>焙烤食品</t>
+          <t>运动营养食品(固态、半固态或粉状)</t>
         </is>
       </c>
       <c r="F47" s="19" t="inlineStr">
@@ -5183,7 +5183,7 @@
       <c r="D48" s="19" t="n"/>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>辅食营养补充品</t>
+          <t>运动营养食品(液态)</t>
         </is>
       </c>
       <c r="F48" s="19" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="G48" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H48" s="19" t="n"/>
@@ -5224,7 +5224,7 @@
       <c r="D49" s="19" t="n"/>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>运动营养食品(固态、半固态或粉状)</t>
+          <t>孕妇及乳母营养补充食品</t>
         </is>
       </c>
       <c r="F49" s="19" t="inlineStr">
@@ -5258,14 +5258,14 @@
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+          <t>婴幼儿辅助食品</t>
         </is>
       </c>
       <c r="C50" s="19" t="n"/>
       <c r="D50" s="19" t="n"/>
       <c r="E50" s="19" t="inlineStr">
         <is>
-          <t>运动营养食品(液态)</t>
+          <t>婴幼儿辅助食品</t>
         </is>
       </c>
       <c r="F50" s="19" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="G50" s="19" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H50" s="19" t="n"/>
@@ -5299,14 +5299,14 @@
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+          <t>婴幼儿配方食品</t>
         </is>
       </c>
       <c r="C51" s="19" t="n"/>
       <c r="D51" s="19" t="n"/>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t>孕妇及乳母营养补充食品</t>
+          <t>婴幼儿配方食品</t>
         </is>
       </c>
       <c r="F51" s="19" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="G51" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.08(以固态产品计)</t>
         </is>
       </c>
       <c r="H51" s="19" t="n"/>
@@ -5325,7 +5325,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J51" s="19" t="n"/>
+      <c r="J51" s="19" t="inlineStr">
+        <is>
+          <t>c 液态婴幼儿配方食品根据8∶1的比例折算其限量。</t>
+        </is>
+      </c>
       <c r="K51" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -5340,14 +5344,14 @@
       </c>
       <c r="B52" s="19" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
+          <t>特殊医学用途配方食品（特殊医学用途婴儿配方食品涉及的品种除外）</t>
         </is>
       </c>
       <c r="C52" s="19" t="n"/>
       <c r="D52" s="19" t="n"/>
       <c r="E52" s="19" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
+          <t>特殊医学用途配方食品(特殊医学用途婴儿配方食品涉及的品种除外)、10岁以上人群的产品</t>
         </is>
       </c>
       <c r="F52" s="19" t="inlineStr">
@@ -5357,7 +5361,7 @@
       </c>
       <c r="G52" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5(以固态产品计)</t>
         </is>
       </c>
       <c r="H52" s="19" t="n"/>
@@ -5381,14 +5385,14 @@
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
-          <t>婴幼儿配方食品</t>
+          <t>特殊医学用途配方食品（特殊医学用途婴儿配方食品涉及的品种除外）</t>
         </is>
       </c>
       <c r="C53" s="19" t="n"/>
       <c r="D53" s="19" t="n"/>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t>婴幼儿配方食品</t>
+          <t>特殊医学用途配方食品(特殊医学用途婴儿配方食品涉及的品种除外)、1~10岁人群的产品</t>
         </is>
       </c>
       <c r="F53" s="19" t="inlineStr">
@@ -5398,7 +5402,7 @@
       </c>
       <c r="G53" s="19" t="inlineStr">
         <is>
-          <t>0.08(以固态产品计)</t>
+          <t>0.15(以固态产品计)</t>
         </is>
       </c>
       <c r="H53" s="19" t="n"/>
@@ -5407,11 +5411,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J53" s="19" t="inlineStr">
-        <is>
-          <t>c 液态婴幼儿配方食品根据8∶1的比例折算其限量。</t>
-        </is>
-      </c>
+      <c r="J53" s="19" t="n"/>
       <c r="K53" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -5421,19 +5421,19 @@
     <row r="54" ht="70" customHeight="1" s="23">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B54" s="19" t="inlineStr">
         <is>
-          <t>特殊医学用途配方食品（特殊医学用途婴儿配方食品涉及的品种除外）</t>
+          <t>肉类（生鲜肉、冷却肉、冷冻肉等）</t>
         </is>
       </c>
       <c r="C54" s="19" t="n"/>
       <c r="D54" s="19" t="n"/>
       <c r="E54" s="19" t="inlineStr">
         <is>
-          <t>特殊医学用途配方食品(特殊医学用途婴儿配方食品涉及的品种除外)、10岁以上人群的产品</t>
+          <t>肉类(畜禽内脏除外)</t>
         </is>
       </c>
       <c r="F54" s="19" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="G54" s="19" t="inlineStr">
         <is>
-          <t>0.5(以固态产品计)</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H54" s="19" t="n"/>
@@ -5462,19 +5462,19 @@
     <row r="55" ht="28" customHeight="1" s="23">
       <c r="A55" s="19" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
-          <t>特殊医学用途配方食品（特殊医学用途婴儿配方食品涉及的品种除外）</t>
+          <t>肉制品（包括内脏制品、血制品）</t>
         </is>
       </c>
       <c r="C55" s="19" t="n"/>
       <c r="D55" s="19" t="n"/>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t>特殊医学用途配方食品(特殊医学用途婴儿配方食品涉及的品种除外)、1~10岁人群的产品</t>
+          <t>肉制品(畜禽内脏制品除外)</t>
         </is>
       </c>
       <c r="F55" s="19" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="G55" s="19" t="inlineStr">
         <is>
-          <t>0.15(以固态产品计)</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H55" s="19" t="n"/>
@@ -5508,14 +5508,14 @@
       </c>
       <c r="B56" s="19" t="inlineStr">
         <is>
-          <t>肉类（生鲜肉、冷却肉、冷冻肉等）</t>
+          <t>肉制品（包括内脏制品、血制品）</t>
         </is>
       </c>
       <c r="C56" s="19" t="n"/>
       <c r="D56" s="19" t="n"/>
       <c r="E56" s="19" t="inlineStr">
         <is>
-          <t>肉类(畜禽内脏除外)</t>
+          <t>畜禽内脏制品</t>
         </is>
       </c>
       <c r="F56" s="19" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="G56" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H56" s="19" t="n"/>
@@ -5549,14 +5549,18 @@
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
-          <t>肉制品（包括内脏制品、血制品）</t>
-        </is>
-      </c>
-      <c r="C57" s="19" t="n"/>
+          <t>肉类（生鲜肉、冷却肉、冷冻肉等）</t>
+        </is>
+      </c>
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>畜禽内脏（例如：肝、肾、肺、肠等）</t>
+        </is>
+      </c>
       <c r="D57" s="19" t="n"/>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t>肉制品(畜禽内脏制品除外)</t>
+          <t>畜禽内脏</t>
         </is>
       </c>
       <c r="F57" s="19" t="inlineStr">
@@ -5566,7 +5570,7 @@
       </c>
       <c r="G57" s="19" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H57" s="19" t="n"/>
@@ -5585,19 +5589,19 @@
     <row r="58" ht="42" customHeight="1" s="23">
       <c r="A58" s="19" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B58" s="19" t="inlineStr">
         <is>
-          <t>肉制品（包括内脏制品、血制品）</t>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
         </is>
       </c>
       <c r="C58" s="19" t="n"/>
       <c r="D58" s="19" t="n"/>
       <c r="E58" s="19" t="inlineStr">
         <is>
-          <t>畜禽内脏制品</t>
+          <t>新鲜蔬菜(芸薹类蔬菜、叶菜蔬菜、豆类蔬菜、生姜、薯类除外)</t>
         </is>
       </c>
       <c r="F58" s="19" t="inlineStr">
@@ -5607,7 +5611,7 @@
       </c>
       <c r="G58" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H58" s="19" t="n"/>
@@ -5626,23 +5630,19 @@
     <row r="59" ht="42" customHeight="1" s="23">
       <c r="A59" s="19" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
-          <t>肉类（生鲜肉、冷却肉、冷冻肉等）</t>
-        </is>
-      </c>
-      <c r="C59" s="19" t="inlineStr">
-        <is>
-          <t>畜禽内脏（例如：肝、肾、肺、肠等）</t>
-        </is>
-      </c>
+          <t>蔬菜制品</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="n"/>
       <c r="D59" s="19" t="n"/>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t>畜禽内脏</t>
+          <t>蔬菜制品(酱腌菜、干制蔬菜除外)</t>
         </is>
       </c>
       <c r="F59" s="19" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="G59" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H59" s="19" t="n"/>
@@ -5679,11 +5679,15 @@
           <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
         </is>
       </c>
-      <c r="C60" s="19" t="n"/>
+      <c r="C60" s="19" t="inlineStr">
+        <is>
+          <t>叶菜蔬菜（包括芸薹类叶菜）</t>
+        </is>
+      </c>
       <c r="D60" s="19" t="n"/>
       <c r="E60" s="19" t="inlineStr">
         <is>
-          <t>新鲜蔬菜(芸薹类蔬菜、叶菜蔬菜、豆类蔬菜、生姜、薯类除外)</t>
+          <t>叶菜蔬菜</t>
         </is>
       </c>
       <c r="F60" s="19" t="inlineStr">
@@ -5693,7 +5697,7 @@
       </c>
       <c r="G60" s="19" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H60" s="19" t="n"/>
@@ -5717,14 +5721,18 @@
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
-          <t>蔬菜制品</t>
-        </is>
-      </c>
-      <c r="C61" s="19" t="n"/>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="inlineStr">
+        <is>
+          <t>芸薹类蔬菜</t>
+        </is>
+      </c>
       <c r="D61" s="19" t="n"/>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t>蔬菜制品(酱腌菜、干制蔬菜除外)</t>
+          <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
         </is>
       </c>
       <c r="F61" s="19" t="inlineStr">
@@ -5734,7 +5742,7 @@
       </c>
       <c r="G61" s="19" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H61" s="19" t="n"/>
@@ -5763,13 +5771,13 @@
       </c>
       <c r="C62" s="19" t="inlineStr">
         <is>
-          <t>叶菜蔬菜（包括芸薹类叶菜）</t>
+          <t>豆类蔬菜</t>
         </is>
       </c>
       <c r="D62" s="19" t="n"/>
       <c r="E62" s="19" t="inlineStr">
         <is>
-          <t>叶菜蔬菜</t>
+          <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
         </is>
       </c>
       <c r="F62" s="19" t="inlineStr">
@@ -5779,7 +5787,7 @@
       </c>
       <c r="G62" s="19" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H62" s="19" t="n"/>
@@ -5808,10 +5816,14 @@
       </c>
       <c r="C63" s="19" t="inlineStr">
         <is>
-          <t>芸薹类蔬菜</t>
-        </is>
-      </c>
-      <c r="D63" s="19" t="n"/>
+          <t>块根和块茎蔬菜（例如：薯类、胡萝卜、萝卜、生姜等）</t>
+        </is>
+      </c>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>生姜</t>
+        </is>
+      </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
           <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
@@ -5841,7 +5853,7 @@
       </c>
     </row>
     <row r="64" ht="42" customHeight="1" s="23">
-      <c r="A64" s="19" t="inlineStr">
+      <c r="A64" s="20" t="inlineStr">
         <is>
           <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
@@ -5853,10 +5865,14 @@
       </c>
       <c r="C64" s="19" t="inlineStr">
         <is>
-          <t>豆类蔬菜</t>
-        </is>
-      </c>
-      <c r="D64" s="19" t="n"/>
+          <t>块根和块茎蔬菜（例如：薯类、胡萝卜、萝卜、生姜等）</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>薯类</t>
+        </is>
+      </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
           <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
@@ -5886,29 +5902,25 @@
       </c>
     </row>
     <row r="65" ht="42" customHeight="1" s="23">
-      <c r="A65" s="19" t="inlineStr">
+      <c r="A65" s="20" t="inlineStr">
         <is>
           <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+          <t>蔬菜制品</t>
         </is>
       </c>
       <c r="C65" s="19" t="inlineStr">
         <is>
-          <t>块根和块茎蔬菜（例如：薯类、胡萝卜、萝卜、生姜等）</t>
-        </is>
-      </c>
-      <c r="D65" s="19" t="inlineStr">
-        <is>
-          <t>生姜</t>
-        </is>
-      </c>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D65" s="19" t="n"/>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
+          <t>酱腌菜</t>
         </is>
       </c>
       <c r="F65" s="19" t="inlineStr">
@@ -5916,9 +5928,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G65" s="19" t="inlineStr">
-        <is>
-          <t>0.2</t>
+      <c r="G65" s="22" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H65" s="19" t="n"/>
@@ -5935,29 +5947,25 @@
       </c>
     </row>
     <row r="66" ht="42" customHeight="1" s="23">
-      <c r="A66" s="20" t="inlineStr">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B66" s="19" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+          <t>蔬菜制品</t>
         </is>
       </c>
       <c r="C66" s="19" t="inlineStr">
         <is>
-          <t>块根和块茎蔬菜（例如：薯类、胡萝卜、萝卜、生姜等）</t>
-        </is>
-      </c>
-      <c r="D66" s="19" t="inlineStr">
-        <is>
-          <t>薯类</t>
-        </is>
-      </c>
+          <t>干制蔬菜</t>
+        </is>
+      </c>
+      <c r="D66" s="19" t="n"/>
       <c r="E66" s="19" t="inlineStr">
         <is>
-          <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
+          <t>干制蔬菜</t>
         </is>
       </c>
       <c r="F66" s="19" t="inlineStr">
@@ -5967,7 +5975,7 @@
       </c>
       <c r="G66" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="H66" s="19" t="n"/>
@@ -5984,7 +5992,7 @@
       </c>
     </row>
     <row r="67" ht="42" customHeight="1" s="23">
-      <c r="A67" s="20" t="inlineStr">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
@@ -5996,7 +6004,7 @@
       </c>
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>酱腌菜</t>
         </is>
       </c>
       <c r="D67" s="19" t="n"/>
@@ -6010,7 +6018,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G67" s="22" t="inlineStr">
+      <c r="G67" s="19" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -6031,23 +6039,19 @@
     <row r="68" ht="28" customHeight="1" s="23">
       <c r="A68" s="19" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
-        </is>
-      </c>
-      <c r="B68" s="19" t="inlineStr">
-        <is>
-          <t>蔬菜制品</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>干制蔬菜</t>
-        </is>
-      </c>
+          <t>藻类及其制品</t>
+        </is>
+      </c>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>新鲜藻类（未经加工的、经表面处理的、预切的、冷冻的藻类）</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="n"/>
       <c r="D68" s="19" t="n"/>
       <c r="E68" s="19" t="inlineStr">
         <is>
-          <t>干制蔬菜</t>
+          <t>新鲜藻类(螺旋藻除外)</t>
         </is>
       </c>
       <c r="F68" s="19" t="inlineStr">
@@ -6057,7 +6061,7 @@
       </c>
       <c r="G68" s="19" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H68" s="19" t="n"/>
@@ -6076,23 +6080,23 @@
     <row r="69" ht="42" customHeight="1" s="23">
       <c r="A69" s="19" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+          <t>藻类及其制品</t>
         </is>
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
-          <t>蔬菜制品</t>
+          <t>新鲜藻类（未经加工的、经表面处理的、预切的、冷冻的藻类）</t>
         </is>
       </c>
       <c r="C69" s="19" t="inlineStr">
         <is>
-          <t>酱腌菜</t>
+          <t>螺旋藻</t>
         </is>
       </c>
       <c r="D69" s="19" t="n"/>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t>酱腌菜</t>
+          <t>螺旋藻</t>
         </is>
       </c>
       <c r="F69" s="19" t="inlineStr">
@@ -6102,7 +6106,7 @@
       </c>
       <c r="G69" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.5(干重计)</t>
         </is>
       </c>
       <c r="H69" s="19" t="n"/>
@@ -6124,16 +6128,16 @@
           <t>藻类及其制品</t>
         </is>
       </c>
-      <c r="B70" s="0" t="inlineStr">
-        <is>
-          <t>新鲜藻类（未经加工的、经表面处理的、预切的、冷冻的藻类）</t>
+      <c r="B70" s="19" t="inlineStr">
+        <is>
+          <t>藻类制品</t>
         </is>
       </c>
       <c r="C70" s="19" t="n"/>
       <c r="D70" s="19" t="n"/>
       <c r="E70" s="19" t="inlineStr">
         <is>
-          <t>新鲜藻类(螺旋藻除外)</t>
+          <t>藻类制品(螺旋藻制品除外)</t>
         </is>
       </c>
       <c r="F70" s="19" t="inlineStr">
@@ -6143,7 +6147,7 @@
       </c>
       <c r="G70" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H70" s="19" t="n"/>
@@ -6167,18 +6171,18 @@
       </c>
       <c r="B71" s="19" t="inlineStr">
         <is>
-          <t>新鲜藻类（未经加工的、经表面处理的、预切的、冷冻的藻类）</t>
+          <t>藻类制品</t>
         </is>
       </c>
       <c r="C71" s="19" t="inlineStr">
         <is>
-          <t>螺旋藻</t>
+          <t>其他藻类制品</t>
         </is>
       </c>
       <c r="D71" s="19" t="n"/>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t>螺旋藻</t>
+          <t>螺旋藻制品</t>
         </is>
       </c>
       <c r="F71" s="19" t="inlineStr">
@@ -6188,7 +6192,7 @@
       </c>
       <c r="G71" s="19" t="inlineStr">
         <is>
-          <t>0.5(干重计)</t>
+          <t>2.0(干重计)</t>
         </is>
       </c>
       <c r="H71" s="19" t="n"/>
@@ -6207,19 +6211,15 @@
     <row r="72">
       <c r="A72" s="19" t="inlineStr">
         <is>
-          <t>藻类及其制品</t>
-        </is>
-      </c>
-      <c r="B72" s="19" t="inlineStr">
-        <is>
-          <t>藻类制品</t>
-        </is>
-      </c>
+          <t>蛋及蛋制品</t>
+        </is>
+      </c>
+      <c r="B72" s="19" t="n"/>
       <c r="C72" s="19" t="n"/>
       <c r="D72" s="19" t="n"/>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>藻类制品(螺旋藻制品除外)</t>
+          <t>蛋及蛋制品</t>
         </is>
       </c>
       <c r="F72" s="19" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="G72" s="19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H72" s="19" t="n"/>
@@ -6248,23 +6248,15 @@
     <row r="73" ht="70" customHeight="1" s="23">
       <c r="A73" s="19" t="inlineStr">
         <is>
-          <t>藻类及其制品</t>
-        </is>
-      </c>
-      <c r="B73" s="19" t="inlineStr">
-        <is>
-          <t>藻类制品</t>
-        </is>
-      </c>
-      <c r="C73" s="19" t="inlineStr">
-        <is>
-          <t>其他藻类制品</t>
-        </is>
-      </c>
+          <t>调味品</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="n"/>
+      <c r="C73" s="19" t="n"/>
       <c r="D73" s="19" t="n"/>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t>螺旋藻制品</t>
+          <t>调味品(香辛料类除外)</t>
         </is>
       </c>
       <c r="F73" s="19" t="inlineStr">
@@ -6274,7 +6266,7 @@
       </c>
       <c r="G73" s="19" t="inlineStr">
         <is>
-          <t>2.0(干重计)</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H73" s="19" t="n"/>
@@ -6293,15 +6285,19 @@
     <row r="74" ht="28" customHeight="1" s="23">
       <c r="A74" s="19" t="inlineStr">
         <is>
-          <t>蛋及蛋制品</t>
-        </is>
-      </c>
-      <c r="B74" s="19" t="n"/>
+          <t>调味品</t>
+        </is>
+      </c>
+      <c r="B74" s="19" t="inlineStr">
+        <is>
+          <t>香辛料类</t>
+        </is>
+      </c>
       <c r="C74" s="19" t="n"/>
       <c r="D74" s="19" t="n"/>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>蛋及蛋制品</t>
+          <t>调味品(香辛料类除外)</t>
         </is>
       </c>
       <c r="F74" s="19" t="inlineStr">
@@ -6311,7 +6307,7 @@
       </c>
       <c r="G74" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H74" s="19" t="n"/>
@@ -6333,12 +6329,16 @@
           <t>调味品</t>
         </is>
       </c>
-      <c r="B75" s="19" t="n"/>
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t>香辛料类</t>
+        </is>
+      </c>
       <c r="C75" s="19" t="n"/>
       <c r="D75" s="19" t="n"/>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>调味品(香辛料类除外)</t>
+          <t>香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外)</t>
         </is>
       </c>
       <c r="F75" s="19" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G75" s="19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H75" s="19" t="n"/>
@@ -6357,7 +6357,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J75" s="19" t="n"/>
+      <c r="J75" s="19" t="inlineStr">
+        <is>
+          <t>b 新鲜香辛料(如姜、葱、蒜等)应按对应的新鲜蔬菜(或新鲜水果)类别执行。</t>
+        </is>
+      </c>
       <c r="K75" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6365,21 +6369,17 @@
       </c>
     </row>
     <row r="76" ht="42" customHeight="1" s="23">
-      <c r="A76" s="19" t="inlineStr">
+      <c r="A76" s="20" t="inlineStr">
         <is>
           <t>调味品</t>
         </is>
       </c>
-      <c r="B76" s="19" t="inlineStr">
-        <is>
-          <t>香辛料类</t>
-        </is>
-      </c>
+      <c r="B76" s="19" t="n"/>
       <c r="C76" s="19" t="n"/>
       <c r="D76" s="19" t="n"/>
       <c r="E76" s="19" t="inlineStr">
         <is>
-          <t>调味品(香辛料类除外)</t>
+          <t>调味品(香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外))</t>
         </is>
       </c>
       <c r="F76" s="19" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="G76" s="19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H76" s="19" t="n"/>
@@ -6398,7 +6398,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J76" s="19" t="n"/>
+      <c r="J76" s="19" t="inlineStr">
+        <is>
+          <t>b 新鲜香辛料(如姜、葱、蒜等)应按对应的新鲜蔬菜(或新鲜水果)类别执行。</t>
+        </is>
+      </c>
       <c r="K76" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6406,21 +6410,17 @@
       </c>
     </row>
     <row r="77" ht="42" customHeight="1" s="23">
-      <c r="A77" s="19" t="inlineStr">
+      <c r="A77" s="20" t="inlineStr">
         <is>
           <t>调味品</t>
         </is>
       </c>
-      <c r="B77" s="19" t="inlineStr">
-        <is>
-          <t>香辛料类</t>
-        </is>
-      </c>
+      <c r="B77" s="19" t="n"/>
       <c r="C77" s="19" t="n"/>
       <c r="D77" s="19" t="n"/>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外)</t>
+          <t>调味品(香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外))</t>
         </is>
       </c>
       <c r="F77" s="19" t="inlineStr">
@@ -6469,7 +6469,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G78" s="19" t="inlineStr">
+      <c r="G78" s="22" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="B79" s="19" t="n"/>
-      <c r="C79" s="19" t="n"/>
+      <c r="C79" s="18" t="n"/>
       <c r="D79" s="19" t="n"/>
       <c r="E79" s="19" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G79" s="19" t="inlineStr">
+      <c r="G79" s="22" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
@@ -6543,7 +6543,7 @@
       <c r="D80" s="19" t="n"/>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>调味品(香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外))</t>
+          <t>调味品(花椒、桂皮、肉桂、多种香辛料混合的香辛料)</t>
         </is>
       </c>
       <c r="F80" s="19" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="G80" s="22" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H80" s="19" t="n"/>
@@ -6562,11 +6562,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J80" s="19" t="inlineStr">
-        <is>
-          <t>b 新鲜香辛料(如姜、葱、蒜等)应按对应的新鲜蔬菜(或新鲜水果)类别执行。</t>
-        </is>
-      </c>
+      <c r="J80" s="19" t="n"/>
       <c r="K80" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6580,11 +6576,11 @@
         </is>
       </c>
       <c r="B81" s="19" t="n"/>
-      <c r="C81" s="18" t="n"/>
+      <c r="C81" s="19" t="n"/>
       <c r="D81" s="19" t="n"/>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>调味品(香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外))</t>
+          <t>调味品(花椒、桂皮、肉桂、多种香辛料混合的香辛料)</t>
         </is>
       </c>
       <c r="F81" s="19" t="inlineStr">
@@ -6594,7 +6590,7 @@
       </c>
       <c r="G81" s="22" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H81" s="19" t="n"/>
@@ -6603,11 +6599,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J81" s="19" t="inlineStr">
-        <is>
-          <t>b 新鲜香辛料(如姜、葱、蒜等)应按对应的新鲜蔬菜(或新鲜水果)类别执行。</t>
-        </is>
-      </c>
+      <c r="J81" s="19" t="n"/>
       <c r="K81" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6658,7 +6650,7 @@
         </is>
       </c>
       <c r="B83" s="19" t="n"/>
-      <c r="C83" s="19" t="n"/>
+      <c r="C83" s="18" t="n"/>
       <c r="D83" s="19" t="n"/>
       <c r="E83" s="19" t="inlineStr">
         <is>
@@ -6691,7 +6683,7 @@
     <row r="84" ht="56" customHeight="1" s="23">
       <c r="A84" s="20" t="inlineStr">
         <is>
-          <t>调味品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B84" s="19" t="n"/>
@@ -6699,7 +6691,7 @@
       <c r="D84" s="19" t="n"/>
       <c r="E84" s="19" t="inlineStr">
         <is>
-          <t>调味品(花椒、桂皮、肉桂、多种香辛料混合的香辛料)</t>
+          <t>谷物及其制品(麦片、面筋、粥类罐头、带馅料面米制品除外)</t>
         </is>
       </c>
       <c r="F84" s="19" t="inlineStr">
@@ -6709,7 +6701,7 @@
       </c>
       <c r="G84" s="22" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H84" s="19" t="n"/>
@@ -6718,7 +6710,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J84" s="19" t="n"/>
+      <c r="J84" s="19" t="inlineStr">
+        <is>
+          <t>a 稻谷以糙米计。</t>
+        </is>
+      </c>
       <c r="K84" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6728,15 +6724,23 @@
     <row r="85" ht="56" customHeight="1" s="23">
       <c r="A85" s="20" t="inlineStr">
         <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B85" s="19" t="n"/>
-      <c r="C85" s="18" t="n"/>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B85" s="19" t="inlineStr">
+        <is>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C85" s="19" t="inlineStr">
+        <is>
+          <t>麦片</t>
+        </is>
+      </c>
       <c r="D85" s="19" t="n"/>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>调味品(花椒、桂皮、肉桂、多种香辛料混合的香辛料)</t>
+          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
       <c r="F85" s="19" t="inlineStr">
@@ -6746,7 +6750,7 @@
       </c>
       <c r="G85" s="22" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H85" s="19" t="n"/>
@@ -6768,12 +6772,24 @@
           <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
-      <c r="B86" s="19" t="n"/>
-      <c r="C86" s="19" t="n"/>
-      <c r="D86" s="19" t="n"/>
+      <c r="B86" s="19" t="inlineStr">
+        <is>
+          <t>谷物制品</t>
+        </is>
+      </c>
+      <c r="C86" s="19" t="inlineStr">
+        <is>
+          <t>小麦粉制品</t>
+        </is>
+      </c>
+      <c r="D86" s="19" t="inlineStr">
+        <is>
+          <t>面筋</t>
+        </is>
+      </c>
       <c r="E86" s="19" t="inlineStr">
         <is>
-          <t>谷物及其制品(麦片、面筋、粥类罐头、带馅料面米制品除外)</t>
+          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
       <c r="F86" s="19" t="inlineStr">
@@ -6781,9 +6797,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G86" s="22" t="inlineStr">
-        <is>
-          <t>0.2</t>
+      <c r="G86" s="30" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H86" s="19" t="n"/>
@@ -6792,11 +6808,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J86" s="19" t="inlineStr">
-        <is>
-          <t>a 稻谷以糙米计。</t>
-        </is>
-      </c>
+      <c r="J86" s="19" t="n"/>
       <c r="K86" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6811,15 +6823,19 @@
       </c>
       <c r="B87" s="19" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
+          <t>谷物制品</t>
         </is>
       </c>
       <c r="C87" s="19" t="inlineStr">
         <is>
-          <t>麦片</t>
-        </is>
-      </c>
-      <c r="D87" s="19" t="n"/>
+          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
+        </is>
+      </c>
+      <c r="D87" s="19" t="inlineStr">
+        <is>
+          <t>粥类罐头</t>
+        </is>
+      </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
           <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
@@ -6830,7 +6846,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G87" s="22" t="inlineStr">
+      <c r="G87" s="30" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -6851,27 +6867,19 @@
     <row r="88" ht="56" customHeight="1" s="23">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>豆类及其制品</t>
         </is>
       </c>
       <c r="B88" s="19" t="inlineStr">
         <is>
-          <t>谷物制品</t>
-        </is>
-      </c>
-      <c r="C88" s="19" t="inlineStr">
-        <is>
-          <t>小麦粉制品</t>
-        </is>
-      </c>
-      <c r="D88" s="19" t="inlineStr">
-        <is>
-          <t>面筋</t>
-        </is>
-      </c>
+          <t>豆类制品</t>
+        </is>
+      </c>
+      <c r="C88" s="19" t="n"/>
+      <c r="D88" s="19" t="n"/>
       <c r="E88" s="19" t="inlineStr">
         <is>
-          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
+          <t>豆类制品(豆浆除外)</t>
         </is>
       </c>
       <c r="F88" s="19" t="inlineStr">
@@ -6881,7 +6889,7 @@
       </c>
       <c r="G88" s="30" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H88" s="19" t="n"/>
@@ -6900,27 +6908,23 @@
     <row r="89" ht="56" customHeight="1" s="23">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>豆类及其制品</t>
         </is>
       </c>
       <c r="B89" s="19" t="inlineStr">
         <is>
-          <t>谷物制品</t>
+          <t>豆类制品</t>
         </is>
       </c>
       <c r="C89" s="19" t="inlineStr">
         <is>
-          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
-        </is>
-      </c>
-      <c r="D89" s="19" t="inlineStr">
-        <is>
-          <t>粥类罐头</t>
-        </is>
-      </c>
+          <t>非发酵豆制品（例如：豆浆、豆腐类、豆干类、腐竹类、熟制豆类、大豆蛋白膨化食品、大豆素肉等）</t>
+        </is>
+      </c>
+      <c r="D89" s="19" t="n"/>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
+          <t>豆浆</t>
         </is>
       </c>
       <c r="F89" s="19" t="inlineStr">
@@ -6930,7 +6934,7 @@
       </c>
       <c r="G89" s="30" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H89" s="19" t="n"/>
@@ -6954,14 +6958,14 @@
       </c>
       <c r="B90" s="19" t="inlineStr">
         <is>
-          <t>豆类制品</t>
+          <t>豆类（干豆、以干豆磨成的粉）</t>
         </is>
       </c>
       <c r="C90" s="19" t="n"/>
       <c r="D90" s="19" t="n"/>
       <c r="E90" s="19" t="inlineStr">
         <is>
-          <t>豆类制品(豆浆除外)</t>
+          <t>豆类</t>
         </is>
       </c>
       <c r="F90" s="19" t="inlineStr">
@@ -6971,7 +6975,7 @@
       </c>
       <c r="G90" s="30" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H90" s="19" t="n"/>
@@ -6990,23 +6994,15 @@
     <row r="91" ht="56" customHeight="1" s="23">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>豆类及其制品</t>
-        </is>
-      </c>
-      <c r="B91" s="19" t="inlineStr">
-        <is>
-          <t>豆类制品</t>
-        </is>
-      </c>
-      <c r="C91" s="19" t="inlineStr">
-        <is>
-          <t>非发酵豆制品（例如：豆浆、豆腐类、豆干类、腐竹类、熟制豆类、大豆蛋白膨化食品、大豆素肉等）</t>
-        </is>
-      </c>
+          <t>酒类</t>
+        </is>
+      </c>
+      <c r="B91" s="19" t="n"/>
+      <c r="C91" s="19" t="n"/>
       <c r="D91" s="19" t="n"/>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t>豆浆</t>
+          <t>酒类(白酒、黄酒除外)</t>
         </is>
       </c>
       <c r="F91" s="19" t="inlineStr">
@@ -7016,7 +7012,7 @@
       </c>
       <c r="G91" s="30" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H91" s="19" t="n"/>
@@ -7035,19 +7031,23 @@
     <row r="92" ht="56" customHeight="1" s="23">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>豆类及其制品</t>
+          <t>酒类</t>
         </is>
       </c>
       <c r="B92" s="19" t="inlineStr">
         <is>
-          <t>豆类（干豆、以干豆磨成的粉）</t>
-        </is>
-      </c>
-      <c r="C92" s="19" t="n"/>
+          <t>蒸馏酒（例如：白酒、白兰地、威士忌、伏特加、朗姆酒等）</t>
+        </is>
+      </c>
+      <c r="C92" s="19" t="inlineStr">
+        <is>
+          <t>白酒</t>
+        </is>
+      </c>
       <c r="D92" s="19" t="n"/>
       <c r="E92" s="19" t="inlineStr">
         <is>
-          <t>豆类</t>
+          <t>白酒、黄酒</t>
         </is>
       </c>
       <c r="F92" s="19" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G92" s="30" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H92" s="19" t="n"/>
@@ -7079,12 +7079,20 @@
           <t>酒类</t>
         </is>
       </c>
-      <c r="B93" s="19" t="n"/>
-      <c r="C93" s="19" t="n"/>
+      <c r="B93" s="19" t="inlineStr">
+        <is>
+          <t>发酵酒(例如:葡萄酒、黄酒、果酒、啤酒等)</t>
+        </is>
+      </c>
+      <c r="C93" s="19" t="inlineStr">
+        <is>
+          <t>黄酒</t>
+        </is>
+      </c>
       <c r="D93" s="19" t="n"/>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t>酒类(白酒、黄酒除外)</t>
+          <t>白酒、黄酒</t>
         </is>
       </c>
       <c r="F93" s="19" t="inlineStr">
@@ -7094,7 +7102,7 @@
       </c>
       <c r="G93" s="30" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H93" s="19" t="n"/>
@@ -7113,23 +7121,15 @@
     <row r="94" ht="56" customHeight="1" s="23">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>酒类</t>
-        </is>
-      </c>
-      <c r="B94" s="19" t="inlineStr">
-        <is>
-          <t>蒸馏酒（例如：白酒、白兰地、威士忌、伏特加、朗姆酒等）</t>
-        </is>
-      </c>
-      <c r="C94" s="19" t="inlineStr">
-        <is>
-          <t>白酒</t>
-        </is>
-      </c>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B94" s="19" t="n"/>
+      <c r="C94" s="19" t="n"/>
       <c r="D94" s="19" t="n"/>
       <c r="E94" s="19" t="inlineStr">
         <is>
-          <t>白酒、黄酒</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F94" s="19" t="inlineStr">
@@ -7158,23 +7158,23 @@
     <row r="95" ht="56" customHeight="1" s="23">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>酒类</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B95" s="19" t="inlineStr">
         <is>
-          <t>发酵酒(例如:葡萄酒、黄酒、果酒、啤酒等)</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C95" s="19" t="inlineStr">
         <is>
-          <t>黄酒</t>
+          <t>双孢菇</t>
         </is>
       </c>
       <c r="D95" s="19" t="n"/>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t>白酒、黄酒</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F95" s="19" t="inlineStr">
@@ -7206,8 +7206,16 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B96" s="19" t="n"/>
-      <c r="C96" s="19" t="n"/>
+      <c r="B96" s="19" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C96" s="19" t="inlineStr">
+        <is>
+          <t>平菇</t>
+        </is>
+      </c>
       <c r="D96" s="19" t="n"/>
       <c r="E96" s="19" t="inlineStr">
         <is>
@@ -7250,7 +7258,7 @@
       </c>
       <c r="C97" s="19" t="inlineStr">
         <is>
-          <t>双孢菇</t>
+          <t>香菇</t>
         </is>
       </c>
       <c r="D97" s="19" t="n"/>
@@ -7295,7 +7303,7 @@
       </c>
       <c r="C98" s="19" t="inlineStr">
         <is>
-          <t>平菇</t>
+          <t>榛蘑</t>
         </is>
       </c>
       <c r="D98" s="19" t="n"/>
@@ -7333,16 +7341,8 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B99" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C99" s="19" t="inlineStr">
-        <is>
-          <t>香菇</t>
-        </is>
-      </c>
+      <c r="B99" s="19" t="n"/>
+      <c r="C99" s="19" t="n"/>
       <c r="D99" s="19" t="n"/>
       <c r="E99" s="19" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="C100" s="19" t="inlineStr">
         <is>
-          <t>榛蘑</t>
+          <t>松茸</t>
         </is>
       </c>
       <c r="D100" s="19" t="n"/>
@@ -7399,7 +7399,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G100" s="30" t="inlineStr">
+      <c r="G100" s="22" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -7423,8 +7423,16 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B101" s="19" t="n"/>
-      <c r="C101" s="19" t="n"/>
+      <c r="B101" s="19" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C101" s="19" t="inlineStr">
+        <is>
+          <t>松露</t>
+        </is>
+      </c>
       <c r="D101" s="19" t="n"/>
       <c r="E101" s="19" t="inlineStr">
         <is>
@@ -7436,7 +7444,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G101" s="30" t="inlineStr">
+      <c r="G101" s="22" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -7465,12 +7473,12 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C102" s="19" t="inlineStr">
-        <is>
-          <t>松茸</t>
-        </is>
-      </c>
-      <c r="D102" s="19" t="n"/>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>青头菌</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="n"/>
       <c r="E102" s="19" t="inlineStr">
         <is>
           <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
@@ -7500,7 +7508,7 @@
       </c>
     </row>
     <row r="103" ht="42" customHeight="1" s="23">
-      <c r="A103" s="20" t="inlineStr">
+      <c r="A103" s="19" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
@@ -7512,7 +7520,7 @@
       </c>
       <c r="C103" s="19" t="inlineStr">
         <is>
-          <t>松露</t>
+          <t>鸡枞</t>
         </is>
       </c>
       <c r="D103" s="19" t="n"/>
@@ -7526,7 +7534,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G103" s="22" t="inlineStr">
+      <c r="G103" s="19" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -7555,12 +7563,12 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>青头菌</t>
-        </is>
-      </c>
-      <c r="D104" s="4" t="n"/>
+      <c r="C104" s="19" t="inlineStr">
+        <is>
+          <t>鸡油菌</t>
+        </is>
+      </c>
+      <c r="D104" s="19" t="n"/>
       <c r="E104" s="19" t="inlineStr">
         <is>
           <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
@@ -7571,7 +7579,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G104" s="22" t="inlineStr">
+      <c r="G104" s="25" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -7590,7 +7598,7 @@
       </c>
     </row>
     <row r="105" ht="42" customHeight="1" s="23">
-      <c r="A105" s="19" t="inlineStr">
+      <c r="A105" s="20" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
@@ -7602,7 +7610,7 @@
       </c>
       <c r="C105" s="19" t="inlineStr">
         <is>
-          <t>鸡枞</t>
+          <t>多汁乳菇</t>
         </is>
       </c>
       <c r="D105" s="19" t="n"/>
@@ -7616,7 +7624,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G105" s="19" t="inlineStr">
+      <c r="G105" s="25" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -7640,16 +7648,8 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B106" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C106" s="19" t="inlineStr">
-        <is>
-          <t>鸡油菌</t>
-        </is>
-      </c>
+      <c r="B106" s="19" t="n"/>
+      <c r="C106" s="19" t="n"/>
       <c r="D106" s="19" t="n"/>
       <c r="E106" s="19" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="C107" s="19" t="inlineStr">
         <is>
-          <t>多汁乳菇</t>
+          <t>银耳</t>
         </is>
       </c>
       <c r="D107" s="19" t="n"/>
@@ -7730,12 +7730,20 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B108" s="19" t="n"/>
-      <c r="C108" s="19" t="n"/>
+      <c r="B108" s="19" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C108" s="19" t="inlineStr">
+        <is>
+          <t>双孢菇</t>
+        </is>
+      </c>
       <c r="D108" s="19" t="n"/>
       <c r="E108" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F108" s="19" t="inlineStr">
@@ -7745,7 +7753,7 @@
       </c>
       <c r="G108" s="25" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H108" s="19" t="n"/>
@@ -7772,15 +7780,15 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C109" s="19" t="inlineStr">
-        <is>
-          <t>银耳</t>
+      <c r="C109" s="0" t="inlineStr">
+        <is>
+          <t>双孢菇</t>
         </is>
       </c>
       <c r="D109" s="19" t="n"/>
       <c r="E109" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F109" s="19" t="inlineStr">
@@ -7790,7 +7798,7 @@
       </c>
       <c r="G109" s="25" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H109" s="19" t="n"/>
@@ -7862,7 +7870,7 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C111" s="0" t="inlineStr">
+      <c r="C111" s="19" t="inlineStr">
         <is>
           <t>双孢菇</t>
         </is>
@@ -7909,13 +7917,13 @@
       </c>
       <c r="C112" s="19" t="inlineStr">
         <is>
-          <t>双孢菇</t>
+          <t>木耳 （毛木耳,黑木耳）</t>
         </is>
       </c>
       <c r="D112" s="19" t="n"/>
       <c r="E112" s="19" t="inlineStr">
         <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F112" s="19" t="inlineStr">
@@ -7925,7 +7933,7 @@
       </c>
       <c r="G112" s="25" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H112" s="19" t="n"/>
@@ -7942,25 +7950,24 @@
       </c>
     </row>
     <row r="113" ht="42" customHeight="1" s="23">
-      <c r="A113" s="20" t="inlineStr">
+      <c r="A113" s="19" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B113" s="19" t="inlineStr">
+      <c r="B113" s="0" t="inlineStr">
         <is>
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C113" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇</t>
-        </is>
-      </c>
-      <c r="D113" s="19" t="n"/>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t>木耳 （毛木耳,黑木耳）</t>
+        </is>
+      </c>
       <c r="E113" s="19" t="inlineStr">
         <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F113" s="19" t="inlineStr">
@@ -7968,9 +7975,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G113" s="25" t="inlineStr">
-        <is>
-          <t>0.3</t>
+      <c r="G113" s="19" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H113" s="19" t="n"/>
@@ -7997,15 +8004,14 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C114" s="19" t="inlineStr">
-        <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
-      <c r="D114" s="19" t="n"/>
-      <c r="E114" s="19" t="inlineStr">
-        <is>
-          <t>木耳及其制品、银耳及其制品</t>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F114" s="19" t="inlineStr">
@@ -8013,12 +8019,11 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G114" s="25" t="inlineStr">
+      <c r="G114" s="19" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="H114" s="19" t="n"/>
       <c r="I114" s="19" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -8032,24 +8037,24 @@
       </c>
     </row>
     <row r="115" ht="28" customHeight="1" s="23">
-      <c r="A115" s="19" t="inlineStr">
+      <c r="A115" s="20" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B115" s="0" t="inlineStr">
+      <c r="B115" s="19" t="inlineStr">
         <is>
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
-      <c r="E115" s="19" t="inlineStr">
-        <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F115" s="19" t="inlineStr">
@@ -8057,12 +8062,11 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G115" s="19" t="inlineStr">
+      <c r="G115" s="31" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="H115" s="19" t="n"/>
       <c r="I115" s="19" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -8086,22 +8090,22 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C116" s="0" t="inlineStr">
+      <c r="C116" s="27" t="inlineStr">
         <is>
           <t>松茸</t>
         </is>
       </c>
-      <c r="E116" s="0" t="inlineStr">
+      <c r="E116" s="27" t="inlineStr">
         <is>
           <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
-      <c r="F116" s="19" t="inlineStr">
+      <c r="F116" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G116" s="19" t="inlineStr">
+      <c r="G116" s="30" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -8119,12 +8123,12 @@
       </c>
     </row>
     <row r="117" ht="42" customHeight="1" s="23">
-      <c r="A117" s="20" t="inlineStr">
+      <c r="A117" s="0" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B117" s="19" t="inlineStr">
+      <c r="B117" s="0" t="inlineStr">
         <is>
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
@@ -8139,45 +8143,44 @@
           <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
-      <c r="F117" s="19" t="inlineStr">
+      <c r="F117" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G117" s="31" t="inlineStr">
+      <c r="G117" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="I117" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J117" s="19" t="n"/>
-      <c r="K117" s="19" t="inlineStr">
+      <c r="I117" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K117" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
       </c>
     </row>
     <row r="118" ht="28" customHeight="1" s="23">
-      <c r="A118" s="20" t="inlineStr">
+      <c r="A118" s="0" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B118" s="19" t="inlineStr">
+      <c r="B118" s="0" t="inlineStr">
         <is>
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C118" s="27" t="inlineStr">
+      <c r="C118" s="0" t="inlineStr">
         <is>
           <t>松茸</t>
         </is>
       </c>
-      <c r="E118" s="27" t="inlineStr">
+      <c r="E118" s="0" t="inlineStr">
         <is>
           <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
         </is>
@@ -8187,18 +8190,17 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G118" s="30" t="inlineStr">
+      <c r="G118" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="I118" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J118" s="19" t="n"/>
-      <c r="K118" s="19" t="inlineStr">
+      <c r="I118" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K118" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
@@ -8249,22 +8251,17 @@
     <row r="120">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>食糖及淀粉糖</t>
         </is>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C120" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
+          <t>食糖（包括方糖、冰片糖、原糖、糖蜜、部分转化糖、槭树糖浆）</t>
         </is>
       </c>
       <c r="E120" s="0" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>食糖及淀粉糖</t>
         </is>
       </c>
       <c r="F120" s="0" t="inlineStr">
@@ -8274,7 +8271,7 @@
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I120" s="0" t="inlineStr">
@@ -8291,22 +8288,12 @@
     <row r="121">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B121" s="0" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C121" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="E121" s="0" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
         </is>
       </c>
       <c r="F121" s="0" t="inlineStr">
@@ -8316,7 +8303,7 @@
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I121" s="0" t="inlineStr">
@@ -8333,17 +8320,17 @@
     <row r="122">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>食糖（包括方糖、冰片糖、原糖、糖蜜、部分转化糖、槭树糖浆）</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="E122" s="0" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
         </is>
       </c>
       <c r="F122" s="0" t="inlineStr">
@@ -8353,7 +8340,7 @@
       </c>
       <c r="G122" s="0" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I122" s="0" t="inlineStr">
@@ -8373,6 +8360,16 @@
           <t>饮料类</t>
         </is>
       </c>
+      <c r="B123" s="0" t="inlineStr">
+        <is>
+          <t>蛋白饮料</t>
+        </is>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
+        </is>
+      </c>
       <c r="E123" s="0" t="inlineStr">
         <is>
           <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
@@ -8407,7 +8404,7 @@
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
         </is>
       </c>
       <c r="E124" s="0" t="inlineStr">
@@ -8442,16 +8439,6 @@
           <t>饮料类</t>
         </is>
       </c>
-      <c r="B125" s="0" t="inlineStr">
-        <is>
-          <t>蛋白饮料</t>
-        </is>
-      </c>
-      <c r="C125" s="0" t="inlineStr">
-        <is>
-          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
-        </is>
-      </c>
       <c r="E125" s="0" t="inlineStr">
         <is>
           <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
@@ -8491,7 +8478,7 @@
       </c>
       <c r="E126" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外)</t>
         </is>
       </c>
       <c r="F126" s="0" t="inlineStr">
@@ -8501,7 +8488,7 @@
       </c>
       <c r="G126" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I126" s="0" t="inlineStr">
@@ -8523,7 +8510,7 @@
       </c>
       <c r="E127" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
         </is>
       </c>
       <c r="F127" s="0" t="inlineStr">
@@ -8533,7 +8520,7 @@
       </c>
       <c r="G127" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I127" s="0" t="inlineStr">
@@ -8553,14 +8540,9 @@
           <t>饮料类</t>
         </is>
       </c>
-      <c r="B128" s="0" t="inlineStr">
-        <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
-        </is>
-      </c>
       <c r="E128" s="0" t="inlineStr">
         <is>
-          <t>果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外)</t>
+          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
         </is>
       </c>
       <c r="F128" s="0" t="inlineStr">
@@ -8592,7 +8574,7 @@
       </c>
       <c r="E129" s="0" t="inlineStr">
         <is>
-          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
+          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
         </is>
       </c>
       <c r="F129" s="0" t="inlineStr">
@@ -8602,7 +8584,7 @@
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="I129" s="0" t="inlineStr">
@@ -8624,7 +8606,7 @@
       </c>
       <c r="E130" s="0" t="inlineStr">
         <is>
-          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
+          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
         </is>
       </c>
       <c r="F130" s="0" t="inlineStr">
@@ -8634,7 +8616,7 @@
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="I130" s="0" t="inlineStr">
@@ -8656,7 +8638,7 @@
       </c>
       <c r="E131" s="0" t="inlineStr">
         <is>
-          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
+          <t>饮料类(葡萄汁)</t>
         </is>
       </c>
       <c r="F131" s="0" t="inlineStr">
@@ -8666,7 +8648,7 @@
       </c>
       <c r="G131" s="0" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="I131" s="0" t="inlineStr">
@@ -8688,7 +8670,7 @@
       </c>
       <c r="E132" s="0" t="inlineStr">
         <is>
-          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
+          <t>饮料类(固体饮料)</t>
         </is>
       </c>
       <c r="F132" s="0" t="inlineStr">
@@ -8698,7 +8680,7 @@
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I132" s="0" t="inlineStr">
@@ -8718,9 +8700,14 @@
           <t>饮料类</t>
         </is>
       </c>
+      <c r="B133" s="0" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
       <c r="E133" s="0" t="inlineStr">
         <is>
-          <t>饮料类(葡萄汁)</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="F133" s="0" t="inlineStr">
@@ -8730,7 +8717,7 @@
       </c>
       <c r="G133" s="0" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="I133" s="0" t="inlineStr">
@@ -8738,9 +8725,9 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="K133" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
+      <c r="K133" s="28" t="inlineStr">
+        <is>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
@@ -8750,9 +8737,19 @@
           <t>饮料类</t>
         </is>
       </c>
+      <c r="B134" s="0" t="inlineStr">
+        <is>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
+        </is>
+      </c>
+      <c r="C134" s="0" t="inlineStr">
+        <is>
+          <t>浓缩果蔬汁（浆）</t>
+        </is>
+      </c>
       <c r="E134" s="0" t="inlineStr">
         <is>
-          <t>饮料类(固体饮料)</t>
+          <t>浓缩果蔬汁(浆)</t>
         </is>
       </c>
       <c r="F134" s="0" t="inlineStr">
@@ -8762,7 +8759,7 @@
       </c>
       <c r="G134" s="0" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I134" s="0" t="inlineStr">
@@ -8784,12 +8781,17 @@
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
+          <t>蛋白饮料</t>
+        </is>
+      </c>
+      <c r="C135" s="0" t="inlineStr">
+        <is>
+          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
         </is>
       </c>
       <c r="E135" s="0" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
+          <t>含乳饮料</t>
         </is>
       </c>
       <c r="F135" s="0" t="inlineStr">
@@ -8799,7 +8801,7 @@
       </c>
       <c r="G135" s="0" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="I135" s="0" t="inlineStr">
@@ -8807,31 +8809,36 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="K135" s="28" t="inlineStr">
-        <is>
-          <t>GB 8538</t>
+      <c r="K135" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.12</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t>饮料类</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
+          <t>谷物制品</t>
         </is>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>浓缩果蔬汁（浆）</t>
+          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
+        </is>
+      </c>
+      <c r="D136" s="0" t="inlineStr">
+        <is>
+          <t>带馅料面米制品</t>
         </is>
       </c>
       <c r="E136" s="0" t="inlineStr">
         <is>
-          <t>浓缩果蔬汁(浆)</t>
+          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
       <c r="F136" s="0" t="inlineStr">
@@ -8850,95 +8857,6 @@
         </is>
       </c>
       <c r="K136" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B137" s="0" t="inlineStr">
-        <is>
-          <t>蛋白饮料</t>
-        </is>
-      </c>
-      <c r="C137" s="0" t="inlineStr">
-        <is>
-          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
-        </is>
-      </c>
-      <c r="E137" s="0" t="inlineStr">
-        <is>
-          <t>含乳饮料</t>
-        </is>
-      </c>
-      <c r="F137" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G137" s="0" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="I137" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K137" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="0" t="inlineStr">
-        <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B138" s="0" t="inlineStr">
-        <is>
-          <t>谷物制品</t>
-        </is>
-      </c>
-      <c r="C138" s="0" t="inlineStr">
-        <is>
-          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
-        </is>
-      </c>
-      <c r="D138" s="0" t="inlineStr">
-        <is>
-          <t>带馅料面米制品</t>
-        </is>
-      </c>
-      <c r="E138" s="0" t="inlineStr">
-        <is>
-          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
-        </is>
-      </c>
-      <c r="F138" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G138" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I138" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K138" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
@@ -11029,12 +10947,12 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>坚果及籽类制品</t>
+          <t>生干坚果及籽类</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>熟制坚果及籽类(带壳、脱壳、包衣)</t>
+          <t>花生</t>
         </is>
       </c>
       <c r="D48" s="4" t="n"/>
@@ -11059,7 +10977,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J48" s="4" t="n"/>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>b 仅限花生</t>
+        </is>
+      </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
           <t>GB 5009.15</t>
@@ -18728,72 +18650,72 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="0" t="inlineStr">
         <is>
           <t>油脂及其制品</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
+      <c r="B79" s="0" t="inlineStr"/>
+      <c r="C79" s="0" t="inlineStr"/>
+      <c r="D79" s="0" t="inlineStr"/>
+      <c r="E79" s="0" t="inlineStr">
         <is>
           <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" s="0" t="inlineStr">
         <is>
           <t>总砷</t>
         </is>
       </c>
-      <c r="G79" t="n">
+      <c r="G79" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
+      <c r="H79" s="0" t="inlineStr"/>
+      <c r="I79" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J79" s="0" t="inlineStr"/>
+      <c r="K79" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="0" t="inlineStr">
         <is>
           <t>油脂及其制品</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
+      <c r="B80" s="0" t="inlineStr"/>
+      <c r="C80" s="0" t="inlineStr"/>
+      <c r="D80" s="0" t="inlineStr"/>
+      <c r="E80" s="0" t="inlineStr">
         <is>
           <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" s="0" t="inlineStr">
         <is>
           <t>无机砷 a</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G80" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
+      <c r="H80" s="0" t="inlineStr"/>
+      <c r="I80" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J80" s="0" t="inlineStr"/>
+      <c r="K80" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -3222,7 +3222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K136"/>
+  <dimension ref="A1:K128"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -6297,7 +6297,7 @@
       <c r="D74" s="19" t="n"/>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>调味品(香辛料类除外)</t>
+          <t>香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外)</t>
         </is>
       </c>
       <c r="F74" s="19" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="G74" s="19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H74" s="19" t="n"/>
@@ -6316,7 +6316,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J74" s="19" t="n"/>
+      <c r="J74" s="19" t="inlineStr">
+        <is>
+          <t>b 新鲜香辛料(如姜、葱、蒜等)应按对应的新鲜蔬菜(或新鲜水果)类别执行。</t>
+        </is>
+      </c>
       <c r="K74" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6324,7 +6328,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="19" t="inlineStr">
+      <c r="A75" s="20" t="inlineStr">
         <is>
           <t>调味品</t>
         </is>
@@ -6334,11 +6338,15 @@
           <t>香辛料类</t>
         </is>
       </c>
-      <c r="C75" s="19" t="n"/>
+      <c r="C75" s="19" t="inlineStr">
+        <is>
+          <t>花椒、桂皮、肉桂、多种香辛料混合的香辛料</t>
+        </is>
+      </c>
       <c r="D75" s="19" t="n"/>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外)</t>
+          <t>花椒、桂皮、肉桂、多种香辛料混合的香辛料</t>
         </is>
       </c>
       <c r="F75" s="19" t="inlineStr">
@@ -6346,9 +6354,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G75" s="19" t="inlineStr">
-        <is>
-          <t>1.5</t>
+      <c r="G75" s="22" t="inlineStr">
+        <is>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H75" s="19" t="n"/>
@@ -6357,11 +6365,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J75" s="19" t="inlineStr">
-        <is>
-          <t>b 新鲜香辛料(如姜、葱、蒜等)应按对应的新鲜蔬菜(或新鲜水果)类别执行。</t>
-        </is>
-      </c>
+      <c r="J75" s="19" t="n"/>
       <c r="K75" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6371,7 +6375,7 @@
     <row r="76" ht="42" customHeight="1" s="23">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>调味品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B76" s="19" t="n"/>
@@ -6379,7 +6383,7 @@
       <c r="D76" s="19" t="n"/>
       <c r="E76" s="19" t="inlineStr">
         <is>
-          <t>调味品(香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外))</t>
+          <t>谷物及其制品(麦片、面筋、粥类罐头、带馅料面米制品除外)</t>
         </is>
       </c>
       <c r="F76" s="19" t="inlineStr">
@@ -6387,9 +6391,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G76" s="19" t="inlineStr">
-        <is>
-          <t>1.5</t>
+      <c r="G76" s="22" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H76" s="19" t="n"/>
@@ -6400,7 +6404,7 @@
       </c>
       <c r="J76" s="19" t="inlineStr">
         <is>
-          <t>b 新鲜香辛料(如姜、葱、蒜等)应按对应的新鲜蔬菜(或新鲜水果)类别执行。</t>
+          <t>a 稻谷以糙米计。</t>
         </is>
       </c>
       <c r="K76" s="19" t="inlineStr">
@@ -6412,15 +6416,23 @@
     <row r="77" ht="42" customHeight="1" s="23">
       <c r="A77" s="20" t="inlineStr">
         <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B77" s="19" t="n"/>
-      <c r="C77" s="19" t="n"/>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B77" s="19" t="inlineStr">
+        <is>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C77" s="19" t="inlineStr">
+        <is>
+          <t>麦片</t>
+        </is>
+      </c>
       <c r="D77" s="19" t="n"/>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>调味品(香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外))</t>
+          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
       <c r="F77" s="19" t="inlineStr">
@@ -6428,9 +6440,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G77" s="19" t="inlineStr">
-        <is>
-          <t>1.5</t>
+      <c r="G77" s="22" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H77" s="19" t="n"/>
@@ -6439,11 +6451,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J77" s="19" t="inlineStr">
-        <is>
-          <t>b 新鲜香辛料(如姜、葱、蒜等)应按对应的新鲜蔬菜(或新鲜水果)类别执行。</t>
-        </is>
-      </c>
+      <c r="J77" s="19" t="n"/>
       <c r="K77" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6453,15 +6461,27 @@
     <row r="78" ht="56" customHeight="1" s="23">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B78" s="19" t="n"/>
-      <c r="C78" s="19" t="n"/>
-      <c r="D78" s="19" t="n"/>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B78" s="19" t="inlineStr">
+        <is>
+          <t>谷物制品</t>
+        </is>
+      </c>
+      <c r="C78" s="19" t="inlineStr">
+        <is>
+          <t>小麦粉制品</t>
+        </is>
+      </c>
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>面筋</t>
+        </is>
+      </c>
       <c r="E78" s="19" t="inlineStr">
         <is>
-          <t>调味品(香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外))</t>
+          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
       <c r="F78" s="19" t="inlineStr">
@@ -6469,9 +6489,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G78" s="22" t="inlineStr">
-        <is>
-          <t>1.5</t>
+      <c r="G78" s="30" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H78" s="19" t="n"/>
@@ -6480,11 +6500,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J78" s="19" t="inlineStr">
-        <is>
-          <t>b 新鲜香辛料(如姜、葱、蒜等)应按对应的新鲜蔬菜(或新鲜水果)类别执行。</t>
-        </is>
-      </c>
+      <c r="J78" s="19" t="n"/>
       <c r="K78" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6494,15 +6510,27 @@
     <row r="79" ht="56" customHeight="1" s="23">
       <c r="A79" s="20" t="inlineStr">
         <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B79" s="19" t="n"/>
-      <c r="C79" s="18" t="n"/>
-      <c r="D79" s="19" t="n"/>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t>谷物制品</t>
+        </is>
+      </c>
+      <c r="C79" s="19" t="inlineStr">
+        <is>
+          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
+        </is>
+      </c>
+      <c r="D79" s="19" t="inlineStr">
+        <is>
+          <t>粥类罐头</t>
+        </is>
+      </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t>调味品(香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外))</t>
+          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
       <c r="F79" s="19" t="inlineStr">
@@ -6510,9 +6538,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G79" s="22" t="inlineStr">
-        <is>
-          <t>1.5</t>
+      <c r="G79" s="30" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H79" s="19" t="n"/>
@@ -6521,11 +6549,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J79" s="19" t="inlineStr">
-        <is>
-          <t>b 新鲜香辛料(如姜、葱、蒜等)应按对应的新鲜蔬菜(或新鲜水果)类别执行。</t>
-        </is>
-      </c>
+      <c r="J79" s="19" t="n"/>
       <c r="K79" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6535,15 +6559,19 @@
     <row r="80" ht="56" customHeight="1" s="23">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B80" s="19" t="n"/>
+          <t>豆类及其制品</t>
+        </is>
+      </c>
+      <c r="B80" s="19" t="inlineStr">
+        <is>
+          <t>豆类制品</t>
+        </is>
+      </c>
       <c r="C80" s="19" t="n"/>
       <c r="D80" s="19" t="n"/>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>调味品(花椒、桂皮、肉桂、多种香辛料混合的香辛料)</t>
+          <t>豆类制品(豆浆除外)</t>
         </is>
       </c>
       <c r="F80" s="19" t="inlineStr">
@@ -6551,9 +6579,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G80" s="22" t="inlineStr">
-        <is>
-          <t>3.0</t>
+      <c r="G80" s="30" t="inlineStr">
+        <is>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H80" s="19" t="n"/>
@@ -6572,15 +6600,23 @@
     <row r="81" ht="56" customHeight="1" s="23">
       <c r="A81" s="20" t="inlineStr">
         <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B81" s="19" t="n"/>
-      <c r="C81" s="19" t="n"/>
+          <t>豆类及其制品</t>
+        </is>
+      </c>
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>豆类制品</t>
+        </is>
+      </c>
+      <c r="C81" s="19" t="inlineStr">
+        <is>
+          <t>非发酵豆制品（例如：豆浆、豆腐类、豆干类、腐竹类、熟制豆类、大豆蛋白膨化食品、大豆素肉等）</t>
+        </is>
+      </c>
       <c r="D81" s="19" t="n"/>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>调味品(花椒、桂皮、肉桂、多种香辛料混合的香辛料)</t>
+          <t>豆浆</t>
         </is>
       </c>
       <c r="F81" s="19" t="inlineStr">
@@ -6588,9 +6624,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G81" s="22" t="inlineStr">
-        <is>
-          <t>3.0</t>
+      <c r="G81" s="30" t="inlineStr">
+        <is>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H81" s="19" t="n"/>
@@ -6609,15 +6645,19 @@
     <row r="82" ht="56" customHeight="1" s="23">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B82" s="19" t="n"/>
+          <t>豆类及其制品</t>
+        </is>
+      </c>
+      <c r="B82" s="19" t="inlineStr">
+        <is>
+          <t>豆类（干豆、以干豆磨成的粉）</t>
+        </is>
+      </c>
       <c r="C82" s="19" t="n"/>
       <c r="D82" s="19" t="n"/>
       <c r="E82" s="19" t="inlineStr">
         <is>
-          <t>调味品(花椒、桂皮、肉桂、多种香辛料混合的香辛料)</t>
+          <t>豆类</t>
         </is>
       </c>
       <c r="F82" s="19" t="inlineStr">
@@ -6625,9 +6665,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G82" s="22" t="inlineStr">
-        <is>
-          <t>3.0</t>
+      <c r="G82" s="30" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H82" s="19" t="n"/>
@@ -6646,15 +6686,15 @@
     <row r="83" ht="56" customHeight="1" s="23">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>调味品</t>
+          <t>酒类</t>
         </is>
       </c>
       <c r="B83" s="19" t="n"/>
-      <c r="C83" s="18" t="n"/>
+      <c r="C83" s="19" t="n"/>
       <c r="D83" s="19" t="n"/>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t>调味品(花椒、桂皮、肉桂、多种香辛料混合的香辛料)</t>
+          <t>酒类(白酒、黄酒除外)</t>
         </is>
       </c>
       <c r="F83" s="19" t="inlineStr">
@@ -6662,9 +6702,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G83" s="22" t="inlineStr">
-        <is>
-          <t>3.0</t>
+      <c r="G83" s="30" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H83" s="19" t="n"/>
@@ -6683,15 +6723,23 @@
     <row r="84" ht="56" customHeight="1" s="23">
       <c r="A84" s="20" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B84" s="19" t="n"/>
-      <c r="C84" s="19" t="n"/>
+          <t>酒类</t>
+        </is>
+      </c>
+      <c r="B84" s="19" t="inlineStr">
+        <is>
+          <t>蒸馏酒（例如：白酒、白兰地、威士忌、伏特加、朗姆酒等）</t>
+        </is>
+      </c>
+      <c r="C84" s="19" t="inlineStr">
+        <is>
+          <t>白酒</t>
+        </is>
+      </c>
       <c r="D84" s="19" t="n"/>
       <c r="E84" s="19" t="inlineStr">
         <is>
-          <t>谷物及其制品(麦片、面筋、粥类罐头、带馅料面米制品除外)</t>
+          <t>白酒、黄酒</t>
         </is>
       </c>
       <c r="F84" s="19" t="inlineStr">
@@ -6699,9 +6747,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G84" s="22" t="inlineStr">
-        <is>
-          <t>0.2</t>
+      <c r="G84" s="30" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H84" s="19" t="n"/>
@@ -6710,11 +6758,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J84" s="19" t="inlineStr">
-        <is>
-          <t>a 稻谷以糙米计。</t>
-        </is>
-      </c>
+      <c r="J84" s="19" t="n"/>
       <c r="K84" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6724,23 +6768,23 @@
     <row r="85" ht="56" customHeight="1" s="23">
       <c r="A85" s="20" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>酒类</t>
         </is>
       </c>
       <c r="B85" s="19" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
+          <t>发酵酒(例如:葡萄酒、黄酒、果酒、啤酒等)</t>
         </is>
       </c>
       <c r="C85" s="19" t="inlineStr">
         <is>
-          <t>麦片</t>
+          <t>黄酒</t>
         </is>
       </c>
       <c r="D85" s="19" t="n"/>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
+          <t>白酒、黄酒</t>
         </is>
       </c>
       <c r="F85" s="19" t="inlineStr">
@@ -6748,7 +6792,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G85" s="22" t="inlineStr">
+      <c r="G85" s="30" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -6769,27 +6813,15 @@
     <row r="86" ht="56" customHeight="1" s="23">
       <c r="A86" s="20" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B86" s="19" t="inlineStr">
-        <is>
-          <t>谷物制品</t>
-        </is>
-      </c>
-      <c r="C86" s="19" t="inlineStr">
-        <is>
-          <t>小麦粉制品</t>
-        </is>
-      </c>
-      <c r="D86" s="19" t="inlineStr">
-        <is>
-          <t>面筋</t>
-        </is>
-      </c>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B86" s="19" t="n"/>
+      <c r="C86" s="19" t="n"/>
+      <c r="D86" s="19" t="n"/>
       <c r="E86" s="19" t="inlineStr">
         <is>
-          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F86" s="19" t="inlineStr">
@@ -6818,27 +6850,23 @@
     <row r="87" ht="56" customHeight="1" s="23">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B87" s="19" t="inlineStr">
         <is>
-          <t>谷物制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C87" s="19" t="inlineStr">
         <is>
-          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
-        </is>
-      </c>
-      <c r="D87" s="19" t="inlineStr">
-        <is>
-          <t>粥类罐头</t>
-        </is>
-      </c>
+          <t>双孢菇</t>
+        </is>
+      </c>
+      <c r="D87" s="19" t="n"/>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F87" s="19" t="inlineStr">
@@ -6867,19 +6895,23 @@
     <row r="88" ht="56" customHeight="1" s="23">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>豆类及其制品</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B88" s="19" t="inlineStr">
         <is>
-          <t>豆类制品</t>
-        </is>
-      </c>
-      <c r="C88" s="19" t="n"/>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C88" s="19" t="inlineStr">
+        <is>
+          <t>平菇</t>
+        </is>
+      </c>
       <c r="D88" s="19" t="n"/>
       <c r="E88" s="19" t="inlineStr">
         <is>
-          <t>豆类制品(豆浆除外)</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F88" s="19" t="inlineStr">
@@ -6889,7 +6921,7 @@
       </c>
       <c r="G88" s="30" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H88" s="19" t="n"/>
@@ -6908,23 +6940,23 @@
     <row r="89" ht="56" customHeight="1" s="23">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>豆类及其制品</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B89" s="19" t="inlineStr">
         <is>
-          <t>豆类制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C89" s="19" t="inlineStr">
         <is>
-          <t>非发酵豆制品（例如：豆浆、豆腐类、豆干类、腐竹类、熟制豆类、大豆蛋白膨化食品、大豆素肉等）</t>
+          <t>香菇</t>
         </is>
       </c>
       <c r="D89" s="19" t="n"/>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t>豆浆</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F89" s="19" t="inlineStr">
@@ -6934,7 +6966,7 @@
       </c>
       <c r="G89" s="30" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H89" s="19" t="n"/>
@@ -6953,19 +6985,23 @@
     <row r="90" ht="56" customHeight="1" s="23">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>豆类及其制品</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B90" s="19" t="inlineStr">
         <is>
-          <t>豆类（干豆、以干豆磨成的粉）</t>
-        </is>
-      </c>
-      <c r="C90" s="19" t="n"/>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="inlineStr">
+        <is>
+          <t>榛蘑</t>
+        </is>
+      </c>
       <c r="D90" s="19" t="n"/>
       <c r="E90" s="19" t="inlineStr">
         <is>
-          <t>豆类</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F90" s="19" t="inlineStr">
@@ -6975,7 +7011,7 @@
       </c>
       <c r="G90" s="30" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H90" s="19" t="n"/>
@@ -6994,7 +7030,7 @@
     <row r="91" ht="56" customHeight="1" s="23">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>酒类</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B91" s="19" t="n"/>
@@ -7002,7 +7038,7 @@
       <c r="D91" s="19" t="n"/>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t>酒类(白酒、黄酒除外)</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F91" s="19" t="inlineStr">
@@ -7012,7 +7048,7 @@
       </c>
       <c r="G91" s="30" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H91" s="19" t="n"/>
@@ -7031,23 +7067,23 @@
     <row r="92" ht="56" customHeight="1" s="23">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>酒类</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B92" s="19" t="inlineStr">
         <is>
-          <t>蒸馏酒（例如：白酒、白兰地、威士忌、伏特加、朗姆酒等）</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C92" s="19" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>松茸</t>
         </is>
       </c>
       <c r="D92" s="19" t="n"/>
       <c r="E92" s="19" t="inlineStr">
         <is>
-          <t>白酒、黄酒</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F92" s="19" t="inlineStr">
@@ -7055,7 +7091,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G92" s="30" t="inlineStr">
+      <c r="G92" s="22" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -7076,23 +7112,23 @@
     <row r="93" ht="56" customHeight="1" s="23">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>酒类</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B93" s="19" t="inlineStr">
         <is>
-          <t>发酵酒(例如:葡萄酒、黄酒、果酒、啤酒等)</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C93" s="19" t="inlineStr">
         <is>
-          <t>黄酒</t>
+          <t>松露</t>
         </is>
       </c>
       <c r="D93" s="19" t="n"/>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t>白酒、黄酒</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F93" s="19" t="inlineStr">
@@ -7100,7 +7136,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G93" s="30" t="inlineStr">
+      <c r="G93" s="22" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -7124,9 +7160,17 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B94" s="19" t="n"/>
-      <c r="C94" s="19" t="n"/>
-      <c r="D94" s="19" t="n"/>
+      <c r="B94" s="19" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>青头菌</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="n"/>
       <c r="E94" s="19" t="inlineStr">
         <is>
           <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
@@ -7137,7 +7181,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G94" s="30" t="inlineStr">
+      <c r="G94" s="22" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -7156,7 +7200,7 @@
       </c>
     </row>
     <row r="95" ht="56" customHeight="1" s="23">
-      <c r="A95" s="20" t="inlineStr">
+      <c r="A95" s="19" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
@@ -7168,7 +7212,7 @@
       </c>
       <c r="C95" s="19" t="inlineStr">
         <is>
-          <t>双孢菇</t>
+          <t>鸡枞</t>
         </is>
       </c>
       <c r="D95" s="19" t="n"/>
@@ -7182,7 +7226,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G95" s="30" t="inlineStr">
+      <c r="G95" s="19" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -7213,7 +7257,7 @@
       </c>
       <c r="C96" s="19" t="inlineStr">
         <is>
-          <t>平菇</t>
+          <t>鸡油菌</t>
         </is>
       </c>
       <c r="D96" s="19" t="n"/>
@@ -7227,7 +7271,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G96" s="30" t="inlineStr">
+      <c r="G96" s="25" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -7258,7 +7302,7 @@
       </c>
       <c r="C97" s="19" t="inlineStr">
         <is>
-          <t>香菇</t>
+          <t>多汁乳菇</t>
         </is>
       </c>
       <c r="D97" s="19" t="n"/>
@@ -7272,7 +7316,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G97" s="30" t="inlineStr">
+      <c r="G97" s="25" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -7296,16 +7340,8 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B98" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C98" s="19" t="inlineStr">
-        <is>
-          <t>榛蘑</t>
-        </is>
-      </c>
+      <c r="B98" s="19" t="n"/>
+      <c r="C98" s="19" t="n"/>
       <c r="D98" s="19" t="n"/>
       <c r="E98" s="19" t="inlineStr">
         <is>
@@ -7317,7 +7353,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G98" s="30" t="inlineStr">
+      <c r="G98" s="25" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -7341,8 +7377,16 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B99" s="19" t="n"/>
-      <c r="C99" s="19" t="n"/>
+      <c r="B99" s="19" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C99" s="19" t="inlineStr">
+        <is>
+          <t>银耳</t>
+        </is>
+      </c>
       <c r="D99" s="19" t="n"/>
       <c r="E99" s="19" t="inlineStr">
         <is>
@@ -7354,7 +7398,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G99" s="30" t="inlineStr">
+      <c r="G99" s="25" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -7385,13 +7429,13 @@
       </c>
       <c r="C100" s="19" t="inlineStr">
         <is>
-          <t>松茸</t>
+          <t>双孢菇</t>
         </is>
       </c>
       <c r="D100" s="19" t="n"/>
       <c r="E100" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F100" s="19" t="inlineStr">
@@ -7399,9 +7443,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G100" s="22" t="inlineStr">
-        <is>
-          <t>0.5</t>
+      <c r="G100" s="25" t="inlineStr">
+        <is>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H100" s="19" t="n"/>
@@ -7428,15 +7472,15 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C101" s="19" t="inlineStr">
-        <is>
-          <t>松露</t>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>双孢菇</t>
         </is>
       </c>
       <c r="D101" s="19" t="n"/>
       <c r="E101" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F101" s="19" t="inlineStr">
@@ -7444,9 +7488,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G101" s="22" t="inlineStr">
-        <is>
-          <t>0.5</t>
+      <c r="G101" s="25" t="inlineStr">
+        <is>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H101" s="19" t="n"/>
@@ -7473,15 +7517,15 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>青头菌</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="n"/>
+      <c r="C102" s="19" t="inlineStr">
+        <is>
+          <t>双孢菇</t>
+        </is>
+      </c>
+      <c r="D102" s="19" t="n"/>
       <c r="E102" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F102" s="19" t="inlineStr">
@@ -7489,9 +7533,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G102" s="22" t="inlineStr">
-        <is>
-          <t>0.5</t>
+      <c r="G102" s="25" t="inlineStr">
+        <is>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H102" s="19" t="n"/>
@@ -7508,7 +7552,7 @@
       </c>
     </row>
     <row r="103" ht="42" customHeight="1" s="23">
-      <c r="A103" s="19" t="inlineStr">
+      <c r="A103" s="20" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
@@ -7520,13 +7564,13 @@
       </c>
       <c r="C103" s="19" t="inlineStr">
         <is>
-          <t>鸡枞</t>
+          <t>双孢菇</t>
         </is>
       </c>
       <c r="D103" s="19" t="n"/>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F103" s="19" t="inlineStr">
@@ -7534,9 +7578,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G103" s="19" t="inlineStr">
-        <is>
-          <t>0.5</t>
+      <c r="G103" s="25" t="inlineStr">
+        <is>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H103" s="19" t="n"/>
@@ -7565,13 +7609,13 @@
       </c>
       <c r="C104" s="19" t="inlineStr">
         <is>
-          <t>鸡油菌</t>
+          <t>木耳 （毛木耳,黑木耳）</t>
         </is>
       </c>
       <c r="D104" s="19" t="n"/>
       <c r="E104" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F104" s="19" t="inlineStr">
@@ -7581,7 +7625,7 @@
       </c>
       <c r="G104" s="25" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H104" s="19" t="n"/>
@@ -7598,25 +7642,24 @@
       </c>
     </row>
     <row r="105" ht="42" customHeight="1" s="23">
-      <c r="A105" s="20" t="inlineStr">
+      <c r="A105" s="19" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B105" s="19" t="inlineStr">
+      <c r="B105" s="0" t="inlineStr">
         <is>
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C105" s="19" t="inlineStr">
-        <is>
-          <t>多汁乳菇</t>
-        </is>
-      </c>
-      <c r="D105" s="19" t="n"/>
+      <c r="C105" s="0" t="inlineStr">
+        <is>
+          <t>木耳 （毛木耳,黑木耳）</t>
+        </is>
+      </c>
       <c r="E105" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F105" s="19" t="inlineStr">
@@ -7624,9 +7667,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G105" s="25" t="inlineStr">
-        <is>
-          <t>0.5</t>
+      <c r="G105" s="19" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H105" s="19" t="n"/>
@@ -7648,12 +7691,19 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B106" s="19" t="n"/>
-      <c r="C106" s="19" t="n"/>
-      <c r="D106" s="19" t="n"/>
-      <c r="E106" s="19" t="inlineStr">
-        <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+      <c r="B106" s="19" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="E106" s="0" t="inlineStr">
+        <is>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F106" s="19" t="inlineStr">
@@ -7661,12 +7711,11 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G106" s="25" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H106" s="19" t="n"/>
+      <c r="G106" s="19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="I106" s="19" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -7690,15 +7739,14 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C107" s="19" t="inlineStr">
-        <is>
-          <t>银耳</t>
-        </is>
-      </c>
-      <c r="D107" s="19" t="n"/>
-      <c r="E107" s="19" t="inlineStr">
-        <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="E107" s="0" t="inlineStr">
+        <is>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F107" s="19" t="inlineStr">
@@ -7706,12 +7754,11 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G107" s="25" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H107" s="19" t="n"/>
+      <c r="G107" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="I107" s="19" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -7735,28 +7782,26 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C108" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇</t>
-        </is>
-      </c>
-      <c r="D108" s="19" t="n"/>
-      <c r="E108" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F108" s="19" t="inlineStr">
+      <c r="C108" s="27" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="E108" s="27" t="inlineStr">
+        <is>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+        </is>
+      </c>
+      <c r="F108" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G108" s="25" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="H108" s="19" t="n"/>
+      <c r="G108" s="30" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="I108" s="19" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -7770,353 +7815,311 @@
       </c>
     </row>
     <row r="109" ht="27" customHeight="1" s="23">
-      <c r="A109" s="20" t="inlineStr">
+      <c r="A109" s="0" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B109" s="19" t="inlineStr">
+      <c r="B109" s="0" t="inlineStr">
         <is>
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t>双孢菇</t>
-        </is>
-      </c>
-      <c r="D109" s="19" t="n"/>
-      <c r="E109" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F109" s="19" t="inlineStr">
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="E109" s="0" t="inlineStr">
+        <is>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+        </is>
+      </c>
+      <c r="F109" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G109" s="25" t="inlineStr">
+      <c r="G109" s="0" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I109" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K109" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="42" customHeight="1" s="23">
+      <c r="A110" s="0" t="inlineStr">
+        <is>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B110" s="0" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C110" s="0" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="E110" s="0" t="inlineStr">
+        <is>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+        </is>
+      </c>
+      <c r="F110" s="0" t="inlineStr">
+        <is>
+          <t>铅</t>
+        </is>
+      </c>
+      <c r="G110" s="0" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I110" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K110" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="28" customHeight="1" s="23">
+      <c r="A111" s="0" t="inlineStr">
+        <is>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B111" s="0" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C111" s="0" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="E111" s="0" t="inlineStr">
+        <is>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+        </is>
+      </c>
+      <c r="F111" s="0" t="inlineStr">
+        <is>
+          <t>铅</t>
+        </is>
+      </c>
+      <c r="G111" s="0" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I111" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K111" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="42" customHeight="1" s="23">
+      <c r="A112" s="0" t="inlineStr">
+        <is>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="B112" s="0" t="inlineStr">
+        <is>
+          <t>食糖（包括方糖、冰片糖、原糖、糖蜜、部分转化糖、槭树糖浆）</t>
+        </is>
+      </c>
+      <c r="E112" s="0" t="inlineStr">
+        <is>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="F112" s="0" t="inlineStr">
+        <is>
+          <t>铅</t>
+        </is>
+      </c>
+      <c r="G112" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I112" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K112" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="42" customHeight="1" s="23">
+      <c r="A113" s="0" t="inlineStr">
+        <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="E113" s="0" t="inlineStr">
+        <is>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+        </is>
+      </c>
+      <c r="F113" s="0" t="inlineStr">
+        <is>
+          <t>铅</t>
+        </is>
+      </c>
+      <c r="G113" s="0" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="H109" s="19" t="n"/>
-      <c r="I109" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J109" s="19" t="n"/>
-      <c r="K109" s="19" t="inlineStr">
+      <c r="I113" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K113" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="42" customHeight="1" s="23">
-      <c r="A110" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B110" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C110" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇</t>
-        </is>
-      </c>
-      <c r="D110" s="19" t="n"/>
-      <c r="E110" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F110" s="19" t="inlineStr">
+    <row r="114" ht="42" customHeight="1" s="23">
+      <c r="A114" s="0" t="inlineStr">
+        <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B114" s="0" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+        </is>
+      </c>
+      <c r="F114" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G110" s="25" t="inlineStr">
+      <c r="G114" s="0" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="H110" s="19" t="n"/>
-      <c r="I110" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J110" s="19" t="n"/>
-      <c r="K110" s="19" t="inlineStr">
+      <c r="I114" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K114" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="28" customHeight="1" s="23">
-      <c r="A111" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B111" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C111" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇</t>
-        </is>
-      </c>
-      <c r="D111" s="19" t="n"/>
-      <c r="E111" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F111" s="19" t="inlineStr">
+    <row r="115" ht="28" customHeight="1" s="23">
+      <c r="A115" s="0" t="inlineStr">
+        <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B115" s="0" t="inlineStr">
+        <is>
+          <t>蛋白饮料</t>
+        </is>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
+        </is>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+        </is>
+      </c>
+      <c r="F115" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G111" s="25" t="inlineStr">
+      <c r="G115" s="0" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="H111" s="19" t="n"/>
-      <c r="I111" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J111" s="19" t="n"/>
-      <c r="K111" s="19" t="inlineStr">
+      <c r="I115" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K115" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="42" customHeight="1" s="23">
-      <c r="A112" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B112" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C112" s="19" t="inlineStr">
-        <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
-      <c r="D112" s="19" t="n"/>
-      <c r="E112" s="19" t="inlineStr">
-        <is>
-          <t>木耳及其制品、银耳及其制品</t>
-        </is>
-      </c>
-      <c r="F112" s="19" t="inlineStr">
+    <row r="116" ht="42" customHeight="1" s="23">
+      <c r="A116" s="0" t="inlineStr">
+        <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B116" s="0" t="inlineStr">
+        <is>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
+        </is>
+      </c>
+      <c r="E116" s="0" t="inlineStr">
+        <is>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+        </is>
+      </c>
+      <c r="F116" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G112" s="25" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="H112" s="19" t="n"/>
-      <c r="I112" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J112" s="19" t="n"/>
-      <c r="K112" s="19" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="42" customHeight="1" s="23">
-      <c r="A113" s="19" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B113" s="0" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C113" s="0" t="inlineStr">
-        <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
-      <c r="E113" s="19" t="inlineStr">
-        <is>
-          <t>木耳及其制品、银耳及其制品</t>
-        </is>
-      </c>
-      <c r="F113" s="19" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G113" s="19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="H113" s="19" t="n"/>
-      <c r="I113" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J113" s="19" t="n"/>
-      <c r="K113" s="19" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="42" customHeight="1" s="23">
-      <c r="A114" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B114" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C114" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
-        </is>
-      </c>
-      <c r="E114" s="0" t="inlineStr">
-        <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F114" s="19" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G114" s="19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I114" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J114" s="19" t="n"/>
-      <c r="K114" s="19" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="28" customHeight="1" s="23">
-      <c r="A115" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B115" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C115" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
-        </is>
-      </c>
-      <c r="E115" s="0" t="inlineStr">
-        <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F115" s="19" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G115" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I115" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J115" s="19" t="n"/>
-      <c r="K115" s="19" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="42" customHeight="1" s="23">
-      <c r="A116" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B116" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C116" s="27" t="inlineStr">
-        <is>
-          <t>松茸</t>
-        </is>
-      </c>
-      <c r="E116" s="27" t="inlineStr">
-        <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F116" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G116" s="30" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I116" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J116" s="19" t="n"/>
-      <c r="K116" s="19" t="inlineStr">
+      <c r="G116" s="0" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I116" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K116" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
@@ -8125,22 +8128,12 @@
     <row r="117" ht="42" customHeight="1" s="23">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B117" s="0" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C117" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="E117" s="0" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
         </is>
       </c>
       <c r="F117" s="0" t="inlineStr">
@@ -8150,7 +8143,7 @@
       </c>
       <c r="G117" s="0" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I117" s="0" t="inlineStr">
@@ -8167,22 +8160,17 @@
     <row r="118" ht="28" customHeight="1" s="23">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C118" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
         </is>
       </c>
       <c r="E118" s="0" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外)</t>
         </is>
       </c>
       <c r="F118" s="0" t="inlineStr">
@@ -8192,7 +8180,7 @@
       </c>
       <c r="G118" s="0" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I118" s="0" t="inlineStr">
@@ -8209,22 +8197,12 @@
     <row r="119">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B119" s="0" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C119" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="E119" s="0" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
         </is>
       </c>
       <c r="F119" s="0" t="inlineStr">
@@ -8234,7 +8212,7 @@
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I119" s="0" t="inlineStr">
@@ -8251,17 +8229,12 @@
     <row r="120">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="B120" s="0" t="inlineStr">
-        <is>
-          <t>食糖（包括方糖、冰片糖、原糖、糖蜜、部分转化糖、槭树糖浆）</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="E120" s="0" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
+          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
         </is>
       </c>
       <c r="F120" s="0" t="inlineStr">
@@ -8271,7 +8244,7 @@
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I120" s="0" t="inlineStr">
@@ -8293,7 +8266,7 @@
       </c>
       <c r="E121" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
         </is>
       </c>
       <c r="F121" s="0" t="inlineStr">
@@ -8303,7 +8276,7 @@
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="I121" s="0" t="inlineStr">
@@ -8323,14 +8296,9 @@
           <t>饮料类</t>
         </is>
       </c>
-      <c r="B122" s="0" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
       <c r="E122" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
         </is>
       </c>
       <c r="F122" s="0" t="inlineStr">
@@ -8340,7 +8308,7 @@
       </c>
       <c r="G122" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="I122" s="0" t="inlineStr">
@@ -8360,19 +8328,9 @@
           <t>饮料类</t>
         </is>
       </c>
-      <c r="B123" s="0" t="inlineStr">
-        <is>
-          <t>蛋白饮料</t>
-        </is>
-      </c>
-      <c r="C123" s="0" t="inlineStr">
-        <is>
-          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
-        </is>
-      </c>
       <c r="E123" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>饮料类(葡萄汁)</t>
         </is>
       </c>
       <c r="F123" s="0" t="inlineStr">
@@ -8382,7 +8340,7 @@
       </c>
       <c r="G123" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="I123" s="0" t="inlineStr">
@@ -8402,14 +8360,9 @@
           <t>饮料类</t>
         </is>
       </c>
-      <c r="B124" s="0" t="inlineStr">
-        <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
-        </is>
-      </c>
       <c r="E124" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>饮料类(固体饮料)</t>
         </is>
       </c>
       <c r="F124" s="0" t="inlineStr">
@@ -8419,7 +8372,7 @@
       </c>
       <c r="G124" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I124" s="0" t="inlineStr">
@@ -8439,9 +8392,14 @@
           <t>饮料类</t>
         </is>
       </c>
+      <c r="B125" s="0" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
       <c r="E125" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="F125" s="0" t="inlineStr">
@@ -8451,7 +8409,7 @@
       </c>
       <c r="G125" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="I125" s="0" t="inlineStr">
@@ -8459,9 +8417,9 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="K125" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
+      <c r="K125" s="28" t="inlineStr">
+        <is>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
@@ -8476,9 +8434,14 @@
           <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
         </is>
       </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t>浓缩果蔬汁（浆）</t>
+        </is>
+      </c>
       <c r="E126" s="0" t="inlineStr">
         <is>
-          <t>果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外)</t>
+          <t>浓缩果蔬汁(浆)</t>
         </is>
       </c>
       <c r="F126" s="0" t="inlineStr">
@@ -8488,7 +8451,7 @@
       </c>
       <c r="G126" s="0" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I126" s="0" t="inlineStr">
@@ -8508,9 +8471,19 @@
           <t>饮料类</t>
         </is>
       </c>
+      <c r="B127" s="0" t="inlineStr">
+        <is>
+          <t>蛋白饮料</t>
+        </is>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
+        </is>
+      </c>
       <c r="E127" s="0" t="inlineStr">
         <is>
-          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
+          <t>含乳饮料</t>
         </is>
       </c>
       <c r="F127" s="0" t="inlineStr">
@@ -8520,7 +8493,7 @@
       </c>
       <c r="G127" s="0" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="I127" s="0" t="inlineStr">
@@ -8537,12 +8510,27 @@
     <row r="128">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t>饮料类</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B128" s="0" t="inlineStr">
+        <is>
+          <t>谷物制品</t>
+        </is>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
+        </is>
+      </c>
+      <c r="D128" s="0" t="inlineStr">
+        <is>
+          <t>带馅料面米制品</t>
         </is>
       </c>
       <c r="E128" s="0" t="inlineStr">
         <is>
-          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
+          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
       <c r="F128" s="0" t="inlineStr">
@@ -8552,7 +8540,7 @@
       </c>
       <c r="G128" s="0" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I128" s="0" t="inlineStr">
@@ -8561,302 +8549,6 @@
         </is>
       </c>
       <c r="K128" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="E129" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
-        </is>
-      </c>
-      <c r="F129" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G129" s="0" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="I129" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K129" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="E130" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
-        </is>
-      </c>
-      <c r="F130" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G130" s="0" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="I130" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K130" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="E131" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(葡萄汁)</t>
-        </is>
-      </c>
-      <c r="F131" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G131" s="0" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="I131" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K131" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="E132" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(固体饮料)</t>
-        </is>
-      </c>
-      <c r="F132" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G132" s="0" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I132" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K132" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B133" s="0" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="E133" s="0" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="F133" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G133" s="0" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="I133" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K133" s="28" t="inlineStr">
-        <is>
-          <t>GB 8538</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B134" s="0" t="inlineStr">
-        <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
-        </is>
-      </c>
-      <c r="C134" s="0" t="inlineStr">
-        <is>
-          <t>浓缩果蔬汁（浆）</t>
-        </is>
-      </c>
-      <c r="E134" s="0" t="inlineStr">
-        <is>
-          <t>浓缩果蔬汁(浆)</t>
-        </is>
-      </c>
-      <c r="F134" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G134" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I134" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K134" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B135" s="0" t="inlineStr">
-        <is>
-          <t>蛋白饮料</t>
-        </is>
-      </c>
-      <c r="C135" s="0" t="inlineStr">
-        <is>
-          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
-        </is>
-      </c>
-      <c r="E135" s="0" t="inlineStr">
-        <is>
-          <t>含乳饮料</t>
-        </is>
-      </c>
-      <c r="F135" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G135" s="0" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="I135" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K135" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="0" t="inlineStr">
-        <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B136" s="0" t="inlineStr">
-        <is>
-          <t>谷物制品</t>
-        </is>
-      </c>
-      <c r="C136" s="0" t="inlineStr">
-        <is>
-          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
-        </is>
-      </c>
-      <c r="D136" s="0" t="inlineStr">
-        <is>
-          <t>带馅料面米制品</t>
-        </is>
-      </c>
-      <c r="E136" s="0" t="inlineStr">
-        <is>
-          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
-        </is>
-      </c>
-      <c r="F136" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G136" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I136" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K136" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -3971,11 +3971,7 @@
           <t>可可制品、巧克力和巧克力制品以及糖果</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
-        </is>
-      </c>
+      <c r="B21" s="19" t="n"/>
       <c r="C21" s="19" t="n"/>
       <c r="D21" s="19" t="n"/>
       <c r="E21" s="19" t="inlineStr">
@@ -7946,11 +7942,7 @@
           <t>食糖及淀粉糖</t>
         </is>
       </c>
-      <c r="B112" s="0" t="inlineStr">
-        <is>
-          <t>食糖（包括方糖、冰片糖、原糖、糖蜜、部分转化糖、槭树糖浆）</t>
-        </is>
-      </c>
+      <c r="B112" s="0" t="n"/>
       <c r="E112" s="0" t="inlineStr">
         <is>
           <t>食糖及淀粉糖</t>
@@ -15620,16 +15612,12 @@
           <t>可可制品、巧克力和巧克力制品以及糖果</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
-        </is>
-      </c>
+      <c r="B17" s="4" t="n"/>
       <c r="C17" s="4" t="n"/>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>可可制品、巧克力和巧克力制品</t>
+          <t>可可制品、巧克力和巧克力制品以及糖果</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -15661,16 +15649,12 @@
           <t>可可制品、巧克力和巧克力制品以及糖果</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
-        </is>
-      </c>
+      <c r="B18" s="4" t="n"/>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>可可制品、巧克力和巧克力制品</t>
+          <t>可可制品、巧克力和巧克力制品以及糖果</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -17854,11 +17838,7 @@
           <t>食糖及淀粉糖</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>食糖（包括方糖、冰片糖、原糖、糖蜜、部分转化糖、槭树糖浆）</t>
-        </is>
-      </c>
+      <c r="B67" s="4" t="n"/>
       <c r="C67" s="4" t="n"/>
       <c r="D67" s="4" t="n"/>
       <c r="E67" s="4" t="inlineStr">
@@ -17895,11 +17875,7 @@
           <t>食糖及淀粉糖</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>食糖（包括方糖、冰片糖、原糖、糖蜜、部分转化糖、槭树糖浆）</t>
-        </is>
-      </c>
+      <c r="B68" s="4" t="n"/>
       <c r="C68" s="4" t="n"/>
       <c r="D68" s="4" t="n"/>
       <c r="E68" s="4" t="inlineStr">

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -2791,16 +2791,8 @@
           <t>肉制品（包括内脏制品、血制品）</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>熟肉制品</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>肉类罐头</t>
-        </is>
-      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
           <t>肉制品(肉类罐头除外)</t>
@@ -2822,7 +2814,11 @@
           <t>μg/kg</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>肉类罐头除外</t>
+        </is>
+      </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
           <t>GB 5009.26</t>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -15023,7 +15023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -15677,94 +15677,84 @@
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" s="23">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>水产动物及其制品</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>鱼类及其制品</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>水产动物及其制品(鱼类及其制品除外)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>总砷</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" s="23">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>水产动物及其制品</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>鱼类及其制品</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>水产动物及其制品(鱼类及其制品除外)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>无机砷 a</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
@@ -15773,19 +15763,23 @@
     <row r="21" ht="56" customHeight="1" s="23">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
+          <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n"/>
+          <t>鲜、冻水产动物</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>鱼类</t>
+        </is>
+      </c>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>鱼油及其制品、磷虾油及其制品</t>
+          <t>鱼类及其制品</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -15814,19 +15808,23 @@
     <row r="22" ht="56" customHeight="1" s="23">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
+          <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n"/>
+          <t>鲜、冻水产动物</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>鱼类</t>
+        </is>
+      </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>鱼油及其制品、磷虾油及其制品</t>
+          <t>鱼类及其制品</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -15859,19 +15857,19 @@
     <row r="23" ht="56" customHeight="1" s="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>油脂及其制品</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>辅食营养补充品</t>
+          <t>鱼油及其制品、磷虾油及其制品</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -15881,7 +15879,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="4" t="n"/>
@@ -15900,29 +15898,29 @@
     <row r="24" ht="56" customHeight="1" s="23">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>油脂及其制品</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(固态、半固态或粉状)</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>鱼油及其制品、磷虾油及其制品</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H24" s="4" t="n"/>
@@ -15931,7 +15929,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n"/>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15953,7 +15955,7 @@
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(液态)</t>
+          <t>辅食营养补充品</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -15963,7 +15965,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H25" s="4" t="n"/>
@@ -15994,7 +15996,7 @@
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>孕妇及乳母营养补充食品</t>
+          <t>运动营养食品(固态、半固态或粉状)</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -16035,17 +16037,17 @@
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>辅食营养补充品</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>运动营养食品(液态)</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H27" s="4" t="n"/>
@@ -16076,17 +16078,17 @@
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(固态、半固态或粉状)</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>孕妇及乳母营养补充食品</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H28" s="4" t="n"/>
@@ -16117,7 +16119,7 @@
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(液态)</t>
+          <t>辅食营养补充品</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -16158,7 +16160,7 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>孕妇及乳母营养补充食品</t>
+          <t>运动营养食品(固态、半固态或粉状)</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -16192,23 +16194,19 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>以水产及动物肝脏为原料的产品</t>
-        </is>
-      </c>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n"/>
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>以水产及动物肝脏为原料的产品</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>运动营养食品(液态)</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -16237,18 +16235,14 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>以水产及动物肝脏为原料的产品</t>
-        </is>
-      </c>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n"/>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>以水产及动物肝脏为原料的产品</t>
+          <t>孕妇及乳母营养补充食品</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -16258,7 +16252,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H32" s="4" t="n"/>
@@ -16267,11 +16261,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -16291,13 +16281,13 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+          <t>以水产及动物肝脏为原料的产品</t>
         </is>
       </c>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+          <t>以水产及动物肝脏为原料的产品</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -16336,13 +16326,13 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+          <t>以水产及动物肝脏为原料的产品</t>
         </is>
       </c>
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+          <t>以水产及动物肝脏为原料的产品</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -16352,7 +16342,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H34" s="4" t="n"/>
@@ -16385,13 +16375,13 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
         </is>
       </c>
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -16430,13 +16420,13 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
         </is>
       </c>
       <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -16446,7 +16436,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H36" s="4" t="n"/>
@@ -16479,13 +16469,13 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>添加藻类的产品</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
         </is>
       </c>
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>添加藻类的产品</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -16524,13 +16514,13 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>添加藻类的产品</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
         </is>
       </c>
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>添加藻类的产品</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -16540,7 +16530,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H38" s="4" t="n"/>
@@ -16563,19 +16553,23 @@
     <row r="39" ht="28" customHeight="1" s="23">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n"/>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>添加藻类的产品</t>
+        </is>
+      </c>
       <c r="D39" s="4" t="n"/>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜</t>
+          <t>添加藻类的产品</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -16585,7 +16579,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H39" s="4" t="n"/>
@@ -16604,19 +16598,23 @@
     <row r="40" ht="28" customHeight="1" s="23">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n"/>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>添加藻类的产品</t>
+        </is>
+      </c>
       <c r="D40" s="4" t="n"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜</t>
+          <t>添加藻类的产品</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -16626,7 +16624,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H40" s="4" t="n"/>
@@ -16635,7 +16633,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J40" s="4" t="n"/>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -16645,15 +16647,19 @@
     <row r="41" ht="28" customHeight="1" s="23">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n"/>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
       <c r="C41" s="4" t="n"/>
       <c r="D41" s="4" t="n"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
+          <t>新鲜蔬菜</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -16661,8 +16667,10 @@
           <t>总砷</t>
         </is>
       </c>
-      <c r="G41" s="10" t="n">
-        <v>0.5</v>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
       <c r="H41" s="4" t="n"/>
       <c r="I41" s="4" t="inlineStr">
@@ -16680,15 +16688,19 @@
     <row r="42" ht="28" customHeight="1" s="23">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n"/>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
       <c r="C42" s="4" t="n"/>
       <c r="D42" s="4" t="n"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
+          <t>新鲜蔬菜</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -16707,11 +16719,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -16724,16 +16732,12 @@
           <t>调味品</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
-        </is>
-      </c>
+      <c r="B43" s="4" t="n"/>
       <c r="C43" s="4" t="n"/>
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>复合调味料</t>
+          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -16741,10 +16745,8 @@
           <t>总砷</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G43" s="10" t="n">
+        <v>0.5</v>
       </c>
       <c r="H43" s="4" t="n"/>
       <c r="I43" s="4" t="inlineStr">
@@ -16765,16 +16767,12 @@
           <t>调味品</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
-        </is>
-      </c>
+      <c r="B44" s="4" t="n"/>
       <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>复合调味料</t>
+          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -16784,7 +16782,7 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H44" s="4" t="n"/>
@@ -16812,14 +16810,14 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>水产调味品</t>
+          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
         </is>
       </c>
       <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="n"/>
-      <c r="E45" s="11" t="inlineStr">
-        <is>
-          <t>水产调味品(鱼类调味品除外)</t>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>复合调味料</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -16853,14 +16851,14 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>水产调味品</t>
+          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
         </is>
       </c>
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>水产调味品(鱼类调味品除外)</t>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>复合调味料</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -16868,8 +16866,10 @@
           <t>无机砷 a</t>
         </is>
       </c>
-      <c r="G46" s="10" t="n">
-        <v>0.5</v>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="inlineStr">
@@ -16899,15 +16899,11 @@
           <t>水产调味品</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>鱼类调味品（例如：鱼露等）</t>
-        </is>
-      </c>
+      <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>鱼类调味品</t>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>水产调味品(鱼类调味品除外)</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -16944,15 +16940,11 @@
           <t>水产调味品</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>鱼类调味品（例如：鱼露等）</t>
-        </is>
-      </c>
+      <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>鱼类调味品</t>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>水产调味品(鱼类调味品除外)</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -16960,10 +16952,8 @@
           <t>无机砷 a</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="G48" s="10" t="n">
+        <v>0.5</v>
       </c>
       <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="inlineStr">
@@ -16985,23 +16975,23 @@
     <row r="49" ht="42" customHeight="1" s="23">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>调味品</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>谷物</t>
+          <t>水产调味品</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>稻谷</t>
+          <t>鱼类调味品（例如：鱼露等）</t>
         </is>
       </c>
       <c r="D49" s="4" t="n"/>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>稻谷</t>
+          <t>鱼类调味品</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -17020,11 +17010,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -17034,23 +17020,23 @@
     <row r="50" ht="42" customHeight="1" s="23">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>调味品</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>谷物</t>
+          <t>水产调味品</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>稻谷</t>
+          <t>鱼类调味品（例如：鱼露等）</t>
         </is>
       </c>
       <c r="D50" s="4" t="n"/>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>稻谷</t>
+          <t>鱼类调味品</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -17060,7 +17046,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H50" s="4" t="n"/>
@@ -17069,7 +17055,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J50" s="4" t="n"/>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -17084,18 +17074,18 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
+          <t>谷物</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>大米（粉）</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>大米(粉)</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -17114,7 +17104,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J51" s="4" t="n"/>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -17129,18 +17123,18 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
+          <t>谷物</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>大米（粉）</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>大米(粉)</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -17150,7 +17144,7 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="H52" s="4" t="n"/>
@@ -17179,13 +17173,13 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>糙米（包括色稻米）</t>
+          <t>大米（粉）</t>
         </is>
       </c>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>糙米</t>
+          <t>大米(粉)</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -17224,13 +17218,13 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>糙米（包括色稻米）</t>
+          <t>大米（粉）</t>
         </is>
       </c>
       <c r="D54" s="4" t="n"/>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>糙米</t>
+          <t>大米(粉)</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -17240,7 +17234,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H54" s="4" t="n"/>
@@ -17259,15 +17253,23 @@
     <row r="55" ht="42" customHeight="1" s="23">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n"/>
-      <c r="C55" s="4" t="n"/>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>糙米（包括色稻米）</t>
+        </is>
+      </c>
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
+          <t>糙米</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -17287,20 +17289,32 @@
         </is>
       </c>
       <c r="J55" s="4" t="n"/>
-      <c r="K55" s="4" t="n"/>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="42" customHeight="1" s="23">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>糙米（包括色稻米）</t>
+        </is>
+      </c>
       <c r="D56" s="4" t="n"/>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
+          <t>糙米</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -17310,7 +17324,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="H56" s="4" t="n"/>
@@ -17319,11 +17333,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J56" s="4" t="n"/>
       <c r="K56" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -17336,20 +17346,12 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -17369,11 +17371,7 @@
         </is>
       </c>
       <c r="J57" s="4" t="n"/>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
+      <c r="K57" s="4" t="n"/>
     </row>
     <row r="58" ht="42" customHeight="1" s="23">
       <c r="A58" s="4" t="inlineStr">
@@ -17381,20 +17379,12 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -17407,11 +17397,7 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>(干重计)</t>
-        </is>
-      </c>
+      <c r="H58" s="4" t="n"/>
       <c r="I58" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -17436,19 +17422,15 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>木耳制品、银耳制品</t>
-        </is>
-      </c>
+          <t>木耳 （毛木耳,黑木耳）</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
@@ -17485,19 +17467,15 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>木耳制品、银耳制品</t>
-        </is>
-      </c>
+          <t>木耳 （毛木耳,黑木耳）</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="n"/>
       <c r="E60" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
@@ -17542,15 +17520,19 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>食用菌制品</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>银耳</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="n"/>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>木耳制品、银耳制品</t>
+        </is>
+      </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
@@ -17587,15 +17569,19 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>食用菌制品</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>银耳</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="n"/>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>木耳制品、银耳制品</t>
+        </is>
+      </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
@@ -17645,13 +17631,13 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>松茸</t>
+          <t>银耳</t>
         </is>
       </c>
       <c r="D63" s="4" t="n"/>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>松茸及其制品</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
@@ -17690,13 +17676,13 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>松茸</t>
+          <t>银耳</t>
         </is>
       </c>
       <c r="D64" s="4" t="n"/>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>松茸及其制品</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
@@ -17706,10 +17692,14 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="n"/>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>(干重计)</t>
+        </is>
+      </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -17734,19 +17724,15 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>松茸制品</t>
-        </is>
-      </c>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="n"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
           <t>松茸及其制品</t>
@@ -17783,19 +17769,15 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>松茸制品</t>
-        </is>
-      </c>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="n"/>
       <c r="E66" s="4" t="inlineStr">
         <is>
           <t>松茸及其制品</t>
@@ -17831,15 +17813,27 @@
     <row r="67" ht="42" customHeight="1" s="23">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="n"/>
-      <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="n"/>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>食用菌制品</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>松茸制品</t>
+        </is>
+      </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
+          <t>松茸及其制品</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -17849,7 +17843,7 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H67" s="4" t="n"/>
@@ -17868,15 +17862,27 @@
     <row r="68" ht="42" customHeight="1" s="23">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="n"/>
-      <c r="C68" s="4" t="n"/>
-      <c r="D68" s="4" t="n"/>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>食用菌制品</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>松茸制品</t>
+        </is>
+      </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
+          <t>松茸及其制品</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
@@ -17886,7 +17892,7 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="H68" s="4" t="n"/>
@@ -17895,7 +17901,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J68" s="4" t="n"/>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -17905,19 +17915,15 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="n"/>
       <c r="C69" s="4" t="n"/>
       <c r="D69" s="4" t="n"/>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
+          <t>食糖及淀粉糖</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -17927,7 +17933,7 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H69" s="4" t="n"/>
@@ -17946,19 +17952,15 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="n"/>
       <c r="C70" s="4" t="n"/>
       <c r="D70" s="4" t="n"/>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
+          <t>食糖及淀粉糖</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -17987,23 +17989,19 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="B71" s="11" t="inlineStr">
-        <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n"/>
       <c r="D71" s="4" t="n"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>鱼类及其制品</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -18013,7 +18011,7 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H71" s="4" t="n"/>
@@ -18032,22 +18030,19 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="B72" s="11" t="inlineStr">
-        <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="n"/>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>鱼类及其制品</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
@@ -18057,7 +18052,7 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H72" s="4" t="n"/>
@@ -18066,94 +18061,101 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J72" s="4" t="inlineStr">
+      <c r="J72" s="4" t="n"/>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>水产动物及其制品</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>水产制品</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>鱼类制品</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>鱼类及其制品</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="n"/>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="n"/>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>水产动物及其制品</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>水产制品</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>鱼类制品</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>鱼类及其制品</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="n"/>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="K72" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="0" t="inlineStr">
-        <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B73" s="0" t="inlineStr">
-        <is>
-          <t>谷物</t>
-        </is>
-      </c>
-      <c r="C73" s="0" t="inlineStr"/>
-      <c r="D73" s="0" t="inlineStr"/>
-      <c r="E73" s="0" t="inlineStr">
-        <is>
-          <t>谷物(稻谷除外)</t>
-        </is>
-      </c>
-      <c r="F73" s="0" t="inlineStr">
-        <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G73" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H73" s="0" t="inlineStr"/>
-      <c r="I73" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J73" s="0" t="inlineStr"/>
-      <c r="K73" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="0" t="inlineStr">
-        <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B74" s="0" t="inlineStr">
-        <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C74" s="0" t="inlineStr"/>
-      <c r="D74" s="0" t="inlineStr"/>
-      <c r="E74" s="0" t="inlineStr">
-        <is>
-          <t>谷物碾磨加工品[糙米、大米(粉)除外]</t>
-        </is>
-      </c>
-      <c r="F74" s="0" t="inlineStr">
-        <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G74" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H74" s="0" t="inlineStr"/>
-      <c r="I74" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J74" s="0" t="inlineStr"/>
-      <c r="K74" s="0" t="inlineStr">
+      <c r="K74" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
@@ -18179,12 +18181,12 @@
       </c>
       <c r="F75" s="0" t="inlineStr">
         <is>
-          <t>无机砷 a</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H75" s="0" t="inlineStr"/>
@@ -18220,12 +18222,12 @@
       </c>
       <c r="F76" s="0" t="inlineStr">
         <is>
-          <t>无机砷 a</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H76" s="0" t="inlineStr"/>
@@ -18244,24 +18246,30 @@
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
-        </is>
-      </c>
-      <c r="B77" s="0" t="inlineStr"/>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="inlineStr">
+        <is>
+          <t>谷物</t>
+        </is>
+      </c>
       <c r="C77" s="0" t="inlineStr"/>
       <c r="D77" s="0" t="inlineStr"/>
       <c r="E77" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>谷物(稻谷除外)</t>
         </is>
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G77" s="0" t="n">
-        <v>0.5</v>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G77" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H77" s="0" t="inlineStr"/>
       <c r="I77" s="0" t="inlineStr">
@@ -18279,15 +18287,19 @@
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
-        </is>
-      </c>
-      <c r="B78" s="0" t="inlineStr"/>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="inlineStr">
+        <is>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
       <c r="C78" s="0" t="inlineStr"/>
       <c r="D78" s="0" t="inlineStr"/>
       <c r="E78" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>谷物碾磨加工品[糙米、大米(粉)除外]</t>
         </is>
       </c>
       <c r="F78" s="0" t="inlineStr">
@@ -18316,7 +18328,7 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B79" s="0" t="inlineStr"/>
@@ -18324,7 +18336,7 @@
       <c r="D79" s="0" t="inlineStr"/>
       <c r="E79" s="0" t="inlineStr">
         <is>
-          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="F79" s="0" t="inlineStr">
@@ -18333,7 +18345,7 @@
         </is>
       </c>
       <c r="G79" s="0" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="H79" s="0" t="inlineStr"/>
       <c r="I79" s="0" t="inlineStr">
@@ -18351,7 +18363,7 @@
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B80" s="0" t="inlineStr"/>
@@ -18359,7 +18371,7 @@
       <c r="D80" s="0" t="inlineStr"/>
       <c r="E80" s="0" t="inlineStr">
         <is>
-          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="F80" s="0" t="inlineStr">
@@ -18380,6 +18392,78 @@
       </c>
       <c r="J80" s="0" t="inlineStr"/>
       <c r="K80" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="inlineStr">
+        <is>
+          <t>油脂及其制品</t>
+        </is>
+      </c>
+      <c r="B81" s="0" t="inlineStr"/>
+      <c r="C81" s="0" t="inlineStr"/>
+      <c r="D81" s="0" t="inlineStr"/>
+      <c r="E81" s="0" t="inlineStr">
+        <is>
+          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
+        </is>
+      </c>
+      <c r="F81" s="0" t="inlineStr">
+        <is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G81" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H81" s="0" t="inlineStr"/>
+      <c r="I81" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J81" s="0" t="inlineStr"/>
+      <c r="K81" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="inlineStr">
+        <is>
+          <t>油脂及其制品</t>
+        </is>
+      </c>
+      <c r="B82" s="0" t="inlineStr"/>
+      <c r="C82" s="0" t="inlineStr"/>
+      <c r="D82" s="0" t="inlineStr"/>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
+        </is>
+      </c>
+      <c r="F82" s="0" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G82" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="0" t="inlineStr"/>
+      <c r="I82" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J82" s="0" t="inlineStr"/>
+      <c r="K82" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -3218,7 +3218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K128"/>
+  <dimension ref="A1:K121"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -4099,15 +4099,15 @@
           <t>水产制品</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>海蜇制品</t>
         </is>
       </c>
       <c r="D24" s="19" t="n"/>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>水产制品(鱼类制品、海蜇制品除外)</t>
+          <t>海蜇制品</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
@@ -4115,9 +4115,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
-        <is>
-          <t>1.0</t>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
       <c r="H24" s="19" t="n"/>
@@ -4146,13 +4146,13 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>海蜇制品</t>
+          <t>鱼类制品</t>
         </is>
       </c>
       <c r="D25" s="19" t="n"/>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>水产制品(鱼类制品、海蜇制品除外)</t>
+          <t>鱼类制品</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="G25" s="19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H25" s="19" t="n"/>
@@ -4179,25 +4179,29 @@
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" s="23">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>水产制品</t>
+          <t>鲜、冻水产动物</t>
         </is>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>海蜇制品</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="n"/>
+          <t>软体动物</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>双壳贝类</t>
+        </is>
+      </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>海蜇制品</t>
+          <t>双壳贝类</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
@@ -4205,9 +4209,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
-        <is>
-          <t>2.0</t>
+      <c r="G26" s="19" t="inlineStr">
+        <is>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H26" s="19" t="n"/>
@@ -4224,25 +4228,29 @@
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" s="23">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>水产制品</t>
+          <t>鲜、冻水产动物</t>
         </is>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="n"/>
+          <t>鱼类</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>非肉食性鱼类</t>
+        </is>
+      </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>鱼类制品</t>
+          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
         </is>
       </c>
       <c r="F27" s="19" t="inlineStr">
@@ -4252,7 +4260,7 @@
       </c>
       <c r="G27" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H27" s="19" t="n"/>
@@ -4281,17 +4289,17 @@
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>软体动物</t>
+          <t>鱼类</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>双壳贝类</t>
+          <t>非肉食性鱼类</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>双壳贝类</t>
+          <t>鱼类、甲壳类</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
@@ -4301,7 +4309,7 @@
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H28" s="19" t="n"/>
@@ -4320,27 +4328,19 @@
     <row r="29" ht="28" customHeight="1" s="23">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>水果及其制品</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>非肉食性鱼类</t>
-        </is>
-      </c>
+          <t>新鲜水果（未经加工的、经表面处理的、去皮或预切的、冷冻的水果）</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="19" t="n"/>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
+          <t>新鲜水果(蔓越莓、醋栗除外)</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H29" s="19" t="n"/>
@@ -4369,27 +4369,19 @@
     <row r="30" ht="42" customHeight="1" s="23">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>水果及其制品</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>非肉食性鱼类</t>
-        </is>
-      </c>
+          <t>水果制品</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
+          <t>水果制品(果酱(泥)、蜜饯、水果干类除外)</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
@@ -4399,7 +4391,7 @@
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H30" s="19" t="n"/>
@@ -4418,27 +4410,23 @@
     <row r="31" ht="28" customHeight="1" s="23">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>水果及其制品</t>
         </is>
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
+          <t>新鲜水果（未经加工的、经表面处理的、去皮或预切的、冷冻的水果）</t>
         </is>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>非肉食性鱼类</t>
-        </is>
-      </c>
+          <t>浆果和其他小粒水果（例如：蔓越莓、醋栗等）</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="n"/>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
+          <t>蔓越莓、醋栗</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
@@ -4448,7 +4436,7 @@
       </c>
       <c r="G31" s="19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H31" s="19" t="n"/>
@@ -4467,27 +4455,23 @@
     <row r="32" ht="56" customHeight="1" s="23">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>水果及其制品</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
+          <t>水果制品</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>非肉食性鱼类</t>
-        </is>
-      </c>
+          <t>果酱（泥）</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="n"/>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
+          <t>果酱(泥)</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
@@ -4497,7 +4481,7 @@
       </c>
       <c r="G32" s="19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="H32" s="19" t="n"/>
@@ -4516,27 +4500,23 @@
     <row r="33" ht="56" customHeight="1" s="23">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>水果及其制品</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
+          <t>水果制品</t>
         </is>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>非肉食性鱼类</t>
-        </is>
-      </c>
+          <t>水果干类</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="n"/>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>鱼类、甲壳类</t>
+          <t>水果干类</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
@@ -4565,27 +4545,23 @@
     <row r="34" ht="56" customHeight="1" s="23">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>水果及其制品</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
+          <t>水果制品</t>
         </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>非肉食性鱼类</t>
-        </is>
-      </c>
+          <t>蜜饯（包括果丹皮）</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="n"/>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>鱼类、甲壳类</t>
+          <t>蜜饯</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
@@ -4595,7 +4571,7 @@
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="H34" s="19" t="n"/>
@@ -4614,27 +4590,15 @@
     <row r="35" ht="56" customHeight="1" s="23">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>非肉食性鱼类</t>
-        </is>
-      </c>
+          <t>油脂及其制品</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="n"/>
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="19" t="n"/>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t>鱼类、甲壳类</t>
+          <t>油脂及其制品</t>
         </is>
       </c>
       <c r="F35" s="19" t="inlineStr">
@@ -4644,7 +4608,7 @@
       </c>
       <c r="G35" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="H35" s="19" t="n"/>
@@ -4663,19 +4627,19 @@
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>水果及其制品</t>
+          <t>淀粉及淀粉制品（包括谷物、豆类和块根植物提取的淀粉）</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>新鲜水果（未经加工的、经表面处理的、去皮或预切的、冷冻的水果）</t>
+          <t>淀粉制品（包括虾味片）</t>
         </is>
       </c>
       <c r="C36" s="19" t="n"/>
       <c r="D36" s="19" t="n"/>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>新鲜水果(蔓越莓、醋栗除外)</t>
+          <t>淀粉制品</t>
         </is>
       </c>
       <c r="F36" s="19" t="inlineStr">
@@ -4685,7 +4649,7 @@
       </c>
       <c r="G36" s="19" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H36" s="19" t="n"/>
@@ -4704,19 +4668,19 @@
     <row r="37" ht="42" customHeight="1" s="23">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>水果及其制品</t>
+          <t>淀粉及淀粉制品（包括谷物、豆类和块根植物提取的淀粉）</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>水果制品</t>
+          <t>食用淀粉</t>
         </is>
       </c>
       <c r="C37" s="19" t="n"/>
       <c r="D37" s="19" t="n"/>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>水果制品(果酱(泥)、蜜饯、水果干类除外)</t>
+          <t>食用淀粉</t>
         </is>
       </c>
       <c r="F37" s="19" t="inlineStr">
@@ -4745,23 +4709,15 @@
     <row r="38" ht="42" customHeight="1" s="23">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>水果及其制品</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="inlineStr">
-        <is>
-          <t>新鲜水果（未经加工的、经表面处理的、去皮或预切的、冷冻的水果）</t>
-        </is>
-      </c>
-      <c r="C38" s="19" t="inlineStr">
-        <is>
-          <t>浆果和其他小粒水果（例如：蔓越莓、醋栗等）</t>
-        </is>
-      </c>
+          <t>焙烤食品</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="n"/>
+      <c r="C38" s="19" t="n"/>
       <c r="D38" s="19" t="n"/>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>蔓越莓、醋栗</t>
+          <t>焙烤食品</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
@@ -4771,7 +4727,7 @@
       </c>
       <c r="G38" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H38" s="19" t="n"/>
@@ -4790,23 +4746,19 @@
     <row r="39" ht="28" customHeight="1" s="23">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>水果及其制品</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
-          <t>水果制品</t>
-        </is>
-      </c>
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>果酱（泥）</t>
-        </is>
-      </c>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="n"/>
       <c r="D39" s="19" t="n"/>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>果酱(泥)</t>
+          <t>辅食营养补充品</t>
         </is>
       </c>
       <c r="F39" s="19" t="inlineStr">
@@ -4816,7 +4768,7 @@
       </c>
       <c r="G39" s="19" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H39" s="19" t="n"/>
@@ -4835,23 +4787,19 @@
     <row r="40" ht="56" customHeight="1" s="23">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>水果及其制品</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>水果制品</t>
-        </is>
-      </c>
-      <c r="C40" s="19" t="inlineStr">
-        <is>
-          <t>水果干类</t>
-        </is>
-      </c>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="n"/>
       <c r="D40" s="19" t="n"/>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>水果干类</t>
+          <t>运动营养食品(固态、半固态或粉状)</t>
         </is>
       </c>
       <c r="F40" s="19" t="inlineStr">
@@ -4880,23 +4828,19 @@
     <row r="41" ht="56" customHeight="1" s="23">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>水果及其制品</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>水果制品</t>
-        </is>
-      </c>
-      <c r="C41" s="19" t="inlineStr">
-        <is>
-          <t>蜜饯（包括果丹皮）</t>
-        </is>
-      </c>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="n"/>
       <c r="D41" s="19" t="n"/>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>蜜饯</t>
+          <t>运动营养食品(液态)</t>
         </is>
       </c>
       <c r="F41" s="19" t="inlineStr">
@@ -4906,7 +4850,7 @@
       </c>
       <c r="G41" s="19" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H41" s="19" t="n"/>
@@ -4925,15 +4869,19 @@
     <row r="42" ht="28" customHeight="1" s="23">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
-        </is>
-      </c>
-      <c r="B42" s="19" t="n"/>
+          <t>特殊膳食用食品</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+        </is>
+      </c>
       <c r="C42" s="19" t="n"/>
       <c r="D42" s="19" t="n"/>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
+          <t>孕妇及乳母营养补充食品</t>
         </is>
       </c>
       <c r="F42" s="19" t="inlineStr">
@@ -4943,7 +4891,7 @@
       </c>
       <c r="G42" s="19" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H42" s="19" t="n"/>
@@ -4962,19 +4910,19 @@
     <row r="43" ht="28" customHeight="1" s="23">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>淀粉及淀粉制品（包括谷物、豆类和块根植物提取的淀粉）</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t>淀粉制品（包括虾味片）</t>
+          <t>婴幼儿辅助食品</t>
         </is>
       </c>
       <c r="C43" s="19" t="n"/>
       <c r="D43" s="19" t="n"/>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>淀粉制品</t>
+          <t>婴幼儿辅助食品</t>
         </is>
       </c>
       <c r="F43" s="19" t="inlineStr">
@@ -4984,7 +4932,7 @@
       </c>
       <c r="G43" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H43" s="19" t="n"/>
@@ -5003,19 +4951,19 @@
     <row r="44" ht="28" customHeight="1" s="23">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>淀粉及淀粉制品（包括谷物、豆类和块根植物提取的淀粉）</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>食用淀粉</t>
+          <t>婴幼儿配方食品</t>
         </is>
       </c>
       <c r="C44" s="19" t="n"/>
       <c r="D44" s="19" t="n"/>
       <c r="E44" s="19" t="inlineStr">
         <is>
-          <t>食用淀粉</t>
+          <t>婴幼儿配方食品</t>
         </is>
       </c>
       <c r="F44" s="19" t="inlineStr">
@@ -5025,7 +4973,7 @@
       </c>
       <c r="G44" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.08(以固态产品计)</t>
         </is>
       </c>
       <c r="H44" s="19" t="n"/>
@@ -5034,7 +4982,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J44" s="19" t="n"/>
+      <c r="J44" s="19" t="inlineStr">
+        <is>
+          <t>c 液态婴幼儿配方食品根据8∶1的比例折算其限量。</t>
+        </is>
+      </c>
       <c r="K44" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -5044,15 +4996,19 @@
     <row r="45" ht="42" customHeight="1" s="23">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>焙烤食品</t>
-        </is>
-      </c>
-      <c r="B45" s="19" t="n"/>
+          <t>特殊膳食用食品</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>特殊医学用途配方食品（特殊医学用途婴儿配方食品涉及的品种除外）</t>
+        </is>
+      </c>
       <c r="C45" s="19" t="n"/>
       <c r="D45" s="19" t="n"/>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>焙烤食品</t>
+          <t>特殊医学用途配方食品(特殊医学用途婴儿配方食品涉及的品种除外)、10岁以上人群的产品</t>
         </is>
       </c>
       <c r="F45" s="19" t="inlineStr">
@@ -5062,7 +5018,7 @@
       </c>
       <c r="G45" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.5(以固态产品计)</t>
         </is>
       </c>
       <c r="H45" s="19" t="n"/>
@@ -5086,14 +5042,14 @@
       </c>
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+          <t>特殊医学用途配方食品（特殊医学用途婴儿配方食品涉及的品种除外）</t>
         </is>
       </c>
       <c r="C46" s="19" t="n"/>
       <c r="D46" s="19" t="n"/>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>辅食营养补充品</t>
+          <t>特殊医学用途配方食品(特殊医学用途婴儿配方食品涉及的品种除外)、1~10岁人群的产品</t>
         </is>
       </c>
       <c r="F46" s="19" t="inlineStr">
@@ -5103,7 +5059,7 @@
       </c>
       <c r="G46" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.15(以固态产品计)</t>
         </is>
       </c>
       <c r="H46" s="19" t="n"/>
@@ -5122,19 +5078,19 @@
     <row r="47" ht="42" customHeight="1" s="23">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+          <t>肉类（生鲜肉、冷却肉、冷冻肉等）</t>
         </is>
       </c>
       <c r="C47" s="19" t="n"/>
       <c r="D47" s="19" t="n"/>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>运动营养食品(固态、半固态或粉状)</t>
+          <t>肉类(畜禽内脏除外)</t>
         </is>
       </c>
       <c r="F47" s="19" t="inlineStr">
@@ -5144,7 +5100,7 @@
       </c>
       <c r="G47" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H47" s="19" t="n"/>
@@ -5163,19 +5119,19 @@
     <row r="48" ht="42" customHeight="1" s="23">
       <c r="A48" s="19" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B48" s="19" t="inlineStr">
         <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+          <t>肉制品（包括内脏制品、血制品）</t>
         </is>
       </c>
       <c r="C48" s="19" t="n"/>
       <c r="D48" s="19" t="n"/>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>运动营养食品(液态)</t>
+          <t>肉制品(畜禽内脏制品除外)</t>
         </is>
       </c>
       <c r="F48" s="19" t="inlineStr">
@@ -5185,7 +5141,7 @@
       </c>
       <c r="G48" s="19" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H48" s="19" t="n"/>
@@ -5204,19 +5160,19 @@
     <row r="49" ht="28" customHeight="1" s="23">
       <c r="A49" s="19" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+          <t>肉制品（包括内脏制品、血制品）</t>
         </is>
       </c>
       <c r="C49" s="19" t="n"/>
       <c r="D49" s="19" t="n"/>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>孕妇及乳母营养补充食品</t>
+          <t>畜禽内脏制品</t>
         </is>
       </c>
       <c r="F49" s="19" t="inlineStr">
@@ -5245,19 +5201,23 @@
     <row r="50" ht="28" customHeight="1" s="23">
       <c r="A50" s="19" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C50" s="19" t="n"/>
+          <t>肉类（生鲜肉、冷却肉、冷冻肉等）</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>畜禽内脏（例如：肝、肾、肺、肠等）</t>
+        </is>
+      </c>
       <c r="D50" s="19" t="n"/>
       <c r="E50" s="19" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
+          <t>畜禽内脏</t>
         </is>
       </c>
       <c r="F50" s="19" t="inlineStr">
@@ -5267,7 +5227,7 @@
       </c>
       <c r="G50" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H50" s="19" t="n"/>
@@ -5286,19 +5246,19 @@
     <row r="51" ht="28" customHeight="1" s="23">
       <c r="A51" s="19" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
-          <t>婴幼儿配方食品</t>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
         </is>
       </c>
       <c r="C51" s="19" t="n"/>
       <c r="D51" s="19" t="n"/>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t>婴幼儿配方食品</t>
+          <t>新鲜蔬菜(芸薹类蔬菜、叶菜蔬菜、豆类蔬菜、生姜、薯类除外)</t>
         </is>
       </c>
       <c r="F51" s="19" t="inlineStr">
@@ -5308,7 +5268,7 @@
       </c>
       <c r="G51" s="19" t="inlineStr">
         <is>
-          <t>0.08(以固态产品计)</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H51" s="19" t="n"/>
@@ -5317,11 +5277,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J51" s="19" t="inlineStr">
-        <is>
-          <t>c 液态婴幼儿配方食品根据8∶1的比例折算其限量。</t>
-        </is>
-      </c>
+      <c r="J51" s="19" t="n"/>
       <c r="K51" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -5331,19 +5287,19 @@
     <row r="52" ht="42" customHeight="1" s="23">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B52" s="19" t="inlineStr">
         <is>
-          <t>特殊医学用途配方食品（特殊医学用途婴儿配方食品涉及的品种除外）</t>
+          <t>蔬菜制品</t>
         </is>
       </c>
       <c r="C52" s="19" t="n"/>
       <c r="D52" s="19" t="n"/>
       <c r="E52" s="19" t="inlineStr">
         <is>
-          <t>特殊医学用途配方食品(特殊医学用途婴儿配方食品涉及的品种除外)、10岁以上人群的产品</t>
+          <t>蔬菜制品(酱腌菜、干制蔬菜除外)</t>
         </is>
       </c>
       <c r="F52" s="19" t="inlineStr">
@@ -5353,7 +5309,7 @@
       </c>
       <c r="G52" s="19" t="inlineStr">
         <is>
-          <t>0.5(以固态产品计)</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H52" s="19" t="n"/>
@@ -5372,19 +5328,23 @@
     <row r="53" ht="28" customHeight="1" s="23">
       <c r="A53" s="19" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
-          <t>特殊医学用途配方食品（特殊医学用途婴儿配方食品涉及的品种除外）</t>
-        </is>
-      </c>
-      <c r="C53" s="19" t="n"/>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>叶菜蔬菜（包括芸薹类叶菜）</t>
+        </is>
+      </c>
       <c r="D53" s="19" t="n"/>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t>特殊医学用途配方食品(特殊医学用途婴儿配方食品涉及的品种除外)、1~10岁人群的产品</t>
+          <t>叶菜蔬菜</t>
         </is>
       </c>
       <c r="F53" s="19" t="inlineStr">
@@ -5394,7 +5354,7 @@
       </c>
       <c r="G53" s="19" t="inlineStr">
         <is>
-          <t>0.15(以固态产品计)</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H53" s="19" t="n"/>
@@ -5413,19 +5373,23 @@
     <row r="54" ht="70" customHeight="1" s="23">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B54" s="19" t="inlineStr">
         <is>
-          <t>肉类（生鲜肉、冷却肉、冷冻肉等）</t>
-        </is>
-      </c>
-      <c r="C54" s="19" t="n"/>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="inlineStr">
+        <is>
+          <t>芸薹类蔬菜</t>
+        </is>
+      </c>
       <c r="D54" s="19" t="n"/>
       <c r="E54" s="19" t="inlineStr">
         <is>
-          <t>肉类(畜禽内脏除外)</t>
+          <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
         </is>
       </c>
       <c r="F54" s="19" t="inlineStr">
@@ -5454,19 +5418,23 @@
     <row r="55" ht="28" customHeight="1" s="23">
       <c r="A55" s="19" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
-          <t>肉制品（包括内脏制品、血制品）</t>
-        </is>
-      </c>
-      <c r="C55" s="19" t="n"/>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="inlineStr">
+        <is>
+          <t>豆类蔬菜</t>
+        </is>
+      </c>
       <c r="D55" s="19" t="n"/>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t>肉制品(畜禽内脏制品除外)</t>
+          <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
         </is>
       </c>
       <c r="F55" s="19" t="inlineStr">
@@ -5476,7 +5444,7 @@
       </c>
       <c r="G55" s="19" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H55" s="19" t="n"/>
@@ -5495,19 +5463,27 @@
     <row r="56" ht="42" customHeight="1" s="23">
       <c r="A56" s="19" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B56" s="19" t="inlineStr">
         <is>
-          <t>肉制品（包括内脏制品、血制品）</t>
-        </is>
-      </c>
-      <c r="C56" s="19" t="n"/>
-      <c r="D56" s="19" t="n"/>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
+      <c r="C56" s="19" t="inlineStr">
+        <is>
+          <t>块根和块茎蔬菜（例如：薯类、胡萝卜、萝卜、生姜等）</t>
+        </is>
+      </c>
+      <c r="D56" s="19" t="inlineStr">
+        <is>
+          <t>生姜</t>
+        </is>
+      </c>
       <c r="E56" s="19" t="inlineStr">
         <is>
-          <t>畜禽内脏制品</t>
+          <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
         </is>
       </c>
       <c r="F56" s="19" t="inlineStr">
@@ -5517,7 +5493,7 @@
       </c>
       <c r="G56" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H56" s="19" t="n"/>
@@ -5534,25 +5510,29 @@
       </c>
     </row>
     <row r="57" ht="42" customHeight="1" s="23">
-      <c r="A57" s="19" t="inlineStr">
-        <is>
-          <t>肉及肉制品</t>
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
-          <t>肉类（生鲜肉、冷却肉、冷冻肉等）</t>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t>畜禽内脏（例如：肝、肾、肺、肠等）</t>
-        </is>
-      </c>
-      <c r="D57" s="19" t="n"/>
+          <t>块根和块茎蔬菜（例如：薯类、胡萝卜、萝卜、生姜等）</t>
+        </is>
+      </c>
+      <c r="D57" s="19" t="inlineStr">
+        <is>
+          <t>薯类</t>
+        </is>
+      </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t>畜禽内脏</t>
+          <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
         </is>
       </c>
       <c r="F57" s="19" t="inlineStr">
@@ -5562,7 +5542,7 @@
       </c>
       <c r="G57" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H57" s="19" t="n"/>
@@ -5579,21 +5559,25 @@
       </c>
     </row>
     <row r="58" ht="42" customHeight="1" s="23">
-      <c r="A58" s="19" t="inlineStr">
+      <c r="A58" s="20" t="inlineStr">
         <is>
           <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B58" s="19" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
-        </is>
-      </c>
-      <c r="C58" s="19" t="n"/>
+          <t>蔬菜制品</t>
+        </is>
+      </c>
+      <c r="C58" s="19" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
       <c r="D58" s="19" t="n"/>
       <c r="E58" s="19" t="inlineStr">
         <is>
-          <t>新鲜蔬菜(芸薹类蔬菜、叶菜蔬菜、豆类蔬菜、生姜、薯类除外)</t>
+          <t>酱腌菜</t>
         </is>
       </c>
       <c r="F58" s="19" t="inlineStr">
@@ -5601,9 +5585,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G58" s="19" t="inlineStr">
-        <is>
-          <t>0.1</t>
+      <c r="G58" s="22" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H58" s="19" t="n"/>
@@ -5630,11 +5614,15 @@
           <t>蔬菜制品</t>
         </is>
       </c>
-      <c r="C59" s="19" t="n"/>
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>干制蔬菜</t>
+        </is>
+      </c>
       <c r="D59" s="19" t="n"/>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t>蔬菜制品(酱腌菜、干制蔬菜除外)</t>
+          <t>干制蔬菜</t>
         </is>
       </c>
       <c r="F59" s="19" t="inlineStr">
@@ -5644,7 +5632,7 @@
       </c>
       <c r="G59" s="19" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="H59" s="19" t="n"/>
@@ -5668,18 +5656,18 @@
       </c>
       <c r="B60" s="19" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+          <t>蔬菜制品</t>
         </is>
       </c>
       <c r="C60" s="19" t="inlineStr">
         <is>
-          <t>叶菜蔬菜（包括芸薹类叶菜）</t>
+          <t>酱腌菜</t>
         </is>
       </c>
       <c r="D60" s="19" t="n"/>
       <c r="E60" s="19" t="inlineStr">
         <is>
-          <t>叶菜蔬菜</t>
+          <t>酱腌菜</t>
         </is>
       </c>
       <c r="F60" s="19" t="inlineStr">
@@ -5689,7 +5677,7 @@
       </c>
       <c r="G60" s="19" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H60" s="19" t="n"/>
@@ -5708,23 +5696,19 @@
     <row r="61" ht="42" customHeight="1" s="23">
       <c r="A61" s="19" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
-        </is>
-      </c>
-      <c r="B61" s="19" t="inlineStr">
-        <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
-        </is>
-      </c>
-      <c r="C61" s="19" t="inlineStr">
-        <is>
-          <t>芸薹类蔬菜</t>
-        </is>
-      </c>
+          <t>藻类及其制品</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>新鲜藻类（未经加工的、经表面处理的、预切的、冷冻的藻类）</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="n"/>
       <c r="D61" s="19" t="n"/>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
+          <t>新鲜藻类(螺旋藻除外)</t>
         </is>
       </c>
       <c r="F61" s="19" t="inlineStr">
@@ -5734,7 +5718,7 @@
       </c>
       <c r="G61" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H61" s="19" t="n"/>
@@ -5753,23 +5737,23 @@
     <row r="62" ht="42" customHeight="1" s="23">
       <c r="A62" s="19" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+          <t>藻类及其制品</t>
         </is>
       </c>
       <c r="B62" s="19" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+          <t>新鲜藻类（未经加工的、经表面处理的、预切的、冷冻的藻类）</t>
         </is>
       </c>
       <c r="C62" s="19" t="inlineStr">
         <is>
-          <t>豆类蔬菜</t>
+          <t>螺旋藻</t>
         </is>
       </c>
       <c r="D62" s="19" t="n"/>
       <c r="E62" s="19" t="inlineStr">
         <is>
-          <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
+          <t>螺旋藻</t>
         </is>
       </c>
       <c r="F62" s="19" t="inlineStr">
@@ -5779,7 +5763,7 @@
       </c>
       <c r="G62" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5(干重计)</t>
         </is>
       </c>
       <c r="H62" s="19" t="n"/>
@@ -5798,27 +5782,19 @@
     <row r="63" ht="42" customHeight="1" s="23">
       <c r="A63" s="19" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+          <t>藻类及其制品</t>
         </is>
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
-        </is>
-      </c>
-      <c r="C63" s="19" t="inlineStr">
-        <is>
-          <t>块根和块茎蔬菜（例如：薯类、胡萝卜、萝卜、生姜等）</t>
-        </is>
-      </c>
-      <c r="D63" s="19" t="inlineStr">
-        <is>
-          <t>生姜</t>
-        </is>
-      </c>
+          <t>藻类制品</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="n"/>
+      <c r="D63" s="19" t="n"/>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
+          <t>藻类制品(螺旋藻制品除外)</t>
         </is>
       </c>
       <c r="F63" s="19" t="inlineStr">
@@ -5828,7 +5804,7 @@
       </c>
       <c r="G63" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H63" s="19" t="n"/>
@@ -5845,29 +5821,25 @@
       </c>
     </row>
     <row r="64" ht="42" customHeight="1" s="23">
-      <c r="A64" s="20" t="inlineStr">
-        <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t>藻类及其制品</t>
         </is>
       </c>
       <c r="B64" s="19" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+          <t>藻类制品</t>
         </is>
       </c>
       <c r="C64" s="19" t="inlineStr">
         <is>
-          <t>块根和块茎蔬菜（例如：薯类、胡萝卜、萝卜、生姜等）</t>
-        </is>
-      </c>
-      <c r="D64" s="19" t="inlineStr">
-        <is>
-          <t>薯类</t>
-        </is>
-      </c>
+          <t>其他藻类制品</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="n"/>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
+          <t>螺旋藻制品</t>
         </is>
       </c>
       <c r="F64" s="19" t="inlineStr">
@@ -5877,7 +5849,7 @@
       </c>
       <c r="G64" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.0(干重计)</t>
         </is>
       </c>
       <c r="H64" s="19" t="n"/>
@@ -5894,25 +5866,17 @@
       </c>
     </row>
     <row r="65" ht="42" customHeight="1" s="23">
-      <c r="A65" s="20" t="inlineStr">
-        <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
-        </is>
-      </c>
-      <c r="B65" s="19" t="inlineStr">
-        <is>
-          <t>蔬菜制品</t>
-        </is>
-      </c>
-      <c r="C65" s="19" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t>蛋及蛋制品</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="n"/>
+      <c r="C65" s="19" t="n"/>
       <c r="D65" s="19" t="n"/>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t>酱腌菜</t>
+          <t>蛋及蛋制品</t>
         </is>
       </c>
       <c r="F65" s="19" t="inlineStr">
@@ -5920,9 +5884,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G65" s="22" t="inlineStr">
-        <is>
-          <t>0.5</t>
+      <c r="G65" s="19" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H65" s="19" t="n"/>
@@ -5941,23 +5905,15 @@
     <row r="66" ht="42" customHeight="1" s="23">
       <c r="A66" s="19" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
-        </is>
-      </c>
-      <c r="B66" s="19" t="inlineStr">
-        <is>
-          <t>蔬菜制品</t>
-        </is>
-      </c>
-      <c r="C66" s="19" t="inlineStr">
-        <is>
-          <t>干制蔬菜</t>
-        </is>
-      </c>
+          <t>调味品</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="n"/>
+      <c r="C66" s="19" t="n"/>
       <c r="D66" s="19" t="n"/>
       <c r="E66" s="19" t="inlineStr">
         <is>
-          <t>干制蔬菜</t>
+          <t>调味品(香辛料类除外)</t>
         </is>
       </c>
       <c r="F66" s="19" t="inlineStr">
@@ -5967,7 +5923,7 @@
       </c>
       <c r="G66" s="19" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H66" s="19" t="n"/>
@@ -5986,23 +5942,19 @@
     <row r="67" ht="42" customHeight="1" s="23">
       <c r="A67" s="19" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+          <t>调味品</t>
         </is>
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
-          <t>蔬菜制品</t>
-        </is>
-      </c>
-      <c r="C67" s="19" t="inlineStr">
-        <is>
-          <t>酱腌菜</t>
-        </is>
-      </c>
+          <t>香辛料类</t>
+        </is>
+      </c>
+      <c r="C67" s="19" t="n"/>
       <c r="D67" s="19" t="n"/>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t>酱腌菜</t>
+          <t>香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外)</t>
         </is>
       </c>
       <c r="F67" s="19" t="inlineStr">
@@ -6012,7 +5964,7 @@
       </c>
       <c r="G67" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H67" s="19" t="n"/>
@@ -6021,7 +5973,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J67" s="19" t="n"/>
+      <c r="J67" s="19" t="inlineStr">
+        <is>
+          <t>b 新鲜香辛料(如姜、葱、蒜等)应按对应的新鲜蔬菜(或新鲜水果)类别执行。</t>
+        </is>
+      </c>
       <c r="K67" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6029,21 +5985,25 @@
       </c>
     </row>
     <row r="68" ht="28" customHeight="1" s="23">
-      <c r="A68" s="19" t="inlineStr">
-        <is>
-          <t>藻类及其制品</t>
-        </is>
-      </c>
-      <c r="B68" s="0" t="inlineStr">
-        <is>
-          <t>新鲜藻类（未经加工的、经表面处理的、预切的、冷冻的藻类）</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="n"/>
+      <c r="A68" s="20" t="inlineStr">
+        <is>
+          <t>调味品</t>
+        </is>
+      </c>
+      <c r="B68" s="19" t="inlineStr">
+        <is>
+          <t>香辛料类</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="inlineStr">
+        <is>
+          <t>花椒、桂皮、肉桂、多种香辛料混合的香辛料</t>
+        </is>
+      </c>
       <c r="D68" s="19" t="n"/>
       <c r="E68" s="19" t="inlineStr">
         <is>
-          <t>新鲜藻类(螺旋藻除外)</t>
+          <t>花椒、桂皮、肉桂、多种香辛料混合的香辛料</t>
         </is>
       </c>
       <c r="F68" s="19" t="inlineStr">
@@ -6051,9 +6011,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G68" s="19" t="inlineStr">
-        <is>
-          <t>0.5</t>
+      <c r="G68" s="22" t="inlineStr">
+        <is>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H68" s="19" t="n"/>
@@ -6070,25 +6030,17 @@
       </c>
     </row>
     <row r="69" ht="42" customHeight="1" s="23">
-      <c r="A69" s="19" t="inlineStr">
-        <is>
-          <t>藻类及其制品</t>
-        </is>
-      </c>
-      <c r="B69" s="19" t="inlineStr">
-        <is>
-          <t>新鲜藻类（未经加工的、经表面处理的、预切的、冷冻的藻类）</t>
-        </is>
-      </c>
-      <c r="C69" s="19" t="inlineStr">
-        <is>
-          <t>螺旋藻</t>
-        </is>
-      </c>
+      <c r="A69" s="20" t="inlineStr">
+        <is>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B69" s="19" t="n"/>
+      <c r="C69" s="19" t="n"/>
       <c r="D69" s="19" t="n"/>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t>螺旋藻</t>
+          <t>谷物及其制品(麦片、面筋、粥类罐头、带馅料面米制品除外)</t>
         </is>
       </c>
       <c r="F69" s="19" t="inlineStr">
@@ -6096,9 +6048,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G69" s="19" t="inlineStr">
-        <is>
-          <t>0.5(干重计)</t>
+      <c r="G69" s="22" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H69" s="19" t="n"/>
@@ -6107,7 +6059,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J69" s="19" t="n"/>
+      <c r="J69" s="19" t="inlineStr">
+        <is>
+          <t>a 稻谷以糙米计。</t>
+        </is>
+      </c>
       <c r="K69" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6115,21 +6071,25 @@
       </c>
     </row>
     <row r="70" ht="42" customHeight="1" s="23">
-      <c r="A70" s="19" t="inlineStr">
-        <is>
-          <t>藻类及其制品</t>
+      <c r="A70" s="20" t="inlineStr">
+        <is>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B70" s="19" t="inlineStr">
         <is>
-          <t>藻类制品</t>
-        </is>
-      </c>
-      <c r="C70" s="19" t="n"/>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C70" s="19" t="inlineStr">
+        <is>
+          <t>麦片</t>
+        </is>
+      </c>
       <c r="D70" s="19" t="n"/>
       <c r="E70" s="19" t="inlineStr">
         <is>
-          <t>藻类制品(螺旋藻制品除外)</t>
+          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
       <c r="F70" s="19" t="inlineStr">
@@ -6137,9 +6097,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G70" s="19" t="inlineStr">
-        <is>
-          <t>1.0</t>
+      <c r="G70" s="22" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H70" s="19" t="n"/>
@@ -6156,25 +6116,29 @@
       </c>
     </row>
     <row r="71" ht="28" customHeight="1" s="23">
-      <c r="A71" s="19" t="inlineStr">
-        <is>
-          <t>藻类及其制品</t>
+      <c r="A71" s="20" t="inlineStr">
+        <is>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B71" s="19" t="inlineStr">
         <is>
-          <t>藻类制品</t>
+          <t>谷物制品</t>
         </is>
       </c>
       <c r="C71" s="19" t="inlineStr">
         <is>
-          <t>其他藻类制品</t>
-        </is>
-      </c>
-      <c r="D71" s="19" t="n"/>
+          <t>小麦粉制品</t>
+        </is>
+      </c>
+      <c r="D71" s="19" t="inlineStr">
+        <is>
+          <t>面筋</t>
+        </is>
+      </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t>螺旋藻制品</t>
+          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
       <c r="F71" s="19" t="inlineStr">
@@ -6182,9 +6146,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G71" s="19" t="inlineStr">
-        <is>
-          <t>2.0(干重计)</t>
+      <c r="G71" s="30" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H71" s="19" t="n"/>
@@ -6201,17 +6165,29 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="19" t="inlineStr">
-        <is>
-          <t>蛋及蛋制品</t>
-        </is>
-      </c>
-      <c r="B72" s="19" t="n"/>
-      <c r="C72" s="19" t="n"/>
-      <c r="D72" s="19" t="n"/>
+      <c r="A72" s="20" t="inlineStr">
+        <is>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B72" s="19" t="inlineStr">
+        <is>
+          <t>谷物制品</t>
+        </is>
+      </c>
+      <c r="C72" s="19" t="inlineStr">
+        <is>
+          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
+        </is>
+      </c>
+      <c r="D72" s="19" t="inlineStr">
+        <is>
+          <t>粥类罐头</t>
+        </is>
+      </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>蛋及蛋制品</t>
+          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
       <c r="F72" s="19" t="inlineStr">
@@ -6219,9 +6195,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G72" s="19" t="inlineStr">
-        <is>
-          <t>0.2</t>
+      <c r="G72" s="30" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H72" s="19" t="n"/>
@@ -6238,17 +6214,21 @@
       </c>
     </row>
     <row r="73" ht="70" customHeight="1" s="23">
-      <c r="A73" s="19" t="inlineStr">
-        <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B73" s="19" t="n"/>
+      <c r="A73" s="20" t="inlineStr">
+        <is>
+          <t>豆类及其制品</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="inlineStr">
+        <is>
+          <t>豆类制品</t>
+        </is>
+      </c>
       <c r="C73" s="19" t="n"/>
       <c r="D73" s="19" t="n"/>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t>调味品(香辛料类除外)</t>
+          <t>豆类制品(豆浆除外)</t>
         </is>
       </c>
       <c r="F73" s="19" t="inlineStr">
@@ -6256,9 +6236,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G73" s="19" t="inlineStr">
-        <is>
-          <t>1.0</t>
+      <c r="G73" s="30" t="inlineStr">
+        <is>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H73" s="19" t="n"/>
@@ -6275,21 +6255,25 @@
       </c>
     </row>
     <row r="74" ht="28" customHeight="1" s="23">
-      <c r="A74" s="19" t="inlineStr">
-        <is>
-          <t>调味品</t>
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>豆类及其制品</t>
         </is>
       </c>
       <c r="B74" s="19" t="inlineStr">
         <is>
-          <t>香辛料类</t>
-        </is>
-      </c>
-      <c r="C74" s="19" t="n"/>
+          <t>豆类制品</t>
+        </is>
+      </c>
+      <c r="C74" s="19" t="inlineStr">
+        <is>
+          <t>非发酵豆制品（例如：豆浆、豆腐类、豆干类、腐竹类、熟制豆类、大豆蛋白膨化食品、大豆素肉等）</t>
+        </is>
+      </c>
       <c r="D74" s="19" t="n"/>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外)</t>
+          <t>豆浆</t>
         </is>
       </c>
       <c r="F74" s="19" t="inlineStr">
@@ -6297,9 +6281,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G74" s="19" t="inlineStr">
-        <is>
-          <t>1.5</t>
+      <c r="G74" s="30" t="inlineStr">
+        <is>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H74" s="19" t="n"/>
@@ -6308,11 +6292,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J74" s="19" t="inlineStr">
-        <is>
-          <t>b 新鲜香辛料(如姜、葱、蒜等)应按对应的新鲜蔬菜(或新鲜水果)类别执行。</t>
-        </is>
-      </c>
+      <c r="J74" s="19" t="n"/>
       <c r="K74" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6322,23 +6302,19 @@
     <row r="75">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>调味品</t>
+          <t>豆类及其制品</t>
         </is>
       </c>
       <c r="B75" s="19" t="inlineStr">
         <is>
-          <t>香辛料类</t>
-        </is>
-      </c>
-      <c r="C75" s="19" t="inlineStr">
-        <is>
-          <t>花椒、桂皮、肉桂、多种香辛料混合的香辛料</t>
-        </is>
-      </c>
+          <t>豆类（干豆、以干豆磨成的粉）</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="n"/>
       <c r="D75" s="19" t="n"/>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>花椒、桂皮、肉桂、多种香辛料混合的香辛料</t>
+          <t>豆类</t>
         </is>
       </c>
       <c r="F75" s="19" t="inlineStr">
@@ -6346,9 +6322,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G75" s="22" t="inlineStr">
-        <is>
-          <t>3.0</t>
+      <c r="G75" s="30" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H75" s="19" t="n"/>
@@ -6367,7 +6343,7 @@
     <row r="76" ht="42" customHeight="1" s="23">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>酒类</t>
         </is>
       </c>
       <c r="B76" s="19" t="n"/>
@@ -6375,7 +6351,7 @@
       <c r="D76" s="19" t="n"/>
       <c r="E76" s="19" t="inlineStr">
         <is>
-          <t>谷物及其制品(麦片、面筋、粥类罐头、带馅料面米制品除外)</t>
+          <t>酒类(白酒、黄酒除外)</t>
         </is>
       </c>
       <c r="F76" s="19" t="inlineStr">
@@ -6383,7 +6359,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G76" s="22" t="inlineStr">
+      <c r="G76" s="30" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
@@ -6394,11 +6370,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J76" s="19" t="inlineStr">
-        <is>
-          <t>a 稻谷以糙米计。</t>
-        </is>
-      </c>
+      <c r="J76" s="19" t="n"/>
       <c r="K76" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6408,23 +6380,23 @@
     <row r="77" ht="42" customHeight="1" s="23">
       <c r="A77" s="20" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>酒类</t>
         </is>
       </c>
       <c r="B77" s="19" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
+          <t>蒸馏酒（例如：白酒、白兰地、威士忌、伏特加、朗姆酒等）</t>
         </is>
       </c>
       <c r="C77" s="19" t="inlineStr">
         <is>
-          <t>麦片</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D77" s="19" t="n"/>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
+          <t>白酒、黄酒</t>
         </is>
       </c>
       <c r="F77" s="19" t="inlineStr">
@@ -6432,7 +6404,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G77" s="22" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -6453,27 +6425,23 @@
     <row r="78" ht="56" customHeight="1" s="23">
       <c r="A78" s="20" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>酒类</t>
         </is>
       </c>
       <c r="B78" s="19" t="inlineStr">
         <is>
-          <t>谷物制品</t>
+          <t>发酵酒(例如:葡萄酒、黄酒、果酒、啤酒等)</t>
         </is>
       </c>
       <c r="C78" s="19" t="inlineStr">
         <is>
-          <t>小麦粉制品</t>
-        </is>
-      </c>
-      <c r="D78" s="19" t="inlineStr">
-        <is>
-          <t>面筋</t>
-        </is>
-      </c>
+          <t>黄酒</t>
+        </is>
+      </c>
+      <c r="D78" s="19" t="n"/>
       <c r="E78" s="19" t="inlineStr">
         <is>
-          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
+          <t>白酒、黄酒</t>
         </is>
       </c>
       <c r="F78" s="19" t="inlineStr">
@@ -6502,27 +6470,15 @@
     <row r="79" ht="56" customHeight="1" s="23">
       <c r="A79" s="20" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B79" s="19" t="inlineStr">
-        <is>
-          <t>谷物制品</t>
-        </is>
-      </c>
-      <c r="C79" s="19" t="inlineStr">
-        <is>
-          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
-        </is>
-      </c>
-      <c r="D79" s="19" t="inlineStr">
-        <is>
-          <t>粥类罐头</t>
-        </is>
-      </c>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="n"/>
+      <c r="C79" s="19" t="n"/>
+      <c r="D79" s="19" t="n"/>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F79" s="19" t="inlineStr">
@@ -6551,19 +6507,23 @@
     <row r="80" ht="56" customHeight="1" s="23">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>豆类及其制品</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B80" s="19" t="inlineStr">
         <is>
-          <t>豆类制品</t>
-        </is>
-      </c>
-      <c r="C80" s="19" t="n"/>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C80" s="19" t="inlineStr">
+        <is>
+          <t>双孢菇</t>
+        </is>
+      </c>
       <c r="D80" s="19" t="n"/>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>豆类制品(豆浆除外)</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F80" s="19" t="inlineStr">
@@ -6573,7 +6533,7 @@
       </c>
       <c r="G80" s="30" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H80" s="19" t="n"/>
@@ -6592,23 +6552,23 @@
     <row r="81" ht="56" customHeight="1" s="23">
       <c r="A81" s="20" t="inlineStr">
         <is>
-          <t>豆类及其制品</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B81" s="19" t="inlineStr">
         <is>
-          <t>豆类制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C81" s="19" t="inlineStr">
         <is>
-          <t>非发酵豆制品（例如：豆浆、豆腐类、豆干类、腐竹类、熟制豆类、大豆蛋白膨化食品、大豆素肉等）</t>
+          <t>平菇</t>
         </is>
       </c>
       <c r="D81" s="19" t="n"/>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>豆浆</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F81" s="19" t="inlineStr">
@@ -6618,7 +6578,7 @@
       </c>
       <c r="G81" s="30" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H81" s="19" t="n"/>
@@ -6637,19 +6597,23 @@
     <row r="82" ht="56" customHeight="1" s="23">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>豆类及其制品</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B82" s="19" t="inlineStr">
         <is>
-          <t>豆类（干豆、以干豆磨成的粉）</t>
-        </is>
-      </c>
-      <c r="C82" s="19" t="n"/>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C82" s="19" t="inlineStr">
+        <is>
+          <t>香菇</t>
+        </is>
+      </c>
       <c r="D82" s="19" t="n"/>
       <c r="E82" s="19" t="inlineStr">
         <is>
-          <t>豆类</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F82" s="19" t="inlineStr">
@@ -6659,7 +6623,7 @@
       </c>
       <c r="G82" s="30" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H82" s="19" t="n"/>
@@ -6678,15 +6642,23 @@
     <row r="83" ht="56" customHeight="1" s="23">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>酒类</t>
-        </is>
-      </c>
-      <c r="B83" s="19" t="n"/>
-      <c r="C83" s="19" t="n"/>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B83" s="19" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C83" s="19" t="inlineStr">
+        <is>
+          <t>榛蘑</t>
+        </is>
+      </c>
       <c r="D83" s="19" t="n"/>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t>酒类(白酒、黄酒除外)</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F83" s="19" t="inlineStr">
@@ -6696,7 +6668,7 @@
       </c>
       <c r="G83" s="30" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H83" s="19" t="n"/>
@@ -6715,23 +6687,15 @@
     <row r="84" ht="56" customHeight="1" s="23">
       <c r="A84" s="20" t="inlineStr">
         <is>
-          <t>酒类</t>
-        </is>
-      </c>
-      <c r="B84" s="19" t="inlineStr">
-        <is>
-          <t>蒸馏酒（例如：白酒、白兰地、威士忌、伏特加、朗姆酒等）</t>
-        </is>
-      </c>
-      <c r="C84" s="19" t="inlineStr">
-        <is>
-          <t>白酒</t>
-        </is>
-      </c>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B84" s="19" t="n"/>
+      <c r="C84" s="19" t="n"/>
       <c r="D84" s="19" t="n"/>
       <c r="E84" s="19" t="inlineStr">
         <is>
-          <t>白酒、黄酒</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F84" s="19" t="inlineStr">
@@ -6760,23 +6724,23 @@
     <row r="85" ht="56" customHeight="1" s="23">
       <c r="A85" s="20" t="inlineStr">
         <is>
-          <t>酒类</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B85" s="19" t="inlineStr">
         <is>
-          <t>发酵酒(例如:葡萄酒、黄酒、果酒、啤酒等)</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C85" s="19" t="inlineStr">
         <is>
-          <t>黄酒</t>
+          <t>松茸</t>
         </is>
       </c>
       <c r="D85" s="19" t="n"/>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>白酒、黄酒</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F85" s="19" t="inlineStr">
@@ -6784,7 +6748,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G85" s="30" t="inlineStr">
+      <c r="G85" s="22" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -6808,8 +6772,16 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B86" s="19" t="n"/>
-      <c r="C86" s="19" t="n"/>
+      <c r="B86" s="19" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C86" s="19" t="inlineStr">
+        <is>
+          <t>松露</t>
+        </is>
+      </c>
       <c r="D86" s="19" t="n"/>
       <c r="E86" s="19" t="inlineStr">
         <is>
@@ -6821,7 +6793,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G86" s="30" t="inlineStr">
+      <c r="G86" s="22" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -6850,12 +6822,12 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C87" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇</t>
-        </is>
-      </c>
-      <c r="D87" s="19" t="n"/>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>青头菌</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="n"/>
       <c r="E87" s="19" t="inlineStr">
         <is>
           <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
@@ -6866,7 +6838,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G87" s="30" t="inlineStr">
+      <c r="G87" s="22" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -6885,7 +6857,7 @@
       </c>
     </row>
     <row r="88" ht="56" customHeight="1" s="23">
-      <c r="A88" s="20" t="inlineStr">
+      <c r="A88" s="19" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
@@ -6897,7 +6869,7 @@
       </c>
       <c r="C88" s="19" t="inlineStr">
         <is>
-          <t>平菇</t>
+          <t>鸡枞</t>
         </is>
       </c>
       <c r="D88" s="19" t="n"/>
@@ -6911,7 +6883,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G88" s="30" t="inlineStr">
+      <c r="G88" s="19" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -6942,7 +6914,7 @@
       </c>
       <c r="C89" s="19" t="inlineStr">
         <is>
-          <t>香菇</t>
+          <t>鸡油菌</t>
         </is>
       </c>
       <c r="D89" s="19" t="n"/>
@@ -6956,7 +6928,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G89" s="30" t="inlineStr">
+      <c r="G89" s="25" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -6987,7 +6959,7 @@
       </c>
       <c r="C90" s="19" t="inlineStr">
         <is>
-          <t>榛蘑</t>
+          <t>多汁乳菇</t>
         </is>
       </c>
       <c r="D90" s="19" t="n"/>
@@ -7001,7 +6973,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G90" s="30" t="inlineStr">
+      <c r="G90" s="25" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -7038,7 +7010,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G91" s="30" t="inlineStr">
+      <c r="G91" s="25" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -7069,7 +7041,7 @@
       </c>
       <c r="C92" s="19" t="inlineStr">
         <is>
-          <t>松茸</t>
+          <t>银耳</t>
         </is>
       </c>
       <c r="D92" s="19" t="n"/>
@@ -7083,7 +7055,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G92" s="22" t="inlineStr">
+      <c r="G92" s="25" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -7114,13 +7086,13 @@
       </c>
       <c r="C93" s="19" t="inlineStr">
         <is>
-          <t>松露</t>
+          <t>双孢菇</t>
         </is>
       </c>
       <c r="D93" s="19" t="n"/>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F93" s="19" t="inlineStr">
@@ -7128,9 +7100,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G93" s="22" t="inlineStr">
-        <is>
-          <t>0.5</t>
+      <c r="G93" s="25" t="inlineStr">
+        <is>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H93" s="19" t="n"/>
@@ -7157,15 +7129,15 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>青头菌</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="n"/>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t>双孢菇</t>
+        </is>
+      </c>
+      <c r="D94" s="19" t="n"/>
       <c r="E94" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F94" s="19" t="inlineStr">
@@ -7173,9 +7145,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G94" s="22" t="inlineStr">
-        <is>
-          <t>0.5</t>
+      <c r="G94" s="25" t="inlineStr">
+        <is>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H94" s="19" t="n"/>
@@ -7192,7 +7164,7 @@
       </c>
     </row>
     <row r="95" ht="56" customHeight="1" s="23">
-      <c r="A95" s="19" t="inlineStr">
+      <c r="A95" s="20" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
@@ -7204,13 +7176,13 @@
       </c>
       <c r="C95" s="19" t="inlineStr">
         <is>
-          <t>鸡枞</t>
+          <t>双孢菇</t>
         </is>
       </c>
       <c r="D95" s="19" t="n"/>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F95" s="19" t="inlineStr">
@@ -7218,9 +7190,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G95" s="19" t="inlineStr">
-        <is>
-          <t>0.5</t>
+      <c r="G95" s="25" t="inlineStr">
+        <is>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H95" s="19" t="n"/>
@@ -7249,13 +7221,13 @@
       </c>
       <c r="C96" s="19" t="inlineStr">
         <is>
-          <t>鸡油菌</t>
+          <t>双孢菇</t>
         </is>
       </c>
       <c r="D96" s="19" t="n"/>
       <c r="E96" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F96" s="19" t="inlineStr">
@@ -7265,7 +7237,7 @@
       </c>
       <c r="G96" s="25" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H96" s="19" t="n"/>
@@ -7294,13 +7266,13 @@
       </c>
       <c r="C97" s="19" t="inlineStr">
         <is>
-          <t>多汁乳菇</t>
+          <t>木耳 （毛木耳,黑木耳）</t>
         </is>
       </c>
       <c r="D97" s="19" t="n"/>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F97" s="19" t="inlineStr">
@@ -7310,7 +7282,7 @@
       </c>
       <c r="G97" s="25" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H97" s="19" t="n"/>
@@ -7327,17 +7299,24 @@
       </c>
     </row>
     <row r="98" ht="56" customHeight="1" s="23">
-      <c r="A98" s="20" t="inlineStr">
+      <c r="A98" s="19" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B98" s="19" t="n"/>
-      <c r="C98" s="19" t="n"/>
-      <c r="D98" s="19" t="n"/>
+      <c r="B98" s="0" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>木耳 （毛木耳,黑木耳）</t>
+        </is>
+      </c>
       <c r="E98" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F98" s="19" t="inlineStr">
@@ -7345,9 +7324,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G98" s="25" t="inlineStr">
-        <is>
-          <t>0.5</t>
+      <c r="G98" s="19" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H98" s="19" t="n"/>
@@ -7374,15 +7353,14 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C99" s="19" t="inlineStr">
-        <is>
-          <t>银耳</t>
-        </is>
-      </c>
-      <c r="D99" s="19" t="n"/>
-      <c r="E99" s="19" t="inlineStr">
-        <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F99" s="19" t="inlineStr">
@@ -7390,12 +7368,11 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G99" s="25" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H99" s="19" t="n"/>
+      <c r="G99" s="19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="I99" s="19" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -7419,15 +7396,14 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C100" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇</t>
-        </is>
-      </c>
-      <c r="D100" s="19" t="n"/>
-      <c r="E100" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="E100" s="0" t="inlineStr">
+        <is>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F100" s="19" t="inlineStr">
@@ -7435,12 +7411,11 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G100" s="25" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="H100" s="19" t="n"/>
+      <c r="G100" s="31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="I100" s="19" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -7464,28 +7439,26 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C101" s="0" t="inlineStr">
-        <is>
-          <t>双孢菇</t>
-        </is>
-      </c>
-      <c r="D101" s="19" t="n"/>
-      <c r="E101" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F101" s="19" t="inlineStr">
+      <c r="C101" s="27" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="E101" s="27" t="inlineStr">
+        <is>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+        </is>
+      </c>
+      <c r="F101" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G101" s="25" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="H101" s="19" t="n"/>
+      <c r="G101" s="30" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="I101" s="19" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -7499,308 +7472,270 @@
       </c>
     </row>
     <row r="102" ht="56" customHeight="1" s="23">
-      <c r="A102" s="20" t="inlineStr">
+      <c r="A102" s="0" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B102" s="19" t="inlineStr">
+      <c r="B102" s="0" t="inlineStr">
         <is>
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C102" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇</t>
-        </is>
-      </c>
-      <c r="D102" s="19" t="n"/>
-      <c r="E102" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F102" s="19" t="inlineStr">
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="E102" s="0" t="inlineStr">
+        <is>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+        </is>
+      </c>
+      <c r="F102" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G102" s="25" t="inlineStr">
+      <c r="G102" s="0" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I102" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K102" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="42" customHeight="1" s="23">
+      <c r="A103" s="0" t="inlineStr">
+        <is>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B103" s="0" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="E103" s="0" t="inlineStr">
+        <is>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+        </is>
+      </c>
+      <c r="F103" s="0" t="inlineStr">
+        <is>
+          <t>铅</t>
+        </is>
+      </c>
+      <c r="G103" s="0" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I103" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K103" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="56" customHeight="1" s="23">
+      <c r="A104" s="0" t="inlineStr">
+        <is>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B104" s="0" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="E104" s="0" t="inlineStr">
+        <is>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+        </is>
+      </c>
+      <c r="F104" s="0" t="inlineStr">
+        <is>
+          <t>铅</t>
+        </is>
+      </c>
+      <c r="G104" s="0" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I104" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K104" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="42" customHeight="1" s="23">
+      <c r="A105" s="0" t="inlineStr">
+        <is>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="B105" s="0" t="n"/>
+      <c r="E105" s="0" t="inlineStr">
+        <is>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="F105" s="0" t="inlineStr">
+        <is>
+          <t>铅</t>
+        </is>
+      </c>
+      <c r="G105" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I105" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K105" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="28" customHeight="1" s="23">
+      <c r="A106" s="0" t="inlineStr">
+        <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="E106" s="0" t="inlineStr">
+        <is>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+        </is>
+      </c>
+      <c r="F106" s="0" t="inlineStr">
+        <is>
+          <t>铅</t>
+        </is>
+      </c>
+      <c r="G106" s="0" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="H102" s="19" t="n"/>
-      <c r="I102" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J102" s="19" t="n"/>
-      <c r="K102" s="19" t="inlineStr">
+      <c r="I106" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K106" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="42" customHeight="1" s="23">
-      <c r="A103" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B103" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C103" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇</t>
-        </is>
-      </c>
-      <c r="D103" s="19" t="n"/>
-      <c r="E103" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F103" s="19" t="inlineStr">
+    <row r="107" ht="28" customHeight="1" s="23">
+      <c r="A107" s="0" t="inlineStr">
+        <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B107" s="0" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="E107" s="0" t="inlineStr">
+        <is>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+        </is>
+      </c>
+      <c r="F107" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G103" s="25" t="inlineStr">
+      <c r="G107" s="0" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="H103" s="19" t="n"/>
-      <c r="I103" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J103" s="19" t="n"/>
-      <c r="K103" s="19" t="inlineStr">
+      <c r="I107" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K107" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="56" customHeight="1" s="23">
-      <c r="A104" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B104" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C104" s="19" t="inlineStr">
-        <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
-      <c r="D104" s="19" t="n"/>
-      <c r="E104" s="19" t="inlineStr">
-        <is>
-          <t>木耳及其制品、银耳及其制品</t>
-        </is>
-      </c>
-      <c r="F104" s="19" t="inlineStr">
+    <row r="108" ht="27" customHeight="1" s="23">
+      <c r="A108" s="0" t="inlineStr">
+        <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B108" s="0" t="inlineStr">
+        <is>
+          <t>蛋白饮料</t>
+        </is>
+      </c>
+      <c r="C108" s="0" t="inlineStr">
+        <is>
+          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
+        </is>
+      </c>
+      <c r="E108" s="0" t="inlineStr">
+        <is>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+        </is>
+      </c>
+      <c r="F108" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G104" s="25" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="H104" s="19" t="n"/>
-      <c r="I104" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J104" s="19" t="n"/>
-      <c r="K104" s="19" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="42" customHeight="1" s="23">
-      <c r="A105" s="19" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B105" s="0" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C105" s="0" t="inlineStr">
-        <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
-      <c r="E105" s="19" t="inlineStr">
-        <is>
-          <t>木耳及其制品、银耳及其制品</t>
-        </is>
-      </c>
-      <c r="F105" s="19" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G105" s="19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="H105" s="19" t="n"/>
-      <c r="I105" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J105" s="19" t="n"/>
-      <c r="K105" s="19" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="28" customHeight="1" s="23">
-      <c r="A106" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B106" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C106" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
-        </is>
-      </c>
-      <c r="E106" s="0" t="inlineStr">
-        <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F106" s="19" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G106" s="19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I106" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J106" s="19" t="n"/>
-      <c r="K106" s="19" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="28" customHeight="1" s="23">
-      <c r="A107" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B107" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C107" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
-        </is>
-      </c>
-      <c r="E107" s="0" t="inlineStr">
-        <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F107" s="19" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G107" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I107" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J107" s="19" t="n"/>
-      <c r="K107" s="19" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="27" customHeight="1" s="23">
-      <c r="A108" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B108" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C108" s="27" t="inlineStr">
-        <is>
-          <t>松茸</t>
-        </is>
-      </c>
-      <c r="E108" s="27" t="inlineStr">
-        <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F108" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G108" s="30" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I108" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J108" s="19" t="n"/>
-      <c r="K108" s="19" t="inlineStr">
+      <c r="G108" s="0" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I108" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K108" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
@@ -7809,22 +7744,17 @@
     <row r="109" ht="27" customHeight="1" s="23">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C109" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
         </is>
       </c>
       <c r="E109" s="0" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
         </is>
       </c>
       <c r="F109" s="0" t="inlineStr">
@@ -7834,7 +7764,7 @@
       </c>
       <c r="G109" s="0" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I109" s="0" t="inlineStr">
@@ -7851,22 +7781,12 @@
     <row r="110" ht="42" customHeight="1" s="23">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B110" s="0" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C110" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="E110" s="0" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
         </is>
       </c>
       <c r="F110" s="0" t="inlineStr">
@@ -7876,7 +7796,7 @@
       </c>
       <c r="G110" s="0" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I110" s="0" t="inlineStr">
@@ -7893,22 +7813,17 @@
     <row r="111" ht="28" customHeight="1" s="23">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C111" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
         </is>
       </c>
       <c r="E111" s="0" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外)</t>
         </is>
       </c>
       <c r="F111" s="0" t="inlineStr">
@@ -7918,7 +7833,7 @@
       </c>
       <c r="G111" s="0" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I111" s="0" t="inlineStr">
@@ -7935,13 +7850,12 @@
     <row r="112" ht="42" customHeight="1" s="23">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="B112" s="0" t="n"/>
+          <t>饮料类</t>
+        </is>
+      </c>
       <c r="E112" s="0" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
+          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
         </is>
       </c>
       <c r="F112" s="0" t="inlineStr">
@@ -7951,7 +7865,7 @@
       </c>
       <c r="G112" s="0" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I112" s="0" t="inlineStr">
@@ -7973,7 +7887,7 @@
       </c>
       <c r="E113" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
         </is>
       </c>
       <c r="F113" s="0" t="inlineStr">
@@ -7983,7 +7897,7 @@
       </c>
       <c r="G113" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I113" s="0" t="inlineStr">
@@ -8003,14 +7917,9 @@
           <t>饮料类</t>
         </is>
       </c>
-      <c r="B114" s="0" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
       <c r="E114" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
         </is>
       </c>
       <c r="F114" s="0" t="inlineStr">
@@ -8020,7 +7929,7 @@
       </c>
       <c r="G114" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="I114" s="0" t="inlineStr">
@@ -8040,19 +7949,9 @@
           <t>饮料类</t>
         </is>
       </c>
-      <c r="B115" s="0" t="inlineStr">
-        <is>
-          <t>蛋白饮料</t>
-        </is>
-      </c>
-      <c r="C115" s="0" t="inlineStr">
-        <is>
-          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
-        </is>
-      </c>
       <c r="E115" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
         </is>
       </c>
       <c r="F115" s="0" t="inlineStr">
@@ -8062,7 +7961,7 @@
       </c>
       <c r="G115" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="I115" s="0" t="inlineStr">
@@ -8082,14 +7981,9 @@
           <t>饮料类</t>
         </is>
       </c>
-      <c r="B116" s="0" t="inlineStr">
-        <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
-        </is>
-      </c>
       <c r="E116" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>饮料类(葡萄汁)</t>
         </is>
       </c>
       <c r="F116" s="0" t="inlineStr">
@@ -8099,7 +7993,7 @@
       </c>
       <c r="G116" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="I116" s="0" t="inlineStr">
@@ -8121,7 +8015,7 @@
       </c>
       <c r="E117" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>饮料类(固体饮料)</t>
         </is>
       </c>
       <c r="F117" s="0" t="inlineStr">
@@ -8131,7 +8025,7 @@
       </c>
       <c r="G117" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I117" s="0" t="inlineStr">
@@ -8153,12 +8047,12 @@
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="E118" s="0" t="inlineStr">
         <is>
-          <t>果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外)</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="F118" s="0" t="inlineStr">
@@ -8168,7 +8062,7 @@
       </c>
       <c r="G118" s="0" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="I118" s="0" t="inlineStr">
@@ -8176,9 +8070,9 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="K118" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
+      <c r="K118" s="28" t="inlineStr">
+        <is>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
@@ -8188,9 +8082,19 @@
           <t>饮料类</t>
         </is>
       </c>
+      <c r="B119" s="0" t="inlineStr">
+        <is>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
+        </is>
+      </c>
+      <c r="C119" s="0" t="inlineStr">
+        <is>
+          <t>浓缩果蔬汁（浆）</t>
+        </is>
+      </c>
       <c r="E119" s="0" t="inlineStr">
         <is>
-          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
+          <t>浓缩果蔬汁(浆)</t>
         </is>
       </c>
       <c r="F119" s="0" t="inlineStr">
@@ -8200,7 +8104,7 @@
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I119" s="0" t="inlineStr">
@@ -8220,9 +8124,19 @@
           <t>饮料类</t>
         </is>
       </c>
+      <c r="B120" s="0" t="inlineStr">
+        <is>
+          <t>蛋白饮料</t>
+        </is>
+      </c>
+      <c r="C120" s="0" t="inlineStr">
+        <is>
+          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
+        </is>
+      </c>
       <c r="E120" s="0" t="inlineStr">
         <is>
-          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
+          <t>含乳饮料</t>
         </is>
       </c>
       <c r="F120" s="0" t="inlineStr">
@@ -8232,7 +8146,7 @@
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="I120" s="0" t="inlineStr">
@@ -8249,12 +8163,27 @@
     <row r="121">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t>饮料类</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B121" s="0" t="inlineStr">
+        <is>
+          <t>谷物制品</t>
+        </is>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
+        </is>
+      </c>
+      <c r="D121" s="0" t="inlineStr">
+        <is>
+          <t>带馅料面米制品</t>
         </is>
       </c>
       <c r="E121" s="0" t="inlineStr">
         <is>
-          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
+          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
       <c r="F121" s="0" t="inlineStr">
@@ -8264,7 +8193,7 @@
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I121" s="0" t="inlineStr">
@@ -8273,270 +8202,6 @@
         </is>
       </c>
       <c r="K121" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="E122" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
-        </is>
-      </c>
-      <c r="F122" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G122" s="0" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="I122" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K122" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="E123" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(葡萄汁)</t>
-        </is>
-      </c>
-      <c r="F123" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G123" s="0" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="I123" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K123" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="E124" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(固体饮料)</t>
-        </is>
-      </c>
-      <c r="F124" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G124" s="0" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I124" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K124" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B125" s="0" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="E125" s="0" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="F125" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G125" s="0" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="I125" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K125" s="28" t="inlineStr">
-        <is>
-          <t>GB 8538</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B126" s="0" t="inlineStr">
-        <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
-        </is>
-      </c>
-      <c r="C126" s="0" t="inlineStr">
-        <is>
-          <t>浓缩果蔬汁（浆）</t>
-        </is>
-      </c>
-      <c r="E126" s="0" t="inlineStr">
-        <is>
-          <t>浓缩果蔬汁(浆)</t>
-        </is>
-      </c>
-      <c r="F126" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G126" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I126" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K126" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B127" s="0" t="inlineStr">
-        <is>
-          <t>蛋白饮料</t>
-        </is>
-      </c>
-      <c r="C127" s="0" t="inlineStr">
-        <is>
-          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
-        </is>
-      </c>
-      <c r="E127" s="0" t="inlineStr">
-        <is>
-          <t>含乳饮料</t>
-        </is>
-      </c>
-      <c r="F127" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G127" s="0" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="I127" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K127" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="0" t="inlineStr">
-        <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B128" s="0" t="inlineStr">
-        <is>
-          <t>谷物制品</t>
-        </is>
-      </c>
-      <c r="C128" s="0" t="inlineStr">
-        <is>
-          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
-        </is>
-      </c>
-      <c r="D128" s="0" t="inlineStr">
-        <is>
-          <t>带馅料面米制品</t>
-        </is>
-      </c>
-      <c r="E128" s="0" t="inlineStr">
-        <is>
-          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
-        </is>
-      </c>
-      <c r="F128" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G128" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I128" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K128" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
@@ -8558,7 +8223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -11036,22 +10701,18 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="inlineStr">
-        <is>
-          <t>软体动物</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>腹足类</t>
-        </is>
-      </c>
+          <t>水产制品</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>水产品罐头</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>双壳贝类、腹足类、头足类、棘皮类</t>
+          <t>鱼类罐头</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -11061,14 +10722,10 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>去除内脏</t>
-        </is>
-      </c>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="n"/>
       <c r="I57" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -11089,22 +10746,18 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="inlineStr">
-        <is>
-          <t>软体动物</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>头足类</t>
-        </is>
-      </c>
+          <t>水产制品</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>其他鱼类制品</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>双壳贝类、腹足类、头足类、棘皮类</t>
+          <t>其他鱼类制品</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -11114,14 +10767,10 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>去除内脏</t>
-        </is>
-      </c>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="n"/>
       <c r="I58" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -11137,23 +10786,15 @@
     <row r="59" ht="42" customHeight="1" s="23">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>棘皮类</t>
-        </is>
-      </c>
+          <t>蛋及蛋制品</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>双壳贝类、腹足类、头足类、棘皮类</t>
+          <t>蛋及蛋制品</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -11163,14 +10804,10 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>去除内脏</t>
-        </is>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="n"/>
       <c r="I59" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -11186,23 +10823,19 @@
     <row r="60" ht="42" customHeight="1" s="23">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>调味品</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>水产品罐头</t>
-        </is>
-      </c>
+          <t>食用盐</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n"/>
       <c r="D60" s="4" t="n"/>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>鱼类罐头</t>
+          <t>食用盐</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
@@ -11212,7 +10845,7 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H60" s="4" t="n"/>
@@ -11231,23 +10864,23 @@
     <row r="61" ht="42" customHeight="1" s="23">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>调味品</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>水产制品</t>
+          <t>水产调味品</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>其他鱼类制品</t>
+          <t>鱼类调味品（例如：鱼露等）</t>
         </is>
       </c>
       <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>其他鱼类制品</t>
+          <t>鱼类调味品</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -11276,15 +10909,19 @@
     <row r="62" ht="42" customHeight="1" s="23">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>蛋及蛋制品</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="n"/>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
       <c r="C62" s="4" t="n"/>
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>蛋及蛋制品</t>
+          <t>包装饮用水(饮用天然矿泉水除外)</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
@@ -11294,38 +10931,42 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="H62" s="4" t="n"/>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>GB 5009.15</t>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
     <row r="63" ht="42" customHeight="1" s="23">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>调味品</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>食用盐</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="n"/>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>饮用天然矿泉水</t>
+        </is>
+      </c>
       <c r="D63" s="4" t="n"/>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>食用盐</t>
+          <t>饮用天然矿泉水</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -11335,42 +10976,42 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="H63" s="4" t="n"/>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>GB 5009.15</t>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
     <row r="64" ht="42" customHeight="1" s="23">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>调味品</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>水产调味品</t>
+          <t>婴幼儿辅助食品</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>鱼类调味品（例如：鱼露等）</t>
+          <t>婴幼儿谷类辅助食品</t>
         </is>
       </c>
       <c r="D64" s="4" t="n"/>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>鱼类调味品</t>
+          <t>婴幼儿谷类辅助食品</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
@@ -11380,7 +11021,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="H64" s="4" t="n"/>
@@ -11397,214 +11038,85 @@
       </c>
     </row>
     <row r="65" ht="42" customHeight="1" s="23">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="n"/>
-      <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水(饮用天然矿泉水除外)</t>
-        </is>
-      </c>
-      <c r="F65" s="12" t="inlineStr">
+      <c r="A65" s="0" t="inlineStr">
+        <is>
+          <t>肉及肉制品</t>
+        </is>
+      </c>
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>肉类（生鲜肉、冷却肉、冷冻肉等）</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr"/>
+      <c r="D65" s="0" t="inlineStr"/>
+      <c r="E65" s="0" t="inlineStr">
+        <is>
+          <t>肉类(畜禽内脏除外)</t>
+        </is>
+      </c>
+      <c r="F65" s="0" t="inlineStr">
         <is>
           <t>镉</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>0.005</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="n"/>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>GB 8538</t>
+      <c r="G65" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H65" s="0" t="inlineStr"/>
+      <c r="I65" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J65" s="0" t="inlineStr"/>
+      <c r="K65" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.15</t>
         </is>
       </c>
     </row>
     <row r="66" ht="56" customHeight="1" s="23">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>饮用天然矿泉水</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="n"/>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>饮用天然矿泉水</t>
-        </is>
-      </c>
-      <c r="F66" s="12" t="inlineStr">
+      <c r="A66" s="0" t="inlineStr">
+        <is>
+          <t>肉及肉制品</t>
+        </is>
+      </c>
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t>肉制品（包括内脏制品、血制品）</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="inlineStr"/>
+      <c r="D66" s="0" t="inlineStr"/>
+      <c r="E66" s="0" t="inlineStr">
+        <is>
+          <t>肉制品(畜禽内脏制品除外)</t>
+        </is>
+      </c>
+      <c r="F66" s="0" t="inlineStr">
         <is>
           <t>镉</t>
         </is>
       </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="n"/>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="J66" s="4" t="n"/>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>GB 8538</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="56" customHeight="1" s="23">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>特殊膳食用食品</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿谷类辅助食品</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿谷类辅助食品</t>
-        </is>
-      </c>
-      <c r="F67" s="12" t="inlineStr">
-        <is>
-          <t>镉</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J67" s="4" t="n"/>
-      <c r="K67" s="4" t="inlineStr">
+      <c r="G66" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H66" s="0" t="inlineStr"/>
+      <c r="I66" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J66" s="0" t="inlineStr"/>
+      <c r="K66" s="0" t="inlineStr">
         <is>
           <t>GB 5009.15</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="56" customHeight="1" s="23">
-      <c r="A68" s="0" t="inlineStr">
-        <is>
-          <t>肉及肉制品</t>
-        </is>
-      </c>
-      <c r="B68" s="0" t="inlineStr">
-        <is>
-          <t>肉类（生鲜肉、冷却肉、冷冻肉等）</t>
-        </is>
-      </c>
-      <c r="C68" s="0" t="inlineStr"/>
-      <c r="D68" s="0" t="inlineStr"/>
-      <c r="E68" s="0" t="inlineStr">
-        <is>
-          <t>肉类(畜禽内脏除外)</t>
-        </is>
-      </c>
-      <c r="F68" s="0" t="inlineStr">
-        <is>
-          <t>镉</t>
-        </is>
-      </c>
-      <c r="G68" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H68" s="0" t="inlineStr"/>
-      <c r="I68" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J68" s="0" t="inlineStr"/>
-      <c r="K68" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="0" t="inlineStr">
-        <is>
-          <t>肉及肉制品</t>
-        </is>
-      </c>
-      <c r="B69" s="0" t="inlineStr">
-        <is>
-          <t>肉制品（包括内脏制品、血制品）</t>
-        </is>
-      </c>
-      <c r="C69" s="0" t="inlineStr"/>
-      <c r="D69" s="0" t="inlineStr"/>
-      <c r="E69" s="0" t="inlineStr">
-        <is>
-          <t>肉制品(畜禽内脏制品除外)</t>
-        </is>
-      </c>
-      <c r="F69" s="0" t="inlineStr">
-        <is>
-          <t>镉</t>
-        </is>
-      </c>
-      <c r="G69" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H69" s="0" t="inlineStr"/>
-      <c r="I69" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J69" s="0" t="inlineStr"/>
-      <c r="K69" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.15</t>
-        </is>
-      </c>
-    </row>
+    <row r="67" ht="56" customHeight="1" s="23"/>
+    <row r="68" ht="56" customHeight="1" s="23"/>
   </sheetData>
   <autoFilter ref="A4:K68"/>
   <mergeCells count="1">
@@ -11620,7 +11132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -11796,11 +11308,19 @@
           <t>鲜、冻水产动物</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>鱼类</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>肉食性鱼类</t>
+        </is>
+      </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品(肉食性鱼类及其制品除外)</t>
+          <t>肉食性鱼类及其制品(金枪鱼、金目鲷、枪鱼、鲨鱼及以上鱼类的制品除外)</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -11837,11 +11357,19 @@
           <t>鲜、冻水产动物</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>鱼类</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>肉食性鱼类</t>
+        </is>
+      </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品(肉食性鱼类及其制品除外)</t>
+          <t>肉食性鱼类及其制品(金枪鱼、金目鲷、枪鱼、鲨鱼及以上鱼类的制品除外)</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -11851,7 +11379,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H8" s="4" t="n"/>
@@ -11879,14 +11407,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
+          <t>鲜、冻水产动物</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>鱼类</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>肉食性鱼类</t>
+        </is>
+      </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品(肉食性鱼类及其制品除外)</t>
+          <t>金枪鱼及其制品</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -11920,14 +11456,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
+          <t>鲜、冻水产动物</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>鱼类</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>肉食性鱼类</t>
+        </is>
+      </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品(肉食性鱼类及其制品除外)</t>
+          <t>金枪鱼及其制品</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -11937,7 +11481,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="H10" s="4" t="n"/>
@@ -11973,10 +11517,14 @@
           <t>鱼类</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>肉食性鱼类</t>
+        </is>
+      </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品(肉食性鱼类及其制品除外)</t>
+          <t>金目鲷及其制品</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -12018,10 +11566,14 @@
           <t>鱼类</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>肉食性鱼类</t>
+        </is>
+      </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品(肉食性鱼类及其制品除外)</t>
+          <t>金目鲷及其制品</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -12031,7 +11583,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H12" s="4" t="n"/>
@@ -12074,7 +11626,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>肉食性鱼类及其制品(金枪鱼、金目鲷、枪鱼、鲨鱼及以上鱼类的制品除外)</t>
+          <t>枪鱼及其制品</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -12123,7 +11675,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>肉食性鱼类及其制品(金枪鱼、金目鲷、枪鱼、鲨鱼及以上鱼类的制品除外)</t>
+          <t>枪鱼及其制品</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -12133,7 +11685,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="H14" s="4" t="n"/>
@@ -12176,7 +11728,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>金枪鱼及其制品</t>
+          <t>鲨鱼及其制品</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -12225,7 +11777,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>金枪鱼及其制品</t>
+          <t>鲨鱼及其制品</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -12235,7 +11787,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H16" s="4" t="n"/>
@@ -12258,27 +11810,19 @@
     <row r="17" ht="28" customHeight="1" s="23">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>肉食性鱼类</t>
-        </is>
-      </c>
+          <t>谷物</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>金目鲷及其制品</t>
+          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -12288,7 +11832,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H17" s="4" t="n"/>
@@ -12297,7 +11841,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12307,27 +11855,19 @@
     <row r="18" ht="28" customHeight="1" s="23">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>肉食性鱼类</t>
-        </is>
-      </c>
+          <t>谷物</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>金目鲷及其制品</t>
+          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -12337,7 +11877,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H18" s="4" t="n"/>
@@ -12346,11 +11886,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12360,27 +11896,19 @@
     <row r="19" ht="28" customHeight="1" s="23">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>肉食性鱼类</t>
-        </is>
-      </c>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>枪鱼及其制品</t>
+          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -12390,7 +11918,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H19" s="4" t="n"/>
@@ -12399,7 +11927,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n"/>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12409,27 +11941,19 @@
     <row r="20" ht="28" customHeight="1" s="23">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>肉食性鱼类</t>
-        </is>
-      </c>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>枪鱼及其制品</t>
+          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -12439,7 +11963,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" s="4" t="n"/>
@@ -12450,7 +11974,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -12462,27 +11986,19 @@
     <row r="21" ht="28" customHeight="1" s="23">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>肉食性鱼类</t>
-        </is>
-      </c>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>鲨鱼及其制品</t>
+          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -12492,7 +12008,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H21" s="4" t="n"/>
@@ -12501,7 +12017,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12511,27 +12031,19 @@
     <row r="22" ht="28" customHeight="1" s="23">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>肉食性鱼类</t>
-        </is>
-      </c>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>鲨鱼及其制品</t>
+          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -12541,7 +12053,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H22" s="4" t="n"/>
@@ -12552,7 +12064,7 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -12564,23 +12076,19 @@
     <row r="23" ht="28" customHeight="1" s="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="n"/>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品(肉食性鱼类及其制品除外)</t>
+          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -12590,7 +12098,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H23" s="4" t="n"/>
@@ -12599,7 +12107,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12609,23 +12121,19 @@
     <row r="24" ht="28" customHeight="1" s="23">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n"/>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="0" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品(肉食性鱼类及其制品除外)</t>
+          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -12635,7 +12143,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H24" s="4" t="n"/>
@@ -12644,9 +12152,9 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>b</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -12658,27 +12166,19 @@
     <row r="25" ht="28" customHeight="1" s="23">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>肉食性鱼类制品</t>
-        </is>
-      </c>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>肉食性鱼类及其制品(金枪鱼、金目鲷、枪鱼、鲨鱼及以上鱼类的制品除外)</t>
+          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -12688,7 +12188,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H25" s="4" t="n"/>
@@ -12697,7 +12197,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n"/>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12707,27 +12211,19 @@
     <row r="26" ht="28" customHeight="1" s="23">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>肉食性鱼类制品</t>
-        </is>
-      </c>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>肉食性鱼类及其制品(金枪鱼、金目鲷、枪鱼、鲨鱼及以上鱼类的制品除外)</t>
+          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -12737,7 +12233,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H26" s="4" t="n"/>
@@ -12748,7 +12244,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -12760,27 +12256,19 @@
     <row r="27" ht="28" customHeight="1" s="23">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>肉食性鱼类制品</t>
-        </is>
-      </c>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>金枪鱼及其制品</t>
+          <t>新鲜蔬菜</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -12790,7 +12278,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H27" s="4" t="n"/>
@@ -12809,27 +12297,19 @@
     <row r="28" ht="28" customHeight="1" s="23">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>肉食性鱼类制品</t>
-        </is>
-      </c>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>金枪鱼及其制品</t>
+          <t>新鲜蔬菜</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -12839,7 +12319,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="4" t="n"/>
@@ -12848,11 +12328,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12862,27 +12338,19 @@
     <row r="29" ht="28" customHeight="1" s="23">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>肉食性鱼类制品</t>
-        </is>
-      </c>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>金目鲷及其制品</t>
+          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -12911,37 +12379,29 @@
     <row r="30" ht="28" customHeight="1" s="23">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>肉食性鱼类制品</t>
-        </is>
-      </c>
+          <t>食用菌制品</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>金目鲷及其制品</t>
+          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>甲基汞 a</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H30" s="4" t="n"/>
@@ -12950,11 +12410,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12964,37 +12420,29 @@
     <row r="31" ht="28" customHeight="1" s="23">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>肉食性鱼类制品</t>
-        </is>
-      </c>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>枪鱼及其制品</t>
+          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞 a</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H31" s="4" t="n"/>
@@ -13003,7 +12451,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n"/>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13013,27 +12465,19 @@
     <row r="32" ht="28" customHeight="1" s="23">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>肉食性鱼类制品</t>
-        </is>
-      </c>
+          <t>食用菌制品</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>枪鱼及其制品</t>
+          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -13043,7 +12487,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H32" s="4" t="n"/>
@@ -13066,27 +12510,23 @@
     <row r="33" ht="28" customHeight="1" s="23">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>水产制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>肉食性鱼类制品</t>
-        </is>
-      </c>
+          <t>木耳（毛木耳,黑木耳）</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>鲨鱼及其制品</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -13115,37 +12555,37 @@
     <row r="34" ht="28" customHeight="1" s="23">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>水产制品</t>
+          <t>食用菌制品</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>鱼类制品</t>
+          <t>其他食用菌制品</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>肉食性鱼类制品</t>
+          <t>木耳制品、银耳制品</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>鲨鱼及其制品</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>甲基汞 a</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H34" s="4" t="n"/>
@@ -13154,11 +12594,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J34" s="4" t="n"/>
       <c r="K34" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13168,32 +12604,40 @@
     <row r="35" ht="28" customHeight="1" s="23">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>谷物</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n"/>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>木耳（毛木耳,黑木耳）</t>
+        </is>
+      </c>
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞 a</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="n"/>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>干重计</t>
+        </is>
+      </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -13201,7 +12645,7 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -13213,19 +12657,27 @@
     <row r="36" ht="28" customHeight="1" s="23">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>谷物</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
+          <t>食用菌制品</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>木耳制品、银耳制品</t>
+        </is>
+      </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -13235,16 +12687,24 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="n"/>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>干重计</t>
+        </is>
+      </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n"/>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13254,19 +12714,23 @@
     <row r="37" ht="28" customHeight="1" s="23">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr"/>
-      <c r="D37" s="4" t="inlineStr"/>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>银耳</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -13276,7 +12740,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H37" s="4" t="n"/>
@@ -13285,11 +12749,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13299,19 +12759,23 @@
     <row r="38" ht="28" customHeight="1" s="23">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr"/>
-      <c r="D38" s="4" t="inlineStr"/>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>银耳</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -13321,10 +12785,14 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="n"/>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>干重计</t>
+        </is>
+      </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -13332,7 +12800,7 @@
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -13344,19 +12812,19 @@
     <row r="39" ht="28" customHeight="1" s="23">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr"/>
-      <c r="D39" s="4" t="inlineStr"/>
+          <t>肉类(生鲜肉、冷却肉、冷冻肉等)</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>肉类</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -13366,7 +12834,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H39" s="4" t="n"/>
@@ -13375,11 +12843,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13389,19 +12853,19 @@
     <row r="40" ht="28" customHeight="1" s="23">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr"/>
-      <c r="D40" s="4" t="inlineStr"/>
+          <t>肉类(生鲜肉、冷却肉、冷冻肉等)</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>肉类</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -13420,11 +12884,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13434,19 +12894,19 @@
     <row r="41" ht="28" customHeight="1" s="23">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr"/>
-      <c r="D41" s="4" t="inlineStr"/>
+          <t>生乳</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -13456,7 +12916,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H41" s="4" t="n"/>
@@ -13465,11 +12925,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13479,19 +12935,19 @@
     <row r="42" ht="28" customHeight="1" s="23">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr"/>
-      <c r="D42" s="0" t="inlineStr"/>
+          <t>生乳</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -13510,11 +12966,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J42" s="0" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13524,19 +12976,19 @@
     <row r="43" ht="28" customHeight="1" s="23">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr"/>
-      <c r="D43" s="4" t="inlineStr"/>
+          <t>巴氏杀菌乳</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -13546,7 +12998,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H43" s="4" t="n"/>
@@ -13555,11 +13007,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J43" s="4" t="n"/>
       <c r="K43" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13569,19 +13017,19 @@
     <row r="44" ht="28" customHeight="1" s="23">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr"/>
-      <c r="D44" s="4" t="inlineStr"/>
+          <t>巴氏杀菌乳</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
@@ -13600,11 +13048,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13614,19 +13058,19 @@
     <row r="45" ht="28" customHeight="1" s="23">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+          <t>灭菌乳</t>
         </is>
       </c>
       <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -13655,19 +13099,19 @@
     <row r="46" ht="28" customHeight="1" s="23">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+          <t>灭菌乳</t>
         </is>
       </c>
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -13696,19 +13140,19 @@
     <row r="47" ht="28" customHeight="1" s="23">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>调制乳</t>
         </is>
       </c>
       <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="n"/>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -13718,7 +13162,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H47" s="4" t="n"/>
@@ -13737,24 +13181,24 @@
     <row r="48" ht="28" customHeight="1" s="23">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>调制乳</t>
         </is>
       </c>
       <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞 a</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -13778,29 +13222,29 @@
     <row r="49" ht="28" customHeight="1" s="23">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>发酵乳</t>
         </is>
       </c>
       <c r="C49" s="4" t="n"/>
       <c r="D49" s="4" t="n"/>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>甲基汞 a</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H49" s="4" t="n"/>
@@ -13809,11 +13253,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13823,19 +13263,19 @@
     <row r="50" ht="28" customHeight="1" s="23">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>发酵乳</t>
         </is>
       </c>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="4" t="n"/>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -13845,7 +13285,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H50" s="4" t="n"/>
@@ -13854,11 +13294,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -13868,23 +13304,19 @@
     <row r="51" ht="28" customHeight="1" s="23">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>蛋及蛋制品</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>木耳（毛木耳,黑木耳）</t>
-        </is>
-      </c>
+          <t>鲜蛋</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n"/>
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>鲜蛋</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -13894,7 +13326,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H51" s="4" t="n"/>
@@ -13913,32 +13345,24 @@
     <row r="52" ht="28" customHeight="1" s="23">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>蛋及蛋制品</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>木耳制品、银耳制品</t>
-        </is>
-      </c>
+          <t>鲜蛋</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>鲜蛋</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞 a</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -13962,28 +13386,24 @@
     <row r="53" ht="28" customHeight="1" s="23">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>调味品</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>木耳（毛木耳,黑木耳）</t>
-        </is>
-      </c>
+          <t>食用盐</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>食用盐</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>甲基汞 a</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -13991,21 +13411,13 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>干重计</t>
-        </is>
-      </c>
+      <c r="H53" s="4" t="n"/>
       <c r="I53" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J53" s="4" t="n"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -14015,27 +13427,19 @@
     <row r="54" ht="28" customHeight="1" s="23">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>调味品</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>木耳制品、银耳制品</t>
-        </is>
-      </c>
+          <t>食用盐</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>食用盐</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -14045,24 +13449,16 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>干重计</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="n"/>
       <c r="I54" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J54" s="4" t="n"/>
       <c r="K54" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -14072,23 +13468,23 @@
     <row r="55" ht="28" customHeight="1" s="23">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>银耳</t>
+          <t>饮用天然矿泉水</t>
         </is>
       </c>
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>饮用天然矿泉水</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -14098,42 +13494,42 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="H55" s="4" t="n"/>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>GB 5009.17</t>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1" s="23">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>银耳</t>
+          <t>饮用天然矿泉水</t>
         </is>
       </c>
       <c r="D56" s="4" t="n"/>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>饮用天然矿泉水</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -14143,46 +13539,42 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>干重计</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="n"/>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="n"/>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>GB 5009.17</t>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1" s="23">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>肉类(生鲜肉、冷却肉、冷冻肉等)</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="n"/>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>婴幼儿罐装辅助食品</t>
+        </is>
+      </c>
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>肉类</t>
+          <t>婴幼儿罐装辅助食品</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -14192,7 +13584,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H57" s="4" t="n"/>
@@ -14211,19 +13603,23 @@
     <row r="58" ht="28" customHeight="1" s="23">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>肉类(生鲜肉、冷却肉、冷冻肉等)</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="n"/>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>婴幼儿罐装辅助食品</t>
+        </is>
+      </c>
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>肉类</t>
+          <t>婴幼儿罐装辅助食品</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -14249,760 +13645,24 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="28" customHeight="1" s="23">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>生乳</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="n"/>
-      <c r="D59" s="4" t="n"/>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F59" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="n"/>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="28" customHeight="1" s="23">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>生乳</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="n"/>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F60" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="n"/>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J60" s="4" t="n"/>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="28" customHeight="1" s="23">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>巴氏杀菌乳</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F61" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="n"/>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J61" s="4" t="n"/>
-      <c r="K61" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="28" customHeight="1" s="23">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>巴氏杀菌乳</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F62" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="n"/>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="n"/>
-      <c r="K62" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="28" customHeight="1" s="23">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>灭菌乳</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="4" t="n"/>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F63" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J63" s="4" t="n"/>
-      <c r="K63" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="28" customHeight="1" s="23">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>灭菌乳</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F64" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="n"/>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J64" s="4" t="n"/>
-      <c r="K64" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="28" customHeight="1" s="23">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>调制乳</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="n"/>
-      <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F65" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="n"/>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="28" customHeight="1" s="23">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>调制乳</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="n"/>
-      <c r="D66" s="4" t="n"/>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F66" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="n"/>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J66" s="4" t="n"/>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="28" customHeight="1" s="23">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>发酵乳</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F67" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J67" s="4" t="n"/>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="28" customHeight="1" s="23">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>发酵乳</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="n"/>
-      <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F68" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="n"/>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J68" s="4" t="n"/>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="28" customHeight="1" s="23">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>蛋及蛋制品</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>鲜蛋</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="n"/>
-      <c r="D69" s="4" t="n"/>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>鲜蛋</t>
-        </is>
-      </c>
-      <c r="F69" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="n"/>
-      <c r="I69" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J69" s="4" t="n"/>
-      <c r="K69" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="28" customHeight="1" s="23">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>蛋及蛋制品</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>鲜蛋</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="n"/>
-      <c r="D70" s="4" t="n"/>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>鲜蛋</t>
-        </is>
-      </c>
-      <c r="F70" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="n"/>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J70" s="4" t="n"/>
-      <c r="K70" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="28" customHeight="1" s="23">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>食用盐</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="n"/>
-      <c r="D71" s="4" t="n"/>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>食用盐</t>
-        </is>
-      </c>
-      <c r="F71" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="n"/>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J71" s="4" t="n"/>
-      <c r="K71" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="28" customHeight="1" s="23">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>食用盐</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="n"/>
-      <c r="D72" s="4" t="n"/>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>食用盐</t>
-        </is>
-      </c>
-      <c r="F72" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="n"/>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J72" s="4" t="n"/>
-      <c r="K72" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="28" customHeight="1" s="23">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>饮用天然矿泉水</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>饮用天然矿泉水</t>
-        </is>
-      </c>
-      <c r="F73" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="J73" s="4" t="n"/>
-      <c r="K73" s="4" t="inlineStr">
-        <is>
-          <t>GB 8538</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="28" customHeight="1" s="23">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>饮用天然矿泉水</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>饮用天然矿泉水</t>
-        </is>
-      </c>
-      <c r="F74" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="n"/>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="J74" s="4" t="n"/>
-      <c r="K74" s="4" t="inlineStr">
-        <is>
-          <t>GB 8538</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="28" customHeight="1" s="23">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>特殊膳食用食品</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿罐装辅助食品</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿罐装辅助食品</t>
-        </is>
-      </c>
-      <c r="F75" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J75" s="4" t="n"/>
-      <c r="K75" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="28" customHeight="1" s="23">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>特殊膳食用食品</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿罐装辅助食品</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="n"/>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿罐装辅助食品</t>
-        </is>
-      </c>
-      <c r="F76" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="n"/>
-      <c r="I76" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J76" s="4" t="n"/>
-      <c r="K76" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
+    <row r="59" ht="28" customHeight="1" s="23"/>
+    <row r="60" ht="28" customHeight="1" s="23"/>
+    <row r="61" ht="28" customHeight="1" s="23"/>
+    <row r="62" ht="28" customHeight="1" s="23"/>
+    <row r="63" ht="28" customHeight="1" s="23"/>
+    <row r="64" ht="28" customHeight="1" s="23"/>
+    <row r="65" ht="28" customHeight="1" s="23"/>
+    <row r="66" ht="28" customHeight="1" s="23"/>
+    <row r="67" ht="28" customHeight="1" s="23"/>
+    <row r="68" ht="28" customHeight="1" s="23"/>
+    <row r="69" ht="28" customHeight="1" s="23"/>
+    <row r="70" ht="28" customHeight="1" s="23"/>
+    <row r="71" ht="28" customHeight="1" s="23"/>
+    <row r="72" ht="28" customHeight="1" s="23"/>
+    <row r="73" ht="28" customHeight="1" s="23"/>
+    <row r="74" ht="28" customHeight="1" s="23"/>
+    <row r="75" ht="28" customHeight="1" s="23"/>
+    <row r="76" ht="28" customHeight="1" s="23"/>
     <row r="77" ht="28" customHeight="1" s="23"/>
     <row r="78" ht="28" customHeight="1" s="23"/>
     <row r="79" ht="28" customHeight="1" s="23"/>
@@ -15677,84 +14337,84 @@
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" s="23">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>水产动物及其制品</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>水产动物及其制品(鱼类及其制品除外)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="0" t="inlineStr">
         <is>
           <t>总砷</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" s="23">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>水产动物及其制品</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>水产动物及其制品(鱼类及其制品除外)</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="0" t="inlineStr">
         <is>
           <t>无机砷 a</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -3218,7 +3218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -6690,8 +6690,16 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B84" s="19" t="n"/>
-      <c r="C84" s="19" t="n"/>
+      <c r="B84" s="19" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C84" s="19" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
       <c r="D84" s="19" t="n"/>
       <c r="E84" s="19" t="inlineStr">
         <is>
@@ -6703,7 +6711,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G84" s="30" t="inlineStr">
+      <c r="G84" s="22" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -6734,7 +6742,7 @@
       </c>
       <c r="C85" s="19" t="inlineStr">
         <is>
-          <t>松茸</t>
+          <t>松露</t>
         </is>
       </c>
       <c r="D85" s="19" t="n"/>
@@ -6777,12 +6785,12 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C86" s="19" t="inlineStr">
-        <is>
-          <t>松露</t>
-        </is>
-      </c>
-      <c r="D86" s="19" t="n"/>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>青头菌</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="n"/>
       <c r="E86" s="19" t="inlineStr">
         <is>
           <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
@@ -6812,7 +6820,7 @@
       </c>
     </row>
     <row r="87" ht="56" customHeight="1" s="23">
-      <c r="A87" s="20" t="inlineStr">
+      <c r="A87" s="19" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
@@ -6822,12 +6830,12 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>青头菌</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="n"/>
+      <c r="C87" s="19" t="inlineStr">
+        <is>
+          <t>鸡枞</t>
+        </is>
+      </c>
+      <c r="D87" s="19" t="n"/>
       <c r="E87" s="19" t="inlineStr">
         <is>
           <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
@@ -6838,7 +6846,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G87" s="22" t="inlineStr">
+      <c r="G87" s="19" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -6857,7 +6865,7 @@
       </c>
     </row>
     <row r="88" ht="56" customHeight="1" s="23">
-      <c r="A88" s="19" t="inlineStr">
+      <c r="A88" s="20" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
@@ -6869,7 +6877,7 @@
       </c>
       <c r="C88" s="19" t="inlineStr">
         <is>
-          <t>鸡枞</t>
+          <t>鸡油菌</t>
         </is>
       </c>
       <c r="D88" s="19" t="n"/>
@@ -6883,7 +6891,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G88" s="19" t="inlineStr">
+      <c r="G88" s="25" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -6914,7 +6922,7 @@
       </c>
       <c r="C89" s="19" t="inlineStr">
         <is>
-          <t>鸡油菌</t>
+          <t>多汁乳菇</t>
         </is>
       </c>
       <c r="D89" s="19" t="n"/>
@@ -6959,7 +6967,7 @@
       </c>
       <c r="C90" s="19" t="inlineStr">
         <is>
-          <t>多汁乳菇</t>
+          <t>银耳</t>
         </is>
       </c>
       <c r="D90" s="19" t="n"/>
@@ -6997,12 +7005,20 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B91" s="19" t="n"/>
-      <c r="C91" s="19" t="n"/>
+      <c r="B91" s="19" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="inlineStr">
+        <is>
+          <t>双孢菇</t>
+        </is>
+      </c>
       <c r="D91" s="19" t="n"/>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F91" s="19" t="inlineStr">
@@ -7012,7 +7028,7 @@
       </c>
       <c r="G91" s="25" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H91" s="19" t="n"/>
@@ -7041,13 +7057,13 @@
       </c>
       <c r="C92" s="19" t="inlineStr">
         <is>
-          <t>银耳</t>
+          <t>木耳 （毛木耳,黑木耳）</t>
         </is>
       </c>
       <c r="D92" s="19" t="n"/>
       <c r="E92" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F92" s="19" t="inlineStr">
@@ -7057,7 +7073,7 @@
       </c>
       <c r="G92" s="25" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H92" s="19" t="n"/>
@@ -7084,15 +7100,14 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C93" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇</t>
-        </is>
-      </c>
-      <c r="D93" s="19" t="n"/>
-      <c r="E93" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="E93" s="0" t="inlineStr">
+        <is>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F93" s="19" t="inlineStr">
@@ -7100,12 +7115,11 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G93" s="25" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="H93" s="19" t="n"/>
+      <c r="G93" s="19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="I93" s="19" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -7119,353 +7133,282 @@
       </c>
     </row>
     <row r="94" ht="56" customHeight="1" s="23">
-      <c r="A94" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B94" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C94" s="0" t="inlineStr">
-        <is>
-          <t>双孢菇</t>
-        </is>
-      </c>
-      <c r="D94" s="19" t="n"/>
-      <c r="E94" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F94" s="19" t="inlineStr">
+      <c r="A94" s="0" t="inlineStr">
+        <is>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="B94" s="0" t="n"/>
+      <c r="E94" s="0" t="inlineStr">
+        <is>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="F94" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G94" s="25" t="inlineStr">
+      <c r="G94" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I94" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K94" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="56" customHeight="1" s="23">
+      <c r="A95" s="0" t="inlineStr">
+        <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="E95" s="0" t="inlineStr">
+        <is>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+        </is>
+      </c>
+      <c r="F95" s="0" t="inlineStr">
+        <is>
+          <t>铅</t>
+        </is>
+      </c>
+      <c r="G95" s="0" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="H94" s="19" t="n"/>
-      <c r="I94" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J94" s="19" t="n"/>
-      <c r="K94" s="19" t="inlineStr">
+      <c r="I95" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K95" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="56" customHeight="1" s="23">
-      <c r="A95" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B95" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C95" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇</t>
-        </is>
-      </c>
-      <c r="D95" s="19" t="n"/>
-      <c r="E95" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F95" s="19" t="inlineStr">
+    <row r="96" ht="56" customHeight="1" s="23">
+      <c r="A96" s="0" t="inlineStr">
+        <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B96" s="0" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="E96" s="0" t="inlineStr">
+        <is>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+        </is>
+      </c>
+      <c r="F96" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G95" s="25" t="inlineStr">
+      <c r="G96" s="0" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="H95" s="19" t="n"/>
-      <c r="I95" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J95" s="19" t="n"/>
-      <c r="K95" s="19" t="inlineStr">
+      <c r="I96" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K96" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="56" customHeight="1" s="23">
-      <c r="A96" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B96" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C96" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇</t>
-        </is>
-      </c>
-      <c r="D96" s="19" t="n"/>
-      <c r="E96" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F96" s="19" t="inlineStr">
+    <row r="97" ht="56" customHeight="1" s="23">
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="inlineStr">
+        <is>
+          <t>蛋白饮料</t>
+        </is>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
+        </is>
+      </c>
+      <c r="E97" s="0" t="inlineStr">
+        <is>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+        </is>
+      </c>
+      <c r="F97" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G96" s="25" t="inlineStr">
+      <c r="G97" s="0" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="H96" s="19" t="n"/>
-      <c r="I96" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J96" s="19" t="n"/>
-      <c r="K96" s="19" t="inlineStr">
+      <c r="I97" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K97" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="56" customHeight="1" s="23">
-      <c r="A97" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B97" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C97" s="19" t="inlineStr">
-        <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
-      <c r="D97" s="19" t="n"/>
-      <c r="E97" s="19" t="inlineStr">
-        <is>
-          <t>木耳及其制品、银耳及其制品</t>
-        </is>
-      </c>
-      <c r="F97" s="19" t="inlineStr">
+    <row r="98" ht="56" customHeight="1" s="23">
+      <c r="A98" s="0" t="inlineStr">
+        <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="inlineStr">
+        <is>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
+        </is>
+      </c>
+      <c r="E98" s="0" t="inlineStr">
+        <is>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+        </is>
+      </c>
+      <c r="F98" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G97" s="25" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="H97" s="19" t="n"/>
-      <c r="I97" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J97" s="19" t="n"/>
-      <c r="K97" s="19" t="inlineStr">
+      <c r="G98" s="0" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I98" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K98" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="56" customHeight="1" s="23">
-      <c r="A98" s="19" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B98" s="0" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C98" s="0" t="inlineStr">
-        <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
-      <c r="E98" s="19" t="inlineStr">
-        <is>
-          <t>木耳及其制品、银耳及其制品</t>
-        </is>
-      </c>
-      <c r="F98" s="19" t="inlineStr">
+    <row r="99" ht="56" customHeight="1" s="23">
+      <c r="A99" s="0" t="inlineStr">
+        <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="inlineStr">
+        <is>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
+        </is>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t>果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外)</t>
+        </is>
+      </c>
+      <c r="F99" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G98" s="19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="H98" s="19" t="n"/>
-      <c r="I98" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J98" s="19" t="n"/>
-      <c r="K98" s="19" t="inlineStr">
+      <c r="G99" s="0" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="I99" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K99" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="56" customHeight="1" s="23">
-      <c r="A99" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B99" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C99" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
-        </is>
-      </c>
-      <c r="E99" s="0" t="inlineStr">
-        <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F99" s="19" t="inlineStr">
+    <row r="100" ht="56" customHeight="1" s="23">
+      <c r="A100" s="0" t="inlineStr">
+        <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="E100" s="0" t="inlineStr">
+        <is>
+          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
+        </is>
+      </c>
+      <c r="F100" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G99" s="19" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I99" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J99" s="19" t="n"/>
-      <c r="K99" s="19" t="inlineStr">
+      <c r="G100" s="0" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="I100" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K100" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="56" customHeight="1" s="23">
-      <c r="A100" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B100" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C100" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
-        </is>
-      </c>
-      <c r="E100" s="0" t="inlineStr">
-        <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F100" s="19" t="inlineStr">
+    <row r="101" ht="56" customHeight="1" s="23">
+      <c r="A101" s="0" t="inlineStr">
+        <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="E101" s="0" t="inlineStr">
+        <is>
+          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
+        </is>
+      </c>
+      <c r="F101" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G100" s="31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I100" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J100" s="19" t="n"/>
-      <c r="K100" s="19" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="56" customHeight="1" s="23">
-      <c r="A101" s="20" t="inlineStr">
-        <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B101" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C101" s="27" t="inlineStr">
-        <is>
-          <t>松茸</t>
-        </is>
-      </c>
-      <c r="E101" s="27" t="inlineStr">
-        <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
-        </is>
-      </c>
-      <c r="F101" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G101" s="30" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I101" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J101" s="19" t="n"/>
-      <c r="K101" s="19" t="inlineStr">
+      <c r="G101" s="0" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="I101" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K101" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
@@ -7474,22 +7417,12 @@
     <row r="102" ht="56" customHeight="1" s="23">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B102" s="0" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C102" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>饮料类(葡萄汁)</t>
         </is>
       </c>
       <c r="F102" s="0" t="inlineStr">
@@ -7499,7 +7432,7 @@
       </c>
       <c r="G102" s="0" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="I102" s="0" t="inlineStr">
@@ -7516,22 +7449,12 @@
     <row r="103" ht="42" customHeight="1" s="23">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B103" s="0" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C103" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>饮料类(固体饮料)</t>
         </is>
       </c>
       <c r="F103" s="0" t="inlineStr">
@@ -7558,22 +7481,17 @@
     <row r="104" ht="56" customHeight="1" s="23">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C104" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="F104" s="0" t="inlineStr">
@@ -7583,7 +7501,7 @@
       </c>
       <c r="G104" s="0" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="I104" s="0" t="inlineStr">
@@ -7591,22 +7509,31 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="K104" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
+      <c r="K104" s="28" t="inlineStr">
+        <is>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
     <row r="105" ht="42" customHeight="1" s="23">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="B105" s="0" t="n"/>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B105" s="0" t="inlineStr">
+        <is>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
+        </is>
+      </c>
+      <c r="C105" s="0" t="inlineStr">
+        <is>
+          <t>浓缩果蔬汁（浆）</t>
+        </is>
+      </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
+          <t>浓缩果蔬汁(浆)</t>
         </is>
       </c>
       <c r="F105" s="0" t="inlineStr">
@@ -7636,9 +7563,19 @@
           <t>饮料类</t>
         </is>
       </c>
+      <c r="B106" s="0" t="inlineStr">
+        <is>
+          <t>蛋白饮料</t>
+        </is>
+      </c>
+      <c r="C106" s="0" t="inlineStr">
+        <is>
+          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
+        </is>
+      </c>
       <c r="E106" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>含乳饮料</t>
         </is>
       </c>
       <c r="F106" s="0" t="inlineStr">
@@ -7648,7 +7585,7 @@
       </c>
       <c r="G106" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="I106" s="0" t="inlineStr">
@@ -7665,17 +7602,27 @@
     <row r="107" ht="28" customHeight="1" s="23">
       <c r="A107" s="0" t="inlineStr">
         <is>
-          <t>饮料类</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
+          <t>谷物制品</t>
+        </is>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
+        </is>
+      </c>
+      <c r="D107" s="0" t="inlineStr">
+        <is>
+          <t>带馅料面米制品</t>
         </is>
       </c>
       <c r="E107" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
       <c r="F107" s="0" t="inlineStr">
@@ -7685,7 +7632,7 @@
       </c>
       <c r="G107" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I107" s="0" t="inlineStr">
@@ -7699,514 +7646,17 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="27" customHeight="1" s="23">
-      <c r="A108" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B108" s="0" t="inlineStr">
-        <is>
-          <t>蛋白饮料</t>
-        </is>
-      </c>
-      <c r="C108" s="0" t="inlineStr">
-        <is>
-          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
-        </is>
-      </c>
-      <c r="E108" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
-        </is>
-      </c>
-      <c r="F108" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G108" s="0" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="I108" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K108" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="27" customHeight="1" s="23">
-      <c r="A109" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B109" s="0" t="inlineStr">
-        <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
-        </is>
-      </c>
-      <c r="E109" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
-        </is>
-      </c>
-      <c r="F109" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G109" s="0" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="I109" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K109" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="42" customHeight="1" s="23">
-      <c r="A110" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="E110" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
-        </is>
-      </c>
-      <c r="F110" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G110" s="0" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="I110" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K110" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="28" customHeight="1" s="23">
-      <c r="A111" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B111" s="0" t="inlineStr">
-        <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
-        </is>
-      </c>
-      <c r="E111" s="0" t="inlineStr">
-        <is>
-          <t>果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外)</t>
-        </is>
-      </c>
-      <c r="F111" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G111" s="0" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="I111" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K111" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="42" customHeight="1" s="23">
-      <c r="A112" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="E112" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
-        </is>
-      </c>
-      <c r="F112" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G112" s="0" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="I112" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K112" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="42" customHeight="1" s="23">
-      <c r="A113" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="E113" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
-        </is>
-      </c>
-      <c r="F113" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G113" s="0" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="I113" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K113" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="42" customHeight="1" s="23">
-      <c r="A114" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="E114" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
-        </is>
-      </c>
-      <c r="F114" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G114" s="0" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="I114" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K114" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="28" customHeight="1" s="23">
-      <c r="A115" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="E115" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
-        </is>
-      </c>
-      <c r="F115" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G115" s="0" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="I115" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K115" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="42" customHeight="1" s="23">
-      <c r="A116" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="E116" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(葡萄汁)</t>
-        </is>
-      </c>
-      <c r="F116" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G116" s="0" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="I116" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K116" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="42" customHeight="1" s="23">
-      <c r="A117" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="E117" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(固体饮料)</t>
-        </is>
-      </c>
-      <c r="F117" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G117" s="0" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I117" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K117" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="28" customHeight="1" s="23">
-      <c r="A118" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B118" s="0" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="E118" s="0" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="F118" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G118" s="0" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="I118" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K118" s="28" t="inlineStr">
-        <is>
-          <t>GB 8538</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B119" s="0" t="inlineStr">
-        <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
-        </is>
-      </c>
-      <c r="C119" s="0" t="inlineStr">
-        <is>
-          <t>浓缩果蔬汁（浆）</t>
-        </is>
-      </c>
-      <c r="E119" s="0" t="inlineStr">
-        <is>
-          <t>浓缩果蔬汁(浆)</t>
-        </is>
-      </c>
-      <c r="F119" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G119" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I119" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K119" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B120" s="0" t="inlineStr">
-        <is>
-          <t>蛋白饮料</t>
-        </is>
-      </c>
-      <c r="C120" s="0" t="inlineStr">
-        <is>
-          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
-        </is>
-      </c>
-      <c r="E120" s="0" t="inlineStr">
-        <is>
-          <t>含乳饮料</t>
-        </is>
-      </c>
-      <c r="F120" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G120" s="0" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="I120" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K120" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="0" t="inlineStr">
-        <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B121" s="0" t="inlineStr">
-        <is>
-          <t>谷物制品</t>
-        </is>
-      </c>
-      <c r="C121" s="0" t="inlineStr">
-        <is>
-          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
-        </is>
-      </c>
-      <c r="D121" s="0" t="inlineStr">
-        <is>
-          <t>带馅料面米制品</t>
-        </is>
-      </c>
-      <c r="E121" s="0" t="inlineStr">
-        <is>
-          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
-        </is>
-      </c>
-      <c r="F121" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G121" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I121" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K121" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
+    <row r="108" ht="27" customHeight="1" s="23"/>
+    <row r="109" ht="27" customHeight="1" s="23"/>
+    <row r="110" ht="42" customHeight="1" s="23"/>
+    <row r="111" ht="28" customHeight="1" s="23"/>
+    <row r="112" ht="42" customHeight="1" s="23"/>
+    <row r="113" ht="42" customHeight="1" s="23"/>
+    <row r="114" ht="42" customHeight="1" s="23"/>
+    <row r="115" ht="28" customHeight="1" s="23"/>
+    <row r="116" ht="42" customHeight="1" s="23"/>
+    <row r="117" ht="42" customHeight="1" s="23"/>
+    <row r="118" ht="28" customHeight="1" s="23"/>
   </sheetData>
   <autoFilter ref="A4:K138"/>
   <mergeCells count="1">
@@ -11132,7 +10582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -11896,19 +11346,19 @@
     <row r="19" ht="28" customHeight="1" s="23">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr"/>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>新鲜蔬菜</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -11918,7 +11368,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H19" s="4" t="n"/>
@@ -11927,11 +11377,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -11941,24 +11387,24 @@
     <row r="20" ht="28" customHeight="1" s="23">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr"/>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>甲基汞 a</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -11972,11 +11418,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -11986,29 +11428,29 @@
     <row r="21" ht="28" customHeight="1" s="23">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞 a</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H21" s="4" t="n"/>
@@ -12019,7 +11461,7 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -12031,24 +11473,28 @@
     <row r="22" ht="28" customHeight="1" s="23">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr"/>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>木耳（毛木耳,黑木耳）</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>甲基汞 a</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -12062,11 +11508,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12076,32 +11518,40 @@
     <row r="23" ht="28" customHeight="1" s="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr"/>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>木耳（毛木耳,黑木耳）</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞 a</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="n"/>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>干重计</t>
+        </is>
+      </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -12109,7 +11559,7 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -12121,29 +11571,29 @@
     <row r="24" ht="28" customHeight="1" s="23">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr"/>
-      <c r="D24" s="0" t="inlineStr"/>
+          <t>肉类(生鲜肉、冷却肉、冷冻肉等)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>肉类</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>甲基汞 a</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H24" s="4" t="n"/>
@@ -12152,11 +11602,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J24" s="0" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12166,29 +11612,29 @@
     <row r="25" ht="28" customHeight="1" s="23">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr"/>
-      <c r="D25" s="4" t="inlineStr"/>
+          <t>肉类(生鲜肉、冷却肉、冷冻肉等)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>肉类</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞 a</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H25" s="4" t="n"/>
@@ -12197,11 +11643,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12211,29 +11653,29 @@
     <row r="26" ht="28" customHeight="1" s="23">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr"/>
+          <t>生乳</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>甲基汞 a</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H26" s="4" t="n"/>
@@ -12242,11 +11684,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12256,29 +11694,29 @@
     <row r="27" ht="28" customHeight="1" s="23">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+          <t>生乳</t>
         </is>
       </c>
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞 a</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H27" s="4" t="n"/>
@@ -12297,29 +11735,29 @@
     <row r="28" ht="28" customHeight="1" s="23">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+          <t>巴氏杀菌乳</t>
         </is>
       </c>
       <c r="C28" s="4" t="n"/>
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>甲基汞 a</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H28" s="4" t="n"/>
@@ -12338,24 +11776,24 @@
     <row r="29" ht="28" customHeight="1" s="23">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>巴氏杀菌乳</t>
         </is>
       </c>
       <c r="C29" s="4" t="n"/>
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞 a</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -12379,19 +11817,19 @@
     <row r="30" ht="28" customHeight="1" s="23">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>灭菌乳</t>
         </is>
       </c>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -12401,7 +11839,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H30" s="4" t="n"/>
@@ -12420,19 +11858,19 @@
     <row r="31" ht="28" customHeight="1" s="23">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>灭菌乳</t>
         </is>
       </c>
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -12442,7 +11880,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H31" s="4" t="n"/>
@@ -12451,11 +11889,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12465,29 +11899,29 @@
     <row r="32" ht="28" customHeight="1" s="23">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>调制乳</t>
         </is>
       </c>
       <c r="C32" s="4" t="n"/>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(木耳及其制品、银耳及其制品除外)</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>甲基汞 a</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H32" s="4" t="n"/>
@@ -12496,11 +11930,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12510,28 +11940,24 @@
     <row r="33" ht="28" customHeight="1" s="23">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>木耳（毛木耳,黑木耳）</t>
-        </is>
-      </c>
+          <t>调制乳</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n"/>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞 a</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -12555,27 +11981,19 @@
     <row r="34" ht="28" customHeight="1" s="23">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>木耳制品、银耳制品</t>
-        </is>
-      </c>
+          <t>发酵乳</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -12585,7 +12003,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H34" s="4" t="n"/>
@@ -12604,23 +12022,19 @@
     <row r="35" ht="28" customHeight="1" s="23">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>乳及乳制品</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>木耳（毛木耳,黑木耳）</t>
-        </is>
-      </c>
+          <t>发酵乳</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n"/>
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -12630,24 +12044,16 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>干重计</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12657,54 +12063,38 @@
     <row r="36" ht="28" customHeight="1" s="23">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>蛋及蛋制品</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>木耳制品、银耳制品</t>
-        </is>
-      </c>
+          <t>鲜蛋</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>鲜蛋</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>甲基汞 a</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>干重计</t>
-        </is>
-      </c>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J36" s="4" t="n"/>
       <c r="K36" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12714,28 +12104,24 @@
     <row r="37" ht="28" customHeight="1" s="23">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>蛋及蛋制品</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>银耳</t>
-        </is>
-      </c>
+          <t>鲜蛋</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n"/>
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>鲜蛋</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞 a</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -12759,28 +12145,24 @@
     <row r="38" ht="28" customHeight="1" s="23">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>调味品</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>银耳</t>
-        </is>
-      </c>
+          <t>食用盐</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n"/>
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>食用盐</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>甲基汞 a</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -12788,21 +12170,13 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>干重计</t>
-        </is>
-      </c>
+      <c r="H38" s="4" t="n"/>
       <c r="I38" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="inlineStr">
         <is>
           <t>GB 5009.17</t>
@@ -12812,29 +12186,29 @@
     <row r="39" ht="28" customHeight="1" s="23">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>调味品</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>肉类(生鲜肉、冷却肉、冷冻肉等)</t>
+          <t>食用盐</t>
         </is>
       </c>
       <c r="C39" s="4" t="n"/>
       <c r="D39" s="4" t="n"/>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>肉类</t>
+          <t>食用盐</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞 a</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H39" s="4" t="n"/>
@@ -12853,111 +12227,123 @@
     <row r="40" ht="28" customHeight="1" s="23">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>肉类(生鲜肉、冷却肉、冷冻肉等)</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n"/>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>饮用天然矿泉水</t>
+        </is>
+      </c>
       <c r="D40" s="4" t="n"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>肉类</t>
+          <t>饮用天然矿泉水</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>甲基汞 a</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="H40" s="4" t="n"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>GB 5009.17</t>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1" s="23">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>乳及乳制品</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>生乳</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n"/>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>饮用天然矿泉水</t>
+        </is>
+      </c>
       <c r="D41" s="4" t="n"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
+          <t>饮用天然矿泉水</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞 a</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H41" s="4" t="n"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>GB 5009.17</t>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1" s="23">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>乳及乳制品</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>生乳</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n"/>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>婴幼儿罐装辅助食品</t>
+        </is>
+      </c>
       <c r="D42" s="4" t="n"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
+          <t>婴幼儿罐装辅助食品</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>甲基汞 a</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H42" s="4" t="n"/>
@@ -12976,29 +12362,33 @@
     <row r="43" ht="28" customHeight="1" s="23">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>乳及乳制品</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>巴氏杀菌乳</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n"/>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>婴幼儿罐装辅助食品</t>
+        </is>
+      </c>
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
+          <t>婴幼儿罐装辅助食品</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞 a</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H43" s="4" t="n"/>
@@ -13014,637 +12404,21 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="28" customHeight="1" s="23">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>巴氏杀菌乳</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="n"/>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28" customHeight="1" s="23">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>灭菌乳</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28" customHeight="1" s="23">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>灭菌乳</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28" customHeight="1" s="23">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>调制乳</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="n"/>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1" s="23">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>调制乳</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="n"/>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1" s="23">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>发酵乳</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="n"/>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28" customHeight="1" s="23">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>乳及乳制品</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>发酵乳</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
-        </is>
-      </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="n"/>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1" s="23">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>蛋及蛋制品</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>鲜蛋</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>鲜蛋</t>
-        </is>
-      </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="n"/>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="28" customHeight="1" s="23">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>蛋及蛋制品</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>鲜蛋</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>鲜蛋</t>
-        </is>
-      </c>
-      <c r="F52" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="n"/>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28" customHeight="1" s="23">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>食用盐</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>食用盐</t>
-        </is>
-      </c>
-      <c r="F53" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="n"/>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="n"/>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28" customHeight="1" s="23">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>食用盐</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>食用盐</t>
-        </is>
-      </c>
-      <c r="F54" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J54" s="4" t="n"/>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="28" customHeight="1" s="23">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>饮用天然矿泉水</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>饮用天然矿泉水</t>
-        </is>
-      </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="n"/>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="n"/>
-      <c r="K55" s="4" t="inlineStr">
-        <is>
-          <t>GB 8538</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="28" customHeight="1" s="23">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>饮用天然矿泉水</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>饮用天然矿泉水</t>
-        </is>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="J56" s="4" t="n"/>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>GB 8538</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="28" customHeight="1" s="23">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>特殊膳食用食品</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿罐装辅助食品</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿罐装辅助食品</t>
-        </is>
-      </c>
-      <c r="F57" s="12" t="inlineStr">
-        <is>
-          <t>总汞</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="n"/>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J57" s="4" t="n"/>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="28" customHeight="1" s="23">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>特殊膳食用食品</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿罐装辅助食品</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿罐装辅助食品</t>
-        </is>
-      </c>
-      <c r="F58" s="12" t="inlineStr">
-        <is>
-          <t>甲基汞 a</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="n"/>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="n"/>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.17</t>
-        </is>
-      </c>
-    </row>
+    <row r="44" ht="28" customHeight="1" s="23"/>
+    <row r="45" ht="28" customHeight="1" s="23"/>
+    <row r="46" ht="28" customHeight="1" s="23"/>
+    <row r="47" ht="28" customHeight="1" s="23"/>
+    <row r="48" ht="28" customHeight="1" s="23"/>
+    <row r="49" ht="28" customHeight="1" s="23"/>
+    <row r="50" ht="28" customHeight="1" s="23"/>
+    <row r="51" ht="28" customHeight="1" s="23"/>
+    <row r="52" ht="28" customHeight="1" s="23"/>
+    <row r="53" ht="28" customHeight="1" s="23"/>
+    <row r="54" ht="28" customHeight="1" s="23"/>
+    <row r="55" ht="28" customHeight="1" s="23"/>
+    <row r="56" ht="28" customHeight="1" s="23"/>
+    <row r="57" ht="28" customHeight="1" s="23"/>
+    <row r="58" ht="28" customHeight="1" s="23"/>
     <row r="59" ht="28" customHeight="1" s="23"/>
     <row r="60" ht="28" customHeight="1" s="23"/>
     <row r="61" ht="28" customHeight="1" s="23"/>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -3218,7 +3218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K108"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -3999,70 +3999,57 @@
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" s="23">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>坚果及籽类</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>坚果及籽类(生咖啡豆及烘焙咖啡豆除外)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>铅</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>GB 5009.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" s="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>坚果及籽类</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>生干坚果及籽类</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>生咖啡豆及烘焙咖啡豆</t>
         </is>
       </c>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>生咖啡豆及烘焙咖啡豆</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H22" s="19" t="n"/>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J22" s="19" t="inlineStr">
-        <is>
-          <t>d 仅限生咖啡豆及烘焙咖啡豆</t>
-        </is>
-      </c>
-      <c r="K22" s="19" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1" s="23">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="n"/>
       <c r="D23" s="19" t="n"/>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>水产制品(鱼类制品、海蜇制品除外)</t>
+          <t>生咖啡豆及烘焙咖啡豆</t>
         </is>
       </c>
       <c r="F23" s="19" t="inlineStr">
@@ -4072,7 +4059,7 @@
       </c>
       <c r="G23" s="19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H23" s="19" t="n"/>
@@ -4081,7 +4068,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J23" s="19" t="n"/>
+      <c r="J23" s="19" t="inlineStr">
+        <is>
+          <t>d 仅限生咖啡豆及烘焙咖啡豆</t>
+        </is>
+      </c>
       <c r="K23" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -4099,15 +4090,11 @@
           <t>水产制品</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>海蜇制品</t>
-        </is>
-      </c>
+      <c r="C24" s="19" t="n"/>
       <c r="D24" s="19" t="n"/>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>海蜇制品</t>
+          <t>水产制品(鱼类制品、海蜇制品除外)</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
@@ -4115,9 +4102,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
-        <is>
-          <t>2.0</t>
+      <c r="G24" s="19" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H24" s="19" t="n"/>
@@ -4146,13 +4133,13 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>鱼类制品</t>
+          <t>海蜇制品</t>
         </is>
       </c>
       <c r="D25" s="19" t="n"/>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>鱼类制品</t>
+          <t>海蜇制品</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
@@ -4160,9 +4147,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G25" s="19" t="inlineStr">
-        <is>
-          <t>0.5</t>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>2.0</t>
         </is>
       </c>
       <c r="H25" s="19" t="n"/>
@@ -4179,29 +4166,25 @@
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" s="23">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
+          <t>水产制品</t>
         </is>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>软体动物</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>双壳贝类</t>
-        </is>
-      </c>
+          <t>鱼类制品</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="n"/>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>双壳贝类</t>
+          <t>鱼类制品</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
@@ -4211,7 +4194,7 @@
       </c>
       <c r="G26" s="19" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H26" s="19" t="n"/>
@@ -4240,17 +4223,17 @@
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>鱼类</t>
+          <t>软体动物</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>非肉食性鱼类</t>
+          <t>双壳贝类</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
+          <t>双壳贝类</t>
         </is>
       </c>
       <c r="F27" s="19" t="inlineStr">
@@ -4260,7 +4243,7 @@
       </c>
       <c r="G27" s="19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H27" s="19" t="n"/>
@@ -4299,7 +4282,7 @@
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>鱼类、甲壳类</t>
+          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
@@ -4309,7 +4292,7 @@
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H28" s="19" t="n"/>
@@ -4328,19 +4311,27 @@
     <row r="29" ht="28" customHeight="1" s="23">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>水果及其制品</t>
+          <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>新鲜水果（未经加工的、经表面处理的、去皮或预切的、冷冻的水果）</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
+          <t>鲜、冻水产动物</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>鱼类</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>非肉食性鱼类</t>
+        </is>
+      </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>新鲜水果(蔓越莓、醋栗除外)</t>
+          <t>鱼类、甲壳类</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
@@ -4350,7 +4341,7 @@
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H29" s="19" t="n"/>
@@ -4374,14 +4365,14 @@
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>水果制品</t>
+          <t>新鲜水果（未经加工的、经表面处理的、去皮或预切的、冷冻的水果）</t>
         </is>
       </c>
       <c r="C30" s="19" t="n"/>
       <c r="D30" s="19" t="n"/>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>水果制品(果酱(泥)、蜜饯、水果干类除外)</t>
+          <t>新鲜水果(蔓越莓、醋栗除外)</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
@@ -4391,7 +4382,7 @@
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H30" s="19" t="n"/>
@@ -4415,18 +4406,14 @@
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>新鲜水果（未经加工的、经表面处理的、去皮或预切的、冷冻的水果）</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>浆果和其他小粒水果（例如：蔓越莓、醋栗等）</t>
-        </is>
-      </c>
+          <t>水果制品</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="n"/>
       <c r="D31" s="19" t="n"/>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>蔓越莓、醋栗</t>
+          <t>水果制品(果酱(泥)、蜜饯、水果干类除外)</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
@@ -4460,18 +4447,18 @@
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>水果制品</t>
+          <t>新鲜水果（未经加工的、经表面处理的、去皮或预切的、冷冻的水果）</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>果酱（泥）</t>
+          <t>浆果和其他小粒水果（例如：蔓越莓、醋栗等）</t>
         </is>
       </c>
       <c r="D32" s="19" t="n"/>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>果酱(泥)</t>
+          <t>蔓越莓、醋栗</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
@@ -4481,7 +4468,7 @@
       </c>
       <c r="G32" s="19" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H32" s="19" t="n"/>
@@ -4510,13 +4497,13 @@
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>水果干类</t>
+          <t>果酱（泥）</t>
         </is>
       </c>
       <c r="D33" s="19" t="n"/>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>水果干类</t>
+          <t>果酱(泥)</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
@@ -4526,7 +4513,7 @@
       </c>
       <c r="G33" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="H33" s="19" t="n"/>
@@ -4555,13 +4542,13 @@
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>蜜饯（包括果丹皮）</t>
+          <t>水果干类</t>
         </is>
       </c>
       <c r="D34" s="19" t="n"/>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>蜜饯</t>
+          <t>水果干类</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
@@ -4571,7 +4558,7 @@
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H34" s="19" t="n"/>
@@ -4590,15 +4577,23 @@
     <row r="35" ht="56" customHeight="1" s="23">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="n"/>
-      <c r="C35" s="19" t="n"/>
+          <t>水果及其制品</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>水果制品</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>蜜饯（包括果丹皮）</t>
+        </is>
+      </c>
       <c r="D35" s="19" t="n"/>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
+          <t>蜜饯</t>
         </is>
       </c>
       <c r="F35" s="19" t="inlineStr">
@@ -4608,7 +4603,7 @@
       </c>
       <c r="G35" s="19" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="H35" s="19" t="n"/>
@@ -4627,19 +4622,15 @@
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>淀粉及淀粉制品（包括谷物、豆类和块根植物提取的淀粉）</t>
-        </is>
-      </c>
-      <c r="B36" s="19" t="inlineStr">
-        <is>
-          <t>淀粉制品（包括虾味片）</t>
-        </is>
-      </c>
+          <t>油脂及其制品</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="n"/>
       <c r="C36" s="19" t="n"/>
       <c r="D36" s="19" t="n"/>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>淀粉制品</t>
+          <t>油脂及其制品</t>
         </is>
       </c>
       <c r="F36" s="19" t="inlineStr">
@@ -4649,7 +4640,7 @@
       </c>
       <c r="G36" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="H36" s="19" t="n"/>
@@ -4673,14 +4664,14 @@
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>食用淀粉</t>
+          <t>淀粉制品（包括虾味片）</t>
         </is>
       </c>
       <c r="C37" s="19" t="n"/>
       <c r="D37" s="19" t="n"/>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>食用淀粉</t>
+          <t>淀粉制品</t>
         </is>
       </c>
       <c r="F37" s="19" t="inlineStr">
@@ -4690,7 +4681,7 @@
       </c>
       <c r="G37" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H37" s="19" t="n"/>
@@ -4709,15 +4700,19 @@
     <row r="38" ht="42" customHeight="1" s="23">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>焙烤食品</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="n"/>
+          <t>淀粉及淀粉制品（包括谷物、豆类和块根植物提取的淀粉）</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>食用淀粉</t>
+        </is>
+      </c>
       <c r="C38" s="19" t="n"/>
       <c r="D38" s="19" t="n"/>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>焙烤食品</t>
+          <t>食用淀粉</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
@@ -4727,7 +4722,7 @@
       </c>
       <c r="G38" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H38" s="19" t="n"/>
@@ -4746,19 +4741,15 @@
     <row r="39" ht="28" customHeight="1" s="23">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
-        </is>
-      </c>
+          <t>焙烤食品</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="n"/>
       <c r="C39" s="19" t="n"/>
       <c r="D39" s="19" t="n"/>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>辅食营养补充品</t>
+          <t>焙烤食品</t>
         </is>
       </c>
       <c r="F39" s="19" t="inlineStr">
@@ -4799,7 +4790,7 @@
       <c r="D40" s="19" t="n"/>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>运动营养食品(固态、半固态或粉状)</t>
+          <t>辅食营养补充品</t>
         </is>
       </c>
       <c r="F40" s="19" t="inlineStr">
@@ -4840,7 +4831,7 @@
       <c r="D41" s="19" t="n"/>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>运动营养食品(液态)</t>
+          <t>运动营养食品(固态、半固态或粉状)</t>
         </is>
       </c>
       <c r="F41" s="19" t="inlineStr">
@@ -4850,7 +4841,7 @@
       </c>
       <c r="G41" s="19" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H41" s="19" t="n"/>
@@ -4881,7 +4872,7 @@
       <c r="D42" s="19" t="n"/>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>孕妇及乳母营养补充食品</t>
+          <t>运动营养食品(液态)</t>
         </is>
       </c>
       <c r="F42" s="19" t="inlineStr">
@@ -4891,7 +4882,7 @@
       </c>
       <c r="G42" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H42" s="19" t="n"/>
@@ -4915,14 +4906,14 @@
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
         </is>
       </c>
       <c r="C43" s="19" t="n"/>
       <c r="D43" s="19" t="n"/>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
+          <t>孕妇及乳母营养补充食品</t>
         </is>
       </c>
       <c r="F43" s="19" t="inlineStr">
@@ -4932,7 +4923,7 @@
       </c>
       <c r="G43" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H43" s="19" t="n"/>
@@ -4956,14 +4947,14 @@
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>婴幼儿配方食品</t>
+          <t>婴幼儿辅助食品</t>
         </is>
       </c>
       <c r="C44" s="19" t="n"/>
       <c r="D44" s="19" t="n"/>
       <c r="E44" s="19" t="inlineStr">
         <is>
-          <t>婴幼儿配方食品</t>
+          <t>婴幼儿辅助食品</t>
         </is>
       </c>
       <c r="F44" s="19" t="inlineStr">
@@ -4973,7 +4964,7 @@
       </c>
       <c r="G44" s="19" t="inlineStr">
         <is>
-          <t>0.08(以固态产品计)</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H44" s="19" t="n"/>
@@ -4982,11 +4973,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J44" s="19" t="inlineStr">
-        <is>
-          <t>c 液态婴幼儿配方食品根据8∶1的比例折算其限量。</t>
-        </is>
-      </c>
+      <c r="J44" s="19" t="n"/>
       <c r="K44" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -5001,14 +4988,14 @@
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>特殊医学用途配方食品（特殊医学用途婴儿配方食品涉及的品种除外）</t>
+          <t>婴幼儿配方食品</t>
         </is>
       </c>
       <c r="C45" s="19" t="n"/>
       <c r="D45" s="19" t="n"/>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>特殊医学用途配方食品(特殊医学用途婴儿配方食品涉及的品种除外)、10岁以上人群的产品</t>
+          <t>婴幼儿配方食品</t>
         </is>
       </c>
       <c r="F45" s="19" t="inlineStr">
@@ -5018,7 +5005,7 @@
       </c>
       <c r="G45" s="19" t="inlineStr">
         <is>
-          <t>0.5(以固态产品计)</t>
+          <t>0.08(以固态产品计)</t>
         </is>
       </c>
       <c r="H45" s="19" t="n"/>
@@ -5027,7 +5014,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J45" s="19" t="n"/>
+      <c r="J45" s="19" t="inlineStr">
+        <is>
+          <t>c 液态婴幼儿配方食品根据8∶1的比例折算其限量。</t>
+        </is>
+      </c>
       <c r="K45" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -5049,7 +5040,7 @@
       <c r="D46" s="19" t="n"/>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>特殊医学用途配方食品(特殊医学用途婴儿配方食品涉及的品种除外)、1~10岁人群的产品</t>
+          <t>特殊医学用途配方食品(特殊医学用途婴儿配方食品涉及的品种除外)、10岁以上人群的产品</t>
         </is>
       </c>
       <c r="F46" s="19" t="inlineStr">
@@ -5059,7 +5050,7 @@
       </c>
       <c r="G46" s="19" t="inlineStr">
         <is>
-          <t>0.15(以固态产品计)</t>
+          <t>0.5(以固态产品计)</t>
         </is>
       </c>
       <c r="H46" s="19" t="n"/>
@@ -5078,19 +5069,19 @@
     <row r="47" ht="42" customHeight="1" s="23">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
-          <t>肉类（生鲜肉、冷却肉、冷冻肉等）</t>
+          <t>特殊医学用途配方食品（特殊医学用途婴儿配方食品涉及的品种除外）</t>
         </is>
       </c>
       <c r="C47" s="19" t="n"/>
       <c r="D47" s="19" t="n"/>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>肉类(畜禽内脏除外)</t>
+          <t>特殊医学用途配方食品(特殊医学用途婴儿配方食品涉及的品种除外)、1~10岁人群的产品</t>
         </is>
       </c>
       <c r="F47" s="19" t="inlineStr">
@@ -5100,7 +5091,7 @@
       </c>
       <c r="G47" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.15(以固态产品计)</t>
         </is>
       </c>
       <c r="H47" s="19" t="n"/>
@@ -5124,14 +5115,14 @@
       </c>
       <c r="B48" s="19" t="inlineStr">
         <is>
-          <t>肉制品（包括内脏制品、血制品）</t>
+          <t>肉类（生鲜肉、冷却肉、冷冻肉等）</t>
         </is>
       </c>
       <c r="C48" s="19" t="n"/>
       <c r="D48" s="19" t="n"/>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>肉制品(畜禽内脏制品除外)</t>
+          <t>肉类(畜禽内脏除外)</t>
         </is>
       </c>
       <c r="F48" s="19" t="inlineStr">
@@ -5141,7 +5132,7 @@
       </c>
       <c r="G48" s="19" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H48" s="19" t="n"/>
@@ -5172,7 +5163,7 @@
       <c r="D49" s="19" t="n"/>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>畜禽内脏制品</t>
+          <t>肉制品(畜禽内脏制品除外)</t>
         </is>
       </c>
       <c r="F49" s="19" t="inlineStr">
@@ -5182,7 +5173,7 @@
       </c>
       <c r="G49" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H49" s="19" t="n"/>
@@ -5206,18 +5197,14 @@
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
-          <t>肉类（生鲜肉、冷却肉、冷冻肉等）</t>
-        </is>
-      </c>
-      <c r="C50" s="19" t="inlineStr">
-        <is>
-          <t>畜禽内脏（例如：肝、肾、肺、肠等）</t>
-        </is>
-      </c>
+          <t>肉制品（包括内脏制品、血制品）</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="n"/>
       <c r="D50" s="19" t="n"/>
       <c r="E50" s="19" t="inlineStr">
         <is>
-          <t>畜禽内脏</t>
+          <t>畜禽内脏制品</t>
         </is>
       </c>
       <c r="F50" s="19" t="inlineStr">
@@ -5246,19 +5233,23 @@
     <row r="51" ht="28" customHeight="1" s="23">
       <c r="A51" s="19" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
-        </is>
-      </c>
-      <c r="C51" s="19" t="n"/>
+          <t>肉类（生鲜肉、冷却肉、冷冻肉等）</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>畜禽内脏（例如：肝、肾、肺、肠等）</t>
+        </is>
+      </c>
       <c r="D51" s="19" t="n"/>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t>新鲜蔬菜(芸薹类蔬菜、叶菜蔬菜、豆类蔬菜、生姜、薯类除外)</t>
+          <t>畜禽内脏</t>
         </is>
       </c>
       <c r="F51" s="19" t="inlineStr">
@@ -5268,7 +5259,7 @@
       </c>
       <c r="G51" s="19" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H51" s="19" t="n"/>
@@ -5292,14 +5283,14 @@
       </c>
       <c r="B52" s="19" t="inlineStr">
         <is>
-          <t>蔬菜制品</t>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
         </is>
       </c>
       <c r="C52" s="19" t="n"/>
       <c r="D52" s="19" t="n"/>
       <c r="E52" s="19" t="inlineStr">
         <is>
-          <t>蔬菜制品(酱腌菜、干制蔬菜除外)</t>
+          <t>新鲜蔬菜(芸薹类蔬菜、叶菜蔬菜、豆类蔬菜、生姜、薯类除外)</t>
         </is>
       </c>
       <c r="F52" s="19" t="inlineStr">
@@ -5309,7 +5300,7 @@
       </c>
       <c r="G52" s="19" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H52" s="19" t="n"/>
@@ -5333,18 +5324,14 @@
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
-        </is>
-      </c>
-      <c r="C53" s="19" t="inlineStr">
-        <is>
-          <t>叶菜蔬菜（包括芸薹类叶菜）</t>
-        </is>
-      </c>
+          <t>蔬菜制品</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="n"/>
       <c r="D53" s="19" t="n"/>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t>叶菜蔬菜</t>
+          <t>蔬菜制品(酱腌菜、干制蔬菜除外)</t>
         </is>
       </c>
       <c r="F53" s="19" t="inlineStr">
@@ -5383,13 +5370,13 @@
       </c>
       <c r="C54" s="19" t="inlineStr">
         <is>
-          <t>芸薹类蔬菜</t>
+          <t>叶菜蔬菜（包括芸薹类叶菜）</t>
         </is>
       </c>
       <c r="D54" s="19" t="n"/>
       <c r="E54" s="19" t="inlineStr">
         <is>
-          <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
+          <t>叶菜蔬菜</t>
         </is>
       </c>
       <c r="F54" s="19" t="inlineStr">
@@ -5399,7 +5386,7 @@
       </c>
       <c r="G54" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H54" s="19" t="n"/>
@@ -5428,7 +5415,7 @@
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t>豆类蔬菜</t>
+          <t>芸薹类蔬菜</t>
         </is>
       </c>
       <c r="D55" s="19" t="n"/>
@@ -5473,14 +5460,10 @@
       </c>
       <c r="C56" s="19" t="inlineStr">
         <is>
-          <t>块根和块茎蔬菜（例如：薯类、胡萝卜、萝卜、生姜等）</t>
-        </is>
-      </c>
-      <c r="D56" s="19" t="inlineStr">
-        <is>
-          <t>生姜</t>
-        </is>
-      </c>
+          <t>豆类蔬菜</t>
+        </is>
+      </c>
+      <c r="D56" s="19" t="n"/>
       <c r="E56" s="19" t="inlineStr">
         <is>
           <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
@@ -5510,7 +5493,7 @@
       </c>
     </row>
     <row r="57" ht="42" customHeight="1" s="23">
-      <c r="A57" s="20" t="inlineStr">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
@@ -5527,7 +5510,7 @@
       </c>
       <c r="D57" s="19" t="inlineStr">
         <is>
-          <t>薯类</t>
+          <t>生姜</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
@@ -5566,18 +5549,22 @@
       </c>
       <c r="B58" s="19" t="inlineStr">
         <is>
-          <t>蔬菜制品</t>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
         </is>
       </c>
       <c r="C58" s="19" t="inlineStr">
         <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D58" s="19" t="n"/>
+          <t>块根和块茎蔬菜（例如：薯类、胡萝卜、萝卜、生姜等）</t>
+        </is>
+      </c>
+      <c r="D58" s="19" t="inlineStr">
+        <is>
+          <t>薯类</t>
+        </is>
+      </c>
       <c r="E58" s="19" t="inlineStr">
         <is>
-          <t>酱腌菜</t>
+          <t>芸薹类蔬菜、豆类蔬菜、生姜、薯类</t>
         </is>
       </c>
       <c r="F58" s="19" t="inlineStr">
@@ -5585,9 +5572,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G58" s="22" t="inlineStr">
-        <is>
-          <t>0.5</t>
+      <c r="G58" s="19" t="inlineStr">
+        <is>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H58" s="19" t="n"/>
@@ -5604,7 +5591,7 @@
       </c>
     </row>
     <row r="59" ht="42" customHeight="1" s="23">
-      <c r="A59" s="19" t="inlineStr">
+      <c r="A59" s="20" t="inlineStr">
         <is>
           <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
@@ -5616,13 +5603,13 @@
       </c>
       <c r="C59" s="19" t="inlineStr">
         <is>
-          <t>干制蔬菜</t>
+          <t>c</t>
         </is>
       </c>
       <c r="D59" s="19" t="n"/>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t>干制蔬菜</t>
+          <t>酱腌菜</t>
         </is>
       </c>
       <c r="F59" s="19" t="inlineStr">
@@ -5630,9 +5617,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G59" s="19" t="inlineStr">
-        <is>
-          <t>0.8</t>
+      <c r="G59" s="22" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H59" s="19" t="n"/>
@@ -5661,13 +5648,13 @@
       </c>
       <c r="C60" s="19" t="inlineStr">
         <is>
-          <t>酱腌菜</t>
+          <t>干制蔬菜</t>
         </is>
       </c>
       <c r="D60" s="19" t="n"/>
       <c r="E60" s="19" t="inlineStr">
         <is>
-          <t>酱腌菜</t>
+          <t>干制蔬菜</t>
         </is>
       </c>
       <c r="F60" s="19" t="inlineStr">
@@ -5677,7 +5664,7 @@
       </c>
       <c r="G60" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="H60" s="19" t="n"/>
@@ -5696,19 +5683,23 @@
     <row r="61" ht="42" customHeight="1" s="23">
       <c r="A61" s="19" t="inlineStr">
         <is>
-          <t>藻类及其制品</t>
-        </is>
-      </c>
-      <c r="B61" s="0" t="inlineStr">
-        <is>
-          <t>新鲜藻类（未经加工的、经表面处理的、预切的、冷冻的藻类）</t>
-        </is>
-      </c>
-      <c r="C61" s="19" t="n"/>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>蔬菜制品</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="inlineStr">
+        <is>
+          <t>酱腌菜</t>
+        </is>
+      </c>
       <c r="D61" s="19" t="n"/>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t>新鲜藻类(螺旋藻除外)</t>
+          <t>酱腌菜</t>
         </is>
       </c>
       <c r="F61" s="19" t="inlineStr">
@@ -5740,20 +5731,16 @@
           <t>藻类及其制品</t>
         </is>
       </c>
-      <c r="B62" s="19" t="inlineStr">
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t>新鲜藻类（未经加工的、经表面处理的、预切的、冷冻的藻类）</t>
         </is>
       </c>
-      <c r="C62" s="19" t="inlineStr">
-        <is>
-          <t>螺旋藻</t>
-        </is>
-      </c>
+      <c r="C62" s="19" t="n"/>
       <c r="D62" s="19" t="n"/>
       <c r="E62" s="19" t="inlineStr">
         <is>
-          <t>螺旋藻</t>
+          <t>新鲜藻类(螺旋藻除外)</t>
         </is>
       </c>
       <c r="F62" s="19" t="inlineStr">
@@ -5763,7 +5750,7 @@
       </c>
       <c r="G62" s="19" t="inlineStr">
         <is>
-          <t>0.5(干重计)</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H62" s="19" t="n"/>
@@ -5787,14 +5774,18 @@
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t>藻类制品</t>
-        </is>
-      </c>
-      <c r="C63" s="19" t="n"/>
+          <t>新鲜藻类（未经加工的、经表面处理的、预切的、冷冻的藻类）</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="inlineStr">
+        <is>
+          <t>螺旋藻</t>
+        </is>
+      </c>
       <c r="D63" s="19" t="n"/>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t>藻类制品(螺旋藻制品除外)</t>
+          <t>螺旋藻</t>
         </is>
       </c>
       <c r="F63" s="19" t="inlineStr">
@@ -5804,7 +5795,7 @@
       </c>
       <c r="G63" s="19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.5(干重计)</t>
         </is>
       </c>
       <c r="H63" s="19" t="n"/>
@@ -5831,15 +5822,11 @@
           <t>藻类制品</t>
         </is>
       </c>
-      <c r="C64" s="19" t="inlineStr">
-        <is>
-          <t>其他藻类制品</t>
-        </is>
-      </c>
+      <c r="C64" s="19" t="n"/>
       <c r="D64" s="19" t="n"/>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>螺旋藻制品</t>
+          <t>藻类制品(螺旋藻制品除外)</t>
         </is>
       </c>
       <c r="F64" s="19" t="inlineStr">
@@ -5849,7 +5836,7 @@
       </c>
       <c r="G64" s="19" t="inlineStr">
         <is>
-          <t>2.0(干重计)</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H64" s="19" t="n"/>
@@ -5868,15 +5855,23 @@
     <row r="65" ht="42" customHeight="1" s="23">
       <c r="A65" s="19" t="inlineStr">
         <is>
-          <t>蛋及蛋制品</t>
-        </is>
-      </c>
-      <c r="B65" s="19" t="n"/>
-      <c r="C65" s="19" t="n"/>
+          <t>藻类及其制品</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>藻类制品</t>
+        </is>
+      </c>
+      <c r="C65" s="19" t="inlineStr">
+        <is>
+          <t>其他藻类制品</t>
+        </is>
+      </c>
       <c r="D65" s="19" t="n"/>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t>蛋及蛋制品</t>
+          <t>螺旋藻制品</t>
         </is>
       </c>
       <c r="F65" s="19" t="inlineStr">
@@ -5886,7 +5881,7 @@
       </c>
       <c r="G65" s="19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.0(干重计)</t>
         </is>
       </c>
       <c r="H65" s="19" t="n"/>
@@ -5905,7 +5900,7 @@
     <row r="66" ht="42" customHeight="1" s="23">
       <c r="A66" s="19" t="inlineStr">
         <is>
-          <t>调味品</t>
+          <t>蛋及蛋制品</t>
         </is>
       </c>
       <c r="B66" s="19" t="n"/>
@@ -5913,7 +5908,7 @@
       <c r="D66" s="19" t="n"/>
       <c r="E66" s="19" t="inlineStr">
         <is>
-          <t>调味品(香辛料类除外)</t>
+          <t>蛋及蛋制品</t>
         </is>
       </c>
       <c r="F66" s="19" t="inlineStr">
@@ -5923,7 +5918,7 @@
       </c>
       <c r="G66" s="19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H66" s="19" t="n"/>
@@ -5945,16 +5940,12 @@
           <t>调味品</t>
         </is>
       </c>
-      <c r="B67" s="19" t="inlineStr">
-        <is>
-          <t>香辛料类</t>
-        </is>
-      </c>
+      <c r="B67" s="19" t="n"/>
       <c r="C67" s="19" t="n"/>
       <c r="D67" s="19" t="n"/>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t>香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外)</t>
+          <t>调味品(香辛料类除外)</t>
         </is>
       </c>
       <c r="F67" s="19" t="inlineStr">
@@ -5964,7 +5955,7 @@
       </c>
       <c r="G67" s="19" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H67" s="19" t="n"/>
@@ -5973,11 +5964,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J67" s="19" t="inlineStr">
-        <is>
-          <t>b 新鲜香辛料(如姜、葱、蒜等)应按对应的新鲜蔬菜(或新鲜水果)类别执行。</t>
-        </is>
-      </c>
+      <c r="J67" s="19" t="n"/>
       <c r="K67" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -5985,7 +5972,7 @@
       </c>
     </row>
     <row r="68" ht="28" customHeight="1" s="23">
-      <c r="A68" s="20" t="inlineStr">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>调味品</t>
         </is>
@@ -5995,15 +5982,11 @@
           <t>香辛料类</t>
         </is>
       </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>花椒、桂皮、肉桂、多种香辛料混合的香辛料</t>
-        </is>
-      </c>
+      <c r="C68" s="19" t="n"/>
       <c r="D68" s="19" t="n"/>
       <c r="E68" s="19" t="inlineStr">
         <is>
-          <t>花椒、桂皮、肉桂、多种香辛料混合的香辛料</t>
+          <t>香辛料类(花椒、桂皮、肉桂、多种香辛料混合的香辛料除外)</t>
         </is>
       </c>
       <c r="F68" s="19" t="inlineStr">
@@ -6011,9 +5994,9 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G68" s="22" t="inlineStr">
-        <is>
-          <t>3.0</t>
+      <c r="G68" s="19" t="inlineStr">
+        <is>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H68" s="19" t="n"/>
@@ -6022,7 +6005,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J68" s="19" t="n"/>
+      <c r="J68" s="19" t="inlineStr">
+        <is>
+          <t>b 新鲜香辛料(如姜、葱、蒜等)应按对应的新鲜蔬菜(或新鲜水果)类别执行。</t>
+        </is>
+      </c>
       <c r="K68" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6032,15 +6019,23 @@
     <row r="69" ht="42" customHeight="1" s="23">
       <c r="A69" s="20" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B69" s="19" t="n"/>
-      <c r="C69" s="19" t="n"/>
+          <t>调味品</t>
+        </is>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>香辛料类</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="inlineStr">
+        <is>
+          <t>花椒、桂皮、肉桂、多种香辛料混合的香辛料</t>
+        </is>
+      </c>
       <c r="D69" s="19" t="n"/>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t>谷物及其制品(麦片、面筋、粥类罐头、带馅料面米制品除外)</t>
+          <t>花椒、桂皮、肉桂、多种香辛料混合的香辛料</t>
         </is>
       </c>
       <c r="F69" s="19" t="inlineStr">
@@ -6050,7 +6045,7 @@
       </c>
       <c r="G69" s="22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H69" s="19" t="n"/>
@@ -6059,11 +6054,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J69" s="19" t="inlineStr">
-        <is>
-          <t>a 稻谷以糙米计。</t>
-        </is>
-      </c>
+      <c r="J69" s="19" t="n"/>
       <c r="K69" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6076,20 +6067,12 @@
           <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
-      <c r="B70" s="19" t="inlineStr">
-        <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C70" s="19" t="inlineStr">
-        <is>
-          <t>麦片</t>
-        </is>
-      </c>
+      <c r="B70" s="19" t="n"/>
+      <c r="C70" s="19" t="n"/>
       <c r="D70" s="19" t="n"/>
       <c r="E70" s="19" t="inlineStr">
         <is>
-          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
+          <t>谷物及其制品(麦片、面筋、粥类罐头、带馅料面米制品除外)</t>
         </is>
       </c>
       <c r="F70" s="19" t="inlineStr">
@@ -6099,7 +6082,7 @@
       </c>
       <c r="G70" s="22" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H70" s="19" t="n"/>
@@ -6108,7 +6091,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J70" s="19" t="n"/>
+      <c r="J70" s="19" t="inlineStr">
+        <is>
+          <t>a 稻谷以糙米计。</t>
+        </is>
+      </c>
       <c r="K70" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6123,19 +6110,15 @@
       </c>
       <c r="B71" s="19" t="inlineStr">
         <is>
-          <t>谷物制品</t>
+          <t>谷物碾磨加工品</t>
         </is>
       </c>
       <c r="C71" s="19" t="inlineStr">
         <is>
-          <t>小麦粉制品</t>
-        </is>
-      </c>
-      <c r="D71" s="19" t="inlineStr">
-        <is>
-          <t>面筋</t>
-        </is>
-      </c>
+          <t>麦片</t>
+        </is>
+      </c>
+      <c r="D71" s="19" t="n"/>
       <c r="E71" s="19" t="inlineStr">
         <is>
           <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
@@ -6146,7 +6129,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G71" s="30" t="inlineStr">
+      <c r="G71" s="22" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -6177,12 +6160,12 @@
       </c>
       <c r="C72" s="19" t="inlineStr">
         <is>
-          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
+          <t>小麦粉制品</t>
         </is>
       </c>
       <c r="D72" s="19" t="inlineStr">
         <is>
-          <t>粥类罐头</t>
+          <t>面筋</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
@@ -6216,19 +6199,27 @@
     <row r="73" ht="70" customHeight="1" s="23">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>豆类及其制品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B73" s="19" t="inlineStr">
         <is>
-          <t>豆类制品</t>
-        </is>
-      </c>
-      <c r="C73" s="19" t="n"/>
-      <c r="D73" s="19" t="n"/>
+          <t>谷物制品</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="inlineStr">
+        <is>
+          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
+        </is>
+      </c>
+      <c r="D73" s="19" t="inlineStr">
+        <is>
+          <t>粥类罐头</t>
+        </is>
+      </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t>豆类制品(豆浆除外)</t>
+          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
       <c r="F73" s="19" t="inlineStr">
@@ -6238,7 +6229,7 @@
       </c>
       <c r="G73" s="30" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H73" s="19" t="n"/>
@@ -6265,15 +6256,11 @@
           <t>豆类制品</t>
         </is>
       </c>
-      <c r="C74" s="19" t="inlineStr">
-        <is>
-          <t>非发酵豆制品（例如：豆浆、豆腐类、豆干类、腐竹类、熟制豆类、大豆蛋白膨化食品、大豆素肉等）</t>
-        </is>
-      </c>
+      <c r="C74" s="19" t="n"/>
       <c r="D74" s="19" t="n"/>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>豆浆</t>
+          <t>豆类制品(豆浆除外)</t>
         </is>
       </c>
       <c r="F74" s="19" t="inlineStr">
@@ -6283,7 +6270,7 @@
       </c>
       <c r="G74" s="30" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H74" s="19" t="n"/>
@@ -6307,14 +6294,18 @@
       </c>
       <c r="B75" s="19" t="inlineStr">
         <is>
-          <t>豆类（干豆、以干豆磨成的粉）</t>
-        </is>
-      </c>
-      <c r="C75" s="19" t="n"/>
+          <t>豆类制品</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="inlineStr">
+        <is>
+          <t>非发酵豆制品（例如：豆浆、豆腐类、豆干类、腐竹类、熟制豆类、大豆蛋白膨化食品、大豆素肉等）</t>
+        </is>
+      </c>
       <c r="D75" s="19" t="n"/>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>豆类</t>
+          <t>豆浆</t>
         </is>
       </c>
       <c r="F75" s="19" t="inlineStr">
@@ -6324,7 +6315,7 @@
       </c>
       <c r="G75" s="30" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="H75" s="19" t="n"/>
@@ -6343,15 +6334,19 @@
     <row r="76" ht="42" customHeight="1" s="23">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>酒类</t>
-        </is>
-      </c>
-      <c r="B76" s="19" t="n"/>
+          <t>豆类及其制品</t>
+        </is>
+      </c>
+      <c r="B76" s="19" t="inlineStr">
+        <is>
+          <t>豆类（干豆、以干豆磨成的粉）</t>
+        </is>
+      </c>
       <c r="C76" s="19" t="n"/>
       <c r="D76" s="19" t="n"/>
       <c r="E76" s="19" t="inlineStr">
         <is>
-          <t>酒类(白酒、黄酒除外)</t>
+          <t>豆类</t>
         </is>
       </c>
       <c r="F76" s="19" t="inlineStr">
@@ -6383,20 +6378,12 @@
           <t>酒类</t>
         </is>
       </c>
-      <c r="B77" s="19" t="inlineStr">
-        <is>
-          <t>蒸馏酒（例如：白酒、白兰地、威士忌、伏特加、朗姆酒等）</t>
-        </is>
-      </c>
-      <c r="C77" s="19" t="inlineStr">
-        <is>
-          <t>白酒</t>
-        </is>
-      </c>
+      <c r="B77" s="19" t="n"/>
+      <c r="C77" s="19" t="n"/>
       <c r="D77" s="19" t="n"/>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>白酒、黄酒</t>
+          <t>酒类(白酒、黄酒除外)</t>
         </is>
       </c>
       <c r="F77" s="19" t="inlineStr">
@@ -6406,7 +6393,7 @@
       </c>
       <c r="G77" s="30" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H77" s="19" t="n"/>
@@ -6430,12 +6417,12 @@
       </c>
       <c r="B78" s="19" t="inlineStr">
         <is>
-          <t>发酵酒(例如:葡萄酒、黄酒、果酒、啤酒等)</t>
+          <t>蒸馏酒（例如：白酒、白兰地、威士忌、伏特加、朗姆酒等）</t>
         </is>
       </c>
       <c r="C78" s="19" t="inlineStr">
         <is>
-          <t>黄酒</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D78" s="19" t="n"/>
@@ -6470,15 +6457,23 @@
     <row r="79" ht="56" customHeight="1" s="23">
       <c r="A79" s="20" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B79" s="19" t="n"/>
-      <c r="C79" s="19" t="n"/>
+          <t>酒类</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t>发酵酒(例如:葡萄酒、黄酒、果酒、啤酒等)</t>
+        </is>
+      </c>
+      <c r="C79" s="19" t="inlineStr">
+        <is>
+          <t>黄酒</t>
+        </is>
+      </c>
       <c r="D79" s="19" t="n"/>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
+          <t>白酒、黄酒</t>
         </is>
       </c>
       <c r="F79" s="19" t="inlineStr">
@@ -6510,16 +6505,8 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B80" s="19" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C80" s="19" t="inlineStr">
-        <is>
-          <t>双孢菇</t>
-        </is>
-      </c>
+      <c r="B80" s="19" t="n"/>
+      <c r="C80" s="19" t="n"/>
       <c r="D80" s="19" t="n"/>
       <c r="E80" s="19" t="inlineStr">
         <is>
@@ -6562,7 +6549,7 @@
       </c>
       <c r="C81" s="19" t="inlineStr">
         <is>
-          <t>平菇</t>
+          <t>双孢菇</t>
         </is>
       </c>
       <c r="D81" s="19" t="n"/>
@@ -6607,7 +6594,7 @@
       </c>
       <c r="C82" s="19" t="inlineStr">
         <is>
-          <t>香菇</t>
+          <t>平菇</t>
         </is>
       </c>
       <c r="D82" s="19" t="n"/>
@@ -6652,7 +6639,7 @@
       </c>
       <c r="C83" s="19" t="inlineStr">
         <is>
-          <t>榛蘑</t>
+          <t>香菇</t>
         </is>
       </c>
       <c r="D83" s="19" t="n"/>
@@ -6697,7 +6684,7 @@
       </c>
       <c r="C84" s="19" t="inlineStr">
         <is>
-          <t>松茸</t>
+          <t>榛蘑</t>
         </is>
       </c>
       <c r="D84" s="19" t="n"/>
@@ -6711,7 +6698,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G84" s="22" t="inlineStr">
+      <c r="G84" s="30" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -6742,7 +6729,7 @@
       </c>
       <c r="C85" s="19" t="inlineStr">
         <is>
-          <t>松露</t>
+          <t>松茸</t>
         </is>
       </c>
       <c r="D85" s="19" t="n"/>
@@ -6785,12 +6772,12 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>青头菌</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="n"/>
+      <c r="C86" s="19" t="inlineStr">
+        <is>
+          <t>松露</t>
+        </is>
+      </c>
+      <c r="D86" s="19" t="n"/>
       <c r="E86" s="19" t="inlineStr">
         <is>
           <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
@@ -6820,7 +6807,7 @@
       </c>
     </row>
     <row r="87" ht="56" customHeight="1" s="23">
-      <c r="A87" s="19" t="inlineStr">
+      <c r="A87" s="20" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
@@ -6830,12 +6817,12 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C87" s="19" t="inlineStr">
-        <is>
-          <t>鸡枞</t>
-        </is>
-      </c>
-      <c r="D87" s="19" t="n"/>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>青头菌</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="n"/>
       <c r="E87" s="19" t="inlineStr">
         <is>
           <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
@@ -6846,7 +6833,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G87" s="19" t="inlineStr">
+      <c r="G87" s="22" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -6865,7 +6852,7 @@
       </c>
     </row>
     <row r="88" ht="56" customHeight="1" s="23">
-      <c r="A88" s="20" t="inlineStr">
+      <c r="A88" s="19" t="inlineStr">
         <is>
           <t>食用菌及其制品</t>
         </is>
@@ -6877,7 +6864,7 @@
       </c>
       <c r="C88" s="19" t="inlineStr">
         <is>
-          <t>鸡油菌</t>
+          <t>鸡枞</t>
         </is>
       </c>
       <c r="D88" s="19" t="n"/>
@@ -6891,7 +6878,7 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G88" s="25" t="inlineStr">
+      <c r="G88" s="19" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -6922,7 +6909,7 @@
       </c>
       <c r="C89" s="19" t="inlineStr">
         <is>
-          <t>多汁乳菇</t>
+          <t>鸡油菌</t>
         </is>
       </c>
       <c r="D89" s="19" t="n"/>
@@ -6967,7 +6954,7 @@
       </c>
       <c r="C90" s="19" t="inlineStr">
         <is>
-          <t>银耳</t>
+          <t>多汁乳菇</t>
         </is>
       </c>
       <c r="D90" s="19" t="n"/>
@@ -7012,13 +6999,13 @@
       </c>
       <c r="C91" s="19" t="inlineStr">
         <is>
-          <t>双孢菇</t>
+          <t>银耳</t>
         </is>
       </c>
       <c r="D91" s="19" t="n"/>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
+          <t>食用菌及其制品(双孢菇、平菇、香菇、榛蘑、牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇、木耳、银耳及以上食用菌的制品除外)</t>
         </is>
       </c>
       <c r="F91" s="19" t="inlineStr">
@@ -7028,7 +7015,7 @@
       </c>
       <c r="G91" s="25" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H91" s="19" t="n"/>
@@ -7057,13 +7044,13 @@
       </c>
       <c r="C92" s="19" t="inlineStr">
         <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
+          <t>双孢菇</t>
         </is>
       </c>
       <c r="D92" s="19" t="n"/>
       <c r="E92" s="19" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="F92" s="19" t="inlineStr">
@@ -7073,7 +7060,7 @@
       </c>
       <c r="G92" s="25" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H92" s="19" t="n"/>
@@ -7100,14 +7087,15 @@
           <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
-      <c r="C93" s="0" t="inlineStr">
-        <is>
-          <t>松茸</t>
-        </is>
-      </c>
-      <c r="E93" s="0" t="inlineStr">
-        <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+      <c r="C93" s="19" t="inlineStr">
+        <is>
+          <t>木耳 （毛木耳,黑木耳）</t>
+        </is>
+      </c>
+      <c r="D93" s="19" t="n"/>
+      <c r="E93" s="19" t="inlineStr">
+        <is>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F93" s="19" t="inlineStr">
@@ -7115,11 +7103,12 @@
           <t>铅</t>
         </is>
       </c>
-      <c r="G93" s="19" t="inlineStr">
+      <c r="G93" s="25" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
+      <c r="H93" s="19" t="n"/>
       <c r="I93" s="19" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -7133,33 +7122,43 @@
       </c>
     </row>
     <row r="94" ht="56" customHeight="1" s="23">
-      <c r="A94" s="0" t="inlineStr">
-        <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="B94" s="0" t="n"/>
+      <c r="A94" s="20" t="inlineStr">
+        <is>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B94" s="19" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
       <c r="E94" s="0" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="F94" s="0" t="inlineStr">
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+        </is>
+      </c>
+      <c r="F94" s="19" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G94" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I94" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K94" s="0" t="inlineStr">
+      <c r="G94" s="19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I94" s="19" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J94" s="19" t="n"/>
+      <c r="K94" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
@@ -7168,12 +7167,13 @@
     <row r="95" ht="56" customHeight="1" s="23">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t>饮料类</t>
-        </is>
-      </c>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="B95" s="0" t="n"/>
       <c r="E95" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>食糖及淀粉糖</t>
         </is>
       </c>
       <c r="F95" s="0" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="G95" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I95" s="0" t="inlineStr">
@@ -7203,11 +7203,6 @@
           <t>饮料类</t>
         </is>
       </c>
-      <c r="B96" s="0" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
       <c r="E96" s="0" t="inlineStr">
         <is>
           <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
@@ -7242,12 +7237,7 @@
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>蛋白饮料</t>
-        </is>
-      </c>
-      <c r="C97" s="0" t="inlineStr">
-        <is>
-          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="E97" s="0" t="inlineStr">
@@ -7284,7 +7274,12 @@
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
+          <t>蛋白饮料</t>
+        </is>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
         </is>
       </c>
       <c r="E98" s="0" t="inlineStr">
@@ -7326,7 +7321,7 @@
       </c>
       <c r="E99" s="0" t="inlineStr">
         <is>
-          <t>果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外)</t>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
         </is>
       </c>
       <c r="F99" s="0" t="inlineStr">
@@ -7336,7 +7331,7 @@
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I99" s="0" t="inlineStr">
@@ -7356,9 +7351,14 @@
           <t>饮料类</t>
         </is>
       </c>
+      <c r="B100" s="0" t="inlineStr">
+        <is>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
+        </is>
+      </c>
       <c r="E100" s="0" t="inlineStr">
         <is>
-          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
+          <t>果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外)</t>
         </is>
       </c>
       <c r="F100" s="0" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="E101" s="0" t="inlineStr">
         <is>
-          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
+          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
         </is>
       </c>
       <c r="F101" s="0" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="G101" s="0" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I101" s="0" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
-          <t>饮料类(葡萄汁)</t>
+          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
         </is>
       </c>
       <c r="F102" s="0" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="G102" s="0" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="I102" s="0" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
-          <t>饮料类(固体饮料)</t>
+          <t>饮料类(葡萄汁)</t>
         </is>
       </c>
       <c r="F103" s="0" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="G103" s="0" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="I103" s="0" t="inlineStr">
@@ -7484,14 +7484,9 @@
           <t>饮料类</t>
         </is>
       </c>
-      <c r="B104" s="0" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
+          <t>饮料类(固体饮料)</t>
         </is>
       </c>
       <c r="F104" s="0" t="inlineStr">
@@ -7501,7 +7496,7 @@
       </c>
       <c r="G104" s="0" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I104" s="0" t="inlineStr">
@@ -7509,9 +7504,9 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="K104" s="28" t="inlineStr">
-        <is>
-          <t>GB 8538</t>
+      <c r="K104" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.12</t>
         </is>
       </c>
     </row>
@@ -7523,17 +7518,12 @@
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
-        </is>
-      </c>
-      <c r="C105" s="0" t="inlineStr">
-        <is>
-          <t>浓缩果蔬汁（浆）</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
-          <t>浓缩果蔬汁(浆)</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="F105" s="0" t="inlineStr">
@@ -7543,7 +7533,7 @@
       </c>
       <c r="G105" s="0" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="I105" s="0" t="inlineStr">
@@ -7551,9 +7541,9 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="K105" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
+      <c r="K105" s="28" t="inlineStr">
+        <is>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
@@ -7565,17 +7555,17 @@
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>蛋白饮料</t>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
+          <t>浓缩果蔬汁（浆）</t>
         </is>
       </c>
       <c r="E106" s="0" t="inlineStr">
         <is>
-          <t>含乳饮料</t>
+          <t>浓缩果蔬汁(浆)</t>
         </is>
       </c>
       <c r="F106" s="0" t="inlineStr">
@@ -7585,7 +7575,7 @@
       </c>
       <c r="G106" s="0" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I106" s="0" t="inlineStr">
@@ -7602,51 +7592,92 @@
     <row r="107" ht="28" customHeight="1" s="23">
       <c r="A107" s="0" t="inlineStr">
         <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B107" s="0" t="inlineStr">
+        <is>
+          <t>蛋白饮料</t>
+        </is>
+      </c>
+      <c r="C107" s="0" t="inlineStr">
+        <is>
+          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
+        </is>
+      </c>
+      <c r="E107" s="0" t="inlineStr">
+        <is>
+          <t>含乳饮料</t>
+        </is>
+      </c>
+      <c r="F107" s="0" t="inlineStr">
+        <is>
+          <t>铅</t>
+        </is>
+      </c>
+      <c r="G107" s="0" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="I107" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K107" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="27" customHeight="1" s="23">
+      <c r="A108" s="0" t="inlineStr">
+        <is>
           <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
-      <c r="B107" s="0" t="inlineStr">
+      <c r="B108" s="0" t="inlineStr">
         <is>
           <t>谷物制品</t>
         </is>
       </c>
-      <c r="C107" s="0" t="inlineStr">
+      <c r="C108" s="0" t="inlineStr">
         <is>
           <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
         </is>
       </c>
-      <c r="D107" s="0" t="inlineStr">
+      <c r="D108" s="0" t="inlineStr">
         <is>
           <t>带馅料面米制品</t>
         </is>
       </c>
-      <c r="E107" s="0" t="inlineStr">
+      <c r="E108" s="0" t="inlineStr">
         <is>
           <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
-      <c r="F107" s="0" t="inlineStr">
+      <c r="F108" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G107" s="0" t="inlineStr">
+      <c r="G108" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I107" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K107" s="0" t="inlineStr">
+      <c r="I108" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K108" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="27" customHeight="1" s="23"/>
     <row r="109" ht="27" customHeight="1" s="23"/>
     <row r="110" ht="42" customHeight="1" s="23"/>
     <row r="111" ht="28" customHeight="1" s="23"/>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -3999,32 +3999,32 @@
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" s="23">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>坚果及籽类</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>坚果及籽类(生咖啡豆及烘焙咖啡豆除外)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
@@ -4270,11 +4270,7 @@
           <t>鲜、冻水产动物</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
+      <c r="C28" s="19" t="n"/>
       <c r="D28" s="19" t="inlineStr">
         <is>
           <t>非肉食性鱼类</t>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -3991,7 +3991,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J21" s="19" t="n"/>
+      <c r="J21" s="19" t="inlineStr">
+        <is>
+          <t>以Pb计</t>
+        </is>
+      </c>
       <c r="K21" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -12484,7 +12488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -13093,7 +13097,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>以As计</t>
+        </is>
+      </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13130,7 +13138,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n"/>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>以As计</t>
+        </is>
+      </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13138,42 +13150,42 @@
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" s="23">
-      <c r="A19" s="0" t="inlineStr">
-        <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="E19" s="0" t="inlineStr">
-        <is>
-          <t>水产动物及其制品(鱼类及其制品除外)</t>
-        </is>
-      </c>
-      <c r="F19" s="0" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>可可制品、巧克力和巧克力制品以及糖果</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>可可制品、巧克力和巧克力制品</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>总砷</t>
         </is>
       </c>
-      <c r="G19" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H19" s="0" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I19" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J19" s="0" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="K19" s="0" t="inlineStr">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>以As计</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
@@ -13192,75 +13204,72 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="56" customHeight="1" s="23">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>水产动物及其制品</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>水产动物及其制品(鱼类及其制品除外)</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
           <t>无机砷 a</t>
         </is>
       </c>
-      <c r="G20" s="0" t="inlineStr">
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="H20" s="0" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I20" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J20" s="0" t="inlineStr">
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="K20" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="56" customHeight="1" s="23">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>鱼类及其制品</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K21" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
@@ -13288,14 +13297,14 @@
           <t>鱼类及其制品</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H22" s="4" t="n"/>
@@ -13304,11 +13313,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13318,29 +13323,33 @@
     <row r="23" ht="56" customHeight="1" s="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
+          <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n"/>
+          <t>鲜、冻水产动物</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>鱼类</t>
+        </is>
+      </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>鱼油及其制品、磷虾油及其制品</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>鱼类及其制品</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H23" s="4" t="n"/>
@@ -13349,7 +13358,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13374,14 +13387,14 @@
           <t>鱼油及其制品、磷虾油及其制品</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H24" s="4" t="n"/>
@@ -13390,11 +13403,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13404,29 +13413,29 @@
     <row r="25" ht="28" customHeight="1" s="23">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>油脂及其制品</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
         </is>
       </c>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>辅食营养补充品</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>鱼油及其制品、磷虾油及其制品</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H25" s="4" t="n"/>
@@ -13435,7 +13444,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n"/>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13457,7 +13470,7 @@
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(固态、半固态或粉状)</t>
+          <t>辅食营养补充品</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -13498,7 +13511,7 @@
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(液态)</t>
+          <t>运动营养食品(固态、半固态或粉状)</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -13508,7 +13521,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H27" s="4" t="n"/>
@@ -13539,7 +13552,7 @@
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>孕妇及乳母营养补充食品</t>
+          <t>运动营养食品(液态)</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -13549,7 +13562,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H28" s="4" t="n"/>
@@ -13580,17 +13593,17 @@
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>辅食营养补充品</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>孕妇及乳母营养补充食品</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H29" s="4" t="n"/>
@@ -13621,7 +13634,7 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(固态、半固态或粉状)</t>
+          <t>辅食营养补充品</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -13662,7 +13675,7 @@
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(液态)</t>
+          <t>运动营养食品(固态、半固态或粉状)</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -13703,7 +13716,7 @@
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>孕妇及乳母营养补充食品</t>
+          <t>运动营养食品(液态)</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -13737,23 +13750,19 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>以水产及动物肝脏为原料的产品</t>
-        </is>
-      </c>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n"/>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>以水产及动物肝脏为原料的产品</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>孕妇及乳母营养补充食品</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -13796,14 +13805,14 @@
           <t>以水产及动物肝脏为原料的产品</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H34" s="4" t="n"/>
@@ -13812,11 +13821,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J34" s="4" t="n"/>
       <c r="K34" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13836,23 +13841,23 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+          <t>以水产及动物肝脏为原料的产品</t>
         </is>
       </c>
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>以水产及动物肝脏为原料的产品</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H35" s="4" t="n"/>
@@ -13861,7 +13866,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n"/>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13890,14 +13899,14 @@
           <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H36" s="4" t="n"/>
@@ -13906,11 +13915,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J36" s="4" t="n"/>
       <c r="K36" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13930,23 +13935,23 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
         </is>
       </c>
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H37" s="4" t="n"/>
@@ -13955,7 +13960,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J37" s="4" t="n"/>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13984,14 +13993,14 @@
           <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H38" s="4" t="n"/>
@@ -14000,11 +14009,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14024,23 +14029,23 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>添加藻类的产品</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
         </is>
       </c>
       <c r="D39" s="4" t="n"/>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>添加藻类的产品</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H39" s="4" t="n"/>
@@ -14049,7 +14054,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J39" s="4" t="n"/>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14078,14 +14087,14 @@
           <t>添加藻类的产品</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H40" s="4" t="n"/>
@@ -14094,11 +14103,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14108,29 +14113,33 @@
     <row r="41" ht="28" customHeight="1" s="23">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n"/>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>添加藻类的产品</t>
+        </is>
+      </c>
       <c r="D41" s="4" t="n"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>添加藻类的产品</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H41" s="4" t="n"/>
@@ -14139,7 +14148,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J41" s="4" t="n"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14164,14 +14177,14 @@
           <t>新鲜蔬菜</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H42" s="4" t="n"/>
@@ -14190,24 +14203,30 @@
     <row r="43" ht="28" customHeight="1" s="23">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n"/>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
       <c r="C43" s="4" t="n"/>
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G43" s="10" t="n">
-        <v>0.5</v>
+          <t>新鲜蔬菜</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H43" s="4" t="n"/>
       <c r="I43" s="4" t="inlineStr">
@@ -14236,15 +14255,13 @@
           <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v>0.5</v>
       </c>
       <c r="H44" s="4" t="n"/>
       <c r="I44" s="4" t="inlineStr">
@@ -14252,11 +14269,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14269,21 +14282,17 @@
           <t>调味品</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
-        </is>
-      </c>
+      <c r="B45" s="4" t="n"/>
       <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>复合调味料</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -14297,7 +14306,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J45" s="4" t="n"/>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14322,14 +14335,14 @@
           <t>复合调味料</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H46" s="4" t="n"/>
@@ -14338,11 +14351,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14357,24 +14366,24 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>水产调味品</t>
+          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
         </is>
       </c>
       <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="n"/>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>水产调味品(鱼类调味品除外)</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>复合调味料</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H47" s="4" t="n"/>
@@ -14383,7 +14392,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J47" s="4" t="n"/>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14408,13 +14421,15 @@
           <t>水产调味品(鱼类调味品除外)</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G48" s="10" t="n">
-        <v>0.5</v>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="inlineStr">
@@ -14422,11 +14437,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14444,26 +14455,20 @@
           <t>水产调味品</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>鱼类调味品（例如：鱼露等）</t>
-        </is>
-      </c>
+      <c r="C49" s="4" t="n"/>
       <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>鱼类调味品</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>水产调味品(鱼类调味品除外)</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="n">
+        <v>0.5</v>
       </c>
       <c r="H49" s="4" t="n"/>
       <c r="I49" s="4" t="inlineStr">
@@ -14471,7 +14476,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J49" s="4" t="n"/>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14500,14 +14509,14 @@
           <t>鱼类调味品</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H50" s="4" t="n"/>
@@ -14516,11 +14525,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14530,33 +14535,33 @@
     <row r="51" ht="42" customHeight="1" s="23">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>调味品</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>谷物</t>
+          <t>水产调味品</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>稻谷</t>
+          <t>鱼类调味品（例如：鱼露等）</t>
         </is>
       </c>
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>稻谷</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>鱼类调味品</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H51" s="4" t="n"/>
@@ -14567,7 +14572,7 @@
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -14598,14 +14603,14 @@
           <t>稻谷</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H52" s="4" t="n"/>
@@ -14614,7 +14619,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J52" s="4" t="n"/>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14629,28 +14638,28 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
+          <t>谷物</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>大米（粉）</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>大米(粉)</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>稻谷</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="H53" s="4" t="n"/>
@@ -14688,14 +14697,14 @@
           <t>大米(粉)</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H54" s="4" t="n"/>
@@ -14724,23 +14733,23 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>糙米（包括色稻米）</t>
+          <t>大米（粉）</t>
         </is>
       </c>
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>糙米</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>大米(粉)</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H55" s="4" t="n"/>
@@ -14778,14 +14787,14 @@
           <t>糙米</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H56" s="4" t="n"/>
@@ -14804,25 +14813,33 @@
     <row r="57" ht="42" customHeight="1" s="23">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="n"/>
-      <c r="C57" s="4" t="n"/>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>糙米（包括色稻米）</t>
+        </is>
+      </c>
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>糙米</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="H57" s="4" t="n"/>
@@ -14832,7 +14849,11 @@
         </is>
       </c>
       <c r="J57" s="4" t="n"/>
-      <c r="K57" s="4" t="n"/>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="42" customHeight="1" s="23">
       <c r="A58" s="4" t="inlineStr">
@@ -14848,14 +14869,14 @@
           <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
-      <c r="F58" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H58" s="4" t="n"/>
@@ -14864,16 +14885,8 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
+      <c r="J58" s="4" t="n"/>
+      <c r="K58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -14881,30 +14894,22 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H59" s="4" t="n"/>
@@ -14913,7 +14918,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J59" s="4" t="n"/>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14942,31 +14951,23 @@
           <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>(干重计)</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="n"/>
       <c r="I60" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14981,41 +14982,45 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>木耳制品、银耳制品</t>
-        </is>
-      </c>
+          <t>木耳 （毛木耳,黑木耳）</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="n"/>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>(干重计)</t>
+        </is>
+      </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J61" s="4" t="n"/>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15048,31 +15053,23 @@
           <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>(干重计)</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="n"/>
       <c r="I62" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15087,37 +15084,49 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>食用菌制品</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>银耳</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="n"/>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>木耳制品、银耳制品</t>
+        </is>
+      </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="n"/>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>(干重计)</t>
+        </is>
+      </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J63" s="4" t="n"/>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15146,31 +15155,23 @@
           <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>(干重计)</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15190,32 +15191,40 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>松茸</t>
+          <t>银耳</t>
         </is>
       </c>
       <c r="D65" s="4" t="n"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>松茸及其制品</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>木耳及其制品、银耳及其制品</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="n"/>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>(干重计)</t>
+        </is>
+      </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J65" s="4" t="n"/>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15244,14 +15253,14 @@
           <t>松茸及其制品</t>
         </is>
       </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H66" s="4" t="n"/>
@@ -15260,11 +15269,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15279,32 +15284,28 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>松茸制品</t>
-        </is>
-      </c>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="n"/>
       <c r="E67" s="4" t="inlineStr">
         <is>
           <t>松茸及其制品</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="H67" s="4" t="n"/>
@@ -15313,7 +15314,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J67" s="4" t="n"/>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15346,14 +15351,14 @@
           <t>松茸及其制品</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H68" s="4" t="n"/>
@@ -15362,11 +15367,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15376,25 +15377,37 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="n"/>
-      <c r="C69" s="4" t="n"/>
-      <c r="D69" s="4" t="n"/>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>食用菌制品</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>松茸制品</t>
+        </is>
+      </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>松茸及其制品</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="H69" s="4" t="n"/>
@@ -15403,7 +15416,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J69" s="4" t="n"/>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15424,14 +15441,14 @@
           <t>食糖及淀粉糖</t>
         </is>
       </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H70" s="4" t="n"/>
@@ -15450,29 +15467,25 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="n"/>
       <c r="C71" s="4" t="n"/>
       <c r="D71" s="4" t="n"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H71" s="4" t="n"/>
@@ -15506,14 +15519,14 @@
           <t>包装饮用水</t>
         </is>
       </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H72" s="4" t="n"/>
@@ -15532,28 +15545,24 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="B73" s="11" t="inlineStr">
-        <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n"/>
       <c r="D73" s="4" t="n"/>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>鱼类及其制品</t>
-        </is>
-      </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -15590,19 +15599,20 @@
           <t>鱼类制品</t>
         </is>
       </c>
+      <c r="D74" s="4" t="n"/>
       <c r="E74" s="4" t="inlineStr">
         <is>
           <t>鱼类及其制品</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H74" s="4" t="n"/>
@@ -15611,53 +15621,56 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="J74" s="4" t="n"/>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>水产动物及其制品</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>水产制品</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>鱼类制品</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>鱼类及其制品</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="K74" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="0" t="inlineStr">
-        <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B75" s="0" t="inlineStr">
-        <is>
-          <t>谷物</t>
-        </is>
-      </c>
-      <c r="C75" s="0" t="inlineStr"/>
-      <c r="D75" s="0" t="inlineStr"/>
-      <c r="E75" s="0" t="inlineStr">
-        <is>
-          <t>谷物(稻谷除外)</t>
-        </is>
-      </c>
-      <c r="F75" s="0" t="inlineStr">
-        <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G75" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H75" s="0" t="inlineStr"/>
-      <c r="I75" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J75" s="0" t="inlineStr"/>
-      <c r="K75" s="0" t="inlineStr">
+      <c r="K75" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
@@ -15671,14 +15684,14 @@
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
+          <t>谷物</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr"/>
       <c r="D76" s="0" t="inlineStr"/>
       <c r="E76" s="0" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品[糙米、大米(粉)除外]</t>
+          <t>谷物(稻谷除外)</t>
         </is>
       </c>
       <c r="F76" s="0" t="inlineStr">
@@ -15712,24 +15725,24 @@
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>谷物</t>
+          <t>谷物碾磨加工品</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr"/>
       <c r="D77" s="0" t="inlineStr"/>
       <c r="E77" s="0" t="inlineStr">
         <is>
-          <t>谷物(稻谷除外)</t>
+          <t>谷物碾磨加工品[糙米、大米(粉)除外]</t>
         </is>
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
-          <t>无机砷 a</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H77" s="0" t="inlineStr"/>
@@ -15753,14 +15766,14 @@
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
+          <t>谷物</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr"/>
       <c r="D78" s="0" t="inlineStr"/>
       <c r="E78" s="0" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品[糙米、大米(粉)除外]</t>
+          <t>谷物(稻谷除外)</t>
         </is>
       </c>
       <c r="F78" s="0" t="inlineStr">
@@ -15789,24 +15802,30 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
-        </is>
-      </c>
-      <c r="B79" s="0" t="inlineStr"/>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="inlineStr">
+        <is>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
       <c r="C79" s="0" t="inlineStr"/>
       <c r="D79" s="0" t="inlineStr"/>
       <c r="E79" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>谷物碾磨加工品[糙米、大米(粉)除外]</t>
         </is>
       </c>
       <c r="F79" s="0" t="inlineStr">
         <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G79" s="0" t="n">
-        <v>0.5</v>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G79" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H79" s="0" t="inlineStr"/>
       <c r="I79" s="0" t="inlineStr">
@@ -15837,13 +15856,11 @@
       </c>
       <c r="F80" s="0" t="inlineStr">
         <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G80" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G80" s="0" t="n">
+        <v>0.5</v>
       </c>
       <c r="H80" s="0" t="inlineStr"/>
       <c r="I80" s="0" t="inlineStr">
@@ -15861,7 +15878,7 @@
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B81" s="0" t="inlineStr"/>
@@ -15869,16 +15886,18 @@
       <c r="D81" s="0" t="inlineStr"/>
       <c r="E81" s="0" t="inlineStr">
         <is>
-          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="F81" s="0" t="inlineStr">
         <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G81" s="0" t="n">
-        <v>0.1</v>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G81" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H81" s="0" t="inlineStr"/>
       <c r="I81" s="0" t="inlineStr">
@@ -15909,13 +15928,11 @@
       </c>
       <c r="F82" s="0" t="inlineStr">
         <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G82" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G82" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="H82" s="0" t="inlineStr"/>
       <c r="I82" s="0" t="inlineStr">
@@ -15925,6 +15942,43 @@
       </c>
       <c r="J82" s="0" t="inlineStr"/>
       <c r="K82" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="inlineStr">
+        <is>
+          <t>油脂及其制品</t>
+        </is>
+      </c>
+      <c r="B83" s="0" t="inlineStr"/>
+      <c r="C83" s="0" t="inlineStr"/>
+      <c r="D83" s="0" t="inlineStr"/>
+      <c r="E83" s="0" t="inlineStr">
+        <is>
+          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
+        </is>
+      </c>
+      <c r="F83" s="0" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G83" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="0" t="inlineStr"/>
+      <c r="I83" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J83" s="0" t="inlineStr"/>
+      <c r="K83" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -4995,7 +4995,7 @@
       <c r="D45" s="19" t="n"/>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>婴幼儿配方食品</t>
+          <t>婴儿配方食品、较大婴儿配方食品、幼儿配方食品、特殊医学用途婴儿配方食品</t>
         </is>
       </c>
       <c r="F45" s="19" t="inlineStr">
@@ -13150,42 +13150,42 @@
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" s="23">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>可可制品、巧克力和巧克力制品以及糖果</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>可可制品、巧克力和巧克力制品</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="0" t="inlineStr">
         <is>
           <t>总砷</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>以As计</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
@@ -16147,7 +16147,7 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿配方食品</t>
+          <t>婴儿配方食品、较大婴儿配方食品、幼儿配方食品、特殊医学用途婴儿配方食品</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -3967,12 +3967,16 @@
           <t>可可制品、巧克力和巧克力制品以及糖果</t>
         </is>
       </c>
-      <c r="B21" s="19" t="n"/>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
+        </is>
+      </c>
       <c r="C21" s="19" t="n"/>
       <c r="D21" s="19" t="n"/>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>可可制品、巧克力和巧克力制品以及糖果</t>
+          <t>可可制品、巧克力和巧克力制品</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
@@ -12488,7 +12492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -13068,82 +13072,84 @@
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" s="23">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>可可制品、巧克力和巧克力制品以及糖果</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>可可制品、巧克力和巧克力制品以及糖果</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>可可制品、巧克力和巧克力制品</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
         <is>
           <t>总砷</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t>以As计</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K17" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" s="23">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>可可制品、巧克力和巧克力制品以及糖果</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>可可制品、巧克力和巧克力制品以及糖果</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>水产动物及其制品</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>水产动物及其制品(鱼类及其制品除外)</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>以As计</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
@@ -13152,124 +13158,134 @@
     <row r="19" ht="28" customHeight="1" s="23">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t>可可制品、巧克力和巧克力制品以及糖果</t>
-        </is>
-      </c>
-      <c r="B19" s="0" t="inlineStr">
-        <is>
-          <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
+          <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>可可制品、巧克力和巧克力制品</t>
+          <t>水产动物及其制品(鱼类及其制品除外)</t>
         </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" s="23">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>水产动物及其制品</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>鲜、冻水产动物</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>鱼类</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>鱼类及其制品</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
           <t>总砷</t>
         </is>
       </c>
-      <c r="G19" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I19" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J19" s="0" t="inlineStr">
-        <is>
-          <t>以As计</t>
-        </is>
-      </c>
-      <c r="K19" s="0" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1" s="23">
-      <c r="A20" s="0" t="inlineStr">
+    <row r="21" ht="56" customHeight="1" s="23">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>水产动物及其制品</t>
         </is>
       </c>
-      <c r="E20" s="0" t="inlineStr">
-        <is>
-          <t>水产动物及其制品(鱼类及其制品除外)</t>
-        </is>
-      </c>
-      <c r="F20" s="0" t="inlineStr">
-        <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G20" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H20" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I20" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J20" s="0" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>鲜、冻水产动物</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>鱼类</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>鱼类及其制品</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="K20" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="56" customHeight="1" s="23">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t>水产动物及其制品(鱼类及其制品除外)</t>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G21" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H21" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I21" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J21" s="0" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="K21" s="0" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
@@ -13278,23 +13294,19 @@
     <row r="22" ht="56" customHeight="1" s="23">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>油脂及其制品</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
+          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n"/>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>鱼类及其制品</t>
+          <t>鱼油及其制品、磷虾油及其制品</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -13323,23 +13335,19 @@
     <row r="23" ht="56" customHeight="1" s="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>油脂及其制品</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
+          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>鱼类及其制品</t>
+          <t>鱼油及其制品、磷虾油及其制品</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -13372,19 +13380,19 @@
     <row r="24" ht="56" customHeight="1" s="23">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>鱼油及其制品、磷虾油及其制品</t>
+          <t>辅食营养补充品</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -13394,7 +13402,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H24" s="4" t="n"/>
@@ -13413,29 +13421,29 @@
     <row r="25" ht="28" customHeight="1" s="23">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
         </is>
       </c>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>鱼油及其制品、磷虾油及其制品</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>运动营养食品(固态、半固态或粉状)</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H25" s="4" t="n"/>
@@ -13444,11 +13452,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13470,7 +13474,7 @@
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>辅食营养补充品</t>
+          <t>运动营养食品(液态)</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -13480,7 +13484,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H26" s="4" t="n"/>
@@ -13511,7 +13515,7 @@
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(固态、半固态或粉状)</t>
+          <t>孕妇及乳母营养补充食品</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -13552,17 +13556,17 @@
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(液态)</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>辅食营养补充品</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="4" t="n"/>
@@ -13593,17 +13597,17 @@
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>孕妇及乳母营养补充食品</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>运动营养食品(固态、半固态或粉状)</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H29" s="4" t="n"/>
@@ -13634,7 +13638,7 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>辅食营养补充品</t>
+          <t>运动营养食品(液态)</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -13675,7 +13679,7 @@
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(固态、半固态或粉状)</t>
+          <t>孕妇及乳母营养补充食品</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -13709,19 +13713,23 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n"/>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>以水产及动物肝脏为原料的产品</t>
+        </is>
+      </c>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(液态)</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>以水产及动物肝脏为原料的产品</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -13750,14 +13758,18 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n"/>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>以水产及动物肝脏为原料的产品</t>
+        </is>
+      </c>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>孕妇及乳母营养补充食品</t>
+          <t>以水产及动物肝脏为原料的产品</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -13767,7 +13779,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H33" s="4" t="n"/>
@@ -13776,7 +13788,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n"/>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13796,13 +13812,13 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>以水产及动物肝脏为原料的产品</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
         </is>
       </c>
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>以水产及动物肝脏为原料的产品</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -13841,13 +13857,13 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>以水产及动物肝脏为原料的产品</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
         </is>
       </c>
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>以水产及动物肝脏为原料的产品</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -13857,7 +13873,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H35" s="4" t="n"/>
@@ -13890,13 +13906,13 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
         </is>
       </c>
       <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -13935,13 +13951,13 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
         </is>
       </c>
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
@@ -13951,7 +13967,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H37" s="4" t="n"/>
@@ -13984,13 +14000,13 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+          <t>添加藻类的产品</t>
         </is>
       </c>
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+          <t>添加藻类的产品</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -14029,13 +14045,13 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+          <t>添加藻类的产品</t>
         </is>
       </c>
       <c r="D39" s="4" t="n"/>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+          <t>添加藻类的产品</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -14045,7 +14061,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H39" s="4" t="n"/>
@@ -14068,23 +14084,19 @@
     <row r="40" ht="28" customHeight="1" s="23">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>添加藻类的产品</t>
-        </is>
-      </c>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n"/>
       <c r="D40" s="4" t="n"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>添加藻类的产品</t>
+          <t>新鲜蔬菜</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -14094,7 +14106,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H40" s="4" t="n"/>
@@ -14113,23 +14125,19 @@
     <row r="41" ht="28" customHeight="1" s="23">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>添加藻类的产品</t>
-        </is>
-      </c>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n"/>
       <c r="D41" s="4" t="n"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>添加藻类的产品</t>
+          <t>新鲜蔬菜</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -14139,7 +14147,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H41" s="4" t="n"/>
@@ -14148,11 +14156,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14162,19 +14166,15 @@
     <row r="42" ht="28" customHeight="1" s="23">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
-        </is>
-      </c>
+          <t>调味品</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n"/>
       <c r="C42" s="4" t="n"/>
       <c r="D42" s="4" t="n"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜</t>
+          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -14182,10 +14182,8 @@
           <t>总砷</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="G42" s="10" t="n">
+        <v>0.5</v>
       </c>
       <c r="H42" s="4" t="n"/>
       <c r="I42" s="4" t="inlineStr">
@@ -14203,19 +14201,15 @@
     <row r="43" ht="28" customHeight="1" s="23">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
-        </is>
-      </c>
+          <t>调味品</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n"/>
       <c r="C43" s="4" t="n"/>
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜</t>
+          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -14234,7 +14228,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J43" s="4" t="n"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14247,12 +14245,16 @@
           <t>调味品</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n"/>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
+        </is>
+      </c>
       <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
+          <t>复合调味料</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -14260,8 +14262,10 @@
           <t>总砷</t>
         </is>
       </c>
-      <c r="G44" s="10" t="n">
-        <v>0.5</v>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H44" s="4" t="n"/>
       <c r="I44" s="4" t="inlineStr">
@@ -14282,12 +14286,16 @@
           <t>调味品</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n"/>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
+        </is>
+      </c>
       <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
+          <t>复合调味料</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -14297,7 +14305,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H45" s="4" t="n"/>
@@ -14325,14 +14333,14 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
+          <t>水产调味品</t>
         </is>
       </c>
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>复合调味料</t>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>水产调味品(鱼类调味品除外)</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -14366,14 +14374,14 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
+          <t>水产调味品</t>
         </is>
       </c>
       <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>复合调味料</t>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>水产调味品(鱼类调味品除外)</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -14381,10 +14389,8 @@
           <t>无机砷 a</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="G47" s="10" t="n">
+        <v>0.5</v>
       </c>
       <c r="H47" s="4" t="n"/>
       <c r="I47" s="4" t="inlineStr">
@@ -14414,11 +14420,15 @@
           <t>水产调味品</t>
         </is>
       </c>
-      <c r="C48" s="4" t="n"/>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>鱼类调味品（例如：鱼露等）</t>
+        </is>
+      </c>
       <c r="D48" s="4" t="n"/>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>水产调味品(鱼类调味品除外)</t>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>鱼类调味品</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -14455,11 +14465,15 @@
           <t>水产调味品</t>
         </is>
       </c>
-      <c r="C49" s="4" t="n"/>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>鱼类调味品（例如：鱼露等）</t>
+        </is>
+      </c>
       <c r="D49" s="4" t="n"/>
-      <c r="E49" s="11" t="inlineStr">
-        <is>
-          <t>水产调味品(鱼类调味品除外)</t>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>鱼类调味品</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -14467,8 +14481,10 @@
           <t>无机砷 a</t>
         </is>
       </c>
-      <c r="G49" s="10" t="n">
-        <v>0.5</v>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="H49" s="4" t="n"/>
       <c r="I49" s="4" t="inlineStr">
@@ -14490,23 +14506,23 @@
     <row r="50" ht="42" customHeight="1" s="23">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>调味品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>水产调味品</t>
+          <t>谷物</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>鱼类调味品（例如：鱼露等）</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="D50" s="4" t="n"/>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>鱼类调味品</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -14525,7 +14541,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J50" s="4" t="n"/>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14535,23 +14555,23 @@
     <row r="51" ht="42" customHeight="1" s="23">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>调味品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>水产调味品</t>
+          <t>谷物</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>鱼类调味品（例如：鱼露等）</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>鱼类调味品</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -14561,7 +14581,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="H51" s="4" t="n"/>
@@ -14570,11 +14590,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14589,18 +14605,18 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>谷物</t>
+          <t>谷物碾磨加工品</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>稻谷</t>
+          <t>大米（粉）</t>
         </is>
       </c>
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>稻谷</t>
+          <t>大米(粉)</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -14619,11 +14635,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14638,18 +14650,18 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>谷物</t>
+          <t>谷物碾磨加工品</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>稻谷</t>
+          <t>大米（粉）</t>
         </is>
       </c>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>稻谷</t>
+          <t>大米(粉)</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -14659,7 +14671,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H53" s="4" t="n"/>
@@ -14688,13 +14700,13 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>大米（粉）</t>
+          <t>糙米（包括色稻米）</t>
         </is>
       </c>
       <c r="D54" s="4" t="n"/>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>大米(粉)</t>
+          <t>糙米</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -14733,13 +14745,13 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>大米（粉）</t>
+          <t>糙米（包括色稻米）</t>
         </is>
       </c>
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>大米(粉)</t>
+          <t>糙米</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -14749,7 +14761,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="H55" s="4" t="n"/>
@@ -14768,23 +14780,15 @@
     <row r="56" ht="42" customHeight="1" s="23">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>糙米（包括色稻米）</t>
-        </is>
-      </c>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n"/>
+      <c r="C56" s="4" t="n"/>
       <c r="D56" s="4" t="n"/>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>糙米</t>
+          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -14804,32 +14808,20 @@
         </is>
       </c>
       <c r="J56" s="4" t="n"/>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
+      <c r="K56" s="4" t="n"/>
     </row>
     <row r="57" ht="42" customHeight="1" s="23">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>糙米（包括色稻米）</t>
-        </is>
-      </c>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>糙米</t>
+          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -14839,7 +14831,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H57" s="4" t="n"/>
@@ -14848,7 +14840,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J57" s="4" t="n"/>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14861,12 +14857,20 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>木耳 （毛木耳,黑木耳）</t>
+        </is>
+      </c>
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -14886,7 +14890,11 @@
         </is>
       </c>
       <c r="J58" s="4" t="n"/>
-      <c r="K58" s="4" t="n"/>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -14894,12 +14902,20 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B59" s="4" t="n"/>
-      <c r="C59" s="4" t="n"/>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>木耳 （毛木耳,黑木耳）</t>
+        </is>
+      </c>
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -14912,7 +14928,11 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="H59" s="4" t="n"/>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>(干重计)</t>
+        </is>
+      </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -14937,15 +14957,19 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>食用菌制品</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="n"/>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>木耳制品、银耳制品</t>
+        </is>
+      </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
@@ -14982,15 +15006,19 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>食用菌制品</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="n"/>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>木耳制品、银耳制品</t>
+        </is>
+      </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
@@ -15035,19 +15063,15 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>木耳制品、银耳制品</t>
-        </is>
-      </c>
+          <t>银耳</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
@@ -15084,19 +15108,15 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>木耳制品、银耳制品</t>
-        </is>
-      </c>
+          <t>银耳</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="n"/>
       <c r="E63" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
@@ -15146,13 +15166,13 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>银耳</t>
+          <t>松茸</t>
         </is>
       </c>
       <c r="D64" s="4" t="n"/>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>松茸及其制品</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
@@ -15191,13 +15211,13 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>银耳</t>
+          <t>松茸</t>
         </is>
       </c>
       <c r="D65" s="4" t="n"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>松茸及其制品</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
@@ -15207,14 +15227,10 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>(干重计)</t>
-        </is>
-      </c>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="n"/>
       <c r="I65" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -15239,15 +15255,19 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>食用菌制品</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>松茸</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="n"/>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>松茸制品</t>
+        </is>
+      </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
           <t>松茸及其制品</t>
@@ -15284,15 +15304,19 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>食用菌制品</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>松茸</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="n"/>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>松茸制品</t>
+        </is>
+      </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
           <t>松茸及其制品</t>
@@ -15328,27 +15352,15 @@
     <row r="68" ht="42" customHeight="1" s="23">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>食用菌制品</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>松茸制品</t>
-        </is>
-      </c>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>松茸及其制品</t>
+          <t>食糖及淀粉糖</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -15358,7 +15370,7 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H68" s="4" t="n"/>
@@ -15377,27 +15389,15 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>食用菌制品</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>松茸制品</t>
-        </is>
-      </c>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>松茸及其制品</t>
+          <t>食糖及淀粉糖</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -15407,7 +15407,7 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H69" s="4" t="n"/>
@@ -15416,11 +15416,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J69" s="4" t="n"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15430,15 +15426,19 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="n"/>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
       <c r="C70" s="4" t="n"/>
       <c r="D70" s="4" t="n"/>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H70" s="4" t="n"/>
@@ -15467,15 +15467,19 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="n"/>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
       <c r="C71" s="4" t="n"/>
       <c r="D71" s="4" t="n"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
@@ -15504,19 +15508,23 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="n"/>
+          <t>水产动物及其制品</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>水产制品</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>鱼类制品</t>
+        </is>
+      </c>
       <c r="D72" s="4" t="n"/>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
+          <t>鱼类及其制品</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -15526,7 +15534,7 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H72" s="4" t="n"/>
@@ -15545,19 +15553,22 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="n"/>
+          <t>水产动物及其制品</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>水产制品</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>鱼类制品</t>
+        </is>
+      </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
+          <t>鱼类及其制品</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
@@ -15567,7 +15578,7 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H73" s="4" t="n"/>
@@ -15576,7 +15587,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J73" s="4" t="n"/>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15584,93 +15599,82 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="B74" s="11" t="inlineStr">
-        <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>鱼类及其制品</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr">
+      <c r="A74" s="0" t="inlineStr">
+        <is>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B74" s="0" t="inlineStr">
+        <is>
+          <t>谷物</t>
+        </is>
+      </c>
+      <c r="C74" s="0" t="inlineStr"/>
+      <c r="D74" s="0" t="inlineStr"/>
+      <c r="E74" s="0" t="inlineStr">
+        <is>
+          <t>谷物(稻谷除外)</t>
+        </is>
+      </c>
+      <c r="F74" s="0" t="inlineStr">
         <is>
           <t>总砷</t>
         </is>
       </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="n"/>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J74" s="4" t="n"/>
-      <c r="K74" s="4" t="inlineStr">
+      <c r="G74" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H74" s="0" t="inlineStr"/>
+      <c r="I74" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J74" s="0" t="inlineStr"/>
+      <c r="K74" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="B75" s="11" t="inlineStr">
-        <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>鱼类及其制品</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="K75" s="4" t="inlineStr">
+      <c r="A75" s="0" t="inlineStr">
+        <is>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B75" s="0" t="inlineStr">
+        <is>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C75" s="0" t="inlineStr"/>
+      <c r="D75" s="0" t="inlineStr"/>
+      <c r="E75" s="0" t="inlineStr">
+        <is>
+          <t>谷物碾磨加工品[糙米、大米(粉)除外]</t>
+        </is>
+      </c>
+      <c r="F75" s="0" t="inlineStr">
+        <is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G75" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H75" s="0" t="inlineStr"/>
+      <c r="I75" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J75" s="0" t="inlineStr"/>
+      <c r="K75" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
@@ -15696,12 +15700,12 @@
       </c>
       <c r="F76" s="0" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H76" s="0" t="inlineStr"/>
@@ -15737,12 +15741,12 @@
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H77" s="0" t="inlineStr"/>
@@ -15761,30 +15765,24 @@
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B78" s="0" t="inlineStr">
-        <is>
-          <t>谷物</t>
-        </is>
-      </c>
+          <t>肉及肉制品</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="inlineStr"/>
       <c r="C78" s="0" t="inlineStr"/>
       <c r="D78" s="0" t="inlineStr"/>
       <c r="E78" s="0" t="inlineStr">
         <is>
-          <t>谷物(稻谷除外)</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="F78" s="0" t="inlineStr">
         <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G78" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G78" s="0" t="n">
+        <v>0.5</v>
       </c>
       <c r="H78" s="0" t="inlineStr"/>
       <c r="I78" s="0" t="inlineStr">
@@ -15802,19 +15800,15 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B79" s="0" t="inlineStr">
-        <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
+          <t>肉及肉制品</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="inlineStr"/>
       <c r="C79" s="0" t="inlineStr"/>
       <c r="D79" s="0" t="inlineStr"/>
       <c r="E79" s="0" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品[糙米、大米(粉)除外]</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="F79" s="0" t="inlineStr">
@@ -15843,7 +15837,7 @@
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>油脂及其制品</t>
         </is>
       </c>
       <c r="B80" s="0" t="inlineStr"/>
@@ -15851,7 +15845,7 @@
       <c r="D80" s="0" t="inlineStr"/>
       <c r="E80" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
         </is>
       </c>
       <c r="F80" s="0" t="inlineStr">
@@ -15860,7 +15854,7 @@
         </is>
       </c>
       <c r="G80" s="0" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="H80" s="0" t="inlineStr"/>
       <c r="I80" s="0" t="inlineStr">
@@ -15878,7 +15872,7 @@
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>油脂及其制品</t>
         </is>
       </c>
       <c r="B81" s="0" t="inlineStr"/>
@@ -15886,7 +15880,7 @@
       <c r="D81" s="0" t="inlineStr"/>
       <c r="E81" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
         </is>
       </c>
       <c r="F81" s="0" t="inlineStr">
@@ -15907,78 +15901,6 @@
       </c>
       <c r="J81" s="0" t="inlineStr"/>
       <c r="K81" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="0" t="inlineStr">
-        <is>
-          <t>油脂及其制品</t>
-        </is>
-      </c>
-      <c r="B82" s="0" t="inlineStr"/>
-      <c r="C82" s="0" t="inlineStr"/>
-      <c r="D82" s="0" t="inlineStr"/>
-      <c r="E82" s="0" t="inlineStr">
-        <is>
-          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
-        </is>
-      </c>
-      <c r="F82" s="0" t="inlineStr">
-        <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G82" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H82" s="0" t="inlineStr"/>
-      <c r="I82" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J82" s="0" t="inlineStr"/>
-      <c r="K82" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="0" t="inlineStr">
-        <is>
-          <t>油脂及其制品</t>
-        </is>
-      </c>
-      <c r="B83" s="0" t="inlineStr"/>
-      <c r="C83" s="0" t="inlineStr"/>
-      <c r="D83" s="0" t="inlineStr"/>
-      <c r="E83" s="0" t="inlineStr">
-        <is>
-          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
-        </is>
-      </c>
-      <c r="F83" s="0" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G83" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="0" t="inlineStr"/>
-      <c r="I83" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J83" s="0" t="inlineStr"/>
-      <c r="K83" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -3218,7 +3218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -7241,12 +7241,12 @@
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
         </is>
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外)</t>
         </is>
       </c>
       <c r="F97" s="0" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="G97" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I97" s="0" t="inlineStr">
@@ -7278,17 +7278,17 @@
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>蛋白饮料</t>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
+          <t>果蔬汁（浆）</t>
         </is>
       </c>
       <c r="E98" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外)</t>
         </is>
       </c>
       <c r="F98" s="0" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="G98" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="I98" s="0" t="inlineStr">
@@ -7323,9 +7323,14 @@
           <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
         </is>
       </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>果蔬汁（浆）</t>
+        </is>
+      </c>
       <c r="E99" s="0" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>葡萄汁</t>
         </is>
       </c>
       <c r="F99" s="0" t="inlineStr">
@@ -7335,7 +7340,7 @@
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="I99" s="0" t="inlineStr">
@@ -7357,12 +7362,12 @@
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
+          <t>固体饮料[包括速溶咖啡、研磨咖啡（烘焙咖啡）]</t>
         </is>
       </c>
       <c r="E100" s="0" t="inlineStr">
         <is>
-          <t>果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外)</t>
+          <t>固体饮料</t>
         </is>
       </c>
       <c r="F100" s="0" t="inlineStr">
@@ -7372,7 +7377,7 @@
       </c>
       <c r="G100" s="0" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I100" s="0" t="inlineStr">
@@ -7380,7 +7385,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="K100" s="0" t="inlineStr">
+      <c r="K100" s="28" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
@@ -7392,9 +7397,19 @@
           <t>饮料类</t>
         </is>
       </c>
+      <c r="B101" s="0" t="inlineStr">
+        <is>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
+        </is>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>浓缩果蔬汁（浆）</t>
+        </is>
+      </c>
       <c r="E101" s="0" t="inlineStr">
         <is>
-          <t>饮料类(果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外))</t>
+          <t>浓缩果蔬汁(浆)</t>
         </is>
       </c>
       <c r="F101" s="0" t="inlineStr">
@@ -7404,7 +7419,7 @@
       </c>
       <c r="G101" s="0" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I101" s="0" t="inlineStr">
@@ -7424,9 +7439,19 @@
           <t>饮料类</t>
         </is>
       </c>
+      <c r="B102" s="0" t="inlineStr">
+        <is>
+          <t>蛋白饮料</t>
+        </is>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
+        </is>
+      </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
-          <t>饮料类(含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外))</t>
+          <t>含乳饮料</t>
         </is>
       </c>
       <c r="F102" s="0" t="inlineStr">
@@ -7453,12 +7478,27 @@
     <row r="103" ht="42" customHeight="1" s="23">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t>饮料类</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B103" s="0" t="inlineStr">
+        <is>
+          <t>谷物制品</t>
+        </is>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
+        </is>
+      </c>
+      <c r="D103" s="0" t="inlineStr">
+        <is>
+          <t>带馅料面米制品</t>
         </is>
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
-          <t>饮料类(葡萄汁)</t>
+          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
       <c r="F103" s="0" t="inlineStr">
@@ -7468,7 +7508,7 @@
       </c>
       <c r="G103" s="0" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I103" s="0" t="inlineStr">
@@ -7482,206 +7522,11 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="56" customHeight="1" s="23">
-      <c r="A104" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="E104" s="0" t="inlineStr">
-        <is>
-          <t>饮料类(固体饮料)</t>
-        </is>
-      </c>
-      <c r="F104" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G104" s="0" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I104" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K104" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="42" customHeight="1" s="23">
-      <c r="A105" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B105" s="0" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="E105" s="0" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="F105" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G105" s="0" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="I105" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K105" s="28" t="inlineStr">
-        <is>
-          <t>GB 8538</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="28" customHeight="1" s="23">
-      <c r="A106" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B106" s="0" t="inlineStr">
-        <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
-        </is>
-      </c>
-      <c r="C106" s="0" t="inlineStr">
-        <is>
-          <t>浓缩果蔬汁（浆）</t>
-        </is>
-      </c>
-      <c r="E106" s="0" t="inlineStr">
-        <is>
-          <t>浓缩果蔬汁(浆)</t>
-        </is>
-      </c>
-      <c r="F106" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G106" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I106" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K106" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="28" customHeight="1" s="23">
-      <c r="A107" s="0" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B107" s="0" t="inlineStr">
-        <is>
-          <t>蛋白饮料</t>
-        </is>
-      </c>
-      <c r="C107" s="0" t="inlineStr">
-        <is>
-          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
-        </is>
-      </c>
-      <c r="E107" s="0" t="inlineStr">
-        <is>
-          <t>含乳饮料</t>
-        </is>
-      </c>
-      <c r="F107" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G107" s="0" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="I107" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K107" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="27" customHeight="1" s="23">
-      <c r="A108" s="0" t="inlineStr">
-        <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B108" s="0" t="inlineStr">
-        <is>
-          <t>谷物制品</t>
-        </is>
-      </c>
-      <c r="C108" s="0" t="inlineStr">
-        <is>
-          <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
-        </is>
-      </c>
-      <c r="D108" s="0" t="inlineStr">
-        <is>
-          <t>带馅料面米制品</t>
-        </is>
-      </c>
-      <c r="E108" s="0" t="inlineStr">
-        <is>
-          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
-        </is>
-      </c>
-      <c r="F108" s="0" t="inlineStr">
-        <is>
-          <t>铅</t>
-        </is>
-      </c>
-      <c r="G108" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I108" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K108" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
-        </is>
-      </c>
-    </row>
+    <row r="104" ht="56" customHeight="1" s="23"/>
+    <row r="105" ht="42" customHeight="1" s="23"/>
+    <row r="106" ht="28" customHeight="1" s="23"/>
+    <row r="107" ht="28" customHeight="1" s="23"/>
+    <row r="108" ht="27" customHeight="1" s="23"/>
     <row r="109" ht="27" customHeight="1" s="23"/>
     <row r="110" ht="42" customHeight="1" s="23"/>
     <row r="111" ht="28" customHeight="1" s="23"/>
@@ -15454,13 +15299,13 @@
       <c r="H70" s="4" t="n"/>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="J70" s="4" t="n"/>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>GB 5009.11</t>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
@@ -15495,13 +15340,13 @@
       <c r="H71" s="4" t="n"/>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="J71" s="4" t="n"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>GB 5009.11</t>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
@@ -18469,12 +18314,16 @@
           <t>饮料类</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n"/>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
       <c r="C35" s="4" t="n"/>
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水(饮用天然矿泉水除外))</t>
+          <t>包装饮用水(饮用天然矿泉水除外)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -18489,12 +18338,12 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>(mg/L, 以NO2-计)</t>
+          <t>(以NO2-计)</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="J35" s="4" t="n"/>
@@ -18510,12 +18359,16 @@
           <t>饮料类</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n"/>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
       <c r="C36" s="4" t="n"/>
       <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水(饮用天然矿泉水除外))</t>
+          <t>包装饮用水(饮用天然矿泉水除外)</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -18531,7 +18384,7 @@
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="J36" s="4" t="n"/>
@@ -18580,7 +18433,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="J37" s="4" t="n"/>
@@ -18629,7 +18482,7 @@
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="J38" s="4" t="n"/>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -6432,7 +6432,7 @@
       <c r="D78" s="19" t="n"/>
       <c r="E78" s="19" t="inlineStr">
         <is>
-          <t>白酒、黄酒</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="F78" s="19" t="inlineStr">
@@ -6451,7 +6451,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J78" s="19" t="n"/>
+      <c r="J78" s="19" t="inlineStr">
+        <is>
+          <t>仅限白酒</t>
+        </is>
+      </c>
       <c r="K78" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
@@ -6477,7 +6481,7 @@
       <c r="D79" s="19" t="n"/>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t>白酒、黄酒</t>
+          <t>黄酒</t>
         </is>
       </c>
       <c r="F79" s="19" t="inlineStr">
@@ -6496,7 +6500,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J79" s="19" t="n"/>
+      <c r="J79" s="19" t="inlineStr">
+        <is>
+          <t>仅限黄酒</t>
+        </is>
+      </c>
       <c r="K79" s="19" t="inlineStr">
         <is>
           <t>GB 5009.12</t>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -15994,11 +15994,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
+      <c r="A8" s="4" t="n"/>
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -15863,16 +15863,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>特殊膳食用食品</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="inlineStr">
@@ -15908,16 +15900,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>特殊膳食用食品</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿配方食品</t>
-        </is>
-      </c>
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="inlineStr">
@@ -15953,11 +15937,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" s="23">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
+      <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -3967,16 +3967,12 @@
           <t>可可制品、巧克力和巧克力制品以及糖果</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
-        </is>
-      </c>
+      <c r="B21" s="19" t="n"/>
       <c r="C21" s="19" t="n"/>
       <c r="D21" s="19" t="n"/>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>可可制品、巧克力和巧克力制品</t>
+          <t>可可制品、巧克力制品以及糖果</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
@@ -12345,7 +12341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -12930,256 +12926,238 @@
           <t>可可制品、巧克力和巧克力制品以及糖果</t>
         </is>
       </c>
-      <c r="B17" s="0" t="inlineStr">
+      <c r="B17" s="0" t="n"/>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>可可制品、巧克力制品以及糖果</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>以As计</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1" s="23">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>可可制品、巧克力和巧克力制品以及糖果</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>可可制品、巧克力制品以及糖果</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>以As计</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1" s="23">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>可可制品、巧克力和巧克力制品以及糖果</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
         </is>
       </c>
-      <c r="E17" s="0" t="inlineStr">
-        <is>
-          <t>可可制品、巧克力和巧克力制品</t>
-        </is>
-      </c>
-      <c r="F17" s="0" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>可可制品、巧克力制品</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>总砷</t>
         </is>
       </c>
-      <c r="G17" s="0" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I17" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J17" s="0" t="inlineStr">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>以As计</t>
         </is>
       </c>
-      <c r="K17" s="0" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="42" customHeight="1" s="23">
-      <c r="A18" s="0" t="inlineStr">
+    <row r="20" ht="28" customHeight="1" s="23">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>可可制品、巧克力和巧克力制品以及糖果</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>可可制品、巧克力制品</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>以As计</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="56" customHeight="1" s="23">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>水产动物及其制品</t>
         </is>
       </c>
-      <c r="E18" s="0" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>水产动物及其制品(鱼类及其制品除外)</t>
         </is>
       </c>
-      <c r="F18" s="0" t="inlineStr">
+      <c r="F21" s="0" t="inlineStr">
         <is>
           <t>总砷</t>
         </is>
       </c>
-      <c r="G18" s="0" t="inlineStr">
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="0" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I18" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J18" s="0" t="inlineStr">
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="K18" s="0" t="inlineStr">
+      <c r="K21" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1" s="23">
-      <c r="A19" s="0" t="inlineStr">
+    <row r="22" ht="56" customHeight="1" s="23">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>水产动物及其制品</t>
         </is>
       </c>
-      <c r="E19" s="0" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>水产动物及其制品(鱼类及其制品除外)</t>
         </is>
       </c>
-      <c r="F19" s="0" t="inlineStr">
+      <c r="F22" s="0" t="inlineStr">
         <is>
           <t>无机砷 a</t>
         </is>
       </c>
-      <c r="G19" s="0" t="inlineStr">
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="H19" s="0" t="inlineStr">
+      <c r="H22" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I19" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J19" s="0" t="inlineStr">
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="K19" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" s="23">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>鱼类及其制品</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="56" customHeight="1" s="23">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>鱼类及其制品</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="56" customHeight="1" s="23">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>油脂及其制品</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>鱼油及其制品、磷虾油及其制品</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K22" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
@@ -13188,29 +13166,33 @@
     <row r="23" ht="56" customHeight="1" s="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
+          <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n"/>
+          <t>鲜、冻水产动物</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>鱼类</t>
+        </is>
+      </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>鱼油及其制品、磷虾油及其制品</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>鱼类及其制品</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="4" t="n"/>
@@ -13219,11 +13201,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13233,29 +13211,33 @@
     <row r="24" ht="56" customHeight="1" s="23">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n"/>
+          <t>鲜、冻水产动物</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>鱼类</t>
+        </is>
+      </c>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>辅食营养补充品</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>鱼类及其制品</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H24" s="4" t="n"/>
@@ -13264,7 +13246,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n"/>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13274,19 +13260,19 @@
     <row r="25" ht="28" customHeight="1" s="23">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>油脂及其制品</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
         </is>
       </c>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(固态、半固态或粉状)</t>
+          <t>鱼油及其制品、磷虾油及其制品</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -13296,7 +13282,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H25" s="4" t="n"/>
@@ -13315,29 +13301,29 @@
     <row r="26" ht="28" customHeight="1" s="23">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>油脂及其制品</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(液态)</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>鱼油及其制品、磷虾油及其制品</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H26" s="4" t="n"/>
@@ -13346,7 +13332,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n"/>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13368,7 +13358,7 @@
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>孕妇及乳母营养补充食品</t>
+          <t>辅食营养补充品</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -13409,17 +13399,17 @@
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>辅食营养补充品</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>运动营养食品(固态、半固态或粉状)</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H28" s="4" t="n"/>
@@ -13450,17 +13440,17 @@
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(固态、半固态或粉状)</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>运动营养食品(液态)</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H29" s="4" t="n"/>
@@ -13491,17 +13481,17 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(液态)</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>孕妇及乳母营养补充食品</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H30" s="4" t="n"/>
@@ -13532,7 +13522,7 @@
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>孕妇及乳母营养补充食品</t>
+          <t>辅食营养补充品</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -13566,23 +13556,19 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>以水产及动物肝脏为原料的产品</t>
-        </is>
-      </c>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n"/>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>以水产及动物肝脏为原料的产品</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>运动营养食品(固态、半固态或粉状)</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -13611,18 +13597,14 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>以水产及动物肝脏为原料的产品</t>
-        </is>
-      </c>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n"/>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>以水产及动物肝脏为原料的产品</t>
+          <t>运动营养食品(液态)</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -13632,7 +13614,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H33" s="4" t="n"/>
@@ -13641,11 +13623,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13660,23 +13638,19 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
-        </is>
-      </c>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>孕妇及乳母营养补充食品</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -13710,23 +13684,23 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+          <t>以水产及动物肝脏为原料的产品</t>
         </is>
       </c>
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>以水产及动物肝脏为原料的产品</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H35" s="4" t="n"/>
@@ -13735,11 +13709,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13759,23 +13729,23 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+          <t>以水产及动物肝脏为原料的产品</t>
         </is>
       </c>
       <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>以水产及动物肝脏为原料的产品</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H36" s="4" t="n"/>
@@ -13784,7 +13754,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n"/>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13804,23 +13778,23 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
         </is>
       </c>
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H37" s="4" t="n"/>
@@ -13829,11 +13803,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13853,23 +13823,23 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>添加藻类的产品</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
         </is>
       </c>
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>添加藻类的产品</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H38" s="4" t="n"/>
@@ -13878,7 +13848,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J38" s="4" t="n"/>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13898,23 +13872,23 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>添加藻类的产品</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
         </is>
       </c>
       <c r="D39" s="4" t="n"/>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>添加藻类的产品</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H39" s="4" t="n"/>
@@ -13923,11 +13897,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13937,29 +13907,33 @@
     <row r="40" ht="28" customHeight="1" s="23">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n"/>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+        </is>
+      </c>
       <c r="D40" s="4" t="n"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H40" s="4" t="n"/>
@@ -13968,7 +13942,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J40" s="4" t="n"/>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13978,24 +13956,28 @@
     <row r="41" ht="28" customHeight="1" s="23">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n"/>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>添加藻类的产品</t>
+        </is>
+      </c>
       <c r="D41" s="4" t="n"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>添加藻类的产品</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -14019,24 +14001,34 @@
     <row r="42" ht="28" customHeight="1" s="23">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
+          <t>特殊膳食用食品</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>添加藻类的产品</t>
+        </is>
+      </c>
       <c r="D42" s="4" t="n"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="n">
-        <v>0.5</v>
+          <t>添加藻类的产品</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
       </c>
       <c r="H42" s="4" t="n"/>
       <c r="I42" s="4" t="inlineStr">
@@ -14044,7 +14036,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J42" s="4" t="n"/>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14054,25 +14050,29 @@
     <row r="43" ht="28" customHeight="1" s="23">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>调味品</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n"/>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
       <c r="C43" s="4" t="n"/>
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>新鲜蔬菜</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H43" s="4" t="n"/>
@@ -14081,11 +14081,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J43" s="4" t="n"/>
       <c r="K43" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14095,24 +14091,24 @@
     <row r="44" ht="28" customHeight="1" s="23">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>调味品</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
         </is>
       </c>
       <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>复合调味料</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>新鲜蔬菜</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -14139,27 +14135,21 @@
           <t>调味品</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
-        </is>
-      </c>
+      <c r="B45" s="4" t="n"/>
       <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>复合调味料</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="n">
+        <v>0.5</v>
       </c>
       <c r="H45" s="4" t="n"/>
       <c r="I45" s="4" t="inlineStr">
@@ -14167,11 +14157,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14184,21 +14170,17 @@
           <t>调味品</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>水产调味品</t>
-        </is>
-      </c>
+      <c r="B46" s="4" t="n"/>
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>水产调味品(鱼类调味品除外)</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -14212,7 +14194,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J46" s="4" t="n"/>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14227,23 +14213,25 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>水产调味品</t>
+          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
         </is>
       </c>
       <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="n"/>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>水产调味品(鱼类调味品除外)</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G47" s="10" t="n">
-        <v>0.5</v>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>复合调味料</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H47" s="4" t="n"/>
       <c r="I47" s="4" t="inlineStr">
@@ -14251,11 +14239,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J47" s="4" t="n"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14270,28 +14254,24 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>水产调味品</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>鱼类调味品（例如：鱼露等）</t>
-        </is>
-      </c>
+          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>鱼类调味品</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>复合调味料</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H48" s="4" t="n"/>
@@ -14300,7 +14280,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J48" s="4" t="n"/>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14318,25 +14302,21 @@
           <t>水产调味品</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>鱼类调味品（例如：鱼露等）</t>
-        </is>
-      </c>
+      <c r="C49" s="4" t="n"/>
       <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>鱼类调味品</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>水产调味品(鱼类调味品除外)</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H49" s="4" t="n"/>
@@ -14345,11 +14325,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14359,34 +14335,28 @@
     <row r="50" ht="42" customHeight="1" s="23">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>调味品</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>谷物</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>稻谷</t>
-        </is>
-      </c>
+          <t>水产调味品</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n"/>
       <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>稻谷</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>水产调味品(鱼类调味品除外)</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>0.5</v>
       </c>
       <c r="H50" s="4" t="n"/>
       <c r="I50" s="4" t="inlineStr">
@@ -14396,7 +14366,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -14408,33 +14378,33 @@
     <row r="51" ht="42" customHeight="1" s="23">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>调味品</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>谷物</t>
+          <t>水产调味品</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>稻谷</t>
+          <t>鱼类调味品（例如：鱼露等）</t>
         </is>
       </c>
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>稻谷</t>
-        </is>
-      </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>鱼类调味品</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H51" s="4" t="n"/>
@@ -14453,33 +14423,33 @@
     <row r="52" ht="42" customHeight="1" s="23">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
+          <t>调味品</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
+          <t>水产调味品</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>大米（粉）</t>
+          <t>鱼类调味品（例如：鱼露等）</t>
         </is>
       </c>
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>大米(粉)</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>鱼类调味品</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H52" s="4" t="n"/>
@@ -14488,7 +14458,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J52" s="4" t="n"/>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14503,28 +14477,28 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
+          <t>谷物</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>大米（粉）</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>大米(粉)</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>稻谷</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H53" s="4" t="n"/>
@@ -14533,7 +14507,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J53" s="4" t="n"/>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14548,28 +14526,28 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
+          <t>谷物</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>糙米（包括色稻米）</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="D54" s="4" t="n"/>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>糙米</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>稻谷</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="H54" s="4" t="n"/>
@@ -14598,23 +14576,23 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>糙米（包括色稻米）</t>
+          <t>大米（粉）</t>
         </is>
       </c>
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>糙米</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>大米(粉)</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H55" s="4" t="n"/>
@@ -14633,25 +14611,33 @@
     <row r="56" ht="42" customHeight="1" s="23">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>大米（粉）</t>
+        </is>
+      </c>
       <c r="D56" s="4" t="n"/>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>大米(粉)</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H56" s="4" t="n"/>
@@ -14661,30 +14647,42 @@
         </is>
       </c>
       <c r="J56" s="4" t="n"/>
-      <c r="K56" s="4" t="n"/>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="42" customHeight="1" s="23">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="n"/>
-      <c r="C57" s="4" t="n"/>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>糙米（包括色稻米）</t>
+        </is>
+      </c>
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
-        </is>
-      </c>
-      <c r="F57" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>糙米</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H57" s="4" t="n"/>
@@ -14693,11 +14691,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14707,33 +14701,33 @@
     <row r="58" ht="42" customHeight="1" s="23">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>谷物碾磨加工品</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
+          <t>糙米（包括色稻米）</t>
         </is>
       </c>
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>糙米</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="H58" s="4" t="n"/>
@@ -14755,52 +14749,32 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
-        </is>
-      </c>
-      <c r="F59" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>(干重计)</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="n"/>
       <c r="I59" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
+      <c r="J59" s="4" t="n"/>
+      <c r="K59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -14808,34 +14782,22 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>食用菌制品</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>木耳制品、银耳制品</t>
-        </is>
-      </c>
+      <c r="B60" s="4" t="n"/>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="n"/>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H60" s="4" t="n"/>
@@ -14844,7 +14806,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J60" s="4" t="n"/>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14859,49 +14825,37 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>木耳制品、银耳制品</t>
-        </is>
-      </c>
+          <t>木耳 （毛木耳,黑木耳）</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>(干重计)</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="n"/>
       <c r="I61" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14921,7 +14875,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>银耳</t>
+          <t>木耳 （毛木耳,黑木耳）</t>
         </is>
       </c>
       <c r="D62" s="4" t="n"/>
@@ -14930,23 +14884,31 @@
           <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="n"/>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>(干重计)</t>
+        </is>
+      </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J62" s="4" t="n"/>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14961,45 +14923,41 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>食用菌制品</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>银耳</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="n"/>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>木耳制品、银耳制品</t>
+        </is>
+      </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>(干重计)</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="n"/>
       <c r="I63" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15014,37 +14972,49 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>食用菌制品</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>松茸</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="n"/>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>木耳制品、银耳制品</t>
+        </is>
+      </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>松茸及其制品</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>木耳及其制品、银耳及其制品</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="n"/>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>(干重计)</t>
+        </is>
+      </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J64" s="4" t="n"/>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15064,23 +15034,23 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>松茸</t>
+          <t>银耳</t>
         </is>
       </c>
       <c r="D65" s="4" t="n"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>松茸及其制品</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>木耳及其制品、银耳及其制品</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H65" s="4" t="n"/>
@@ -15089,11 +15059,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15108,41 +15074,45 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>松茸制品</t>
-        </is>
-      </c>
+          <t>银耳</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="n"/>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>松茸及其制品</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>木耳及其制品、银耳及其制品</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="n"/>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>(干重计)</t>
+        </is>
+      </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J66" s="4" t="n"/>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15157,32 +15127,28 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>松茸制品</t>
-        </is>
-      </c>
+          <t>松茸</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="n"/>
       <c r="E67" s="4" t="inlineStr">
         <is>
           <t>松茸及其制品</t>
         </is>
       </c>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H67" s="4" t="n"/>
@@ -15191,11 +15157,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15205,25 +15167,33 @@
     <row r="68" ht="42" customHeight="1" s="23">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="n"/>
-      <c r="C68" s="4" t="n"/>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
       <c r="D68" s="4" t="n"/>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>松茸及其制品</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="H68" s="4" t="n"/>
@@ -15232,7 +15202,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J68" s="4" t="n"/>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15242,20 +15216,32 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="n"/>
-      <c r="C69" s="4" t="n"/>
-      <c r="D69" s="4" t="n"/>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>食用菌制品</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>松茸制品</t>
+        </is>
+      </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="F69" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>松茸及其制品</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -15279,110 +15265,110 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>饮料类</t>
+          <t>食用菌及其制品</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="n"/>
-      <c r="D70" s="4" t="n"/>
+          <t>食用菌制品</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>松茸制品</t>
+        </is>
+      </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>松茸及其制品</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="H70" s="4" t="n"/>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="J70" s="4" t="n"/>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>GB 8538</t>
+          <t>GB 5009.11</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="n"/>
       <c r="C71" s="4" t="n"/>
       <c r="D71" s="4" t="n"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H71" s="4" t="n"/>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>mg/kg</t>
         </is>
       </c>
       <c r="J71" s="4" t="n"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>GB 8538</t>
+          <t>GB 5009.11</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="B72" s="11" t="inlineStr">
-        <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n"/>
+      <c r="C72" s="4" t="n"/>
       <c r="D72" s="4" t="n"/>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>鱼类及其制品</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -15406,169 +15392,173 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="B73" s="11" t="inlineStr">
-        <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n"/>
+      <c r="D73" s="4" t="n"/>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>鱼类及其制品</t>
-        </is>
-      </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H73" s="4" t="n"/>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="n"/>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>GB 8538</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n"/>
+      <c r="D74" s="4" t="n"/>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="n"/>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="n"/>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>GB 8538</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>水产动物及其制品</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>水产制品</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>鱼类制品</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>鱼类及其制品</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>水产动物及其制品</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>水产制品</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>鱼类制品</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>鱼类及其制品</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="K73" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="0" t="inlineStr">
-        <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B74" s="0" t="inlineStr">
-        <is>
-          <t>谷物</t>
-        </is>
-      </c>
-      <c r="C74" s="0" t="inlineStr"/>
-      <c r="D74" s="0" t="inlineStr"/>
-      <c r="E74" s="0" t="inlineStr">
-        <is>
-          <t>谷物(稻谷除外)</t>
-        </is>
-      </c>
-      <c r="F74" s="0" t="inlineStr">
-        <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G74" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H74" s="0" t="inlineStr"/>
-      <c r="I74" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J74" s="0" t="inlineStr"/>
-      <c r="K74" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="0" t="inlineStr">
-        <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B75" s="0" t="inlineStr">
-        <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C75" s="0" t="inlineStr"/>
-      <c r="D75" s="0" t="inlineStr"/>
-      <c r="E75" s="0" t="inlineStr">
-        <is>
-          <t>谷物碾磨加工品[糙米、大米(粉)除外]</t>
-        </is>
-      </c>
-      <c r="F75" s="0" t="inlineStr">
-        <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G75" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H75" s="0" t="inlineStr"/>
-      <c r="I75" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J75" s="0" t="inlineStr"/>
-      <c r="K75" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="0" t="inlineStr">
-        <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B76" s="0" t="inlineStr">
-        <is>
-          <t>谷物</t>
-        </is>
-      </c>
-      <c r="C76" s="0" t="inlineStr"/>
-      <c r="D76" s="0" t="inlineStr"/>
-      <c r="E76" s="0" t="inlineStr">
-        <is>
-          <t>谷物(稻谷除外)</t>
-        </is>
-      </c>
-      <c r="F76" s="0" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G76" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="0" t="inlineStr"/>
-      <c r="I76" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J76" s="0" t="inlineStr"/>
-      <c r="K76" s="0" t="inlineStr">
+      <c r="K76" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
@@ -15582,24 +15572,24 @@
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
+          <t>谷物</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr"/>
       <c r="D77" s="0" t="inlineStr"/>
       <c r="E77" s="0" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品[糙米、大米(粉)除外]</t>
+          <t>谷物(稻谷除外)</t>
         </is>
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
-          <t>无机砷 a</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H77" s="0" t="inlineStr"/>
@@ -15618,15 +15608,19 @@
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
-        </is>
-      </c>
-      <c r="B78" s="0" t="inlineStr"/>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="inlineStr">
+        <is>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
       <c r="C78" s="0" t="inlineStr"/>
       <c r="D78" s="0" t="inlineStr"/>
       <c r="E78" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>谷物碾磨加工品[糙米、大米(粉)除外]</t>
         </is>
       </c>
       <c r="F78" s="0" t="inlineStr">
@@ -15634,8 +15628,10 @@
           <t>总砷</t>
         </is>
       </c>
-      <c r="G78" s="0" t="n">
-        <v>0.5</v>
+      <c r="G78" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
       <c r="H78" s="0" t="inlineStr"/>
       <c r="I78" s="0" t="inlineStr">
@@ -15653,15 +15649,19 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
-        </is>
-      </c>
-      <c r="B79" s="0" t="inlineStr"/>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="inlineStr">
+        <is>
+          <t>谷物</t>
+        </is>
+      </c>
       <c r="C79" s="0" t="inlineStr"/>
       <c r="D79" s="0" t="inlineStr"/>
       <c r="E79" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>谷物(稻谷除外)</t>
         </is>
       </c>
       <c r="F79" s="0" t="inlineStr">
@@ -15690,24 +15690,30 @@
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
-        </is>
-      </c>
-      <c r="B80" s="0" t="inlineStr"/>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="inlineStr">
+        <is>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
       <c r="C80" s="0" t="inlineStr"/>
       <c r="D80" s="0" t="inlineStr"/>
       <c r="E80" s="0" t="inlineStr">
         <is>
-          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
+          <t>谷物碾磨加工品[糙米、大米(粉)除外]</t>
         </is>
       </c>
       <c r="F80" s="0" t="inlineStr">
         <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G80" s="0" t="n">
-        <v>0.1</v>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G80" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H80" s="0" t="inlineStr"/>
       <c r="I80" s="0" t="inlineStr">
@@ -15725,7 +15731,7 @@
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="B81" s="0" t="inlineStr"/>
@@ -15733,18 +15739,16 @@
       <c r="D81" s="0" t="inlineStr"/>
       <c r="E81" s="0" t="inlineStr">
         <is>
-          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="F81" s="0" t="inlineStr">
         <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G81" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G81" s="0" t="n">
+        <v>0.5</v>
       </c>
       <c r="H81" s="0" t="inlineStr"/>
       <c r="I81" s="0" t="inlineStr">
@@ -15754,6 +15758,115 @@
       </c>
       <c r="J81" s="0" t="inlineStr"/>
       <c r="K81" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="inlineStr">
+        <is>
+          <t>肉及肉制品</t>
+        </is>
+      </c>
+      <c r="B82" s="0" t="inlineStr"/>
+      <c r="C82" s="0" t="inlineStr"/>
+      <c r="D82" s="0" t="inlineStr"/>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t>肉及肉制品</t>
+        </is>
+      </c>
+      <c r="F82" s="0" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G82" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="0" t="inlineStr"/>
+      <c r="I82" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J82" s="0" t="inlineStr"/>
+      <c r="K82" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="inlineStr">
+        <is>
+          <t>油脂及其制品</t>
+        </is>
+      </c>
+      <c r="B83" s="0" t="inlineStr"/>
+      <c r="C83" s="0" t="inlineStr"/>
+      <c r="D83" s="0" t="inlineStr"/>
+      <c r="E83" s="0" t="inlineStr">
+        <is>
+          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
+        </is>
+      </c>
+      <c r="F83" s="0" t="inlineStr">
+        <is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G83" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H83" s="0" t="inlineStr"/>
+      <c r="I83" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J83" s="0" t="inlineStr"/>
+      <c r="K83" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="inlineStr">
+        <is>
+          <t>油脂及其制品</t>
+        </is>
+      </c>
+      <c r="B84" s="0" t="inlineStr"/>
+      <c r="C84" s="0" t="inlineStr"/>
+      <c r="D84" s="0" t="inlineStr"/>
+      <c r="E84" s="0" t="inlineStr">
+        <is>
+          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
+        </is>
+      </c>
+      <c r="F84" s="0" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G84" s="0" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="0" t="inlineStr"/>
+      <c r="I84" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J84" s="0" t="inlineStr"/>
+      <c r="K84" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
@@ -15863,8 +15976,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>特殊膳食用食品</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="inlineStr">
@@ -15900,8 +16021,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>特殊膳食用食品</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>婴幼儿配方食品</t>
+        </is>
+      </c>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="inlineStr">
@@ -15937,7 +16066,11 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" s="23">
-      <c r="A7" s="4" t="n"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -12959,121 +12959,121 @@
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" s="23">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>可可制品、巧克力和巧克力制品以及糖果</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>可可制品、巧克力制品以及糖果</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="0" t="inlineStr">
         <is>
           <t>无机砷 a</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t>以As计</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" s="23">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>可可制品、巧克力和巧克力制品以及糖果</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>可可制品、巧克力制品</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="0" t="inlineStr">
         <is>
           <t>总砷</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>以As计</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" s="23">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>可可制品、巧克力和巧克力制品以及糖果</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>可可制品、巧克力制品</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="0" t="inlineStr">
         <is>
           <t>无机砷 a</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
         <is>
           <t>以As计</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
@@ -13684,10 +13684,14 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
+          <t>婴幼儿罐装辅助食品</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
           <t>以水产及动物肝脏为原料的产品</t>
         </is>
       </c>
-      <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
           <t>以水产及动物肝脏为原料的产品</t>
@@ -13729,10 +13733,14 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
+          <t>婴幼儿罐装辅助食品</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
           <t>以水产及动物肝脏为原料的产品</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
           <t>以水产及动物肝脏为原料的产品</t>
@@ -13778,10 +13786,10 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="n"/>
+          <t>婴幼儿罐装辅助食品</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
           <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
@@ -13823,10 +13831,10 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="n"/>
+          <t>婴幼儿罐装辅助食品</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
           <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
@@ -13872,10 +13880,10 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="n"/>
+          <t>婴幼儿谷类辅助食品</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
       <c r="E39" s="4" t="inlineStr">
         <is>
           <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
@@ -13917,10 +13925,10 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="n"/>
+          <t>婴幼儿谷类辅助食品</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
           <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
@@ -13966,10 +13974,14 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
+          <t>婴幼儿谷类辅助食品</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
           <t>添加藻类的产品</t>
         </is>
       </c>
-      <c r="D41" s="4" t="n"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
           <t>添加藻类的产品</t>
@@ -14011,10 +14023,14 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
+          <t>婴幼儿谷类辅助食品</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
           <t>添加藻类的产品</t>
         </is>
       </c>
-      <c r="D42" s="4" t="n"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
           <t>添加藻类的产品</t>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -15992,16 +15992,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>特殊膳食用食品</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="inlineStr">
@@ -16037,16 +16029,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>特殊膳食用食品</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿配方食品</t>
-        </is>
-      </c>
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="inlineStr">
@@ -16082,11 +16066,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" s="23">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
+      <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -3972,7 +3972,7 @@
       <c r="D21" s="19" t="n"/>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>可可制品、巧克力制品以及糖果</t>
+          <t>可可制品、巧克力和巧克力制品以及糖果</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
@@ -12341,7 +12341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -12926,10 +12926,14 @@
           <t>可可制品、巧克力和巧克力制品以及糖果</t>
         </is>
       </c>
-      <c r="B17" s="0" t="n"/>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
+        </is>
+      </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t>可可制品、巧克力制品以及糖果</t>
+          <t>可可制品、巧克力和巧克力制品</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
@@ -12964,9 +12968,14 @@
           <t>可可制品、巧克力和巧克力制品以及糖果</t>
         </is>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
+        </is>
+      </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t>可可制品、巧克力制品以及糖果</t>
+          <t>可可制品、巧克力和巧克力制品</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
@@ -12998,17 +13007,12 @@
     <row r="19" ht="28" customHeight="1" s="23">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t>可可制品、巧克力和巧克力制品以及糖果</t>
-        </is>
-      </c>
-      <c r="B19" s="0" t="inlineStr">
-        <is>
-          <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
+          <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>可可制品、巧克力制品</t>
+          <t>水产动物及其制品(鱼类及其制品除外)</t>
         </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
@@ -13018,6 +13022,11 @@
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
           <t>0.5</t>
         </is>
       </c>
@@ -13028,7 +13037,7 @@
       </c>
       <c r="J19" s="0" t="inlineStr">
         <is>
-          <t>以As计</t>
+          <t>a</t>
         </is>
       </c>
       <c r="K19" s="0" t="inlineStr">
@@ -13040,17 +13049,12 @@
     <row r="20" ht="28" customHeight="1" s="23">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t>可可制品、巧克力和巧克力制品以及糖果</t>
-        </is>
-      </c>
-      <c r="B20" s="0" t="inlineStr">
-        <is>
-          <t>可可制品、巧克力和巧克力制品（包括代可可脂巧克力及制品）</t>
+          <t>水产动物及其制品</t>
         </is>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t>可可制品、巧克力制品</t>
+          <t>水产动物及其制品(鱼类及其制品除外)</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
@@ -13060,6 +13064,11 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H20" s="0" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
@@ -13070,7 +13079,7 @@
       </c>
       <c r="J20" s="0" t="inlineStr">
         <is>
-          <t>以As计</t>
+          <t>a</t>
         </is>
       </c>
       <c r="K20" s="0" t="inlineStr">
@@ -13080,84 +13089,94 @@
       </c>
     </row>
     <row r="21" ht="56" customHeight="1" s="23">
-      <c r="A21" s="0" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>水产动物及其制品</t>
         </is>
       </c>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t>水产动物及其制品(鱼类及其制品除外)</t>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>鲜、冻水产动物</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>鱼类</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>鱼类及其制品</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>总砷</t>
         </is>
       </c>
-      <c r="G21" s="0" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H21" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I21" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J21" s="0" t="inlineStr">
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="56" customHeight="1" s="23">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>水产动物及其制品</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>鲜、冻水产动物</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>鱼类</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>鱼类及其制品</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="K21" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="56" customHeight="1" s="23">
-      <c r="A22" s="0" t="inlineStr">
-        <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t>水产动物及其制品(鱼类及其制品除外)</t>
-        </is>
-      </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H22" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I22" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J22" s="0" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="K22" s="0" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
@@ -13166,23 +13185,19 @@
     <row r="23" ht="56" customHeight="1" s="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>油脂及其制品</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
+          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>鱼类及其制品</t>
+          <t>鱼油及其制品、磷虾油及其制品</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -13211,23 +13226,19 @@
     <row r="24" ht="56" customHeight="1" s="23">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>水产动物及其制品</t>
+          <t>油脂及其制品</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
+          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>鱼类及其制品</t>
+          <t>鱼油及其制品、磷虾油及其制品</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -13260,19 +13271,19 @@
     <row r="25" ht="28" customHeight="1" s="23">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
         </is>
       </c>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>鱼油及其制品、磷虾油及其制品</t>
+          <t>辅食营养补充品</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -13282,7 +13293,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H25" s="4" t="n"/>
@@ -13301,29 +13312,29 @@
     <row r="26" ht="28" customHeight="1" s="23">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>油脂及其制品</t>
+          <t>特殊膳食用食品</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>鱼油及其制品、磷虾油及其制品</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>运动营养食品(固态、半固态或粉状)</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H26" s="4" t="n"/>
@@ -13332,11 +13343,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13358,7 +13365,7 @@
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>辅食营养补充品</t>
+          <t>运动营养食品(液态)</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -13368,7 +13375,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H27" s="4" t="n"/>
@@ -13399,7 +13406,7 @@
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(固态、半固态或粉状)</t>
+          <t>孕妇及乳母营养补充食品</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -13440,17 +13447,17 @@
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(液态)</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>辅食营养补充品</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H29" s="4" t="n"/>
@@ -13481,17 +13488,17 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>孕妇及乳母营养补充食品</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>总砷</t>
+          <t>运动营养食品(固态、半固态或粉状)</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H30" s="4" t="n"/>
@@ -13522,7 +13529,7 @@
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>辅食营养补充品</t>
+          <t>运动营养食品(液态)</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -13563,7 +13570,7 @@
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(固态、半固态或粉状)</t>
+          <t>孕妇及乳母营养补充食品</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -13597,19 +13604,27 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>婴幼儿罐装辅助食品</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>以水产及动物肝脏为原料的产品</t>
+        </is>
+      </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>运动营养食品(液态)</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
+          <t>以水产及动物肝脏为原料的产品</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>总砷</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -13638,14 +13653,22 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="n"/>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>婴幼儿罐装辅助食品</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>以水产及动物肝脏为原料的产品</t>
+        </is>
+      </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>孕妇及乳母营养补充食品</t>
+          <t>以水产及动物肝脏为原料的产品</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -13655,7 +13678,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H34" s="4" t="n"/>
@@ -13664,7 +13687,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J34" s="4" t="n"/>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -13687,14 +13714,10 @@
           <t>婴幼儿罐装辅助食品</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>以水产及动物肝脏为原料的产品</t>
-        </is>
-      </c>
+      <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>以水产及动物肝脏为原料的产品</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -13736,14 +13759,10 @@
           <t>婴幼儿罐装辅助食品</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>以水产及动物肝脏为原料的产品</t>
-        </is>
-      </c>
+      <c r="D36" s="4" t="inlineStr"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>以水产及动物肝脏为原料的产品</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -13753,7 +13772,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H36" s="4" t="n"/>
@@ -13786,13 +13805,13 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品</t>
+          <t>婴幼儿谷类辅助食品</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -13831,13 +13850,13 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品</t>
+          <t>婴幼儿谷类辅助食品</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -13847,7 +13866,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H38" s="4" t="n"/>
@@ -13883,10 +13902,14 @@
           <t>婴幼儿谷类辅助食品</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>添加藻类的产品</t>
+        </is>
+      </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+          <t>添加藻类的产品</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -13928,10 +13951,14 @@
           <t>婴幼儿谷类辅助食品</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>添加藻类的产品</t>
+        </is>
+      </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+          <t>添加藻类的产品</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -13941,7 +13968,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="H40" s="4" t="n"/>
@@ -13964,27 +13991,19 @@
     <row r="41" ht="28" customHeight="1" s="23">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿谷类辅助食品</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>添加藻类的产品</t>
-        </is>
-      </c>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>添加藻类的产品</t>
+          <t>新鲜蔬菜</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -13994,7 +14013,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H41" s="4" t="n"/>
@@ -14013,27 +14032,19 @@
     <row r="42" ht="28" customHeight="1" s="23">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>特殊膳食用食品</t>
+          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>婴幼儿谷类辅助食品</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>添加藻类的产品</t>
-        </is>
-      </c>
+          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>添加藻类的产品</t>
+          <t>新鲜蔬菜</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -14043,7 +14054,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H42" s="4" t="n"/>
@@ -14052,11 +14063,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14066,19 +14073,15 @@
     <row r="43" ht="28" customHeight="1" s="23">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
-        </is>
-      </c>
+          <t>调味品</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n"/>
       <c r="C43" s="4" t="n"/>
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜</t>
+          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -14086,10 +14089,8 @@
           <t>总砷</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="G43" s="10" t="n">
+        <v>0.5</v>
       </c>
       <c r="H43" s="4" t="n"/>
       <c r="I43" s="4" t="inlineStr">
@@ -14107,19 +14108,15 @@
     <row r="44" ht="28" customHeight="1" s="23">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>蔬菜及其制品（包括薯类，不包括食用菌）</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>新鲜蔬菜（未经加工的、经表面处理的、去皮或预切的、冷冻的蔬菜）</t>
-        </is>
-      </c>
+          <t>调味品</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n"/>
       <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>新鲜蔬菜</t>
+          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -14138,7 +14135,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J44" s="4" t="n"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14151,12 +14152,16 @@
           <t>调味品</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n"/>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
+        </is>
+      </c>
       <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
+          <t>复合调味料</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -14164,8 +14169,10 @@
           <t>总砷</t>
         </is>
       </c>
-      <c r="G45" s="10" t="n">
-        <v>0.5</v>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H45" s="4" t="n"/>
       <c r="I45" s="4" t="inlineStr">
@@ -14186,12 +14193,16 @@
           <t>调味品</t>
         </is>
       </c>
-      <c r="B46" s="4" t="n"/>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
+        </is>
+      </c>
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>调味品 (水产调味品、复合调味料和香辛料类除外)</t>
+          <t>复合调味料</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -14201,7 +14212,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H46" s="4" t="n"/>
@@ -14229,14 +14240,14 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
+          <t>水产调味品</t>
         </is>
       </c>
       <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>复合调味料</t>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>水产调味品(鱼类调味品除外)</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -14270,14 +14281,14 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>复合调味料（例如：调味料酒、固体汤料、鸡精、鸡粉、蛋黄酱、沙拉酱、调味清汁等）</t>
+          <t>水产调味品</t>
         </is>
       </c>
       <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>复合调味料</t>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>水产调味品(鱼类调味品除外)</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -14285,10 +14296,8 @@
           <t>无机砷 a</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="G48" s="10" t="n">
+        <v>0.5</v>
       </c>
       <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="inlineStr">
@@ -14318,11 +14327,15 @@
           <t>水产调味品</t>
         </is>
       </c>
-      <c r="C49" s="4" t="n"/>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>鱼类调味品（例如：鱼露等）</t>
+        </is>
+      </c>
       <c r="D49" s="4" t="n"/>
-      <c r="E49" s="11" t="inlineStr">
-        <is>
-          <t>水产调味品(鱼类调味品除外)</t>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>鱼类调味品</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -14359,11 +14372,15 @@
           <t>水产调味品</t>
         </is>
       </c>
-      <c r="C50" s="4" t="n"/>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>鱼类调味品（例如：鱼露等）</t>
+        </is>
+      </c>
       <c r="D50" s="4" t="n"/>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>水产调味品(鱼类调味品除外)</t>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>鱼类调味品</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -14371,8 +14388,10 @@
           <t>无机砷 a</t>
         </is>
       </c>
-      <c r="G50" s="10" t="n">
-        <v>0.5</v>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
       </c>
       <c r="H50" s="4" t="n"/>
       <c r="I50" s="4" t="inlineStr">
@@ -14394,23 +14413,23 @@
     <row r="51" ht="42" customHeight="1" s="23">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>调味品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>水产调味品</t>
+          <t>谷物</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>鱼类调味品（例如：鱼露等）</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>鱼类调味品</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -14429,7 +14448,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J51" s="4" t="n"/>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14439,23 +14462,23 @@
     <row r="52" ht="42" customHeight="1" s="23">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>调味品</t>
+          <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>水产调味品</t>
+          <t>谷物</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>鱼类调味品（例如：鱼露等）</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>鱼类调味品</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -14465,7 +14488,7 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="H52" s="4" t="n"/>
@@ -14474,11 +14497,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14493,18 +14512,18 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>谷物</t>
+          <t>谷物碾磨加工品</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>稻谷</t>
+          <t>大米（粉）</t>
         </is>
       </c>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>稻谷</t>
+          <t>大米(粉)</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -14523,11 +14542,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J53" s="4" t="n"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14542,18 +14557,18 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>谷物</t>
+          <t>谷物碾磨加工品</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>稻谷</t>
+          <t>大米（粉）</t>
         </is>
       </c>
       <c r="D54" s="4" t="n"/>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>稻谷</t>
+          <t>大米(粉)</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -14563,7 +14578,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="H54" s="4" t="n"/>
@@ -14592,13 +14607,13 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>大米（粉）</t>
+          <t>糙米（包括色稻米）</t>
         </is>
       </c>
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>大米(粉)</t>
+          <t>糙米</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -14637,13 +14652,13 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>大米（粉）</t>
+          <t>糙米（包括色稻米）</t>
         </is>
       </c>
       <c r="D56" s="4" t="n"/>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>大米(粉)</t>
+          <t>糙米</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -14653,7 +14668,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="H56" s="4" t="n"/>
@@ -14672,23 +14687,15 @@
     <row r="57" ht="42" customHeight="1" s="23">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>糙米（包括色稻米）</t>
-        </is>
-      </c>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>糙米</t>
+          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -14708,32 +14715,20 @@
         </is>
       </c>
       <c r="J57" s="4" t="n"/>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
+      <c r="K57" s="4" t="n"/>
     </row>
     <row r="58" ht="42" customHeight="1" s="23">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>糙米（包括色稻米）</t>
-        </is>
-      </c>
+          <t>食用菌及其制品</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>糙米</t>
+          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -14743,7 +14738,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H58" s="4" t="n"/>
@@ -14752,7 +14747,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J58" s="4" t="n"/>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -14765,12 +14764,20 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B59" s="4" t="n"/>
-      <c r="C59" s="4" t="n"/>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>木耳 （毛木耳,黑木耳）</t>
+        </is>
+      </c>
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -14790,7 +14797,11 @@
         </is>
       </c>
       <c r="J59" s="4" t="n"/>
-      <c r="K59" s="4" t="n"/>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>GB 5009.11</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -14798,12 +14809,20 @@
           <t>食用菌及其制品</t>
         </is>
       </c>
-      <c r="B60" s="4" t="n"/>
-      <c r="C60" s="4" t="n"/>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>木耳 （毛木耳,黑木耳）</t>
+        </is>
+      </c>
       <c r="D60" s="4" t="n"/>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品(松茸及其制品、木耳及其制品、银耳及其制品除外)</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -14816,7 +14835,11 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="H60" s="4" t="n"/>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>(干重计)</t>
+        </is>
+      </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -14841,15 +14864,19 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>食用菌制品</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="n"/>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>木耳制品、银耳制品</t>
+        </is>
+      </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
@@ -14886,15 +14913,19 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>食用菌制品</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="n"/>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>木耳制品、银耳制品</t>
+        </is>
+      </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
@@ -14939,19 +14970,15 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>木耳制品、银耳制品</t>
-        </is>
-      </c>
+          <t>银耳</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="n"/>
       <c r="E63" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
@@ -14988,19 +15015,15 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>食用菌制品</t>
+          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>木耳制品、银耳制品</t>
-        </is>
-      </c>
+          <t>银耳</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="n"/>
       <c r="E64" s="4" t="inlineStr">
         <is>
           <t>木耳及其制品、银耳及其制品</t>
@@ -15050,13 +15073,13 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>银耳</t>
+          <t>松茸</t>
         </is>
       </c>
       <c r="D65" s="4" t="n"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>松茸及其制品</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -15095,13 +15118,13 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>银耳</t>
+          <t>松茸</t>
         </is>
       </c>
       <c r="D66" s="4" t="n"/>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>松茸及其制品</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
@@ -15111,14 +15134,10 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>(干重计)</t>
-        </is>
-      </c>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="n"/>
       <c r="I66" s="4" t="inlineStr">
         <is>
           <t>mg/kg</t>
@@ -15143,15 +15162,19 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>食用菌制品</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>松茸</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="n"/>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>松茸制品</t>
+        </is>
+      </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
           <t>松茸及其制品</t>
@@ -15188,15 +15211,19 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>新鲜食用菌（未经加工的、经表面处理的、预切的、冷冻的食用菌）</t>
+          <t>食用菌制品</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>松茸</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="n"/>
+          <t>其他食用菌制品</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>松茸制品</t>
+        </is>
+      </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
           <t>松茸及其制品</t>
@@ -15232,27 +15259,15 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>食用菌制品</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>松茸制品</t>
-        </is>
-      </c>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>松茸及其制品</t>
+          <t>食糖及淀粉糖</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -15262,7 +15277,7 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="H69" s="4" t="n"/>
@@ -15281,27 +15296,15 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>食用菌及其制品</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>食用菌制品</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>其他食用菌制品</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>松茸制品</t>
-        </is>
-      </c>
+          <t>食糖及淀粉糖</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="n"/>
+      <c r="C70" s="4" t="n"/>
+      <c r="D70" s="4" t="n"/>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>松茸及其制品</t>
+          <t>食糖及淀粉糖</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -15311,7 +15314,7 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H70" s="4" t="n"/>
@@ -15320,11 +15323,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J70" s="4" t="n"/>
       <c r="K70" s="4" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
@@ -15334,15 +15333,19 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="n"/>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
       <c r="C71" s="4" t="n"/>
       <c r="D71" s="4" t="n"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -15352,34 +15355,38 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H71" s="4" t="n"/>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="J71" s="4" t="n"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>GB 5009.11</t>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="n"/>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
       <c r="C72" s="4" t="n"/>
       <c r="D72" s="4" t="n"/>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>食糖及淀粉糖</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
@@ -15395,32 +15402,36 @@
       <c r="H72" s="4" t="n"/>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>mg/L</t>
         </is>
       </c>
       <c r="J72" s="4" t="n"/>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>GB 5009.11</t>
+          <t>GB 8538</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="n"/>
+          <t>水产动物及其制品</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>水产制品</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>鱼类制品</t>
+        </is>
+      </c>
       <c r="D73" s="4" t="n"/>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
+          <t>鱼类及其制品</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -15430,38 +15441,41 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H73" s="4" t="n"/>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>mg/kg</t>
         </is>
       </c>
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>GB 8538</t>
+          <t>GB 5009.11</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="n"/>
-      <c r="D74" s="4" t="n"/>
+          <t>水产动物及其制品</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>水产制品</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>鱼类制品</t>
+        </is>
+      </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
+          <t>鱼类及其制品</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
@@ -15471,110 +15485,103 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="H74" s="4" t="n"/>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="J74" s="4" t="n"/>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>GB 8538</t>
+          <t>GB 5009.11</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="B75" s="11" t="inlineStr">
-        <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>鱼类及其制品</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="inlineStr">
+      <c r="A75" s="0" t="inlineStr">
+        <is>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B75" s="0" t="inlineStr">
+        <is>
+          <t>谷物</t>
+        </is>
+      </c>
+      <c r="C75" s="0" t="inlineStr"/>
+      <c r="D75" s="0" t="inlineStr"/>
+      <c r="E75" s="0" t="inlineStr">
+        <is>
+          <t>谷物(稻谷除外)</t>
+        </is>
+      </c>
+      <c r="F75" s="0" t="inlineStr">
         <is>
           <t>总砷</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J75" s="4" t="n"/>
-      <c r="K75" s="4" t="inlineStr">
+      <c r="G75" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H75" s="0" t="inlineStr"/>
+      <c r="I75" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J75" s="0" t="inlineStr"/>
+      <c r="K75" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>水产动物及其制品</t>
-        </is>
-      </c>
-      <c r="B76" s="11" t="inlineStr">
-        <is>
-          <t>水产制品</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>鱼类制品</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>鱼类及其制品</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="n"/>
-      <c r="I76" s="4" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="K76" s="4" t="inlineStr">
+      <c r="A76" s="0" t="inlineStr">
+        <is>
+          <t>谷物及其制品（不包括焙烤制品）</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="inlineStr">
+        <is>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
+      <c r="C76" s="0" t="inlineStr"/>
+      <c r="D76" s="0" t="inlineStr"/>
+      <c r="E76" s="0" t="inlineStr">
+        <is>
+          <t>谷物碾磨加工品[糙米、大米(粉)除外]</t>
+        </is>
+      </c>
+      <c r="F76" s="0" t="inlineStr">
+        <is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G76" s="0" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="H76" s="0" t="inlineStr"/>
+      <c r="I76" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J76" s="0" t="inlineStr"/>
+      <c r="K76" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>
@@ -15600,12 +15607,12 @@
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H77" s="0" t="inlineStr"/>
@@ -15641,12 +15648,12 @@
       </c>
       <c r="F78" s="0" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>无机砷 a</t>
         </is>
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H78" s="0" t="inlineStr"/>
@@ -15665,30 +15672,24 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B79" s="0" t="inlineStr">
-        <is>
-          <t>谷物</t>
-        </is>
-      </c>
+          <t>肉及肉制品</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="inlineStr"/>
       <c r="C79" s="0" t="inlineStr"/>
       <c r="D79" s="0" t="inlineStr"/>
       <c r="E79" s="0" t="inlineStr">
         <is>
-          <t>谷物(稻谷除外)</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="F79" s="0" t="inlineStr">
         <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G79" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>总砷</t>
+        </is>
+      </c>
+      <c r="G79" s="0" t="n">
+        <v>0.5</v>
       </c>
       <c r="H79" s="0" t="inlineStr"/>
       <c r="I79" s="0" t="inlineStr">
@@ -15706,19 +15707,15 @@
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t>谷物及其制品（不包括焙烤制品）</t>
-        </is>
-      </c>
-      <c r="B80" s="0" t="inlineStr">
-        <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
+          <t>肉及肉制品</t>
+        </is>
+      </c>
+      <c r="B80" s="0" t="inlineStr"/>
       <c r="C80" s="0" t="inlineStr"/>
       <c r="D80" s="0" t="inlineStr"/>
       <c r="E80" s="0" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品[糙米、大米(粉)除外]</t>
+          <t>肉及肉制品</t>
         </is>
       </c>
       <c r="F80" s="0" t="inlineStr">
@@ -15747,7 +15744,7 @@
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>油脂及其制品</t>
         </is>
       </c>
       <c r="B81" s="0" t="inlineStr"/>
@@ -15755,7 +15752,7 @@
       <c r="D81" s="0" t="inlineStr"/>
       <c r="E81" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
         </is>
       </c>
       <c r="F81" s="0" t="inlineStr">
@@ -15764,7 +15761,7 @@
         </is>
       </c>
       <c r="G81" s="0" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="H81" s="0" t="inlineStr"/>
       <c r="I81" s="0" t="inlineStr">
@@ -15782,7 +15779,7 @@
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>油脂及其制品</t>
         </is>
       </c>
       <c r="B82" s="0" t="inlineStr"/>
@@ -15790,7 +15787,7 @@
       <c r="D82" s="0" t="inlineStr"/>
       <c r="E82" s="0" t="inlineStr">
         <is>
-          <t>肉及肉制品</t>
+          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
         </is>
       </c>
       <c r="F82" s="0" t="inlineStr">
@@ -15811,78 +15808,6 @@
       </c>
       <c r="J82" s="0" t="inlineStr"/>
       <c r="K82" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="0" t="inlineStr">
-        <is>
-          <t>油脂及其制品</t>
-        </is>
-      </c>
-      <c r="B83" s="0" t="inlineStr"/>
-      <c r="C83" s="0" t="inlineStr"/>
-      <c r="D83" s="0" t="inlineStr"/>
-      <c r="E83" s="0" t="inlineStr">
-        <is>
-          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
-        </is>
-      </c>
-      <c r="F83" s="0" t="inlineStr">
-        <is>
-          <t>总砷</t>
-        </is>
-      </c>
-      <c r="G83" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H83" s="0" t="inlineStr"/>
-      <c r="I83" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J83" s="0" t="inlineStr"/>
-      <c r="K83" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="0" t="inlineStr">
-        <is>
-          <t>油脂及其制品</t>
-        </is>
-      </c>
-      <c r="B84" s="0" t="inlineStr"/>
-      <c r="C84" s="0" t="inlineStr"/>
-      <c r="D84" s="0" t="inlineStr"/>
-      <c r="E84" s="0" t="inlineStr">
-        <is>
-          <t>油脂及其制品(鱼油及其制品、磷虾油及其制品除外)</t>
-        </is>
-      </c>
-      <c r="F84" s="0" t="inlineStr">
-        <is>
-          <t>无机砷 a</t>
-        </is>
-      </c>
-      <c r="G84" s="0" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H84" s="0" t="inlineStr"/>
-      <c r="I84" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J84" s="0" t="inlineStr"/>
-      <c r="K84" s="0" t="inlineStr">
         <is>
           <t>GB 5009.11</t>
         </is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -3218,7 +3218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" style="23" min="1" max="1"/>
@@ -7238,39 +7238,32 @@
       </c>
     </row>
     <row r="97" ht="56" customHeight="1" s="23">
-      <c r="A97" s="0" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>饮料类</t>
         </is>
       </c>
-      <c r="B97" s="0" t="inlineStr">
-        <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
-        </is>
-      </c>
-      <c r="E97" s="0" t="inlineStr">
-        <is>
-          <t>果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外)</t>
-        </is>
-      </c>
-      <c r="F97" s="0" t="inlineStr">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G97" s="0" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="I97" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K97" s="0" t="inlineStr">
-        <is>
-          <t>GB 5009.12</t>
+      <c r="G97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>mg/L</t>
         </is>
       </c>
     </row>
@@ -7285,14 +7278,9 @@
           <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
         </is>
       </c>
-      <c r="C98" s="0" t="inlineStr">
-        <is>
-          <t>果蔬汁（浆）</t>
-        </is>
-      </c>
       <c r="E98" s="0" t="inlineStr">
         <is>
-          <t>含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外)</t>
+          <t>果蔬汁类及其饮料(含浆果及小粒水果的果蔬汁类及其饮料、浓缩果蔬汁(浆)除外)</t>
         </is>
       </c>
       <c r="F98" s="0" t="inlineStr">
@@ -7302,7 +7290,7 @@
       </c>
       <c r="G98" s="0" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="I98" s="0" t="inlineStr">
@@ -7334,7 +7322,7 @@
       </c>
       <c r="E99" s="0" t="inlineStr">
         <is>
-          <t>葡萄汁</t>
+          <t>含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外)</t>
         </is>
       </c>
       <c r="F99" s="0" t="inlineStr">
@@ -7344,7 +7332,7 @@
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="I99" s="0" t="inlineStr">
@@ -7366,12 +7354,17 @@
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>固体饮料[包括速溶咖啡、研磨咖啡（烘焙咖啡）]</t>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
+        </is>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>果蔬汁（浆）</t>
         </is>
       </c>
       <c r="E100" s="0" t="inlineStr">
         <is>
-          <t>固体饮料</t>
+          <t>葡萄汁</t>
         </is>
       </c>
       <c r="F100" s="0" t="inlineStr">
@@ -7381,7 +7374,7 @@
       </c>
       <c r="G100" s="0" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="I100" s="0" t="inlineStr">
@@ -7389,7 +7382,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="K100" s="28" t="inlineStr">
+      <c r="K100" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
@@ -7403,17 +7396,12 @@
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
-        </is>
-      </c>
-      <c r="C101" s="0" t="inlineStr">
-        <is>
-          <t>浓缩果蔬汁（浆）</t>
+          <t>固体饮料[包括速溶咖啡、研磨咖啡（烘焙咖啡）]</t>
         </is>
       </c>
       <c r="E101" s="0" t="inlineStr">
         <is>
-          <t>浓缩果蔬汁(浆)</t>
+          <t>固体饮料</t>
         </is>
       </c>
       <c r="F101" s="0" t="inlineStr">
@@ -7423,7 +7411,7 @@
       </c>
       <c r="G101" s="0" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I101" s="0" t="inlineStr">
@@ -7431,7 +7419,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="K101" s="0" t="inlineStr">
+      <c r="K101" s="28" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
@@ -7445,17 +7433,17 @@
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>蛋白饮料</t>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
+          <t>浓缩果蔬汁（浆）</t>
         </is>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
-          <t>含乳饮料</t>
+          <t>浓缩果蔬汁(浆)</t>
         </is>
       </c>
       <c r="F102" s="0" t="inlineStr">
@@ -7465,7 +7453,7 @@
       </c>
       <c r="G102" s="0" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I102" s="0" t="inlineStr">
@@ -7482,51 +7470,92 @@
     <row r="103" ht="42" customHeight="1" s="23">
       <c r="A103" s="0" t="inlineStr">
         <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B103" s="0" t="inlineStr">
+        <is>
+          <t>蛋白饮料</t>
+        </is>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
+        </is>
+      </c>
+      <c r="E103" s="0" t="inlineStr">
+        <is>
+          <t>含乳饮料</t>
+        </is>
+      </c>
+      <c r="F103" s="0" t="inlineStr">
+        <is>
+          <t>铅</t>
+        </is>
+      </c>
+      <c r="G103" s="0" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="I103" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K103" s="0" t="inlineStr">
+        <is>
+          <t>GB 5009.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="56" customHeight="1" s="23">
+      <c r="A104" s="0" t="inlineStr">
+        <is>
           <t>谷物及其制品（不包括焙烤制品）</t>
         </is>
       </c>
-      <c r="B103" s="0" t="inlineStr">
+      <c r="B104" s="0" t="inlineStr">
         <is>
           <t>谷物制品</t>
         </is>
       </c>
-      <c r="C103" s="0" t="inlineStr">
+      <c r="C104" s="0" t="inlineStr">
         <is>
           <t>其他谷物制品[例如：带馅（料）面米制品、粥类罐头等]</t>
         </is>
       </c>
-      <c r="D103" s="0" t="inlineStr">
+      <c r="D104" s="0" t="inlineStr">
         <is>
           <t>带馅料面米制品</t>
         </is>
       </c>
-      <c r="E103" s="0" t="inlineStr">
+      <c r="E104" s="0" t="inlineStr">
         <is>
           <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
-      <c r="F103" s="0" t="inlineStr">
+      <c r="F104" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G103" s="0" t="inlineStr">
+      <c r="G104" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I103" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K103" s="0" t="inlineStr">
+      <c r="I104" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K104" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="56" customHeight="1" s="23"/>
     <row r="105" ht="42" customHeight="1" s="23"/>
     <row r="106" ht="28" customHeight="1" s="23"/>
     <row r="107" ht="28" customHeight="1" s="23"/>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -7238,30 +7238,30 @@
       </c>
     </row>
     <row r="97" ht="56" customHeight="1" s="23">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="0" t="inlineStr">
         <is>
           <t>饮料类</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="0" t="inlineStr">
         <is>
           <t>包装饮用水</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E97" s="0" t="inlineStr">
         <is>
           <t>包装饮用水</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F97" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G97" t="n">
+      <c r="G97" s="0" t="n">
         <v>0.01</v>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I97" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
@@ -7315,11 +7315,7 @@
           <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
         </is>
       </c>
-      <c r="C99" s="0" t="inlineStr">
-        <is>
-          <t>果蔬汁（浆）</t>
-        </is>
-      </c>
+      <c r="C99" s="0" t="n"/>
       <c r="E99" s="0" t="inlineStr">
         <is>
           <t>含浆果及小粒水果的果蔬汁类及其饮料(葡萄汁除外)</t>
@@ -7389,37 +7385,42 @@
       </c>
     </row>
     <row r="101" ht="56" customHeight="1" s="23">
-      <c r="A101" s="0" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>饮料类</t>
         </is>
       </c>
-      <c r="B101" s="0" t="inlineStr">
-        <is>
-          <t>固体饮料[包括速溶咖啡、研磨咖啡（烘焙咖啡）]</t>
-        </is>
-      </c>
-      <c r="E101" s="0" t="inlineStr">
-        <is>
-          <t>固体饮料</t>
-        </is>
-      </c>
-      <c r="F101" s="0" t="inlineStr">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>浓缩果蔬汁（浆）</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>浓缩果蔬汁(浆)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G101" s="0" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I101" s="0" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K101" s="28" t="inlineStr">
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>
@@ -7433,17 +7434,12 @@
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
-        </is>
-      </c>
-      <c r="C102" s="0" t="inlineStr">
-        <is>
-          <t>浓缩果蔬汁（浆）</t>
+          <t>固体饮料[包括速溶咖啡、研磨咖啡（烘焙咖啡）]</t>
         </is>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
-          <t>浓缩果蔬汁(浆)</t>
+          <t>固体饮料</t>
         </is>
       </c>
       <c r="F102" s="0" t="inlineStr">
@@ -7453,7 +7449,7 @@
       </c>
       <c r="G102" s="0" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I102" s="0" t="inlineStr">
@@ -7461,7 +7457,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="K102" s="0" t="inlineStr">
+      <c r="K102" s="28" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -3165,11 +3165,7 @@
           <t>调味品</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>其他调味品</t>
-        </is>
-      </c>
+      <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="inlineStr">
@@ -7385,42 +7381,42 @@
       </c>
     </row>
     <row r="101" ht="56" customHeight="1" s="23">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="0" t="inlineStr">
         <is>
           <t>饮料类</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="0" t="inlineStr">
         <is>
           <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="0" t="inlineStr">
         <is>
           <t>浓缩果蔬汁（浆）</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E101" s="0" t="inlineStr">
         <is>
           <t>浓缩果蔬汁(浆)</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F101" s="0" t="inlineStr">
         <is>
           <t>铅</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G101" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
+      <c r="I101" s="0" t="inlineStr">
+        <is>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="K101" s="0" t="inlineStr">
         <is>
           <t>GB 5009.12</t>
         </is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -7349,11 +7349,7 @@
           <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
         </is>
       </c>
-      <c r="C100" s="0" t="inlineStr">
-        <is>
-          <t>果蔬汁（浆）</t>
-        </is>
-      </c>
+      <c r="C100" s="0" t="n"/>
       <c r="E100" s="0" t="inlineStr">
         <is>
           <t>葡萄汁</t>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -13207,10 +13207,14 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n"/>
+          <t>油脂制品</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>其他油脂制品</t>
+        </is>
+      </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -13248,10 +13252,14 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>动物油脂（例如：猪油、牛油、鱼油、磷虾油等）</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n"/>
+          <t>油脂制品</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>其他油脂制品</t>
+        </is>
+      </c>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="inlineStr">
         <is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -4036,16 +4036,8 @@
           <t>坚果及籽类</t>
         </is>
       </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>生干坚果及籽类</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>生咖啡豆及烘焙咖啡豆</t>
-        </is>
-      </c>
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="19" t="n"/>
       <c r="D23" s="19" t="n"/>
       <c r="E23" s="19" t="inlineStr">
         <is>
@@ -9641,16 +9633,8 @@
           <t>坚果及籽类</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>生干坚果及籽类</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>花生</t>
-        </is>
-      </c>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="4" t="inlineStr">
         <is>

--- a/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
+++ b/data/gb2762/_gb2762_2025_12项污染物_v6_synced.xlsx
@@ -15926,8 +15926,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>特殊膳食用食品</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="inlineStr">
@@ -15963,8 +15971,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>特殊膳食用食品</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>婴幼儿配方食品</t>
+        </is>
+      </c>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="inlineStr">
@@ -16000,7 +16016,11 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" s="23">
-      <c r="A7" s="4" t="n"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
@@ -16037,8 +16057,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="n"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>饮料类</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="inlineStr">
